--- a/storage/app/estimateTemplate/comprehensiveOfRecommend.xlsx
+++ b/storage/app/estimateTemplate/comprehensiveOfRecommend.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yokoyama\Desktop\火災見積\テンプレート\new\mark\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8972529-2621-4FE5-8C2B-9AB9CBA8AC0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AD55695-7369-402B-878D-E94F1644140F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{0E9C5CA5-184F-4C06-AA15-1AF55B55AFB9}"/>
+    <workbookView xWindow="28680" yWindow="-75" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{0E9C5CA5-184F-4C06-AA15-1AF55B55AFB9}"/>
   </bookViews>
   <sheets>
     <sheet name="おすすめ(総合)" sheetId="2" r:id="rId1"/>
@@ -1087,7 +1087,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="6" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="150">
+  <cellXfs count="151">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1166,97 +1166,175 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="17" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="17" fillId="2" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="17" fillId="2" borderId="31" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="17" fillId="2" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="17" fillId="2" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="17" fillId="2" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="26" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="17" fillId="2" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="17" fillId="2" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="8" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="28" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="16" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="16" fillId="0" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="16" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="16" fillId="0" borderId="29" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="9" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="9" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="180" fontId="18" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="182" fontId="9" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="9" fillId="0" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="9" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="9" fillId="0" borderId="29" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="24" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="58" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -1266,6 +1344,18 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -1290,6 +1380,12 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1299,12 +1395,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="2" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1350,190 +1440,103 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="17" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="17" fillId="2" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="17" fillId="2" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="17" fillId="2" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="17" fillId="2" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="17" fillId="2" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="17" fillId="2" borderId="31" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="17" fillId="2" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="18" fillId="0" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="182" fontId="9" fillId="0" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="9" fillId="0" borderId="29" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="24" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="26" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="8" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="28" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="16" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="16" fillId="0" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="16" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="16" fillId="0" borderId="29" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="33" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="34" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="35" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="33" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="34" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1912,10 +1915,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="O1" s="58"/>
-      <c r="P1" s="58"/>
-      <c r="Q1" s="58"/>
-      <c r="R1" s="58"/>
+      <c r="O1" s="84"/>
+      <c r="P1" s="84"/>
+      <c r="Q1" s="84"/>
+      <c r="R1" s="84"/>
     </row>
     <row r="2" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="O2" s="25"/>
@@ -1925,16 +1928,16 @@
     </row>
     <row r="3" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A3" s="3"/>
-      <c r="O3" s="27"/>
-      <c r="P3" s="27"/>
-      <c r="Q3" s="27"/>
-      <c r="R3" s="27"/>
+      <c r="O3" s="118"/>
+      <c r="P3" s="118"/>
+      <c r="Q3" s="118"/>
+      <c r="R3" s="118"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="O4" s="27"/>
-      <c r="P4" s="27"/>
-      <c r="Q4" s="27"/>
-      <c r="R4" s="27"/>
+      <c r="O4" s="118"/>
+      <c r="P4" s="118"/>
+      <c r="Q4" s="118"/>
+      <c r="R4" s="118"/>
     </row>
     <row r="5" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="N5" s="24"/>
@@ -1997,196 +2000,196 @@
       <c r="R10" s="20"/>
     </row>
     <row r="11" spans="1:18" ht="21" x14ac:dyDescent="0.4">
-      <c r="A11" s="59" t="s">
+      <c r="A11" s="85" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="59"/>
-      <c r="C11" s="59"/>
-      <c r="D11" s="59"/>
-      <c r="E11" s="59"/>
-      <c r="F11" s="59"/>
-      <c r="G11" s="59"/>
-      <c r="H11" s="59"/>
-      <c r="I11" s="59"/>
-      <c r="J11" s="59"/>
-      <c r="K11" s="59"/>
-      <c r="L11" s="59"/>
-      <c r="M11" s="59"/>
-      <c r="N11" s="59"/>
-      <c r="O11" s="59"/>
-      <c r="P11" s="59"/>
-      <c r="Q11" s="59"/>
-      <c r="R11" s="59"/>
+      <c r="B11" s="85"/>
+      <c r="C11" s="85"/>
+      <c r="D11" s="85"/>
+      <c r="E11" s="85"/>
+      <c r="F11" s="85"/>
+      <c r="G11" s="85"/>
+      <c r="H11" s="85"/>
+      <c r="I11" s="85"/>
+      <c r="J11" s="85"/>
+      <c r="K11" s="85"/>
+      <c r="L11" s="85"/>
+      <c r="M11" s="85"/>
+      <c r="N11" s="85"/>
+      <c r="O11" s="85"/>
+      <c r="P11" s="85"/>
+      <c r="Q11" s="85"/>
+      <c r="R11" s="85"/>
     </row>
     <row r="14" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="15" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
-      <c r="A15" s="66" t="s">
+      <c r="A15" s="96" t="s">
         <v>1</v>
       </c>
-      <c r="B15" s="66"/>
-      <c r="C15" s="66"/>
-      <c r="D15" s="66"/>
-      <c r="E15" s="66"/>
-      <c r="F15" s="66"/>
-      <c r="G15" s="66"/>
-      <c r="H15" s="66"/>
-      <c r="I15" s="66"/>
-      <c r="J15" s="66"/>
-      <c r="K15" s="66"/>
-      <c r="L15" s="66"/>
-      <c r="M15" s="66"/>
-      <c r="N15" s="66"/>
-      <c r="O15" s="66"/>
-      <c r="P15" s="66"/>
-      <c r="Q15" s="66"/>
-      <c r="R15" s="66"/>
+      <c r="B15" s="96"/>
+      <c r="C15" s="96"/>
+      <c r="D15" s="96"/>
+      <c r="E15" s="96"/>
+      <c r="F15" s="96"/>
+      <c r="G15" s="96"/>
+      <c r="H15" s="96"/>
+      <c r="I15" s="96"/>
+      <c r="J15" s="96"/>
+      <c r="K15" s="96"/>
+      <c r="L15" s="96"/>
+      <c r="M15" s="96"/>
+      <c r="N15" s="96"/>
+      <c r="O15" s="96"/>
+      <c r="P15" s="96"/>
+      <c r="Q15" s="96"/>
+      <c r="R15" s="96"/>
     </row>
     <row r="18" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
-      <c r="A18" s="67" t="s">
+      <c r="A18" s="97" t="s">
         <v>2</v>
       </c>
-      <c r="B18" s="67"/>
-      <c r="C18" s="67"/>
-      <c r="D18" s="67"/>
-      <c r="E18" s="67"/>
-      <c r="F18" s="67"/>
-      <c r="G18" s="67"/>
-      <c r="H18" s="67"/>
-      <c r="I18" s="67"/>
-      <c r="J18" s="67"/>
-      <c r="K18" s="67"/>
-      <c r="L18" s="67"/>
-      <c r="M18" s="67"/>
-      <c r="N18" s="67"/>
-      <c r="O18" s="67"/>
-      <c r="P18" s="67"/>
-      <c r="Q18" s="67"/>
-      <c r="R18" s="67"/>
+      <c r="B18" s="97"/>
+      <c r="C18" s="97"/>
+      <c r="D18" s="97"/>
+      <c r="E18" s="97"/>
+      <c r="F18" s="97"/>
+      <c r="G18" s="97"/>
+      <c r="H18" s="97"/>
+      <c r="I18" s="97"/>
+      <c r="J18" s="97"/>
+      <c r="K18" s="97"/>
+      <c r="L18" s="97"/>
+      <c r="M18" s="97"/>
+      <c r="N18" s="97"/>
+      <c r="O18" s="97"/>
+      <c r="P18" s="97"/>
+      <c r="Q18" s="97"/>
+      <c r="R18" s="97"/>
     </row>
     <row r="19" spans="1:18" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="20" spans="1:18" ht="12.75" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="57" t="s">
+      <c r="A20" s="89" t="s">
         <v>3</v>
       </c>
-      <c r="B20" s="46"/>
-      <c r="C20" s="46"/>
-      <c r="D20" s="60"/>
-      <c r="E20" s="61"/>
-      <c r="F20" s="61"/>
-      <c r="G20" s="61"/>
-      <c r="H20" s="61"/>
-      <c r="I20" s="61"/>
-      <c r="J20" s="61"/>
-      <c r="K20" s="61"/>
-      <c r="L20" s="61"/>
-      <c r="M20" s="61"/>
-      <c r="N20" s="61"/>
-      <c r="O20" s="61"/>
-      <c r="P20" s="61"/>
-      <c r="Q20" s="61"/>
-      <c r="R20" s="62"/>
+      <c r="B20" s="33"/>
+      <c r="C20" s="33"/>
+      <c r="D20" s="90"/>
+      <c r="E20" s="91"/>
+      <c r="F20" s="91"/>
+      <c r="G20" s="91"/>
+      <c r="H20" s="91"/>
+      <c r="I20" s="91"/>
+      <c r="J20" s="91"/>
+      <c r="K20" s="91"/>
+      <c r="L20" s="91"/>
+      <c r="M20" s="91"/>
+      <c r="N20" s="91"/>
+      <c r="O20" s="91"/>
+      <c r="P20" s="91"/>
+      <c r="Q20" s="91"/>
+      <c r="R20" s="92"/>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A21" s="44"/>
-      <c r="B21" s="45"/>
-      <c r="C21" s="45"/>
-      <c r="D21" s="63"/>
-      <c r="E21" s="64"/>
-      <c r="F21" s="64"/>
-      <c r="G21" s="64"/>
-      <c r="H21" s="64"/>
-      <c r="I21" s="64"/>
-      <c r="J21" s="64"/>
-      <c r="K21" s="64"/>
-      <c r="L21" s="64"/>
-      <c r="M21" s="64"/>
-      <c r="N21" s="64"/>
-      <c r="O21" s="64"/>
-      <c r="P21" s="64"/>
-      <c r="Q21" s="64"/>
-      <c r="R21" s="65"/>
+      <c r="A21" s="86"/>
+      <c r="B21" s="35"/>
+      <c r="C21" s="35"/>
+      <c r="D21" s="93"/>
+      <c r="E21" s="94"/>
+      <c r="F21" s="94"/>
+      <c r="G21" s="94"/>
+      <c r="H21" s="94"/>
+      <c r="I21" s="94"/>
+      <c r="J21" s="94"/>
+      <c r="K21" s="94"/>
+      <c r="L21" s="94"/>
+      <c r="M21" s="94"/>
+      <c r="N21" s="94"/>
+      <c r="O21" s="94"/>
+      <c r="P21" s="94"/>
+      <c r="Q21" s="94"/>
+      <c r="R21" s="95"/>
     </row>
     <row r="22" spans="1:18" ht="5.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="44" t="s">
+      <c r="A22" s="86" t="s">
         <v>4</v>
       </c>
-      <c r="B22" s="45"/>
-      <c r="C22" s="45"/>
+      <c r="B22" s="35"/>
+      <c r="C22" s="35"/>
       <c r="D22" s="19"/>
       <c r="L22" s="18"/>
-      <c r="M22" s="88" t="s">
+      <c r="M22" s="63" t="s">
         <v>5</v>
       </c>
-      <c r="N22" s="89"/>
-      <c r="O22" s="79"/>
-      <c r="P22" s="80"/>
-      <c r="Q22" s="80"/>
-      <c r="R22" s="81"/>
+      <c r="N22" s="64"/>
+      <c r="O22" s="109"/>
+      <c r="P22" s="110"/>
+      <c r="Q22" s="110"/>
+      <c r="R22" s="111"/>
     </row>
     <row r="23" spans="1:18" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="44"/>
-      <c r="B23" s="45"/>
-      <c r="C23" s="45"/>
-      <c r="D23" s="124"/>
-      <c r="E23" s="125"/>
-      <c r="F23" s="125"/>
-      <c r="G23" s="125"/>
-      <c r="H23" s="125"/>
-      <c r="I23" s="125"/>
-      <c r="J23" s="125"/>
-      <c r="K23" s="125"/>
-      <c r="L23" s="126"/>
-      <c r="M23" s="88"/>
-      <c r="N23" s="89"/>
-      <c r="O23" s="82"/>
-      <c r="P23" s="83"/>
-      <c r="Q23" s="83"/>
-      <c r="R23" s="84"/>
+      <c r="A23" s="86"/>
+      <c r="B23" s="35"/>
+      <c r="C23" s="35"/>
+      <c r="D23" s="37"/>
+      <c r="E23" s="38"/>
+      <c r="F23" s="38"/>
+      <c r="G23" s="38"/>
+      <c r="H23" s="38"/>
+      <c r="I23" s="38"/>
+      <c r="J23" s="38"/>
+      <c r="K23" s="38"/>
+      <c r="L23" s="39"/>
+      <c r="M23" s="63"/>
+      <c r="N23" s="64"/>
+      <c r="O23" s="112"/>
+      <c r="P23" s="113"/>
+      <c r="Q23" s="113"/>
+      <c r="R23" s="114"/>
     </row>
     <row r="24" spans="1:18" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="44"/>
-      <c r="B24" s="45"/>
-      <c r="C24" s="45"/>
-      <c r="D24" s="127"/>
-      <c r="E24" s="125"/>
-      <c r="F24" s="125"/>
-      <c r="G24" s="125"/>
-      <c r="H24" s="125"/>
-      <c r="I24" s="125"/>
-      <c r="J24" s="125"/>
-      <c r="K24" s="125"/>
-      <c r="L24" s="126"/>
-      <c r="M24" s="88"/>
-      <c r="N24" s="89"/>
-      <c r="O24" s="82"/>
-      <c r="P24" s="83"/>
-      <c r="Q24" s="83"/>
-      <c r="R24" s="84"/>
+      <c r="A24" s="86"/>
+      <c r="B24" s="35"/>
+      <c r="C24" s="35"/>
+      <c r="D24" s="40"/>
+      <c r="E24" s="38"/>
+      <c r="F24" s="38"/>
+      <c r="G24" s="38"/>
+      <c r="H24" s="38"/>
+      <c r="I24" s="38"/>
+      <c r="J24" s="38"/>
+      <c r="K24" s="38"/>
+      <c r="L24" s="39"/>
+      <c r="M24" s="63"/>
+      <c r="N24" s="64"/>
+      <c r="O24" s="112"/>
+      <c r="P24" s="113"/>
+      <c r="Q24" s="113"/>
+      <c r="R24" s="114"/>
     </row>
     <row r="25" spans="1:18" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="44"/>
-      <c r="B25" s="45"/>
-      <c r="C25" s="45"/>
-      <c r="D25" s="127"/>
-      <c r="E25" s="125"/>
-      <c r="F25" s="125"/>
-      <c r="G25" s="125"/>
-      <c r="H25" s="125"/>
-      <c r="I25" s="125"/>
-      <c r="J25" s="125"/>
-      <c r="K25" s="125"/>
-      <c r="L25" s="126"/>
-      <c r="M25" s="88"/>
-      <c r="N25" s="89"/>
-      <c r="O25" s="82"/>
-      <c r="P25" s="83"/>
-      <c r="Q25" s="83"/>
-      <c r="R25" s="84"/>
+      <c r="A25" s="86"/>
+      <c r="B25" s="35"/>
+      <c r="C25" s="35"/>
+      <c r="D25" s="40"/>
+      <c r="E25" s="38"/>
+      <c r="F25" s="38"/>
+      <c r="G25" s="38"/>
+      <c r="H25" s="38"/>
+      <c r="I25" s="38"/>
+      <c r="J25" s="38"/>
+      <c r="K25" s="38"/>
+      <c r="L25" s="39"/>
+      <c r="M25" s="63"/>
+      <c r="N25" s="64"/>
+      <c r="O25" s="112"/>
+      <c r="P25" s="113"/>
+      <c r="Q25" s="113"/>
+      <c r="R25" s="114"/>
     </row>
     <row r="26" spans="1:18" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="44"/>
-      <c r="B26" s="45"/>
-      <c r="C26" s="45"/>
+      <c r="A26" s="86"/>
+      <c r="B26" s="35"/>
+      <c r="C26" s="35"/>
       <c r="D26" s="17"/>
       <c r="E26" s="16"/>
       <c r="F26" s="15"/>
@@ -2196,17 +2199,17 @@
       <c r="J26" s="14"/>
       <c r="K26" s="14"/>
       <c r="L26" s="13"/>
-      <c r="M26" s="88"/>
-      <c r="N26" s="89"/>
-      <c r="O26" s="82"/>
-      <c r="P26" s="83"/>
-      <c r="Q26" s="83"/>
-      <c r="R26" s="84"/>
+      <c r="M26" s="63"/>
+      <c r="N26" s="64"/>
+      <c r="O26" s="112"/>
+      <c r="P26" s="113"/>
+      <c r="Q26" s="113"/>
+      <c r="R26" s="114"/>
     </row>
     <row r="27" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="44"/>
-      <c r="B27" s="45"/>
-      <c r="C27" s="45"/>
+      <c r="A27" s="86"/>
+      <c r="B27" s="35"/>
+      <c r="C27" s="35"/>
       <c r="D27" s="12"/>
       <c r="F27" s="10"/>
       <c r="G27" s="11"/>
@@ -2214,17 +2217,17 @@
       <c r="I27" s="9"/>
       <c r="J27" s="9"/>
       <c r="L27" s="8"/>
-      <c r="M27" s="88"/>
-      <c r="N27" s="89"/>
-      <c r="O27" s="82"/>
-      <c r="P27" s="83"/>
-      <c r="Q27" s="83"/>
-      <c r="R27" s="84"/>
+      <c r="M27" s="63"/>
+      <c r="N27" s="64"/>
+      <c r="O27" s="112"/>
+      <c r="P27" s="113"/>
+      <c r="Q27" s="113"/>
+      <c r="R27" s="114"/>
     </row>
     <row r="28" spans="1:18" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="49"/>
-      <c r="B28" s="50"/>
-      <c r="C28" s="50"/>
+      <c r="A28" s="87"/>
+      <c r="B28" s="88"/>
+      <c r="C28" s="88"/>
       <c r="D28" s="7"/>
       <c r="E28" s="6"/>
       <c r="F28" s="6"/>
@@ -2234,346 +2237,346 @@
       <c r="J28" s="6"/>
       <c r="K28" s="6"/>
       <c r="L28" s="5"/>
-      <c r="M28" s="90"/>
-      <c r="N28" s="91"/>
-      <c r="O28" s="85"/>
-      <c r="P28" s="86"/>
-      <c r="Q28" s="86"/>
-      <c r="R28" s="87"/>
+      <c r="M28" s="65"/>
+      <c r="N28" s="66"/>
+      <c r="O28" s="115"/>
+      <c r="P28" s="116"/>
+      <c r="Q28" s="116"/>
+      <c r="R28" s="117"/>
     </row>
     <row r="29" spans="1:18" ht="12.75" thickTop="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="1:18" ht="12.75" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="31" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="57" t="s">
+      <c r="A31" s="89" t="s">
         <v>6</v>
       </c>
-      <c r="B31" s="46"/>
-      <c r="C31" s="46"/>
-      <c r="D31" s="40"/>
-      <c r="E31" s="40"/>
-      <c r="F31" s="40"/>
-      <c r="G31" s="40"/>
-      <c r="H31" s="40"/>
-      <c r="I31" s="40"/>
-      <c r="J31" s="46" t="s">
+      <c r="B31" s="33"/>
+      <c r="C31" s="33"/>
+      <c r="D31" s="98"/>
+      <c r="E31" s="98"/>
+      <c r="F31" s="98"/>
+      <c r="G31" s="98"/>
+      <c r="H31" s="98"/>
+      <c r="I31" s="98"/>
+      <c r="J31" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="K31" s="46"/>
-      <c r="L31" s="46"/>
-      <c r="M31" s="40"/>
-      <c r="N31" s="40"/>
-      <c r="O31" s="40"/>
-      <c r="P31" s="40"/>
-      <c r="Q31" s="40"/>
-      <c r="R31" s="41"/>
+      <c r="K31" s="33"/>
+      <c r="L31" s="33"/>
+      <c r="M31" s="98"/>
+      <c r="N31" s="98"/>
+      <c r="O31" s="98"/>
+      <c r="P31" s="98"/>
+      <c r="Q31" s="98"/>
+      <c r="R31" s="128"/>
     </row>
     <row r="32" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="44"/>
-      <c r="B32" s="45"/>
-      <c r="C32" s="45"/>
-      <c r="D32" s="42"/>
-      <c r="E32" s="42"/>
-      <c r="F32" s="42"/>
-      <c r="G32" s="42"/>
-      <c r="H32" s="42"/>
-      <c r="I32" s="42"/>
-      <c r="J32" s="45"/>
-      <c r="K32" s="45"/>
-      <c r="L32" s="45"/>
-      <c r="M32" s="42"/>
-      <c r="N32" s="42"/>
-      <c r="O32" s="42"/>
-      <c r="P32" s="42"/>
-      <c r="Q32" s="42"/>
-      <c r="R32" s="43"/>
+      <c r="A32" s="86"/>
+      <c r="B32" s="35"/>
+      <c r="C32" s="35"/>
+      <c r="D32" s="99"/>
+      <c r="E32" s="99"/>
+      <c r="F32" s="99"/>
+      <c r="G32" s="99"/>
+      <c r="H32" s="99"/>
+      <c r="I32" s="99"/>
+      <c r="J32" s="35"/>
+      <c r="K32" s="35"/>
+      <c r="L32" s="35"/>
+      <c r="M32" s="99"/>
+      <c r="N32" s="99"/>
+      <c r="O32" s="99"/>
+      <c r="P32" s="99"/>
+      <c r="Q32" s="99"/>
+      <c r="R32" s="129"/>
     </row>
     <row r="33" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="44" t="s">
+      <c r="A33" s="86" t="s">
         <v>8</v>
       </c>
-      <c r="B33" s="45"/>
-      <c r="C33" s="45"/>
-      <c r="D33" s="42"/>
-      <c r="E33" s="42"/>
-      <c r="F33" s="42"/>
-      <c r="G33" s="42"/>
-      <c r="H33" s="42"/>
-      <c r="I33" s="42"/>
-      <c r="J33" s="45" t="s">
+      <c r="B33" s="35"/>
+      <c r="C33" s="35"/>
+      <c r="D33" s="99"/>
+      <c r="E33" s="99"/>
+      <c r="F33" s="99"/>
+      <c r="G33" s="99"/>
+      <c r="H33" s="99"/>
+      <c r="I33" s="99"/>
+      <c r="J33" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="K33" s="45"/>
-      <c r="L33" s="45"/>
-      <c r="M33" s="42"/>
-      <c r="N33" s="42"/>
-      <c r="O33" s="42"/>
-      <c r="P33" s="42"/>
-      <c r="Q33" s="42"/>
-      <c r="R33" s="43"/>
+      <c r="K33" s="35"/>
+      <c r="L33" s="35"/>
+      <c r="M33" s="99"/>
+      <c r="N33" s="99"/>
+      <c r="O33" s="99"/>
+      <c r="P33" s="99"/>
+      <c r="Q33" s="99"/>
+      <c r="R33" s="129"/>
     </row>
     <row r="34" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="44"/>
-      <c r="B34" s="45"/>
-      <c r="C34" s="45"/>
-      <c r="D34" s="42"/>
-      <c r="E34" s="42"/>
-      <c r="F34" s="42"/>
-      <c r="G34" s="42"/>
-      <c r="H34" s="42"/>
-      <c r="I34" s="42"/>
-      <c r="J34" s="45"/>
-      <c r="K34" s="45"/>
-      <c r="L34" s="45"/>
-      <c r="M34" s="42"/>
-      <c r="N34" s="42"/>
-      <c r="O34" s="42"/>
-      <c r="P34" s="42"/>
-      <c r="Q34" s="42"/>
-      <c r="R34" s="43"/>
+      <c r="A34" s="86"/>
+      <c r="B34" s="35"/>
+      <c r="C34" s="35"/>
+      <c r="D34" s="99"/>
+      <c r="E34" s="99"/>
+      <c r="F34" s="99"/>
+      <c r="G34" s="99"/>
+      <c r="H34" s="99"/>
+      <c r="I34" s="99"/>
+      <c r="J34" s="35"/>
+      <c r="K34" s="35"/>
+      <c r="L34" s="35"/>
+      <c r="M34" s="99"/>
+      <c r="N34" s="99"/>
+      <c r="O34" s="99"/>
+      <c r="P34" s="99"/>
+      <c r="Q34" s="99"/>
+      <c r="R34" s="129"/>
     </row>
     <row r="35" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="44" t="s">
+      <c r="A35" s="86" t="s">
         <v>10</v>
       </c>
-      <c r="B35" s="45"/>
-      <c r="C35" s="45"/>
-      <c r="D35" s="51"/>
-      <c r="E35" s="52"/>
-      <c r="F35" s="52"/>
-      <c r="G35" s="52"/>
-      <c r="H35" s="52"/>
-      <c r="I35" s="52"/>
-      <c r="J35" s="52"/>
-      <c r="K35" s="52"/>
-      <c r="L35" s="52"/>
-      <c r="M35" s="52"/>
-      <c r="N35" s="52"/>
-      <c r="O35" s="52"/>
-      <c r="P35" s="52"/>
-      <c r="Q35" s="52"/>
-      <c r="R35" s="53"/>
+      <c r="B35" s="35"/>
+      <c r="C35" s="35"/>
+      <c r="D35" s="132"/>
+      <c r="E35" s="133"/>
+      <c r="F35" s="133"/>
+      <c r="G35" s="133"/>
+      <c r="H35" s="133"/>
+      <c r="I35" s="133"/>
+      <c r="J35" s="133"/>
+      <c r="K35" s="133"/>
+      <c r="L35" s="133"/>
+      <c r="M35" s="133"/>
+      <c r="N35" s="133"/>
+      <c r="O35" s="133"/>
+      <c r="P35" s="133"/>
+      <c r="Q35" s="133"/>
+      <c r="R35" s="134"/>
     </row>
     <row r="36" spans="1:18" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A36" s="49"/>
-      <c r="B36" s="50"/>
-      <c r="C36" s="50"/>
-      <c r="D36" s="54"/>
-      <c r="E36" s="55"/>
-      <c r="F36" s="55"/>
-      <c r="G36" s="55"/>
-      <c r="H36" s="55"/>
-      <c r="I36" s="55"/>
-      <c r="J36" s="55"/>
-      <c r="K36" s="55"/>
-      <c r="L36" s="55"/>
-      <c r="M36" s="55"/>
-      <c r="N36" s="55"/>
-      <c r="O36" s="55"/>
-      <c r="P36" s="55"/>
-      <c r="Q36" s="55"/>
-      <c r="R36" s="56"/>
+      <c r="A36" s="87"/>
+      <c r="B36" s="88"/>
+      <c r="C36" s="88"/>
+      <c r="D36" s="135"/>
+      <c r="E36" s="136"/>
+      <c r="F36" s="136"/>
+      <c r="G36" s="136"/>
+      <c r="H36" s="136"/>
+      <c r="I36" s="136"/>
+      <c r="J36" s="136"/>
+      <c r="K36" s="136"/>
+      <c r="L36" s="136"/>
+      <c r="M36" s="136"/>
+      <c r="N36" s="136"/>
+      <c r="O36" s="136"/>
+      <c r="P36" s="136"/>
+      <c r="Q36" s="136"/>
+      <c r="R36" s="137"/>
     </row>
     <row r="37" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="68"/>
-      <c r="B37" s="69"/>
-      <c r="C37" s="69"/>
-      <c r="D37" s="69"/>
-      <c r="E37" s="69"/>
-      <c r="F37" s="69"/>
-      <c r="G37" s="69"/>
-      <c r="H37" s="69"/>
-      <c r="I37" s="69"/>
-      <c r="J37" s="69"/>
-      <c r="K37" s="69"/>
-      <c r="L37" s="69"/>
-      <c r="M37" s="69"/>
-      <c r="N37" s="69"/>
-      <c r="O37" s="69"/>
-      <c r="P37" s="69"/>
-      <c r="Q37" s="69"/>
-      <c r="R37" s="69"/>
+      <c r="A37" s="100"/>
+      <c r="B37" s="101"/>
+      <c r="C37" s="101"/>
+      <c r="D37" s="101"/>
+      <c r="E37" s="101"/>
+      <c r="F37" s="101"/>
+      <c r="G37" s="101"/>
+      <c r="H37" s="101"/>
+      <c r="I37" s="101"/>
+      <c r="J37" s="101"/>
+      <c r="K37" s="101"/>
+      <c r="L37" s="101"/>
+      <c r="M37" s="101"/>
+      <c r="N37" s="101"/>
+      <c r="O37" s="101"/>
+      <c r="P37" s="101"/>
+      <c r="Q37" s="101"/>
+      <c r="R37" s="101"/>
     </row>
     <row r="38" spans="1:18" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="70"/>
-      <c r="B38" s="70"/>
-      <c r="C38" s="70"/>
-      <c r="D38" s="70"/>
-      <c r="E38" s="70"/>
-      <c r="F38" s="70"/>
-      <c r="G38" s="70"/>
-      <c r="H38" s="70"/>
-      <c r="I38" s="70"/>
-      <c r="J38" s="70"/>
-      <c r="K38" s="70"/>
-      <c r="L38" s="70"/>
-      <c r="M38" s="70"/>
-      <c r="N38" s="70"/>
-      <c r="O38" s="70"/>
-      <c r="P38" s="70"/>
-      <c r="Q38" s="70"/>
-      <c r="R38" s="70"/>
+      <c r="A38" s="102"/>
+      <c r="B38" s="102"/>
+      <c r="C38" s="102"/>
+      <c r="D38" s="102"/>
+      <c r="E38" s="102"/>
+      <c r="F38" s="102"/>
+      <c r="G38" s="102"/>
+      <c r="H38" s="102"/>
+      <c r="I38" s="102"/>
+      <c r="J38" s="102"/>
+      <c r="K38" s="102"/>
+      <c r="L38" s="102"/>
+      <c r="M38" s="102"/>
+      <c r="N38" s="102"/>
+      <c r="O38" s="102"/>
+      <c r="P38" s="102"/>
+      <c r="Q38" s="102"/>
+      <c r="R38" s="102"/>
     </row>
     <row r="39" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="57" t="s">
+      <c r="A39" s="89" t="s">
         <v>11</v>
       </c>
-      <c r="B39" s="46"/>
-      <c r="C39" s="46"/>
-      <c r="D39" s="46" t="s">
+      <c r="B39" s="33"/>
+      <c r="C39" s="33"/>
+      <c r="D39" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="E39" s="46"/>
-      <c r="F39" s="46"/>
-      <c r="G39" s="71"/>
-      <c r="H39" s="46" t="s">
+      <c r="E39" s="33"/>
+      <c r="F39" s="33"/>
+      <c r="G39" s="34"/>
+      <c r="H39" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="I39" s="46"/>
-      <c r="J39" s="46"/>
-      <c r="K39" s="46" t="s">
+      <c r="I39" s="33"/>
+      <c r="J39" s="33"/>
+      <c r="K39" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="L39" s="46"/>
-      <c r="M39" s="46"/>
-      <c r="N39" s="71"/>
-      <c r="O39" s="46" t="s">
+      <c r="L39" s="33"/>
+      <c r="M39" s="33"/>
+      <c r="N39" s="34"/>
+      <c r="O39" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="P39" s="46"/>
-      <c r="Q39" s="46"/>
-      <c r="R39" s="47"/>
+      <c r="P39" s="33"/>
+      <c r="Q39" s="33"/>
+      <c r="R39" s="130"/>
     </row>
     <row r="40" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="44"/>
-      <c r="B40" s="45"/>
-      <c r="C40" s="45"/>
-      <c r="D40" s="45"/>
-      <c r="E40" s="45"/>
-      <c r="F40" s="45"/>
-      <c r="G40" s="72"/>
-      <c r="H40" s="45"/>
-      <c r="I40" s="45"/>
-      <c r="J40" s="45"/>
-      <c r="K40" s="45"/>
-      <c r="L40" s="45"/>
-      <c r="M40" s="45"/>
-      <c r="N40" s="72"/>
-      <c r="O40" s="45"/>
-      <c r="P40" s="45"/>
-      <c r="Q40" s="45"/>
-      <c r="R40" s="48"/>
+      <c r="A40" s="86"/>
+      <c r="B40" s="35"/>
+      <c r="C40" s="35"/>
+      <c r="D40" s="35"/>
+      <c r="E40" s="35"/>
+      <c r="F40" s="35"/>
+      <c r="G40" s="36"/>
+      <c r="H40" s="35"/>
+      <c r="I40" s="35"/>
+      <c r="J40" s="35"/>
+      <c r="K40" s="35"/>
+      <c r="L40" s="35"/>
+      <c r="M40" s="35"/>
+      <c r="N40" s="36"/>
+      <c r="O40" s="35"/>
+      <c r="P40" s="35"/>
+      <c r="Q40" s="35"/>
+      <c r="R40" s="131"/>
     </row>
     <row r="41" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="118" t="s">
+      <c r="A41" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="B41" s="119"/>
-      <c r="C41" s="120"/>
-      <c r="D41" s="102"/>
-      <c r="E41" s="103"/>
-      <c r="F41" s="103"/>
-      <c r="G41" s="104"/>
-      <c r="H41" s="108" t="s">
+      <c r="B41" s="28"/>
+      <c r="C41" s="29"/>
+      <c r="D41" s="55"/>
+      <c r="E41" s="56"/>
+      <c r="F41" s="56"/>
+      <c r="G41" s="57"/>
+      <c r="H41" s="71" t="s">
         <v>14</v>
       </c>
-      <c r="I41" s="109"/>
-      <c r="J41" s="110"/>
-      <c r="K41" s="102"/>
-      <c r="L41" s="103"/>
-      <c r="M41" s="103"/>
-      <c r="N41" s="104"/>
-      <c r="O41" s="114"/>
-      <c r="P41" s="114"/>
-      <c r="Q41" s="114"/>
-      <c r="R41" s="115"/>
+      <c r="I41" s="72"/>
+      <c r="J41" s="73"/>
+      <c r="K41" s="55"/>
+      <c r="L41" s="56"/>
+      <c r="M41" s="56"/>
+      <c r="N41" s="57"/>
+      <c r="O41" s="77"/>
+      <c r="P41" s="77"/>
+      <c r="Q41" s="77"/>
+      <c r="R41" s="78"/>
     </row>
     <row r="42" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="121"/>
-      <c r="B42" s="122"/>
-      <c r="C42" s="123"/>
-      <c r="D42" s="105"/>
-      <c r="E42" s="106"/>
-      <c r="F42" s="106"/>
-      <c r="G42" s="107"/>
-      <c r="H42" s="111"/>
-      <c r="I42" s="112"/>
-      <c r="J42" s="113"/>
-      <c r="K42" s="105"/>
-      <c r="L42" s="106"/>
-      <c r="M42" s="106"/>
-      <c r="N42" s="107"/>
-      <c r="O42" s="114"/>
-      <c r="P42" s="114"/>
-      <c r="Q42" s="114"/>
-      <c r="R42" s="115"/>
+      <c r="A42" s="30"/>
+      <c r="B42" s="31"/>
+      <c r="C42" s="32"/>
+      <c r="D42" s="58"/>
+      <c r="E42" s="59"/>
+      <c r="F42" s="59"/>
+      <c r="G42" s="60"/>
+      <c r="H42" s="74"/>
+      <c r="I42" s="75"/>
+      <c r="J42" s="76"/>
+      <c r="K42" s="58"/>
+      <c r="L42" s="59"/>
+      <c r="M42" s="59"/>
+      <c r="N42" s="60"/>
+      <c r="O42" s="77"/>
+      <c r="P42" s="77"/>
+      <c r="Q42" s="77"/>
+      <c r="R42" s="78"/>
     </row>
     <row r="43" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="118" t="s">
+      <c r="A43" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="B43" s="119"/>
-      <c r="C43" s="120"/>
-      <c r="D43" s="102"/>
-      <c r="E43" s="103"/>
-      <c r="F43" s="103"/>
-      <c r="G43" s="104"/>
-      <c r="H43" s="136" t="s">
+      <c r="B43" s="28"/>
+      <c r="C43" s="29"/>
+      <c r="D43" s="55"/>
+      <c r="E43" s="56"/>
+      <c r="F43" s="56"/>
+      <c r="G43" s="57"/>
+      <c r="H43" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="I43" s="119"/>
-      <c r="J43" s="120"/>
-      <c r="K43" s="102"/>
-      <c r="L43" s="103"/>
-      <c r="M43" s="103"/>
-      <c r="N43" s="104"/>
-      <c r="O43" s="114"/>
-      <c r="P43" s="114"/>
-      <c r="Q43" s="114"/>
-      <c r="R43" s="115"/>
+      <c r="I43" s="28"/>
+      <c r="J43" s="29"/>
+      <c r="K43" s="55"/>
+      <c r="L43" s="56"/>
+      <c r="M43" s="56"/>
+      <c r="N43" s="57"/>
+      <c r="O43" s="77"/>
+      <c r="P43" s="77"/>
+      <c r="Q43" s="77"/>
+      <c r="R43" s="78"/>
     </row>
     <row r="44" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="121"/>
-      <c r="B44" s="122"/>
-      <c r="C44" s="123"/>
-      <c r="D44" s="105"/>
-      <c r="E44" s="106"/>
-      <c r="F44" s="106"/>
-      <c r="G44" s="107"/>
-      <c r="H44" s="137"/>
-      <c r="I44" s="122"/>
-      <c r="J44" s="123"/>
-      <c r="K44" s="105"/>
-      <c r="L44" s="106"/>
-      <c r="M44" s="106"/>
-      <c r="N44" s="107"/>
-      <c r="O44" s="114"/>
-      <c r="P44" s="114"/>
-      <c r="Q44" s="114"/>
-      <c r="R44" s="115"/>
+      <c r="A44" s="30"/>
+      <c r="B44" s="31"/>
+      <c r="C44" s="32"/>
+      <c r="D44" s="58"/>
+      <c r="E44" s="59"/>
+      <c r="F44" s="59"/>
+      <c r="G44" s="60"/>
+      <c r="H44" s="62"/>
+      <c r="I44" s="31"/>
+      <c r="J44" s="32"/>
+      <c r="K44" s="58"/>
+      <c r="L44" s="59"/>
+      <c r="M44" s="59"/>
+      <c r="N44" s="60"/>
+      <c r="O44" s="77"/>
+      <c r="P44" s="77"/>
+      <c r="Q44" s="77"/>
+      <c r="R44" s="78"/>
     </row>
     <row r="45" spans="1:18" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A45" s="134" t="s">
+      <c r="A45" s="53" t="s">
         <v>17</v>
       </c>
-      <c r="B45" s="135"/>
-      <c r="C45" s="135"/>
-      <c r="D45" s="100"/>
-      <c r="E45" s="100"/>
-      <c r="F45" s="100"/>
-      <c r="G45" s="101"/>
-      <c r="H45" s="135" t="s">
+      <c r="B45" s="54"/>
+      <c r="C45" s="54"/>
+      <c r="D45" s="69"/>
+      <c r="E45" s="69"/>
+      <c r="F45" s="69"/>
+      <c r="G45" s="70"/>
+      <c r="H45" s="54" t="s">
         <v>17</v>
       </c>
-      <c r="I45" s="135"/>
-      <c r="J45" s="135"/>
-      <c r="K45" s="100"/>
-      <c r="L45" s="100"/>
-      <c r="M45" s="100"/>
-      <c r="N45" s="101"/>
-      <c r="O45" s="116"/>
-      <c r="P45" s="116"/>
-      <c r="Q45" s="116"/>
-      <c r="R45" s="117"/>
+      <c r="I45" s="54"/>
+      <c r="J45" s="54"/>
+      <c r="K45" s="69"/>
+      <c r="L45" s="69"/>
+      <c r="M45" s="69"/>
+      <c r="N45" s="70"/>
+      <c r="O45" s="79"/>
+      <c r="P45" s="79"/>
+      <c r="Q45" s="79"/>
+      <c r="R45" s="80"/>
     </row>
     <row r="46" spans="1:18" ht="20.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.4"/>
     <row r="47" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -2585,128 +2588,128 @@
       </c>
     </row>
     <row r="49" spans="1:18" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="128"/>
-      <c r="B49" s="129"/>
-      <c r="C49" s="130"/>
-      <c r="D49" s="92"/>
-      <c r="E49" s="93"/>
-      <c r="F49" s="93"/>
-      <c r="G49" s="93"/>
-      <c r="H49" s="98"/>
-      <c r="I49" s="92"/>
-      <c r="J49" s="93"/>
-      <c r="K49" s="93"/>
-      <c r="L49" s="93"/>
-      <c r="M49" s="98"/>
-      <c r="N49" s="92"/>
-      <c r="O49" s="93"/>
-      <c r="P49" s="93"/>
-      <c r="Q49" s="93"/>
-      <c r="R49" s="94"/>
+      <c r="A49" s="41"/>
+      <c r="B49" s="42"/>
+      <c r="C49" s="43"/>
+      <c r="D49" s="47"/>
+      <c r="E49" s="48"/>
+      <c r="F49" s="48"/>
+      <c r="G49" s="48"/>
+      <c r="H49" s="49"/>
+      <c r="I49" s="47"/>
+      <c r="J49" s="48"/>
+      <c r="K49" s="48"/>
+      <c r="L49" s="48"/>
+      <c r="M49" s="49"/>
+      <c r="N49" s="47"/>
+      <c r="O49" s="48"/>
+      <c r="P49" s="48"/>
+      <c r="Q49" s="48"/>
+      <c r="R49" s="67"/>
     </row>
     <row r="50" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="131"/>
-      <c r="B50" s="132"/>
-      <c r="C50" s="133"/>
-      <c r="D50" s="95"/>
-      <c r="E50" s="96"/>
-      <c r="F50" s="96"/>
-      <c r="G50" s="96"/>
-      <c r="H50" s="99"/>
-      <c r="I50" s="95"/>
-      <c r="J50" s="96"/>
-      <c r="K50" s="96"/>
-      <c r="L50" s="96"/>
-      <c r="M50" s="99"/>
-      <c r="N50" s="95"/>
-      <c r="O50" s="96"/>
-      <c r="P50" s="96"/>
-      <c r="Q50" s="96"/>
-      <c r="R50" s="97"/>
+      <c r="A50" s="44"/>
+      <c r="B50" s="45"/>
+      <c r="C50" s="46"/>
+      <c r="D50" s="50"/>
+      <c r="E50" s="51"/>
+      <c r="F50" s="51"/>
+      <c r="G50" s="51"/>
+      <c r="H50" s="52"/>
+      <c r="I50" s="50"/>
+      <c r="J50" s="51"/>
+      <c r="K50" s="51"/>
+      <c r="L50" s="51"/>
+      <c r="M50" s="52"/>
+      <c r="N50" s="50"/>
+      <c r="O50" s="51"/>
+      <c r="P50" s="51"/>
+      <c r="Q50" s="51"/>
+      <c r="R50" s="68"/>
     </row>
     <row r="51" spans="1:18" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A51" s="30" t="s">
+      <c r="A51" s="120" t="s">
         <v>19</v>
       </c>
-      <c r="B51" s="31"/>
-      <c r="C51" s="32"/>
-      <c r="D51" s="28"/>
-      <c r="E51" s="28"/>
-      <c r="F51" s="28"/>
-      <c r="G51" s="28"/>
-      <c r="H51" s="28"/>
-      <c r="I51" s="28"/>
-      <c r="J51" s="28"/>
-      <c r="K51" s="28"/>
-      <c r="L51" s="28"/>
-      <c r="M51" s="28"/>
-      <c r="N51" s="28"/>
-      <c r="O51" s="28"/>
-      <c r="P51" s="28"/>
-      <c r="Q51" s="28"/>
-      <c r="R51" s="29"/>
+      <c r="B51" s="121"/>
+      <c r="C51" s="122"/>
+      <c r="D51" s="83"/>
+      <c r="E51" s="83"/>
+      <c r="F51" s="83"/>
+      <c r="G51" s="83"/>
+      <c r="H51" s="83"/>
+      <c r="I51" s="83"/>
+      <c r="J51" s="83"/>
+      <c r="K51" s="83"/>
+      <c r="L51" s="83"/>
+      <c r="M51" s="83"/>
+      <c r="N51" s="83"/>
+      <c r="O51" s="83"/>
+      <c r="P51" s="83"/>
+      <c r="Q51" s="83"/>
+      <c r="R51" s="119"/>
     </row>
     <row r="52" spans="1:18" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A52" s="33"/>
-      <c r="B52" s="34"/>
-      <c r="C52" s="35"/>
-      <c r="D52" s="28"/>
-      <c r="E52" s="28"/>
-      <c r="F52" s="28"/>
-      <c r="G52" s="28"/>
-      <c r="H52" s="28"/>
-      <c r="I52" s="28"/>
-      <c r="J52" s="28"/>
-      <c r="K52" s="28"/>
-      <c r="L52" s="28"/>
-      <c r="M52" s="28"/>
-      <c r="N52" s="28"/>
-      <c r="O52" s="28"/>
-      <c r="P52" s="28"/>
-      <c r="Q52" s="28"/>
-      <c r="R52" s="29"/>
+      <c r="A52" s="123"/>
+      <c r="B52" s="124"/>
+      <c r="C52" s="125"/>
+      <c r="D52" s="83"/>
+      <c r="E52" s="83"/>
+      <c r="F52" s="83"/>
+      <c r="G52" s="83"/>
+      <c r="H52" s="83"/>
+      <c r="I52" s="83"/>
+      <c r="J52" s="83"/>
+      <c r="K52" s="83"/>
+      <c r="L52" s="83"/>
+      <c r="M52" s="83"/>
+      <c r="N52" s="83"/>
+      <c r="O52" s="83"/>
+      <c r="P52" s="83"/>
+      <c r="Q52" s="83"/>
+      <c r="R52" s="119"/>
     </row>
     <row r="53" spans="1:18" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A53" s="73" t="s">
+      <c r="A53" s="103" t="s">
         <v>20</v>
       </c>
-      <c r="B53" s="74"/>
-      <c r="C53" s="75"/>
-      <c r="D53" s="36"/>
-      <c r="E53" s="36"/>
-      <c r="F53" s="36"/>
-      <c r="G53" s="36"/>
-      <c r="H53" s="36"/>
-      <c r="I53" s="36"/>
-      <c r="J53" s="36"/>
-      <c r="K53" s="36"/>
-      <c r="L53" s="36"/>
-      <c r="M53" s="36"/>
-      <c r="N53" s="36"/>
-      <c r="O53" s="36"/>
-      <c r="P53" s="36"/>
-      <c r="Q53" s="36"/>
-      <c r="R53" s="37"/>
+      <c r="B53" s="104"/>
+      <c r="C53" s="105"/>
+      <c r="D53" s="81"/>
+      <c r="E53" s="81"/>
+      <c r="F53" s="81"/>
+      <c r="G53" s="81"/>
+      <c r="H53" s="81"/>
+      <c r="I53" s="81"/>
+      <c r="J53" s="81"/>
+      <c r="K53" s="81"/>
+      <c r="L53" s="81"/>
+      <c r="M53" s="81"/>
+      <c r="N53" s="81"/>
+      <c r="O53" s="81"/>
+      <c r="P53" s="81"/>
+      <c r="Q53" s="81"/>
+      <c r="R53" s="126"/>
     </row>
     <row r="54" spans="1:18" s="2" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="76"/>
-      <c r="B54" s="77"/>
-      <c r="C54" s="78"/>
-      <c r="D54" s="38"/>
-      <c r="E54" s="38"/>
-      <c r="F54" s="38"/>
-      <c r="G54" s="38"/>
-      <c r="H54" s="38"/>
-      <c r="I54" s="38"/>
-      <c r="J54" s="38"/>
-      <c r="K54" s="38"/>
-      <c r="L54" s="38"/>
-      <c r="M54" s="38"/>
-      <c r="N54" s="38"/>
-      <c r="O54" s="38"/>
-      <c r="P54" s="38"/>
-      <c r="Q54" s="38"/>
-      <c r="R54" s="39"/>
+      <c r="A54" s="106"/>
+      <c r="B54" s="107"/>
+      <c r="C54" s="108"/>
+      <c r="D54" s="82"/>
+      <c r="E54" s="82"/>
+      <c r="F54" s="82"/>
+      <c r="G54" s="82"/>
+      <c r="H54" s="82"/>
+      <c r="I54" s="82"/>
+      <c r="J54" s="82"/>
+      <c r="K54" s="82"/>
+      <c r="L54" s="82"/>
+      <c r="M54" s="82"/>
+      <c r="N54" s="82"/>
+      <c r="O54" s="82"/>
+      <c r="P54" s="82"/>
+      <c r="Q54" s="82"/>
+      <c r="R54" s="127"/>
     </row>
     <row r="55" spans="1:18" s="2" customFormat="1" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.15"/>
     <row r="56" spans="1:18" s="2" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -2721,26 +2724,22 @@
   </sheetData>
   <sheetProtection formatCells="0"/>
   <mergeCells count="52">
-    <mergeCell ref="A43:C44"/>
-    <mergeCell ref="D39:G40"/>
-    <mergeCell ref="D23:L25"/>
-    <mergeCell ref="A49:C50"/>
-    <mergeCell ref="D49:H50"/>
-    <mergeCell ref="A45:C45"/>
-    <mergeCell ref="H45:J45"/>
-    <mergeCell ref="A41:C42"/>
-    <mergeCell ref="D43:G44"/>
-    <mergeCell ref="H43:J44"/>
-    <mergeCell ref="M22:N28"/>
-    <mergeCell ref="N49:R50"/>
-    <mergeCell ref="I49:M50"/>
-    <mergeCell ref="D45:G45"/>
-    <mergeCell ref="D41:G42"/>
-    <mergeCell ref="H41:J42"/>
-    <mergeCell ref="K41:N42"/>
-    <mergeCell ref="O41:R45"/>
-    <mergeCell ref="K43:N44"/>
-    <mergeCell ref="K45:N45"/>
+    <mergeCell ref="O3:R4"/>
+    <mergeCell ref="D51:H52"/>
+    <mergeCell ref="N51:R52"/>
+    <mergeCell ref="A51:C52"/>
+    <mergeCell ref="N53:R54"/>
+    <mergeCell ref="M31:R32"/>
+    <mergeCell ref="M33:R34"/>
+    <mergeCell ref="A33:C34"/>
+    <mergeCell ref="O39:R40"/>
+    <mergeCell ref="A35:C36"/>
+    <mergeCell ref="D33:I34"/>
+    <mergeCell ref="J33:L34"/>
+    <mergeCell ref="D35:R36"/>
+    <mergeCell ref="A31:C32"/>
+    <mergeCell ref="J31:L32"/>
+    <mergeCell ref="D53:H54"/>
     <mergeCell ref="I53:M54"/>
     <mergeCell ref="I51:M52"/>
     <mergeCell ref="O1:R1"/>
@@ -2757,22 +2756,26 @@
     <mergeCell ref="K39:N40"/>
     <mergeCell ref="A53:C54"/>
     <mergeCell ref="O22:R28"/>
-    <mergeCell ref="O3:R4"/>
-    <mergeCell ref="D51:H52"/>
-    <mergeCell ref="N51:R52"/>
-    <mergeCell ref="A51:C52"/>
-    <mergeCell ref="N53:R54"/>
-    <mergeCell ref="M31:R32"/>
-    <mergeCell ref="M33:R34"/>
-    <mergeCell ref="A33:C34"/>
-    <mergeCell ref="O39:R40"/>
-    <mergeCell ref="A35:C36"/>
-    <mergeCell ref="D33:I34"/>
-    <mergeCell ref="J33:L34"/>
-    <mergeCell ref="D35:R36"/>
-    <mergeCell ref="A31:C32"/>
-    <mergeCell ref="J31:L32"/>
-    <mergeCell ref="D53:H54"/>
+    <mergeCell ref="M22:N28"/>
+    <mergeCell ref="N49:R50"/>
+    <mergeCell ref="I49:M50"/>
+    <mergeCell ref="D45:G45"/>
+    <mergeCell ref="D41:G42"/>
+    <mergeCell ref="H41:J42"/>
+    <mergeCell ref="K41:N42"/>
+    <mergeCell ref="O41:R45"/>
+    <mergeCell ref="K43:N44"/>
+    <mergeCell ref="K45:N45"/>
+    <mergeCell ref="A43:C44"/>
+    <mergeCell ref="D39:G40"/>
+    <mergeCell ref="D23:L25"/>
+    <mergeCell ref="A49:C50"/>
+    <mergeCell ref="D49:H50"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="H45:J45"/>
+    <mergeCell ref="A41:C42"/>
+    <mergeCell ref="D43:G44"/>
+    <mergeCell ref="H43:J44"/>
   </mergeCells>
   <phoneticPr fontId="20"/>
   <printOptions horizontalCentered="1"/>
@@ -2800,62 +2803,62 @@
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="140" t="s">
+      <c r="E2" s="148" t="s">
         <v>22</v>
       </c>
-      <c r="F2" s="140"/>
-      <c r="G2" s="140" t="s">
+      <c r="F2" s="148"/>
+      <c r="G2" s="148" t="s">
         <v>23</v>
       </c>
-      <c r="H2" s="140"/>
-      <c r="I2" s="140" t="s">
+      <c r="H2" s="148"/>
+      <c r="I2" s="148" t="s">
         <v>24</v>
       </c>
-      <c r="J2" s="140"/>
-      <c r="K2" s="140" t="s">
+      <c r="J2" s="148"/>
+      <c r="K2" s="148" t="s">
         <v>25</v>
       </c>
-      <c r="L2" s="140"/>
-      <c r="M2" s="140" t="s">
+      <c r="L2" s="148"/>
+      <c r="M2" s="148" t="s">
         <v>26</v>
       </c>
-      <c r="N2" s="140"/>
+      <c r="N2" s="148"/>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B3" s="138" t="s">
+      <c r="B3" s="145" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="138"/>
+      <c r="C3" s="145"/>
       <c r="D3" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="138"/>
-      <c r="F3" s="138"/>
-      <c r="G3" s="139"/>
-      <c r="H3" s="139"/>
-      <c r="I3" s="138"/>
-      <c r="J3" s="138"/>
-      <c r="K3" s="138"/>
-      <c r="L3" s="138"/>
-      <c r="M3" s="138"/>
-      <c r="N3" s="138"/>
+      <c r="E3" s="145"/>
+      <c r="F3" s="145"/>
+      <c r="G3" s="149"/>
+      <c r="H3" s="149"/>
+      <c r="I3" s="145"/>
+      <c r="J3" s="145"/>
+      <c r="K3" s="145"/>
+      <c r="L3" s="145"/>
+      <c r="M3" s="145"/>
+      <c r="N3" s="145"/>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B4" s="138"/>
-      <c r="C4" s="138"/>
+      <c r="B4" s="145"/>
+      <c r="C4" s="145"/>
       <c r="D4" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="138"/>
-      <c r="F4" s="138"/>
-      <c r="G4" s="138"/>
-      <c r="H4" s="138"/>
-      <c r="I4" s="138"/>
-      <c r="J4" s="138"/>
-      <c r="K4" s="138"/>
-      <c r="L4" s="138"/>
-      <c r="M4" s="138"/>
-      <c r="N4" s="138"/>
+      <c r="E4" s="145"/>
+      <c r="F4" s="145"/>
+      <c r="G4" s="145"/>
+      <c r="H4" s="145"/>
+      <c r="I4" s="145"/>
+      <c r="J4" s="145"/>
+      <c r="K4" s="145"/>
+      <c r="L4" s="145"/>
+      <c r="M4" s="145"/>
+      <c r="N4" s="145"/>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B5" s="1"/>
@@ -2876,39 +2879,39 @@
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
-      <c r="E6" s="145" t="s">
+      <c r="E6" s="143" t="s">
         <v>22</v>
       </c>
-      <c r="F6" s="146"/>
-      <c r="G6" s="145" t="s">
+      <c r="F6" s="144"/>
+      <c r="G6" s="143" t="s">
         <v>23</v>
       </c>
-      <c r="H6" s="146"/>
-      <c r="I6" s="145" t="s">
+      <c r="H6" s="144"/>
+      <c r="I6" s="143" t="s">
         <v>24</v>
       </c>
-      <c r="J6" s="146"/>
-      <c r="K6" s="145" t="s">
+      <c r="J6" s="144"/>
+      <c r="K6" s="143" t="s">
         <v>25</v>
       </c>
-      <c r="L6" s="146"/>
-      <c r="M6" s="145" t="s">
+      <c r="L6" s="144"/>
+      <c r="M6" s="143" t="s">
         <v>26</v>
       </c>
-      <c r="N6" s="146"/>
+      <c r="N6" s="144"/>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B7" s="138" t="s">
+      <c r="B7" s="145" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="138"/>
+      <c r="C7" s="145"/>
       <c r="D7" s="26" t="s">
         <v>28</v>
       </c>
       <c r="E7" s="141"/>
       <c r="F7" s="142"/>
-      <c r="G7" s="143"/>
-      <c r="H7" s="144"/>
+      <c r="G7" s="146"/>
+      <c r="H7" s="147"/>
       <c r="I7" s="141"/>
       <c r="J7" s="142"/>
       <c r="K7" s="141"/>
@@ -2917,8 +2920,8 @@
       <c r="N7" s="142"/>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B8" s="138"/>
-      <c r="C8" s="138"/>
+      <c r="B8" s="145"/>
+      <c r="C8" s="145"/>
       <c r="D8" s="26" t="s">
         <v>29</v>
       </c>
@@ -2952,39 +2955,39 @@
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
-      <c r="E10" s="145" t="s">
+      <c r="E10" s="143" t="s">
         <v>22</v>
       </c>
-      <c r="F10" s="146"/>
-      <c r="G10" s="145" t="s">
+      <c r="F10" s="144"/>
+      <c r="G10" s="143" t="s">
         <v>23</v>
       </c>
-      <c r="H10" s="146"/>
-      <c r="I10" s="145" t="s">
+      <c r="H10" s="144"/>
+      <c r="I10" s="143" t="s">
         <v>24</v>
       </c>
-      <c r="J10" s="146"/>
-      <c r="K10" s="145" t="s">
+      <c r="J10" s="144"/>
+      <c r="K10" s="143" t="s">
         <v>25</v>
       </c>
-      <c r="L10" s="146"/>
-      <c r="M10" s="145" t="s">
+      <c r="L10" s="144"/>
+      <c r="M10" s="143" t="s">
         <v>26</v>
       </c>
-      <c r="N10" s="146"/>
+      <c r="N10" s="144"/>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B11" s="138" t="s">
+      <c r="B11" s="145" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="138"/>
+      <c r="C11" s="145"/>
       <c r="D11" s="26" t="s">
         <v>28</v>
       </c>
       <c r="E11" s="141"/>
       <c r="F11" s="142"/>
-      <c r="G11" s="143"/>
-      <c r="H11" s="144"/>
+      <c r="G11" s="146"/>
+      <c r="H11" s="147"/>
       <c r="I11" s="141"/>
       <c r="J11" s="142"/>
       <c r="K11" s="141"/>
@@ -2993,8 +2996,8 @@
       <c r="N11" s="142"/>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B12" s="138"/>
-      <c r="C12" s="138"/>
+      <c r="B12" s="145"/>
+      <c r="C12" s="145"/>
       <c r="D12" s="26" t="s">
         <v>29</v>
       </c>
@@ -3043,39 +3046,39 @@
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
-      <c r="E15" s="145" t="s">
+      <c r="E15" s="143" t="s">
         <v>22</v>
       </c>
-      <c r="F15" s="146"/>
-      <c r="G15" s="145" t="s">
+      <c r="F15" s="144"/>
+      <c r="G15" s="143" t="s">
         <v>23</v>
       </c>
-      <c r="H15" s="146"/>
-      <c r="I15" s="145" t="s">
+      <c r="H15" s="144"/>
+      <c r="I15" s="143" t="s">
         <v>24</v>
       </c>
-      <c r="J15" s="146"/>
-      <c r="K15" s="145" t="s">
+      <c r="J15" s="144"/>
+      <c r="K15" s="143" t="s">
         <v>25</v>
       </c>
-      <c r="L15" s="146"/>
-      <c r="M15" s="145" t="s">
+      <c r="L15" s="144"/>
+      <c r="M15" s="143" t="s">
         <v>26</v>
       </c>
-      <c r="N15" s="146"/>
+      <c r="N15" s="144"/>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B16" s="138" t="s">
+      <c r="B16" s="145" t="s">
         <v>32</v>
       </c>
-      <c r="C16" s="138"/>
+      <c r="C16" s="145"/>
       <c r="D16" s="26" t="s">
         <v>28</v>
       </c>
       <c r="E16" s="141"/>
       <c r="F16" s="142"/>
-      <c r="G16" s="143"/>
-      <c r="H16" s="144"/>
+      <c r="G16" s="146"/>
+      <c r="H16" s="147"/>
       <c r="I16" s="141"/>
       <c r="J16" s="142"/>
       <c r="K16" s="141"/>
@@ -3084,8 +3087,8 @@
       <c r="N16" s="142"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B17" s="138"/>
-      <c r="C17" s="138"/>
+      <c r="B17" s="145"/>
+      <c r="C17" s="145"/>
       <c r="D17" s="26" t="s">
         <v>29</v>
       </c>
@@ -3101,97 +3104,173 @@
       <c r="N17" s="142"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B20" s="147"/>
-      <c r="C20" s="147"/>
-      <c r="D20" s="147"/>
-      <c r="E20" s="147" t="s">
+      <c r="B20" s="138"/>
+      <c r="C20" s="138"/>
+      <c r="D20" s="138"/>
+      <c r="E20" s="138" t="s">
         <v>33</v>
       </c>
-      <c r="F20" s="147"/>
+      <c r="F20" s="138"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B21" s="147" t="s">
+      <c r="B21" s="138" t="s">
         <v>34</v>
       </c>
-      <c r="C21" s="147"/>
-      <c r="D21" s="147"/>
-      <c r="E21" s="148"/>
-      <c r="F21" s="148"/>
+      <c r="C21" s="138"/>
+      <c r="D21" s="138"/>
+      <c r="E21" s="139"/>
+      <c r="F21" s="139"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B22" s="147" t="s">
+      <c r="B22" s="138" t="s">
         <v>35</v>
       </c>
-      <c r="C22" s="147"/>
-      <c r="D22" s="147"/>
-      <c r="E22" s="148"/>
-      <c r="F22" s="148"/>
+      <c r="C22" s="138"/>
+      <c r="D22" s="138"/>
+      <c r="E22" s="139"/>
+      <c r="F22" s="139"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B23" s="147" t="s">
+      <c r="B23" s="138" t="s">
         <v>36</v>
       </c>
-      <c r="C23" s="147"/>
-      <c r="D23" s="147"/>
-      <c r="E23" s="148"/>
-      <c r="F23" s="148"/>
+      <c r="C23" s="138"/>
+      <c r="D23" s="138"/>
+      <c r="E23" s="139"/>
+      <c r="F23" s="139"/>
     </row>
     <row r="24" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B24" s="147" t="s">
+      <c r="B24" s="138" t="s">
         <v>37</v>
       </c>
-      <c r="C24" s="147"/>
-      <c r="D24" s="147"/>
-      <c r="E24" s="148"/>
-      <c r="F24" s="148"/>
+      <c r="C24" s="138"/>
+      <c r="D24" s="138"/>
+      <c r="E24" s="139"/>
+      <c r="F24" s="139"/>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B25" s="147" t="s">
+      <c r="B25" s="138" t="s">
         <v>38</v>
       </c>
-      <c r="C25" s="147"/>
-      <c r="D25" s="147"/>
-      <c r="E25" s="148"/>
-      <c r="F25" s="148"/>
+      <c r="C25" s="138"/>
+      <c r="D25" s="138"/>
+      <c r="E25" s="139"/>
+      <c r="F25" s="139"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B26" s="147" t="s">
+      <c r="B26" s="138" t="s">
         <v>39</v>
       </c>
-      <c r="C26" s="147"/>
-      <c r="D26" s="147"/>
-      <c r="E26" s="149"/>
-      <c r="F26" s="149"/>
+      <c r="C26" s="138"/>
+      <c r="D26" s="138"/>
+      <c r="E26" s="150"/>
+      <c r="F26" s="150"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B27" s="147" t="s">
+      <c r="B27" s="138" t="s">
         <v>40</v>
       </c>
-      <c r="C27" s="147"/>
-      <c r="D27" s="147"/>
-      <c r="E27" s="149"/>
-      <c r="F27" s="149"/>
+      <c r="C27" s="138"/>
+      <c r="D27" s="138"/>
+      <c r="E27" s="140"/>
+      <c r="F27" s="140"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B28" s="147" t="s">
+      <c r="B28" s="138" t="s">
         <v>41</v>
       </c>
-      <c r="C28" s="147"/>
-      <c r="D28" s="147"/>
-      <c r="E28" s="148"/>
-      <c r="F28" s="148"/>
+      <c r="C28" s="138"/>
+      <c r="D28" s="138"/>
+      <c r="E28" s="139"/>
+      <c r="F28" s="139"/>
     </row>
     <row r="29" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B29" s="147" t="s">
+      <c r="B29" s="138" t="s">
         <v>42</v>
       </c>
-      <c r="C29" s="147"/>
-      <c r="D29" s="147"/>
-      <c r="E29" s="148"/>
-      <c r="F29" s="148"/>
+      <c r="C29" s="138"/>
+      <c r="D29" s="138"/>
+      <c r="E29" s="139"/>
+      <c r="F29" s="139"/>
     </row>
   </sheetData>
   <mergeCells count="84">
+    <mergeCell ref="B3:C4"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="B7:C8"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="M8:N8"/>
+    <mergeCell ref="B11:C12"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="B16:C17"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="K16:L16"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="E25:F25"/>
     <mergeCell ref="B29:D29"/>
     <mergeCell ref="E29:F29"/>
     <mergeCell ref="B26:D26"/>
@@ -3200,82 +3279,6 @@
     <mergeCell ref="E27:F27"/>
     <mergeCell ref="B28:D28"/>
     <mergeCell ref="E28:F28"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="K15:L15"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="B16:C17"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="K16:L16"/>
-    <mergeCell ref="M11:N11"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="M10:N10"/>
-    <mergeCell ref="B11:C12"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="M7:N7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="M8:N8"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="B7:C8"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="B3:C4"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="K3:L3"/>
   </mergeCells>
   <phoneticPr fontId="20"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/storage/app/estimateTemplate/comprehensiveOfRecommend.xlsx
+++ b/storage/app/estimateTemplate/comprehensiveOfRecommend.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yokoyama\Desktop\火災見積\テンプレート\new\mark\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AD55695-7369-402B-878D-E94F1644140F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F6553DA-306D-426E-9411-83B5EF86F6D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-75" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{0E9C5CA5-184F-4C06-AA15-1AF55B55AFB9}"/>
+    <workbookView xWindow="30" yWindow="750" windowWidth="28770" windowHeight="15450" xr2:uid="{0E9C5CA5-184F-4C06-AA15-1AF55B55AFB9}"/>
   </bookViews>
   <sheets>
     <sheet name="おすすめ(総合)" sheetId="2" r:id="rId1"/>
@@ -446,14 +446,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="8">
+  <numFmts count="7">
     <numFmt numFmtId="6" formatCode="&quot;¥&quot;#,##0;[Red]&quot;¥&quot;\-#,##0"/>
     <numFmt numFmtId="176" formatCode="#&quot;階&quot;&quot;建&quot;&quot;て&quot;"/>
     <numFmt numFmtId="177" formatCode="#&quot;棟&quot;"/>
     <numFmt numFmtId="178" formatCode="&quot;延&quot;&quot;面&quot;&quot;積&quot;\ 0.00_ &quot;㎡&quot;"/>
     <numFmt numFmtId="179" formatCode="#,##0_ &quot;千&quot;&quot;円&quot;"/>
     <numFmt numFmtId="180" formatCode="#,##0_ &quot;円&quot;"/>
-    <numFmt numFmtId="181" formatCode="0_ &quot;年&quot;"/>
     <numFmt numFmtId="182" formatCode="#,##0_ &quot;円&quot;&quot;お&quot;&quot;得&quot;"/>
   </numFmts>
   <fonts count="21" x14ac:knownFonts="1">
@@ -1087,7 +1086,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="6" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="151">
+  <cellXfs count="150">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1166,175 +1165,97 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="18" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="18" fillId="0" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="182" fontId="9" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="9" fillId="0" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="9" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="9" fillId="0" borderId="29" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="24" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="17" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="17" fillId="2" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="17" fillId="2" borderId="31" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="17" fillId="2" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="17" fillId="2" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="17" fillId="2" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="26" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="17" fillId="2" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="17" fillId="2" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="8" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="28" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="16" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="16" fillId="0" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="16" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="16" fillId="0" borderId="29" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="9" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="9" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="58" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -1344,18 +1265,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -1380,12 +1289,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1395,6 +1298,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="2" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1440,65 +1349,158 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="182" fontId="9" fillId="0" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="9" fillId="0" borderId="29" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="24" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="26" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="8" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="28" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="16" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="16" fillId="0" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="16" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="16" fillId="0" borderId="29" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="35" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="33" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="34" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1509,34 +1511,28 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="33" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="34" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="35" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="31" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1915,10 +1911,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="O1" s="84"/>
-      <c r="P1" s="84"/>
-      <c r="Q1" s="84"/>
-      <c r="R1" s="84"/>
+      <c r="O1" s="58"/>
+      <c r="P1" s="58"/>
+      <c r="Q1" s="58"/>
+      <c r="R1" s="58"/>
     </row>
     <row r="2" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="O2" s="25"/>
@@ -1928,16 +1924,16 @@
     </row>
     <row r="3" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A3" s="3"/>
-      <c r="O3" s="118"/>
-      <c r="P3" s="118"/>
-      <c r="Q3" s="118"/>
-      <c r="R3" s="118"/>
+      <c r="O3" s="27"/>
+      <c r="P3" s="27"/>
+      <c r="Q3" s="27"/>
+      <c r="R3" s="27"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="O4" s="118"/>
-      <c r="P4" s="118"/>
-      <c r="Q4" s="118"/>
-      <c r="R4" s="118"/>
+      <c r="O4" s="27"/>
+      <c r="P4" s="27"/>
+      <c r="Q4" s="27"/>
+      <c r="R4" s="27"/>
     </row>
     <row r="5" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="N5" s="24"/>
@@ -2000,196 +1996,196 @@
       <c r="R10" s="20"/>
     </row>
     <row r="11" spans="1:18" ht="21" x14ac:dyDescent="0.4">
-      <c r="A11" s="85" t="s">
+      <c r="A11" s="59" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="85"/>
-      <c r="C11" s="85"/>
-      <c r="D11" s="85"/>
-      <c r="E11" s="85"/>
-      <c r="F11" s="85"/>
-      <c r="G11" s="85"/>
-      <c r="H11" s="85"/>
-      <c r="I11" s="85"/>
-      <c r="J11" s="85"/>
-      <c r="K11" s="85"/>
-      <c r="L11" s="85"/>
-      <c r="M11" s="85"/>
-      <c r="N11" s="85"/>
-      <c r="O11" s="85"/>
-      <c r="P11" s="85"/>
-      <c r="Q11" s="85"/>
-      <c r="R11" s="85"/>
+      <c r="B11" s="59"/>
+      <c r="C11" s="59"/>
+      <c r="D11" s="59"/>
+      <c r="E11" s="59"/>
+      <c r="F11" s="59"/>
+      <c r="G11" s="59"/>
+      <c r="H11" s="59"/>
+      <c r="I11" s="59"/>
+      <c r="J11" s="59"/>
+      <c r="K11" s="59"/>
+      <c r="L11" s="59"/>
+      <c r="M11" s="59"/>
+      <c r="N11" s="59"/>
+      <c r="O11" s="59"/>
+      <c r="P11" s="59"/>
+      <c r="Q11" s="59"/>
+      <c r="R11" s="59"/>
     </row>
     <row r="14" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="15" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
-      <c r="A15" s="96" t="s">
+      <c r="A15" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="B15" s="96"/>
-      <c r="C15" s="96"/>
-      <c r="D15" s="96"/>
-      <c r="E15" s="96"/>
-      <c r="F15" s="96"/>
-      <c r="G15" s="96"/>
-      <c r="H15" s="96"/>
-      <c r="I15" s="96"/>
-      <c r="J15" s="96"/>
-      <c r="K15" s="96"/>
-      <c r="L15" s="96"/>
-      <c r="M15" s="96"/>
-      <c r="N15" s="96"/>
-      <c r="O15" s="96"/>
-      <c r="P15" s="96"/>
-      <c r="Q15" s="96"/>
-      <c r="R15" s="96"/>
+      <c r="B15" s="66"/>
+      <c r="C15" s="66"/>
+      <c r="D15" s="66"/>
+      <c r="E15" s="66"/>
+      <c r="F15" s="66"/>
+      <c r="G15" s="66"/>
+      <c r="H15" s="66"/>
+      <c r="I15" s="66"/>
+      <c r="J15" s="66"/>
+      <c r="K15" s="66"/>
+      <c r="L15" s="66"/>
+      <c r="M15" s="66"/>
+      <c r="N15" s="66"/>
+      <c r="O15" s="66"/>
+      <c r="P15" s="66"/>
+      <c r="Q15" s="66"/>
+      <c r="R15" s="66"/>
     </row>
     <row r="18" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
-      <c r="A18" s="97" t="s">
+      <c r="A18" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="B18" s="97"/>
-      <c r="C18" s="97"/>
-      <c r="D18" s="97"/>
-      <c r="E18" s="97"/>
-      <c r="F18" s="97"/>
-      <c r="G18" s="97"/>
-      <c r="H18" s="97"/>
-      <c r="I18" s="97"/>
-      <c r="J18" s="97"/>
-      <c r="K18" s="97"/>
-      <c r="L18" s="97"/>
-      <c r="M18" s="97"/>
-      <c r="N18" s="97"/>
-      <c r="O18" s="97"/>
-      <c r="P18" s="97"/>
-      <c r="Q18" s="97"/>
-      <c r="R18" s="97"/>
+      <c r="B18" s="67"/>
+      <c r="C18" s="67"/>
+      <c r="D18" s="67"/>
+      <c r="E18" s="67"/>
+      <c r="F18" s="67"/>
+      <c r="G18" s="67"/>
+      <c r="H18" s="67"/>
+      <c r="I18" s="67"/>
+      <c r="J18" s="67"/>
+      <c r="K18" s="67"/>
+      <c r="L18" s="67"/>
+      <c r="M18" s="67"/>
+      <c r="N18" s="67"/>
+      <c r="O18" s="67"/>
+      <c r="P18" s="67"/>
+      <c r="Q18" s="67"/>
+      <c r="R18" s="67"/>
     </row>
     <row r="19" spans="1:18" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="20" spans="1:18" ht="12.75" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="89" t="s">
+      <c r="A20" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="B20" s="33"/>
-      <c r="C20" s="33"/>
-      <c r="D20" s="90"/>
-      <c r="E20" s="91"/>
-      <c r="F20" s="91"/>
-      <c r="G20" s="91"/>
-      <c r="H20" s="91"/>
-      <c r="I20" s="91"/>
-      <c r="J20" s="91"/>
-      <c r="K20" s="91"/>
-      <c r="L20" s="91"/>
-      <c r="M20" s="91"/>
-      <c r="N20" s="91"/>
-      <c r="O20" s="91"/>
-      <c r="P20" s="91"/>
-      <c r="Q20" s="91"/>
-      <c r="R20" s="92"/>
+      <c r="B20" s="46"/>
+      <c r="C20" s="46"/>
+      <c r="D20" s="60"/>
+      <c r="E20" s="61"/>
+      <c r="F20" s="61"/>
+      <c r="G20" s="61"/>
+      <c r="H20" s="61"/>
+      <c r="I20" s="61"/>
+      <c r="J20" s="61"/>
+      <c r="K20" s="61"/>
+      <c r="L20" s="61"/>
+      <c r="M20" s="61"/>
+      <c r="N20" s="61"/>
+      <c r="O20" s="61"/>
+      <c r="P20" s="61"/>
+      <c r="Q20" s="61"/>
+      <c r="R20" s="62"/>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A21" s="86"/>
-      <c r="B21" s="35"/>
-      <c r="C21" s="35"/>
-      <c r="D21" s="93"/>
-      <c r="E21" s="94"/>
-      <c r="F21" s="94"/>
-      <c r="G21" s="94"/>
-      <c r="H21" s="94"/>
-      <c r="I21" s="94"/>
-      <c r="J21" s="94"/>
-      <c r="K21" s="94"/>
-      <c r="L21" s="94"/>
-      <c r="M21" s="94"/>
-      <c r="N21" s="94"/>
-      <c r="O21" s="94"/>
-      <c r="P21" s="94"/>
-      <c r="Q21" s="94"/>
-      <c r="R21" s="95"/>
+      <c r="A21" s="44"/>
+      <c r="B21" s="45"/>
+      <c r="C21" s="45"/>
+      <c r="D21" s="63"/>
+      <c r="E21" s="64"/>
+      <c r="F21" s="64"/>
+      <c r="G21" s="64"/>
+      <c r="H21" s="64"/>
+      <c r="I21" s="64"/>
+      <c r="J21" s="64"/>
+      <c r="K21" s="64"/>
+      <c r="L21" s="64"/>
+      <c r="M21" s="64"/>
+      <c r="N21" s="64"/>
+      <c r="O21" s="64"/>
+      <c r="P21" s="64"/>
+      <c r="Q21" s="64"/>
+      <c r="R21" s="65"/>
     </row>
     <row r="22" spans="1:18" ht="5.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="86" t="s">
+      <c r="A22" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="B22" s="35"/>
-      <c r="C22" s="35"/>
+      <c r="B22" s="45"/>
+      <c r="C22" s="45"/>
       <c r="D22" s="19"/>
       <c r="L22" s="18"/>
-      <c r="M22" s="63" t="s">
+      <c r="M22" s="88" t="s">
         <v>5</v>
       </c>
-      <c r="N22" s="64"/>
-      <c r="O22" s="109"/>
-      <c r="P22" s="110"/>
-      <c r="Q22" s="110"/>
-      <c r="R22" s="111"/>
+      <c r="N22" s="89"/>
+      <c r="O22" s="79"/>
+      <c r="P22" s="80"/>
+      <c r="Q22" s="80"/>
+      <c r="R22" s="81"/>
     </row>
     <row r="23" spans="1:18" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="86"/>
-      <c r="B23" s="35"/>
-      <c r="C23" s="35"/>
-      <c r="D23" s="37"/>
-      <c r="E23" s="38"/>
-      <c r="F23" s="38"/>
-      <c r="G23" s="38"/>
-      <c r="H23" s="38"/>
-      <c r="I23" s="38"/>
-      <c r="J23" s="38"/>
-      <c r="K23" s="38"/>
-      <c r="L23" s="39"/>
-      <c r="M23" s="63"/>
-      <c r="N23" s="64"/>
-      <c r="O23" s="112"/>
-      <c r="P23" s="113"/>
-      <c r="Q23" s="113"/>
-      <c r="R23" s="114"/>
+      <c r="A23" s="44"/>
+      <c r="B23" s="45"/>
+      <c r="C23" s="45"/>
+      <c r="D23" s="116"/>
+      <c r="E23" s="117"/>
+      <c r="F23" s="117"/>
+      <c r="G23" s="117"/>
+      <c r="H23" s="117"/>
+      <c r="I23" s="117"/>
+      <c r="J23" s="117"/>
+      <c r="K23" s="117"/>
+      <c r="L23" s="118"/>
+      <c r="M23" s="88"/>
+      <c r="N23" s="89"/>
+      <c r="O23" s="82"/>
+      <c r="P23" s="83"/>
+      <c r="Q23" s="83"/>
+      <c r="R23" s="84"/>
     </row>
     <row r="24" spans="1:18" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="86"/>
-      <c r="B24" s="35"/>
-      <c r="C24" s="35"/>
-      <c r="D24" s="40"/>
-      <c r="E24" s="38"/>
-      <c r="F24" s="38"/>
-      <c r="G24" s="38"/>
-      <c r="H24" s="38"/>
-      <c r="I24" s="38"/>
-      <c r="J24" s="38"/>
-      <c r="K24" s="38"/>
-      <c r="L24" s="39"/>
-      <c r="M24" s="63"/>
-      <c r="N24" s="64"/>
-      <c r="O24" s="112"/>
-      <c r="P24" s="113"/>
-      <c r="Q24" s="113"/>
-      <c r="R24" s="114"/>
+      <c r="A24" s="44"/>
+      <c r="B24" s="45"/>
+      <c r="C24" s="45"/>
+      <c r="D24" s="119"/>
+      <c r="E24" s="117"/>
+      <c r="F24" s="117"/>
+      <c r="G24" s="117"/>
+      <c r="H24" s="117"/>
+      <c r="I24" s="117"/>
+      <c r="J24" s="117"/>
+      <c r="K24" s="117"/>
+      <c r="L24" s="118"/>
+      <c r="M24" s="88"/>
+      <c r="N24" s="89"/>
+      <c r="O24" s="82"/>
+      <c r="P24" s="83"/>
+      <c r="Q24" s="83"/>
+      <c r="R24" s="84"/>
     </row>
     <row r="25" spans="1:18" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="86"/>
-      <c r="B25" s="35"/>
-      <c r="C25" s="35"/>
-      <c r="D25" s="40"/>
-      <c r="E25" s="38"/>
-      <c r="F25" s="38"/>
-      <c r="G25" s="38"/>
-      <c r="H25" s="38"/>
-      <c r="I25" s="38"/>
-      <c r="J25" s="38"/>
-      <c r="K25" s="38"/>
-      <c r="L25" s="39"/>
-      <c r="M25" s="63"/>
-      <c r="N25" s="64"/>
-      <c r="O25" s="112"/>
-      <c r="P25" s="113"/>
-      <c r="Q25" s="113"/>
-      <c r="R25" s="114"/>
+      <c r="A25" s="44"/>
+      <c r="B25" s="45"/>
+      <c r="C25" s="45"/>
+      <c r="D25" s="119"/>
+      <c r="E25" s="117"/>
+      <c r="F25" s="117"/>
+      <c r="G25" s="117"/>
+      <c r="H25" s="117"/>
+      <c r="I25" s="117"/>
+      <c r="J25" s="117"/>
+      <c r="K25" s="117"/>
+      <c r="L25" s="118"/>
+      <c r="M25" s="88"/>
+      <c r="N25" s="89"/>
+      <c r="O25" s="82"/>
+      <c r="P25" s="83"/>
+      <c r="Q25" s="83"/>
+      <c r="R25" s="84"/>
     </row>
     <row r="26" spans="1:18" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="86"/>
-      <c r="B26" s="35"/>
-      <c r="C26" s="35"/>
+      <c r="A26" s="44"/>
+      <c r="B26" s="45"/>
+      <c r="C26" s="45"/>
       <c r="D26" s="17"/>
       <c r="E26" s="16"/>
       <c r="F26" s="15"/>
@@ -2199,17 +2195,17 @@
       <c r="J26" s="14"/>
       <c r="K26" s="14"/>
       <c r="L26" s="13"/>
-      <c r="M26" s="63"/>
-      <c r="N26" s="64"/>
-      <c r="O26" s="112"/>
-      <c r="P26" s="113"/>
-      <c r="Q26" s="113"/>
-      <c r="R26" s="114"/>
+      <c r="M26" s="88"/>
+      <c r="N26" s="89"/>
+      <c r="O26" s="82"/>
+      <c r="P26" s="83"/>
+      <c r="Q26" s="83"/>
+      <c r="R26" s="84"/>
     </row>
     <row r="27" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="86"/>
-      <c r="B27" s="35"/>
-      <c r="C27" s="35"/>
+      <c r="A27" s="44"/>
+      <c r="B27" s="45"/>
+      <c r="C27" s="45"/>
       <c r="D27" s="12"/>
       <c r="F27" s="10"/>
       <c r="G27" s="11"/>
@@ -2217,17 +2213,17 @@
       <c r="I27" s="9"/>
       <c r="J27" s="9"/>
       <c r="L27" s="8"/>
-      <c r="M27" s="63"/>
-      <c r="N27" s="64"/>
-      <c r="O27" s="112"/>
-      <c r="P27" s="113"/>
-      <c r="Q27" s="113"/>
-      <c r="R27" s="114"/>
+      <c r="M27" s="88"/>
+      <c r="N27" s="89"/>
+      <c r="O27" s="82"/>
+      <c r="P27" s="83"/>
+      <c r="Q27" s="83"/>
+      <c r="R27" s="84"/>
     </row>
     <row r="28" spans="1:18" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="87"/>
-      <c r="B28" s="88"/>
-      <c r="C28" s="88"/>
+      <c r="A28" s="49"/>
+      <c r="B28" s="50"/>
+      <c r="C28" s="50"/>
       <c r="D28" s="7"/>
       <c r="E28" s="6"/>
       <c r="F28" s="6"/>
@@ -2237,346 +2233,346 @@
       <c r="J28" s="6"/>
       <c r="K28" s="6"/>
       <c r="L28" s="5"/>
-      <c r="M28" s="65"/>
-      <c r="N28" s="66"/>
-      <c r="O28" s="115"/>
-      <c r="P28" s="116"/>
-      <c r="Q28" s="116"/>
-      <c r="R28" s="117"/>
+      <c r="M28" s="90"/>
+      <c r="N28" s="91"/>
+      <c r="O28" s="85"/>
+      <c r="P28" s="86"/>
+      <c r="Q28" s="86"/>
+      <c r="R28" s="87"/>
     </row>
     <row r="29" spans="1:18" ht="12.75" thickTop="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="1:18" ht="12.75" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="31" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="89" t="s">
+      <c r="A31" s="57" t="s">
         <v>6</v>
       </c>
-      <c r="B31" s="33"/>
-      <c r="C31" s="33"/>
-      <c r="D31" s="98"/>
-      <c r="E31" s="98"/>
-      <c r="F31" s="98"/>
-      <c r="G31" s="98"/>
-      <c r="H31" s="98"/>
-      <c r="I31" s="98"/>
-      <c r="J31" s="33" t="s">
+      <c r="B31" s="46"/>
+      <c r="C31" s="46"/>
+      <c r="D31" s="40"/>
+      <c r="E31" s="40"/>
+      <c r="F31" s="40"/>
+      <c r="G31" s="40"/>
+      <c r="H31" s="40"/>
+      <c r="I31" s="40"/>
+      <c r="J31" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="K31" s="33"/>
-      <c r="L31" s="33"/>
-      <c r="M31" s="98"/>
-      <c r="N31" s="98"/>
-      <c r="O31" s="98"/>
-      <c r="P31" s="98"/>
-      <c r="Q31" s="98"/>
-      <c r="R31" s="128"/>
+      <c r="K31" s="46"/>
+      <c r="L31" s="46"/>
+      <c r="M31" s="40"/>
+      <c r="N31" s="40"/>
+      <c r="O31" s="40"/>
+      <c r="P31" s="40"/>
+      <c r="Q31" s="40"/>
+      <c r="R31" s="41"/>
     </row>
     <row r="32" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="86"/>
-      <c r="B32" s="35"/>
-      <c r="C32" s="35"/>
-      <c r="D32" s="99"/>
-      <c r="E32" s="99"/>
-      <c r="F32" s="99"/>
-      <c r="G32" s="99"/>
-      <c r="H32" s="99"/>
-      <c r="I32" s="99"/>
-      <c r="J32" s="35"/>
-      <c r="K32" s="35"/>
-      <c r="L32" s="35"/>
-      <c r="M32" s="99"/>
-      <c r="N32" s="99"/>
-      <c r="O32" s="99"/>
-      <c r="P32" s="99"/>
-      <c r="Q32" s="99"/>
-      <c r="R32" s="129"/>
+      <c r="A32" s="44"/>
+      <c r="B32" s="45"/>
+      <c r="C32" s="45"/>
+      <c r="D32" s="42"/>
+      <c r="E32" s="42"/>
+      <c r="F32" s="42"/>
+      <c r="G32" s="42"/>
+      <c r="H32" s="42"/>
+      <c r="I32" s="42"/>
+      <c r="J32" s="45"/>
+      <c r="K32" s="45"/>
+      <c r="L32" s="45"/>
+      <c r="M32" s="42"/>
+      <c r="N32" s="42"/>
+      <c r="O32" s="42"/>
+      <c r="P32" s="42"/>
+      <c r="Q32" s="42"/>
+      <c r="R32" s="43"/>
     </row>
     <row r="33" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="86" t="s">
+      <c r="A33" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="B33" s="35"/>
-      <c r="C33" s="35"/>
-      <c r="D33" s="99"/>
-      <c r="E33" s="99"/>
-      <c r="F33" s="99"/>
-      <c r="G33" s="99"/>
-      <c r="H33" s="99"/>
-      <c r="I33" s="99"/>
-      <c r="J33" s="35" t="s">
+      <c r="B33" s="45"/>
+      <c r="C33" s="45"/>
+      <c r="D33" s="42"/>
+      <c r="E33" s="42"/>
+      <c r="F33" s="42"/>
+      <c r="G33" s="42"/>
+      <c r="H33" s="42"/>
+      <c r="I33" s="42"/>
+      <c r="J33" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="K33" s="35"/>
-      <c r="L33" s="35"/>
-      <c r="M33" s="99"/>
-      <c r="N33" s="99"/>
-      <c r="O33" s="99"/>
-      <c r="P33" s="99"/>
-      <c r="Q33" s="99"/>
-      <c r="R33" s="129"/>
+      <c r="K33" s="45"/>
+      <c r="L33" s="45"/>
+      <c r="M33" s="42"/>
+      <c r="N33" s="42"/>
+      <c r="O33" s="42"/>
+      <c r="P33" s="42"/>
+      <c r="Q33" s="42"/>
+      <c r="R33" s="43"/>
     </row>
     <row r="34" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="86"/>
-      <c r="B34" s="35"/>
-      <c r="C34" s="35"/>
-      <c r="D34" s="99"/>
-      <c r="E34" s="99"/>
-      <c r="F34" s="99"/>
-      <c r="G34" s="99"/>
-      <c r="H34" s="99"/>
-      <c r="I34" s="99"/>
-      <c r="J34" s="35"/>
-      <c r="K34" s="35"/>
-      <c r="L34" s="35"/>
-      <c r="M34" s="99"/>
-      <c r="N34" s="99"/>
-      <c r="O34" s="99"/>
-      <c r="P34" s="99"/>
-      <c r="Q34" s="99"/>
-      <c r="R34" s="129"/>
+      <c r="A34" s="44"/>
+      <c r="B34" s="45"/>
+      <c r="C34" s="45"/>
+      <c r="D34" s="42"/>
+      <c r="E34" s="42"/>
+      <c r="F34" s="42"/>
+      <c r="G34" s="42"/>
+      <c r="H34" s="42"/>
+      <c r="I34" s="42"/>
+      <c r="J34" s="45"/>
+      <c r="K34" s="45"/>
+      <c r="L34" s="45"/>
+      <c r="M34" s="42"/>
+      <c r="N34" s="42"/>
+      <c r="O34" s="42"/>
+      <c r="P34" s="42"/>
+      <c r="Q34" s="42"/>
+      <c r="R34" s="43"/>
     </row>
     <row r="35" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="86" t="s">
+      <c r="A35" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="B35" s="35"/>
-      <c r="C35" s="35"/>
-      <c r="D35" s="132"/>
-      <c r="E35" s="133"/>
-      <c r="F35" s="133"/>
-      <c r="G35" s="133"/>
-      <c r="H35" s="133"/>
-      <c r="I35" s="133"/>
-      <c r="J35" s="133"/>
-      <c r="K35" s="133"/>
-      <c r="L35" s="133"/>
-      <c r="M35" s="133"/>
-      <c r="N35" s="133"/>
-      <c r="O35" s="133"/>
-      <c r="P35" s="133"/>
-      <c r="Q35" s="133"/>
-      <c r="R35" s="134"/>
+      <c r="B35" s="45"/>
+      <c r="C35" s="45"/>
+      <c r="D35" s="51"/>
+      <c r="E35" s="52"/>
+      <c r="F35" s="52"/>
+      <c r="G35" s="52"/>
+      <c r="H35" s="52"/>
+      <c r="I35" s="52"/>
+      <c r="J35" s="52"/>
+      <c r="K35" s="52"/>
+      <c r="L35" s="52"/>
+      <c r="M35" s="52"/>
+      <c r="N35" s="52"/>
+      <c r="O35" s="52"/>
+      <c r="P35" s="52"/>
+      <c r="Q35" s="52"/>
+      <c r="R35" s="53"/>
     </row>
     <row r="36" spans="1:18" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A36" s="87"/>
-      <c r="B36" s="88"/>
-      <c r="C36" s="88"/>
-      <c r="D36" s="135"/>
-      <c r="E36" s="136"/>
-      <c r="F36" s="136"/>
-      <c r="G36" s="136"/>
-      <c r="H36" s="136"/>
-      <c r="I36" s="136"/>
-      <c r="J36" s="136"/>
-      <c r="K36" s="136"/>
-      <c r="L36" s="136"/>
-      <c r="M36" s="136"/>
-      <c r="N36" s="136"/>
-      <c r="O36" s="136"/>
-      <c r="P36" s="136"/>
-      <c r="Q36" s="136"/>
-      <c r="R36" s="137"/>
+      <c r="A36" s="49"/>
+      <c r="B36" s="50"/>
+      <c r="C36" s="50"/>
+      <c r="D36" s="54"/>
+      <c r="E36" s="55"/>
+      <c r="F36" s="55"/>
+      <c r="G36" s="55"/>
+      <c r="H36" s="55"/>
+      <c r="I36" s="55"/>
+      <c r="J36" s="55"/>
+      <c r="K36" s="55"/>
+      <c r="L36" s="55"/>
+      <c r="M36" s="55"/>
+      <c r="N36" s="55"/>
+      <c r="O36" s="55"/>
+      <c r="P36" s="55"/>
+      <c r="Q36" s="55"/>
+      <c r="R36" s="56"/>
     </row>
     <row r="37" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="100"/>
-      <c r="B37" s="101"/>
-      <c r="C37" s="101"/>
-      <c r="D37" s="101"/>
-      <c r="E37" s="101"/>
-      <c r="F37" s="101"/>
-      <c r="G37" s="101"/>
-      <c r="H37" s="101"/>
-      <c r="I37" s="101"/>
-      <c r="J37" s="101"/>
-      <c r="K37" s="101"/>
-      <c r="L37" s="101"/>
-      <c r="M37" s="101"/>
-      <c r="N37" s="101"/>
-      <c r="O37" s="101"/>
-      <c r="P37" s="101"/>
-      <c r="Q37" s="101"/>
-      <c r="R37" s="101"/>
+      <c r="A37" s="68"/>
+      <c r="B37" s="69"/>
+      <c r="C37" s="69"/>
+      <c r="D37" s="69"/>
+      <c r="E37" s="69"/>
+      <c r="F37" s="69"/>
+      <c r="G37" s="69"/>
+      <c r="H37" s="69"/>
+      <c r="I37" s="69"/>
+      <c r="J37" s="69"/>
+      <c r="K37" s="69"/>
+      <c r="L37" s="69"/>
+      <c r="M37" s="69"/>
+      <c r="N37" s="69"/>
+      <c r="O37" s="69"/>
+      <c r="P37" s="69"/>
+      <c r="Q37" s="69"/>
+      <c r="R37" s="69"/>
     </row>
     <row r="38" spans="1:18" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="102"/>
-      <c r="B38" s="102"/>
-      <c r="C38" s="102"/>
-      <c r="D38" s="102"/>
-      <c r="E38" s="102"/>
-      <c r="F38" s="102"/>
-      <c r="G38" s="102"/>
-      <c r="H38" s="102"/>
-      <c r="I38" s="102"/>
-      <c r="J38" s="102"/>
-      <c r="K38" s="102"/>
-      <c r="L38" s="102"/>
-      <c r="M38" s="102"/>
-      <c r="N38" s="102"/>
-      <c r="O38" s="102"/>
-      <c r="P38" s="102"/>
-      <c r="Q38" s="102"/>
-      <c r="R38" s="102"/>
+      <c r="A38" s="70"/>
+      <c r="B38" s="70"/>
+      <c r="C38" s="70"/>
+      <c r="D38" s="70"/>
+      <c r="E38" s="70"/>
+      <c r="F38" s="70"/>
+      <c r="G38" s="70"/>
+      <c r="H38" s="70"/>
+      <c r="I38" s="70"/>
+      <c r="J38" s="70"/>
+      <c r="K38" s="70"/>
+      <c r="L38" s="70"/>
+      <c r="M38" s="70"/>
+      <c r="N38" s="70"/>
+      <c r="O38" s="70"/>
+      <c r="P38" s="70"/>
+      <c r="Q38" s="70"/>
+      <c r="R38" s="70"/>
     </row>
     <row r="39" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="89" t="s">
+      <c r="A39" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="B39" s="33"/>
-      <c r="C39" s="33"/>
-      <c r="D39" s="33" t="s">
+      <c r="B39" s="46"/>
+      <c r="C39" s="46"/>
+      <c r="D39" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="E39" s="33"/>
-      <c r="F39" s="33"/>
-      <c r="G39" s="34"/>
-      <c r="H39" s="33" t="s">
+      <c r="E39" s="46"/>
+      <c r="F39" s="46"/>
+      <c r="G39" s="71"/>
+      <c r="H39" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="I39" s="33"/>
-      <c r="J39" s="33"/>
-      <c r="K39" s="33" t="s">
+      <c r="I39" s="46"/>
+      <c r="J39" s="46"/>
+      <c r="K39" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="L39" s="33"/>
-      <c r="M39" s="33"/>
-      <c r="N39" s="34"/>
-      <c r="O39" s="33" t="s">
+      <c r="L39" s="46"/>
+      <c r="M39" s="46"/>
+      <c r="N39" s="71"/>
+      <c r="O39" s="46" t="s">
         <v>21</v>
       </c>
-      <c r="P39" s="33"/>
-      <c r="Q39" s="33"/>
-      <c r="R39" s="130"/>
+      <c r="P39" s="46"/>
+      <c r="Q39" s="46"/>
+      <c r="R39" s="47"/>
     </row>
     <row r="40" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="86"/>
-      <c r="B40" s="35"/>
-      <c r="C40" s="35"/>
-      <c r="D40" s="35"/>
-      <c r="E40" s="35"/>
-      <c r="F40" s="35"/>
-      <c r="G40" s="36"/>
-      <c r="H40" s="35"/>
-      <c r="I40" s="35"/>
-      <c r="J40" s="35"/>
-      <c r="K40" s="35"/>
-      <c r="L40" s="35"/>
-      <c r="M40" s="35"/>
-      <c r="N40" s="36"/>
-      <c r="O40" s="35"/>
-      <c r="P40" s="35"/>
-      <c r="Q40" s="35"/>
-      <c r="R40" s="131"/>
+      <c r="A40" s="44"/>
+      <c r="B40" s="45"/>
+      <c r="C40" s="45"/>
+      <c r="D40" s="45"/>
+      <c r="E40" s="45"/>
+      <c r="F40" s="45"/>
+      <c r="G40" s="72"/>
+      <c r="H40" s="45"/>
+      <c r="I40" s="45"/>
+      <c r="J40" s="45"/>
+      <c r="K40" s="45"/>
+      <c r="L40" s="45"/>
+      <c r="M40" s="45"/>
+      <c r="N40" s="72"/>
+      <c r="O40" s="45"/>
+      <c r="P40" s="45"/>
+      <c r="Q40" s="45"/>
+      <c r="R40" s="48"/>
     </row>
     <row r="41" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="27" t="s">
+      <c r="A41" s="110" t="s">
         <v>13</v>
       </c>
-      <c r="B41" s="28"/>
-      <c r="C41" s="29"/>
-      <c r="D41" s="55"/>
-      <c r="E41" s="56"/>
-      <c r="F41" s="56"/>
-      <c r="G41" s="57"/>
-      <c r="H41" s="71" t="s">
+      <c r="B41" s="111"/>
+      <c r="C41" s="112"/>
+      <c r="D41" s="94"/>
+      <c r="E41" s="95"/>
+      <c r="F41" s="95"/>
+      <c r="G41" s="96"/>
+      <c r="H41" s="100" t="s">
         <v>14</v>
       </c>
-      <c r="I41" s="72"/>
-      <c r="J41" s="73"/>
-      <c r="K41" s="55"/>
-      <c r="L41" s="56"/>
-      <c r="M41" s="56"/>
-      <c r="N41" s="57"/>
-      <c r="O41" s="77"/>
-      <c r="P41" s="77"/>
-      <c r="Q41" s="77"/>
-      <c r="R41" s="78"/>
+      <c r="I41" s="101"/>
+      <c r="J41" s="102"/>
+      <c r="K41" s="94"/>
+      <c r="L41" s="95"/>
+      <c r="M41" s="95"/>
+      <c r="N41" s="96"/>
+      <c r="O41" s="106"/>
+      <c r="P41" s="106"/>
+      <c r="Q41" s="106"/>
+      <c r="R41" s="107"/>
     </row>
     <row r="42" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="30"/>
-      <c r="B42" s="31"/>
-      <c r="C42" s="32"/>
-      <c r="D42" s="58"/>
-      <c r="E42" s="59"/>
-      <c r="F42" s="59"/>
-      <c r="G42" s="60"/>
-      <c r="H42" s="74"/>
-      <c r="I42" s="75"/>
-      <c r="J42" s="76"/>
-      <c r="K42" s="58"/>
-      <c r="L42" s="59"/>
-      <c r="M42" s="59"/>
-      <c r="N42" s="60"/>
-      <c r="O42" s="77"/>
-      <c r="P42" s="77"/>
-      <c r="Q42" s="77"/>
-      <c r="R42" s="78"/>
+      <c r="A42" s="113"/>
+      <c r="B42" s="114"/>
+      <c r="C42" s="115"/>
+      <c r="D42" s="97"/>
+      <c r="E42" s="98"/>
+      <c r="F42" s="98"/>
+      <c r="G42" s="99"/>
+      <c r="H42" s="103"/>
+      <c r="I42" s="104"/>
+      <c r="J42" s="105"/>
+      <c r="K42" s="97"/>
+      <c r="L42" s="98"/>
+      <c r="M42" s="98"/>
+      <c r="N42" s="99"/>
+      <c r="O42" s="106"/>
+      <c r="P42" s="106"/>
+      <c r="Q42" s="106"/>
+      <c r="R42" s="107"/>
     </row>
     <row r="43" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="27" t="s">
+      <c r="A43" s="110" t="s">
         <v>15</v>
       </c>
-      <c r="B43" s="28"/>
-      <c r="C43" s="29"/>
-      <c r="D43" s="55"/>
-      <c r="E43" s="56"/>
-      <c r="F43" s="56"/>
-      <c r="G43" s="57"/>
-      <c r="H43" s="61" t="s">
+      <c r="B43" s="111"/>
+      <c r="C43" s="112"/>
+      <c r="D43" s="94"/>
+      <c r="E43" s="95"/>
+      <c r="F43" s="95"/>
+      <c r="G43" s="96"/>
+      <c r="H43" s="128" t="s">
         <v>16</v>
       </c>
-      <c r="I43" s="28"/>
-      <c r="J43" s="29"/>
-      <c r="K43" s="55"/>
-      <c r="L43" s="56"/>
-      <c r="M43" s="56"/>
-      <c r="N43" s="57"/>
-      <c r="O43" s="77"/>
-      <c r="P43" s="77"/>
-      <c r="Q43" s="77"/>
-      <c r="R43" s="78"/>
+      <c r="I43" s="111"/>
+      <c r="J43" s="112"/>
+      <c r="K43" s="94"/>
+      <c r="L43" s="95"/>
+      <c r="M43" s="95"/>
+      <c r="N43" s="96"/>
+      <c r="O43" s="106"/>
+      <c r="P43" s="106"/>
+      <c r="Q43" s="106"/>
+      <c r="R43" s="107"/>
     </row>
     <row r="44" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="30"/>
-      <c r="B44" s="31"/>
-      <c r="C44" s="32"/>
-      <c r="D44" s="58"/>
-      <c r="E44" s="59"/>
-      <c r="F44" s="59"/>
-      <c r="G44" s="60"/>
-      <c r="H44" s="62"/>
-      <c r="I44" s="31"/>
-      <c r="J44" s="32"/>
-      <c r="K44" s="58"/>
-      <c r="L44" s="59"/>
-      <c r="M44" s="59"/>
-      <c r="N44" s="60"/>
-      <c r="O44" s="77"/>
-      <c r="P44" s="77"/>
-      <c r="Q44" s="77"/>
-      <c r="R44" s="78"/>
+      <c r="A44" s="113"/>
+      <c r="B44" s="114"/>
+      <c r="C44" s="115"/>
+      <c r="D44" s="97"/>
+      <c r="E44" s="98"/>
+      <c r="F44" s="98"/>
+      <c r="G44" s="99"/>
+      <c r="H44" s="129"/>
+      <c r="I44" s="114"/>
+      <c r="J44" s="115"/>
+      <c r="K44" s="97"/>
+      <c r="L44" s="98"/>
+      <c r="M44" s="98"/>
+      <c r="N44" s="99"/>
+      <c r="O44" s="106"/>
+      <c r="P44" s="106"/>
+      <c r="Q44" s="106"/>
+      <c r="R44" s="107"/>
     </row>
     <row r="45" spans="1:18" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A45" s="53" t="s">
+      <c r="A45" s="126" t="s">
         <v>17</v>
       </c>
-      <c r="B45" s="54"/>
-      <c r="C45" s="54"/>
-      <c r="D45" s="69"/>
-      <c r="E45" s="69"/>
-      <c r="F45" s="69"/>
-      <c r="G45" s="70"/>
-      <c r="H45" s="54" t="s">
+      <c r="B45" s="127"/>
+      <c r="C45" s="127"/>
+      <c r="D45" s="92"/>
+      <c r="E45" s="92"/>
+      <c r="F45" s="92"/>
+      <c r="G45" s="93"/>
+      <c r="H45" s="127" t="s">
         <v>17</v>
       </c>
-      <c r="I45" s="54"/>
-      <c r="J45" s="54"/>
-      <c r="K45" s="69"/>
-      <c r="L45" s="69"/>
-      <c r="M45" s="69"/>
-      <c r="N45" s="70"/>
-      <c r="O45" s="79"/>
-      <c r="P45" s="79"/>
-      <c r="Q45" s="79"/>
-      <c r="R45" s="80"/>
+      <c r="I45" s="127"/>
+      <c r="J45" s="127"/>
+      <c r="K45" s="92"/>
+      <c r="L45" s="92"/>
+      <c r="M45" s="92"/>
+      <c r="N45" s="93"/>
+      <c r="O45" s="108"/>
+      <c r="P45" s="108"/>
+      <c r="Q45" s="108"/>
+      <c r="R45" s="109"/>
     </row>
     <row r="46" spans="1:18" ht="20.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.4"/>
     <row r="47" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -2588,128 +2584,128 @@
       </c>
     </row>
     <row r="49" spans="1:18" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="41"/>
-      <c r="B49" s="42"/>
-      <c r="C49" s="43"/>
-      <c r="D49" s="47"/>
-      <c r="E49" s="48"/>
-      <c r="F49" s="48"/>
-      <c r="G49" s="48"/>
-      <c r="H49" s="49"/>
-      <c r="I49" s="47"/>
-      <c r="J49" s="48"/>
-      <c r="K49" s="48"/>
-      <c r="L49" s="48"/>
-      <c r="M49" s="49"/>
-      <c r="N49" s="47"/>
-      <c r="O49" s="48"/>
-      <c r="P49" s="48"/>
-      <c r="Q49" s="48"/>
-      <c r="R49" s="67"/>
+      <c r="A49" s="120"/>
+      <c r="B49" s="121"/>
+      <c r="C49" s="122"/>
+      <c r="D49" s="142"/>
+      <c r="E49" s="143"/>
+      <c r="F49" s="143"/>
+      <c r="G49" s="143"/>
+      <c r="H49" s="144"/>
+      <c r="I49" s="142"/>
+      <c r="J49" s="143"/>
+      <c r="K49" s="143"/>
+      <c r="L49" s="143"/>
+      <c r="M49" s="144"/>
+      <c r="N49" s="142"/>
+      <c r="O49" s="143"/>
+      <c r="P49" s="143"/>
+      <c r="Q49" s="143"/>
+      <c r="R49" s="145"/>
     </row>
     <row r="50" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="44"/>
-      <c r="B50" s="45"/>
-      <c r="C50" s="46"/>
-      <c r="D50" s="50"/>
-      <c r="E50" s="51"/>
-      <c r="F50" s="51"/>
-      <c r="G50" s="51"/>
-      <c r="H50" s="52"/>
-      <c r="I50" s="50"/>
-      <c r="J50" s="51"/>
-      <c r="K50" s="51"/>
-      <c r="L50" s="51"/>
-      <c r="M50" s="52"/>
-      <c r="N50" s="50"/>
-      <c r="O50" s="51"/>
-      <c r="P50" s="51"/>
-      <c r="Q50" s="51"/>
-      <c r="R50" s="68"/>
+      <c r="A50" s="123"/>
+      <c r="B50" s="124"/>
+      <c r="C50" s="125"/>
+      <c r="D50" s="146"/>
+      <c r="E50" s="147"/>
+      <c r="F50" s="147"/>
+      <c r="G50" s="147"/>
+      <c r="H50" s="148"/>
+      <c r="I50" s="146"/>
+      <c r="J50" s="147"/>
+      <c r="K50" s="147"/>
+      <c r="L50" s="147"/>
+      <c r="M50" s="148"/>
+      <c r="N50" s="146"/>
+      <c r="O50" s="147"/>
+      <c r="P50" s="147"/>
+      <c r="Q50" s="147"/>
+      <c r="R50" s="149"/>
     </row>
     <row r="51" spans="1:18" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A51" s="120" t="s">
+      <c r="A51" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="B51" s="121"/>
-      <c r="C51" s="122"/>
-      <c r="D51" s="83"/>
-      <c r="E51" s="83"/>
-      <c r="F51" s="83"/>
-      <c r="G51" s="83"/>
-      <c r="H51" s="83"/>
-      <c r="I51" s="83"/>
-      <c r="J51" s="83"/>
-      <c r="K51" s="83"/>
-      <c r="L51" s="83"/>
-      <c r="M51" s="83"/>
-      <c r="N51" s="83"/>
-      <c r="O51" s="83"/>
-      <c r="P51" s="83"/>
-      <c r="Q51" s="83"/>
-      <c r="R51" s="119"/>
+      <c r="B51" s="31"/>
+      <c r="C51" s="32"/>
+      <c r="D51" s="28"/>
+      <c r="E51" s="28"/>
+      <c r="F51" s="28"/>
+      <c r="G51" s="28"/>
+      <c r="H51" s="28"/>
+      <c r="I51" s="28"/>
+      <c r="J51" s="28"/>
+      <c r="K51" s="28"/>
+      <c r="L51" s="28"/>
+      <c r="M51" s="28"/>
+      <c r="N51" s="28"/>
+      <c r="O51" s="28"/>
+      <c r="P51" s="28"/>
+      <c r="Q51" s="28"/>
+      <c r="R51" s="29"/>
     </row>
     <row r="52" spans="1:18" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A52" s="123"/>
-      <c r="B52" s="124"/>
-      <c r="C52" s="125"/>
-      <c r="D52" s="83"/>
-      <c r="E52" s="83"/>
-      <c r="F52" s="83"/>
-      <c r="G52" s="83"/>
-      <c r="H52" s="83"/>
-      <c r="I52" s="83"/>
-      <c r="J52" s="83"/>
-      <c r="K52" s="83"/>
-      <c r="L52" s="83"/>
-      <c r="M52" s="83"/>
-      <c r="N52" s="83"/>
-      <c r="O52" s="83"/>
-      <c r="P52" s="83"/>
-      <c r="Q52" s="83"/>
-      <c r="R52" s="119"/>
+      <c r="A52" s="33"/>
+      <c r="B52" s="34"/>
+      <c r="C52" s="35"/>
+      <c r="D52" s="28"/>
+      <c r="E52" s="28"/>
+      <c r="F52" s="28"/>
+      <c r="G52" s="28"/>
+      <c r="H52" s="28"/>
+      <c r="I52" s="28"/>
+      <c r="J52" s="28"/>
+      <c r="K52" s="28"/>
+      <c r="L52" s="28"/>
+      <c r="M52" s="28"/>
+      <c r="N52" s="28"/>
+      <c r="O52" s="28"/>
+      <c r="P52" s="28"/>
+      <c r="Q52" s="28"/>
+      <c r="R52" s="29"/>
     </row>
     <row r="53" spans="1:18" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A53" s="103" t="s">
+      <c r="A53" s="73" t="s">
         <v>20</v>
       </c>
-      <c r="B53" s="104"/>
-      <c r="C53" s="105"/>
-      <c r="D53" s="81"/>
-      <c r="E53" s="81"/>
-      <c r="F53" s="81"/>
-      <c r="G53" s="81"/>
-      <c r="H53" s="81"/>
-      <c r="I53" s="81"/>
-      <c r="J53" s="81"/>
-      <c r="K53" s="81"/>
-      <c r="L53" s="81"/>
-      <c r="M53" s="81"/>
-      <c r="N53" s="81"/>
-      <c r="O53" s="81"/>
-      <c r="P53" s="81"/>
-      <c r="Q53" s="81"/>
-      <c r="R53" s="126"/>
+      <c r="B53" s="74"/>
+      <c r="C53" s="75"/>
+      <c r="D53" s="36"/>
+      <c r="E53" s="36"/>
+      <c r="F53" s="36"/>
+      <c r="G53" s="36"/>
+      <c r="H53" s="36"/>
+      <c r="I53" s="36"/>
+      <c r="J53" s="36"/>
+      <c r="K53" s="36"/>
+      <c r="L53" s="36"/>
+      <c r="M53" s="36"/>
+      <c r="N53" s="36"/>
+      <c r="O53" s="36"/>
+      <c r="P53" s="36"/>
+      <c r="Q53" s="36"/>
+      <c r="R53" s="37"/>
     </row>
     <row r="54" spans="1:18" s="2" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="106"/>
-      <c r="B54" s="107"/>
-      <c r="C54" s="108"/>
-      <c r="D54" s="82"/>
-      <c r="E54" s="82"/>
-      <c r="F54" s="82"/>
-      <c r="G54" s="82"/>
-      <c r="H54" s="82"/>
-      <c r="I54" s="82"/>
-      <c r="J54" s="82"/>
-      <c r="K54" s="82"/>
-      <c r="L54" s="82"/>
-      <c r="M54" s="82"/>
-      <c r="N54" s="82"/>
-      <c r="O54" s="82"/>
-      <c r="P54" s="82"/>
-      <c r="Q54" s="82"/>
-      <c r="R54" s="127"/>
+      <c r="A54" s="76"/>
+      <c r="B54" s="77"/>
+      <c r="C54" s="78"/>
+      <c r="D54" s="38"/>
+      <c r="E54" s="38"/>
+      <c r="F54" s="38"/>
+      <c r="G54" s="38"/>
+      <c r="H54" s="38"/>
+      <c r="I54" s="38"/>
+      <c r="J54" s="38"/>
+      <c r="K54" s="38"/>
+      <c r="L54" s="38"/>
+      <c r="M54" s="38"/>
+      <c r="N54" s="38"/>
+      <c r="O54" s="38"/>
+      <c r="P54" s="38"/>
+      <c r="Q54" s="38"/>
+      <c r="R54" s="39"/>
     </row>
     <row r="55" spans="1:18" s="2" customFormat="1" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.15"/>
     <row r="56" spans="1:18" s="2" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -2724,6 +2720,42 @@
   </sheetData>
   <sheetProtection formatCells="0"/>
   <mergeCells count="52">
+    <mergeCell ref="A43:C44"/>
+    <mergeCell ref="D39:G40"/>
+    <mergeCell ref="D23:L25"/>
+    <mergeCell ref="A49:C50"/>
+    <mergeCell ref="D49:H50"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="H45:J45"/>
+    <mergeCell ref="A41:C42"/>
+    <mergeCell ref="D43:G44"/>
+    <mergeCell ref="H43:J44"/>
+    <mergeCell ref="M22:N28"/>
+    <mergeCell ref="N49:R50"/>
+    <mergeCell ref="I49:M50"/>
+    <mergeCell ref="D45:G45"/>
+    <mergeCell ref="D41:G42"/>
+    <mergeCell ref="H41:J42"/>
+    <mergeCell ref="K41:N42"/>
+    <mergeCell ref="O41:R45"/>
+    <mergeCell ref="K43:N44"/>
+    <mergeCell ref="K45:N45"/>
+    <mergeCell ref="I53:M54"/>
+    <mergeCell ref="I51:M52"/>
+    <mergeCell ref="O1:R1"/>
+    <mergeCell ref="A11:R11"/>
+    <mergeCell ref="A22:C28"/>
+    <mergeCell ref="A20:C21"/>
+    <mergeCell ref="D20:R21"/>
+    <mergeCell ref="A15:R15"/>
+    <mergeCell ref="A18:R18"/>
+    <mergeCell ref="D31:I32"/>
+    <mergeCell ref="A37:R38"/>
+    <mergeCell ref="H39:J40"/>
+    <mergeCell ref="A39:C40"/>
+    <mergeCell ref="K39:N40"/>
+    <mergeCell ref="A53:C54"/>
+    <mergeCell ref="O22:R28"/>
     <mergeCell ref="O3:R4"/>
     <mergeCell ref="D51:H52"/>
     <mergeCell ref="N51:R52"/>
@@ -2740,42 +2772,6 @@
     <mergeCell ref="A31:C32"/>
     <mergeCell ref="J31:L32"/>
     <mergeCell ref="D53:H54"/>
-    <mergeCell ref="I53:M54"/>
-    <mergeCell ref="I51:M52"/>
-    <mergeCell ref="O1:R1"/>
-    <mergeCell ref="A11:R11"/>
-    <mergeCell ref="A22:C28"/>
-    <mergeCell ref="A20:C21"/>
-    <mergeCell ref="D20:R21"/>
-    <mergeCell ref="A15:R15"/>
-    <mergeCell ref="A18:R18"/>
-    <mergeCell ref="D31:I32"/>
-    <mergeCell ref="A37:R38"/>
-    <mergeCell ref="H39:J40"/>
-    <mergeCell ref="A39:C40"/>
-    <mergeCell ref="K39:N40"/>
-    <mergeCell ref="A53:C54"/>
-    <mergeCell ref="O22:R28"/>
-    <mergeCell ref="M22:N28"/>
-    <mergeCell ref="N49:R50"/>
-    <mergeCell ref="I49:M50"/>
-    <mergeCell ref="D45:G45"/>
-    <mergeCell ref="D41:G42"/>
-    <mergeCell ref="H41:J42"/>
-    <mergeCell ref="K41:N42"/>
-    <mergeCell ref="O41:R45"/>
-    <mergeCell ref="K43:N44"/>
-    <mergeCell ref="K45:N45"/>
-    <mergeCell ref="A43:C44"/>
-    <mergeCell ref="D39:G40"/>
-    <mergeCell ref="D23:L25"/>
-    <mergeCell ref="A49:C50"/>
-    <mergeCell ref="D49:H50"/>
-    <mergeCell ref="A45:C45"/>
-    <mergeCell ref="H45:J45"/>
-    <mergeCell ref="A41:C42"/>
-    <mergeCell ref="D43:G44"/>
-    <mergeCell ref="H43:J44"/>
   </mergeCells>
   <phoneticPr fontId="20"/>
   <printOptions horizontalCentered="1"/>
@@ -2803,62 +2799,62 @@
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="148" t="s">
+      <c r="E2" s="132" t="s">
         <v>22</v>
       </c>
-      <c r="F2" s="148"/>
-      <c r="G2" s="148" t="s">
+      <c r="F2" s="132"/>
+      <c r="G2" s="132" t="s">
         <v>23</v>
       </c>
-      <c r="H2" s="148"/>
-      <c r="I2" s="148" t="s">
+      <c r="H2" s="132"/>
+      <c r="I2" s="132" t="s">
         <v>24</v>
       </c>
-      <c r="J2" s="148"/>
-      <c r="K2" s="148" t="s">
+      <c r="J2" s="132"/>
+      <c r="K2" s="132" t="s">
         <v>25</v>
       </c>
-      <c r="L2" s="148"/>
-      <c r="M2" s="148" t="s">
+      <c r="L2" s="132"/>
+      <c r="M2" s="132" t="s">
         <v>26</v>
       </c>
-      <c r="N2" s="148"/>
+      <c r="N2" s="132"/>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B3" s="145" t="s">
+      <c r="B3" s="130" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="145"/>
+      <c r="C3" s="130"/>
       <c r="D3" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="145"/>
-      <c r="F3" s="145"/>
-      <c r="G3" s="149"/>
-      <c r="H3" s="149"/>
-      <c r="I3" s="145"/>
-      <c r="J3" s="145"/>
-      <c r="K3" s="145"/>
-      <c r="L3" s="145"/>
-      <c r="M3" s="145"/>
-      <c r="N3" s="145"/>
+      <c r="E3" s="130"/>
+      <c r="F3" s="130"/>
+      <c r="G3" s="131"/>
+      <c r="H3" s="131"/>
+      <c r="I3" s="130"/>
+      <c r="J3" s="130"/>
+      <c r="K3" s="130"/>
+      <c r="L3" s="130"/>
+      <c r="M3" s="130"/>
+      <c r="N3" s="130"/>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B4" s="145"/>
-      <c r="C4" s="145"/>
+      <c r="B4" s="130"/>
+      <c r="C4" s="130"/>
       <c r="D4" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="145"/>
-      <c r="F4" s="145"/>
-      <c r="G4" s="145"/>
-      <c r="H4" s="145"/>
-      <c r="I4" s="145"/>
-      <c r="J4" s="145"/>
-      <c r="K4" s="145"/>
-      <c r="L4" s="145"/>
-      <c r="M4" s="145"/>
-      <c r="N4" s="145"/>
+      <c r="E4" s="130"/>
+      <c r="F4" s="130"/>
+      <c r="G4" s="130"/>
+      <c r="H4" s="130"/>
+      <c r="I4" s="130"/>
+      <c r="J4" s="130"/>
+      <c r="K4" s="130"/>
+      <c r="L4" s="130"/>
+      <c r="M4" s="130"/>
+      <c r="N4" s="130"/>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B5" s="1"/>
@@ -2879,62 +2875,62 @@
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
-      <c r="E6" s="143" t="s">
+      <c r="E6" s="137" t="s">
         <v>22</v>
       </c>
-      <c r="F6" s="144"/>
-      <c r="G6" s="143" t="s">
+      <c r="F6" s="138"/>
+      <c r="G6" s="137" t="s">
         <v>23</v>
       </c>
-      <c r="H6" s="144"/>
-      <c r="I6" s="143" t="s">
+      <c r="H6" s="138"/>
+      <c r="I6" s="137" t="s">
         <v>24</v>
       </c>
-      <c r="J6" s="144"/>
-      <c r="K6" s="143" t="s">
+      <c r="J6" s="138"/>
+      <c r="K6" s="137" t="s">
         <v>25</v>
       </c>
-      <c r="L6" s="144"/>
-      <c r="M6" s="143" t="s">
+      <c r="L6" s="138"/>
+      <c r="M6" s="137" t="s">
         <v>26</v>
       </c>
-      <c r="N6" s="144"/>
+      <c r="N6" s="138"/>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B7" s="145" t="s">
+      <c r="B7" s="130" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="145"/>
+      <c r="C7" s="130"/>
       <c r="D7" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="E7" s="141"/>
-      <c r="F7" s="142"/>
-      <c r="G7" s="146"/>
-      <c r="H7" s="147"/>
-      <c r="I7" s="141"/>
-      <c r="J7" s="142"/>
-      <c r="K7" s="141"/>
-      <c r="L7" s="142"/>
-      <c r="M7" s="141"/>
-      <c r="N7" s="142"/>
+      <c r="E7" s="133"/>
+      <c r="F7" s="134"/>
+      <c r="G7" s="135"/>
+      <c r="H7" s="136"/>
+      <c r="I7" s="133"/>
+      <c r="J7" s="134"/>
+      <c r="K7" s="133"/>
+      <c r="L7" s="134"/>
+      <c r="M7" s="133"/>
+      <c r="N7" s="134"/>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B8" s="145"/>
-      <c r="C8" s="145"/>
+      <c r="B8" s="130"/>
+      <c r="C8" s="130"/>
       <c r="D8" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="E8" s="141"/>
-      <c r="F8" s="142"/>
-      <c r="G8" s="141"/>
-      <c r="H8" s="142"/>
-      <c r="I8" s="141"/>
-      <c r="J8" s="142"/>
-      <c r="K8" s="141"/>
-      <c r="L8" s="142"/>
-      <c r="M8" s="141"/>
-      <c r="N8" s="142"/>
+      <c r="E8" s="133"/>
+      <c r="F8" s="134"/>
+      <c r="G8" s="133"/>
+      <c r="H8" s="134"/>
+      <c r="I8" s="133"/>
+      <c r="J8" s="134"/>
+      <c r="K8" s="133"/>
+      <c r="L8" s="134"/>
+      <c r="M8" s="133"/>
+      <c r="N8" s="134"/>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B9" s="1"/>
@@ -2955,62 +2951,62 @@
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
-      <c r="E10" s="143" t="s">
+      <c r="E10" s="137" t="s">
         <v>22</v>
       </c>
-      <c r="F10" s="144"/>
-      <c r="G10" s="143" t="s">
+      <c r="F10" s="138"/>
+      <c r="G10" s="137" t="s">
         <v>23</v>
       </c>
-      <c r="H10" s="144"/>
-      <c r="I10" s="143" t="s">
+      <c r="H10" s="138"/>
+      <c r="I10" s="137" t="s">
         <v>24</v>
       </c>
-      <c r="J10" s="144"/>
-      <c r="K10" s="143" t="s">
+      <c r="J10" s="138"/>
+      <c r="K10" s="137" t="s">
         <v>25</v>
       </c>
-      <c r="L10" s="144"/>
-      <c r="M10" s="143" t="s">
+      <c r="L10" s="138"/>
+      <c r="M10" s="137" t="s">
         <v>26</v>
       </c>
-      <c r="N10" s="144"/>
+      <c r="N10" s="138"/>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B11" s="145" t="s">
+      <c r="B11" s="130" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="145"/>
+      <c r="C11" s="130"/>
       <c r="D11" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="E11" s="141"/>
-      <c r="F11" s="142"/>
-      <c r="G11" s="146"/>
-      <c r="H11" s="147"/>
-      <c r="I11" s="141"/>
-      <c r="J11" s="142"/>
-      <c r="K11" s="141"/>
-      <c r="L11" s="142"/>
-      <c r="M11" s="141"/>
-      <c r="N11" s="142"/>
+      <c r="E11" s="133"/>
+      <c r="F11" s="134"/>
+      <c r="G11" s="135"/>
+      <c r="H11" s="136"/>
+      <c r="I11" s="133"/>
+      <c r="J11" s="134"/>
+      <c r="K11" s="133"/>
+      <c r="L11" s="134"/>
+      <c r="M11" s="133"/>
+      <c r="N11" s="134"/>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B12" s="145"/>
-      <c r="C12" s="145"/>
+      <c r="B12" s="130"/>
+      <c r="C12" s="130"/>
       <c r="D12" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="E12" s="141"/>
-      <c r="F12" s="142"/>
-      <c r="G12" s="141"/>
-      <c r="H12" s="142"/>
-      <c r="I12" s="141"/>
-      <c r="J12" s="142"/>
-      <c r="K12" s="141"/>
-      <c r="L12" s="142"/>
-      <c r="M12" s="141"/>
-      <c r="N12" s="142"/>
+      <c r="E12" s="133"/>
+      <c r="F12" s="134"/>
+      <c r="G12" s="133"/>
+      <c r="H12" s="134"/>
+      <c r="I12" s="133"/>
+      <c r="J12" s="134"/>
+      <c r="K12" s="133"/>
+      <c r="L12" s="134"/>
+      <c r="M12" s="133"/>
+      <c r="N12" s="134"/>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B13" s="1"/>
@@ -3046,231 +3042,155 @@
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
-      <c r="E15" s="143" t="s">
+      <c r="E15" s="137" t="s">
         <v>22</v>
       </c>
-      <c r="F15" s="144"/>
-      <c r="G15" s="143" t="s">
+      <c r="F15" s="138"/>
+      <c r="G15" s="137" t="s">
         <v>23</v>
       </c>
-      <c r="H15" s="144"/>
-      <c r="I15" s="143" t="s">
+      <c r="H15" s="138"/>
+      <c r="I15" s="137" t="s">
         <v>24</v>
       </c>
-      <c r="J15" s="144"/>
-      <c r="K15" s="143" t="s">
+      <c r="J15" s="138"/>
+      <c r="K15" s="137" t="s">
         <v>25</v>
       </c>
-      <c r="L15" s="144"/>
-      <c r="M15" s="143" t="s">
+      <c r="L15" s="138"/>
+      <c r="M15" s="137" t="s">
         <v>26</v>
       </c>
-      <c r="N15" s="144"/>
+      <c r="N15" s="138"/>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B16" s="145" t="s">
+      <c r="B16" s="130" t="s">
         <v>32</v>
       </c>
-      <c r="C16" s="145"/>
+      <c r="C16" s="130"/>
       <c r="D16" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="E16" s="141"/>
-      <c r="F16" s="142"/>
-      <c r="G16" s="146"/>
-      <c r="H16" s="147"/>
-      <c r="I16" s="141"/>
-      <c r="J16" s="142"/>
-      <c r="K16" s="141"/>
-      <c r="L16" s="142"/>
-      <c r="M16" s="141"/>
-      <c r="N16" s="142"/>
+      <c r="E16" s="133"/>
+      <c r="F16" s="134"/>
+      <c r="G16" s="135"/>
+      <c r="H16" s="136"/>
+      <c r="I16" s="133"/>
+      <c r="J16" s="134"/>
+      <c r="K16" s="133"/>
+      <c r="L16" s="134"/>
+      <c r="M16" s="133"/>
+      <c r="N16" s="134"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B17" s="145"/>
-      <c r="C17" s="145"/>
+      <c r="B17" s="130"/>
+      <c r="C17" s="130"/>
       <c r="D17" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="E17" s="141"/>
-      <c r="F17" s="142"/>
-      <c r="G17" s="141"/>
-      <c r="H17" s="142"/>
-      <c r="I17" s="141"/>
-      <c r="J17" s="142"/>
-      <c r="K17" s="141"/>
-      <c r="L17" s="142"/>
-      <c r="M17" s="141"/>
-      <c r="N17" s="142"/>
+      <c r="E17" s="133"/>
+      <c r="F17" s="134"/>
+      <c r="G17" s="133"/>
+      <c r="H17" s="134"/>
+      <c r="I17" s="133"/>
+      <c r="J17" s="134"/>
+      <c r="K17" s="133"/>
+      <c r="L17" s="134"/>
+      <c r="M17" s="133"/>
+      <c r="N17" s="134"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B20" s="138"/>
-      <c r="C20" s="138"/>
-      <c r="D20" s="138"/>
-      <c r="E20" s="138" t="s">
+      <c r="B20" s="139"/>
+      <c r="C20" s="139"/>
+      <c r="D20" s="139"/>
+      <c r="E20" s="139" t="s">
         <v>33</v>
       </c>
-      <c r="F20" s="138"/>
+      <c r="F20" s="139"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B21" s="138" t="s">
+      <c r="B21" s="139" t="s">
         <v>34</v>
       </c>
-      <c r="C21" s="138"/>
-      <c r="D21" s="138"/>
-      <c r="E21" s="139"/>
-      <c r="F21" s="139"/>
+      <c r="C21" s="139"/>
+      <c r="D21" s="139"/>
+      <c r="E21" s="140"/>
+      <c r="F21" s="140"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B22" s="138" t="s">
+      <c r="B22" s="139" t="s">
         <v>35</v>
       </c>
-      <c r="C22" s="138"/>
-      <c r="D22" s="138"/>
-      <c r="E22" s="139"/>
-      <c r="F22" s="139"/>
+      <c r="C22" s="139"/>
+      <c r="D22" s="139"/>
+      <c r="E22" s="140"/>
+      <c r="F22" s="140"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B23" s="138" t="s">
+      <c r="B23" s="139" t="s">
         <v>36</v>
       </c>
-      <c r="C23" s="138"/>
-      <c r="D23" s="138"/>
-      <c r="E23" s="139"/>
-      <c r="F23" s="139"/>
+      <c r="C23" s="139"/>
+      <c r="D23" s="139"/>
+      <c r="E23" s="140"/>
+      <c r="F23" s="140"/>
     </row>
     <row r="24" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B24" s="138" t="s">
+      <c r="B24" s="139" t="s">
         <v>37</v>
       </c>
-      <c r="C24" s="138"/>
-      <c r="D24" s="138"/>
-      <c r="E24" s="139"/>
-      <c r="F24" s="139"/>
+      <c r="C24" s="139"/>
+      <c r="D24" s="139"/>
+      <c r="E24" s="140"/>
+      <c r="F24" s="140"/>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B25" s="138" t="s">
+      <c r="B25" s="139" t="s">
         <v>38</v>
       </c>
-      <c r="C25" s="138"/>
-      <c r="D25" s="138"/>
-      <c r="E25" s="139"/>
-      <c r="F25" s="139"/>
+      <c r="C25" s="139"/>
+      <c r="D25" s="139"/>
+      <c r="E25" s="140"/>
+      <c r="F25" s="140"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B26" s="138" t="s">
+      <c r="B26" s="139" t="s">
         <v>39</v>
       </c>
-      <c r="C26" s="138"/>
-      <c r="D26" s="138"/>
-      <c r="E26" s="150"/>
-      <c r="F26" s="150"/>
+      <c r="C26" s="139"/>
+      <c r="D26" s="139"/>
+      <c r="E26" s="140"/>
+      <c r="F26" s="140"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B27" s="138" t="s">
+      <c r="B27" s="139" t="s">
         <v>40</v>
       </c>
-      <c r="C27" s="138"/>
-      <c r="D27" s="138"/>
-      <c r="E27" s="140"/>
-      <c r="F27" s="140"/>
+      <c r="C27" s="139"/>
+      <c r="D27" s="139"/>
+      <c r="E27" s="141"/>
+      <c r="F27" s="141"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B28" s="138" t="s">
+      <c r="B28" s="139" t="s">
         <v>41</v>
       </c>
-      <c r="C28" s="138"/>
-      <c r="D28" s="138"/>
-      <c r="E28" s="139"/>
-      <c r="F28" s="139"/>
+      <c r="C28" s="139"/>
+      <c r="D28" s="139"/>
+      <c r="E28" s="140"/>
+      <c r="F28" s="140"/>
     </row>
     <row r="29" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B29" s="138" t="s">
+      <c r="B29" s="139" t="s">
         <v>42</v>
       </c>
-      <c r="C29" s="138"/>
-      <c r="D29" s="138"/>
-      <c r="E29" s="139"/>
-      <c r="F29" s="139"/>
+      <c r="C29" s="139"/>
+      <c r="D29" s="139"/>
+      <c r="E29" s="140"/>
+      <c r="F29" s="140"/>
     </row>
   </sheetData>
   <mergeCells count="84">
-    <mergeCell ref="B3:C4"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="B7:C8"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="M7:N7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="M8:N8"/>
-    <mergeCell ref="B11:C12"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="M10:N10"/>
-    <mergeCell ref="M11:N11"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="B16:C17"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="K16:L16"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="K15:L15"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="E25:F25"/>
     <mergeCell ref="B29:D29"/>
     <mergeCell ref="E29:F29"/>
     <mergeCell ref="B26:D26"/>
@@ -3279,6 +3199,82 @@
     <mergeCell ref="E27:F27"/>
     <mergeCell ref="B28:D28"/>
     <mergeCell ref="E28:F28"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="B16:C17"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="K16:L16"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="B11:C12"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="M8:N8"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="B7:C8"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="B3:C4"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="K3:L3"/>
   </mergeCells>
   <phoneticPr fontId="20"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/storage/app/estimateTemplate/comprehensiveOfRecommend.xlsx
+++ b/storage/app/estimateTemplate/comprehensiveOfRecommend.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yokoyama\Desktop\火災見積\テンプレート\new\mark\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yokoyama\Desktop\修正用ふぉうるだ\a\estimateTemplate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F6553DA-306D-426E-9411-83B5EF86F6D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FF07D3A-2562-479A-B078-DD902561999F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30" yWindow="750" windowWidth="28770" windowHeight="15450" xr2:uid="{0E9C5CA5-184F-4C06-AA15-1AF55B55AFB9}"/>
+    <workbookView xWindow="30" yWindow="90" windowWidth="28770" windowHeight="15435" xr2:uid="{0E9C5CA5-184F-4C06-AA15-1AF55B55AFB9}"/>
   </bookViews>
   <sheets>
     <sheet name="おすすめ(総合)" sheetId="2" r:id="rId1"/>
@@ -453,7 +453,7 @@
     <numFmt numFmtId="178" formatCode="&quot;延&quot;&quot;面&quot;&quot;積&quot;\ 0.00_ &quot;㎡&quot;"/>
     <numFmt numFmtId="179" formatCode="#,##0_ &quot;千&quot;&quot;円&quot;"/>
     <numFmt numFmtId="180" formatCode="#,##0_ &quot;円&quot;"/>
-    <numFmt numFmtId="182" formatCode="#,##0_ &quot;円&quot;&quot;お&quot;&quot;得&quot;"/>
+    <numFmt numFmtId="181" formatCode="#,##0_ &quot;円&quot;&quot;お&quot;&quot;得&quot;"/>
   </numFmts>
   <fonts count="21" x14ac:knownFonts="1">
     <font>
@@ -1165,97 +1165,169 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="26" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="8" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="28" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="16" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="16" fillId="0" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="16" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="16" fillId="0" borderId="29" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="9" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="9" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="180" fontId="18" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="182" fontId="9" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="9" fillId="0" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="9" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="182" fontId="9" fillId="0" borderId="29" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="24" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="58" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -1265,6 +1337,18 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -1289,6 +1373,12 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1298,12 +1388,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="2" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1349,191 +1433,107 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="18" fillId="0" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="9" fillId="0" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="9" fillId="0" borderId="29" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="24" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="33" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="34" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="35" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="9" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="26" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="8" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="28" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="16" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="16" fillId="0" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="16" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="16" fillId="0" borderId="29" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="35" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="33" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="34" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="3" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="4" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="31" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="5" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="10" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1911,10 +1911,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="O1" s="58"/>
-      <c r="P1" s="58"/>
-      <c r="Q1" s="58"/>
-      <c r="R1" s="58"/>
+      <c r="O1" s="82"/>
+      <c r="P1" s="82"/>
+      <c r="Q1" s="82"/>
+      <c r="R1" s="82"/>
     </row>
     <row r="2" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="O2" s="25"/>
@@ -1924,16 +1924,16 @@
     </row>
     <row r="3" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A3" s="3"/>
-      <c r="O3" s="27"/>
-      <c r="P3" s="27"/>
-      <c r="Q3" s="27"/>
-      <c r="R3" s="27"/>
+      <c r="O3" s="116"/>
+      <c r="P3" s="116"/>
+      <c r="Q3" s="116"/>
+      <c r="R3" s="116"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="O4" s="27"/>
-      <c r="P4" s="27"/>
-      <c r="Q4" s="27"/>
-      <c r="R4" s="27"/>
+      <c r="O4" s="116"/>
+      <c r="P4" s="116"/>
+      <c r="Q4" s="116"/>
+      <c r="R4" s="116"/>
     </row>
     <row r="5" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="N5" s="24"/>
@@ -1996,196 +1996,196 @@
       <c r="R10" s="20"/>
     </row>
     <row r="11" spans="1:18" ht="21" x14ac:dyDescent="0.4">
-      <c r="A11" s="59" t="s">
+      <c r="A11" s="83" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="59"/>
-      <c r="C11" s="59"/>
-      <c r="D11" s="59"/>
-      <c r="E11" s="59"/>
-      <c r="F11" s="59"/>
-      <c r="G11" s="59"/>
-      <c r="H11" s="59"/>
-      <c r="I11" s="59"/>
-      <c r="J11" s="59"/>
-      <c r="K11" s="59"/>
-      <c r="L11" s="59"/>
-      <c r="M11" s="59"/>
-      <c r="N11" s="59"/>
-      <c r="O11" s="59"/>
-      <c r="P11" s="59"/>
-      <c r="Q11" s="59"/>
-      <c r="R11" s="59"/>
+      <c r="B11" s="83"/>
+      <c r="C11" s="83"/>
+      <c r="D11" s="83"/>
+      <c r="E11" s="83"/>
+      <c r="F11" s="83"/>
+      <c r="G11" s="83"/>
+      <c r="H11" s="83"/>
+      <c r="I11" s="83"/>
+      <c r="J11" s="83"/>
+      <c r="K11" s="83"/>
+      <c r="L11" s="83"/>
+      <c r="M11" s="83"/>
+      <c r="N11" s="83"/>
+      <c r="O11" s="83"/>
+      <c r="P11" s="83"/>
+      <c r="Q11" s="83"/>
+      <c r="R11" s="83"/>
     </row>
     <row r="14" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="15" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
-      <c r="A15" s="66" t="s">
+      <c r="A15" s="94" t="s">
         <v>1</v>
       </c>
-      <c r="B15" s="66"/>
-      <c r="C15" s="66"/>
-      <c r="D15" s="66"/>
-      <c r="E15" s="66"/>
-      <c r="F15" s="66"/>
-      <c r="G15" s="66"/>
-      <c r="H15" s="66"/>
-      <c r="I15" s="66"/>
-      <c r="J15" s="66"/>
-      <c r="K15" s="66"/>
-      <c r="L15" s="66"/>
-      <c r="M15" s="66"/>
-      <c r="N15" s="66"/>
-      <c r="O15" s="66"/>
-      <c r="P15" s="66"/>
-      <c r="Q15" s="66"/>
-      <c r="R15" s="66"/>
+      <c r="B15" s="94"/>
+      <c r="C15" s="94"/>
+      <c r="D15" s="94"/>
+      <c r="E15" s="94"/>
+      <c r="F15" s="94"/>
+      <c r="G15" s="94"/>
+      <c r="H15" s="94"/>
+      <c r="I15" s="94"/>
+      <c r="J15" s="94"/>
+      <c r="K15" s="94"/>
+      <c r="L15" s="94"/>
+      <c r="M15" s="94"/>
+      <c r="N15" s="94"/>
+      <c r="O15" s="94"/>
+      <c r="P15" s="94"/>
+      <c r="Q15" s="94"/>
+      <c r="R15" s="94"/>
     </row>
     <row r="18" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
-      <c r="A18" s="67" t="s">
+      <c r="A18" s="95" t="s">
         <v>2</v>
       </c>
-      <c r="B18" s="67"/>
-      <c r="C18" s="67"/>
-      <c r="D18" s="67"/>
-      <c r="E18" s="67"/>
-      <c r="F18" s="67"/>
-      <c r="G18" s="67"/>
-      <c r="H18" s="67"/>
-      <c r="I18" s="67"/>
-      <c r="J18" s="67"/>
-      <c r="K18" s="67"/>
-      <c r="L18" s="67"/>
-      <c r="M18" s="67"/>
-      <c r="N18" s="67"/>
-      <c r="O18" s="67"/>
-      <c r="P18" s="67"/>
-      <c r="Q18" s="67"/>
-      <c r="R18" s="67"/>
+      <c r="B18" s="95"/>
+      <c r="C18" s="95"/>
+      <c r="D18" s="95"/>
+      <c r="E18" s="95"/>
+      <c r="F18" s="95"/>
+      <c r="G18" s="95"/>
+      <c r="H18" s="95"/>
+      <c r="I18" s="95"/>
+      <c r="J18" s="95"/>
+      <c r="K18" s="95"/>
+      <c r="L18" s="95"/>
+      <c r="M18" s="95"/>
+      <c r="N18" s="95"/>
+      <c r="O18" s="95"/>
+      <c r="P18" s="95"/>
+      <c r="Q18" s="95"/>
+      <c r="R18" s="95"/>
     </row>
     <row r="19" spans="1:18" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="20" spans="1:18" ht="12.75" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="57" t="s">
+      <c r="A20" s="87" t="s">
         <v>3</v>
       </c>
-      <c r="B20" s="46"/>
-      <c r="C20" s="46"/>
-      <c r="D20" s="60"/>
-      <c r="E20" s="61"/>
-      <c r="F20" s="61"/>
-      <c r="G20" s="61"/>
-      <c r="H20" s="61"/>
-      <c r="I20" s="61"/>
-      <c r="J20" s="61"/>
-      <c r="K20" s="61"/>
-      <c r="L20" s="61"/>
-      <c r="M20" s="61"/>
-      <c r="N20" s="61"/>
-      <c r="O20" s="61"/>
-      <c r="P20" s="61"/>
-      <c r="Q20" s="61"/>
-      <c r="R20" s="62"/>
+      <c r="B20" s="33"/>
+      <c r="C20" s="33"/>
+      <c r="D20" s="88"/>
+      <c r="E20" s="89"/>
+      <c r="F20" s="89"/>
+      <c r="G20" s="89"/>
+      <c r="H20" s="89"/>
+      <c r="I20" s="89"/>
+      <c r="J20" s="89"/>
+      <c r="K20" s="89"/>
+      <c r="L20" s="89"/>
+      <c r="M20" s="89"/>
+      <c r="N20" s="89"/>
+      <c r="O20" s="89"/>
+      <c r="P20" s="89"/>
+      <c r="Q20" s="89"/>
+      <c r="R20" s="90"/>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A21" s="44"/>
-      <c r="B21" s="45"/>
-      <c r="C21" s="45"/>
-      <c r="D21" s="63"/>
-      <c r="E21" s="64"/>
-      <c r="F21" s="64"/>
-      <c r="G21" s="64"/>
-      <c r="H21" s="64"/>
-      <c r="I21" s="64"/>
-      <c r="J21" s="64"/>
-      <c r="K21" s="64"/>
-      <c r="L21" s="64"/>
-      <c r="M21" s="64"/>
-      <c r="N21" s="64"/>
-      <c r="O21" s="64"/>
-      <c r="P21" s="64"/>
-      <c r="Q21" s="64"/>
-      <c r="R21" s="65"/>
+      <c r="A21" s="84"/>
+      <c r="B21" s="35"/>
+      <c r="C21" s="35"/>
+      <c r="D21" s="91"/>
+      <c r="E21" s="92"/>
+      <c r="F21" s="92"/>
+      <c r="G21" s="92"/>
+      <c r="H21" s="92"/>
+      <c r="I21" s="92"/>
+      <c r="J21" s="92"/>
+      <c r="K21" s="92"/>
+      <c r="L21" s="92"/>
+      <c r="M21" s="92"/>
+      <c r="N21" s="92"/>
+      <c r="O21" s="92"/>
+      <c r="P21" s="92"/>
+      <c r="Q21" s="92"/>
+      <c r="R21" s="93"/>
     </row>
     <row r="22" spans="1:18" ht="5.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="44" t="s">
+      <c r="A22" s="84" t="s">
         <v>4</v>
       </c>
-      <c r="B22" s="45"/>
-      <c r="C22" s="45"/>
+      <c r="B22" s="35"/>
+      <c r="C22" s="35"/>
       <c r="D22" s="19"/>
       <c r="L22" s="18"/>
-      <c r="M22" s="88" t="s">
+      <c r="M22" s="63" t="s">
         <v>5</v>
       </c>
-      <c r="N22" s="89"/>
-      <c r="O22" s="79"/>
-      <c r="P22" s="80"/>
-      <c r="Q22" s="80"/>
-      <c r="R22" s="81"/>
+      <c r="N22" s="64"/>
+      <c r="O22" s="107"/>
+      <c r="P22" s="108"/>
+      <c r="Q22" s="108"/>
+      <c r="R22" s="109"/>
     </row>
     <row r="23" spans="1:18" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="44"/>
-      <c r="B23" s="45"/>
-      <c r="C23" s="45"/>
-      <c r="D23" s="116"/>
-      <c r="E23" s="117"/>
-      <c r="F23" s="117"/>
-      <c r="G23" s="117"/>
-      <c r="H23" s="117"/>
-      <c r="I23" s="117"/>
-      <c r="J23" s="117"/>
-      <c r="K23" s="117"/>
-      <c r="L23" s="118"/>
-      <c r="M23" s="88"/>
-      <c r="N23" s="89"/>
-      <c r="O23" s="82"/>
-      <c r="P23" s="83"/>
-      <c r="Q23" s="83"/>
-      <c r="R23" s="84"/>
+      <c r="A23" s="84"/>
+      <c r="B23" s="35"/>
+      <c r="C23" s="35"/>
+      <c r="D23" s="37"/>
+      <c r="E23" s="38"/>
+      <c r="F23" s="38"/>
+      <c r="G23" s="38"/>
+      <c r="H23" s="38"/>
+      <c r="I23" s="38"/>
+      <c r="J23" s="38"/>
+      <c r="K23" s="38"/>
+      <c r="L23" s="39"/>
+      <c r="M23" s="63"/>
+      <c r="N23" s="64"/>
+      <c r="O23" s="110"/>
+      <c r="P23" s="111"/>
+      <c r="Q23" s="111"/>
+      <c r="R23" s="112"/>
     </row>
     <row r="24" spans="1:18" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="44"/>
-      <c r="B24" s="45"/>
-      <c r="C24" s="45"/>
-      <c r="D24" s="119"/>
-      <c r="E24" s="117"/>
-      <c r="F24" s="117"/>
-      <c r="G24" s="117"/>
-      <c r="H24" s="117"/>
-      <c r="I24" s="117"/>
-      <c r="J24" s="117"/>
-      <c r="K24" s="117"/>
-      <c r="L24" s="118"/>
-      <c r="M24" s="88"/>
-      <c r="N24" s="89"/>
-      <c r="O24" s="82"/>
-      <c r="P24" s="83"/>
-      <c r="Q24" s="83"/>
-      <c r="R24" s="84"/>
+      <c r="A24" s="84"/>
+      <c r="B24" s="35"/>
+      <c r="C24" s="35"/>
+      <c r="D24" s="40"/>
+      <c r="E24" s="38"/>
+      <c r="F24" s="38"/>
+      <c r="G24" s="38"/>
+      <c r="H24" s="38"/>
+      <c r="I24" s="38"/>
+      <c r="J24" s="38"/>
+      <c r="K24" s="38"/>
+      <c r="L24" s="39"/>
+      <c r="M24" s="63"/>
+      <c r="N24" s="64"/>
+      <c r="O24" s="110"/>
+      <c r="P24" s="111"/>
+      <c r="Q24" s="111"/>
+      <c r="R24" s="112"/>
     </row>
     <row r="25" spans="1:18" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="44"/>
-      <c r="B25" s="45"/>
-      <c r="C25" s="45"/>
-      <c r="D25" s="119"/>
-      <c r="E25" s="117"/>
-      <c r="F25" s="117"/>
-      <c r="G25" s="117"/>
-      <c r="H25" s="117"/>
-      <c r="I25" s="117"/>
-      <c r="J25" s="117"/>
-      <c r="K25" s="117"/>
-      <c r="L25" s="118"/>
-      <c r="M25" s="88"/>
-      <c r="N25" s="89"/>
-      <c r="O25" s="82"/>
-      <c r="P25" s="83"/>
-      <c r="Q25" s="83"/>
-      <c r="R25" s="84"/>
+      <c r="A25" s="84"/>
+      <c r="B25" s="35"/>
+      <c r="C25" s="35"/>
+      <c r="D25" s="40"/>
+      <c r="E25" s="38"/>
+      <c r="F25" s="38"/>
+      <c r="G25" s="38"/>
+      <c r="H25" s="38"/>
+      <c r="I25" s="38"/>
+      <c r="J25" s="38"/>
+      <c r="K25" s="38"/>
+      <c r="L25" s="39"/>
+      <c r="M25" s="63"/>
+      <c r="N25" s="64"/>
+      <c r="O25" s="110"/>
+      <c r="P25" s="111"/>
+      <c r="Q25" s="111"/>
+      <c r="R25" s="112"/>
     </row>
     <row r="26" spans="1:18" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="44"/>
-      <c r="B26" s="45"/>
-      <c r="C26" s="45"/>
+      <c r="A26" s="84"/>
+      <c r="B26" s="35"/>
+      <c r="C26" s="35"/>
       <c r="D26" s="17"/>
       <c r="E26" s="16"/>
       <c r="F26" s="15"/>
@@ -2195,17 +2195,17 @@
       <c r="J26" s="14"/>
       <c r="K26" s="14"/>
       <c r="L26" s="13"/>
-      <c r="M26" s="88"/>
-      <c r="N26" s="89"/>
-      <c r="O26" s="82"/>
-      <c r="P26" s="83"/>
-      <c r="Q26" s="83"/>
-      <c r="R26" s="84"/>
+      <c r="M26" s="63"/>
+      <c r="N26" s="64"/>
+      <c r="O26" s="110"/>
+      <c r="P26" s="111"/>
+      <c r="Q26" s="111"/>
+      <c r="R26" s="112"/>
     </row>
     <row r="27" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="44"/>
-      <c r="B27" s="45"/>
-      <c r="C27" s="45"/>
+      <c r="A27" s="84"/>
+      <c r="B27" s="35"/>
+      <c r="C27" s="35"/>
       <c r="D27" s="12"/>
       <c r="F27" s="10"/>
       <c r="G27" s="11"/>
@@ -2213,17 +2213,17 @@
       <c r="I27" s="9"/>
       <c r="J27" s="9"/>
       <c r="L27" s="8"/>
-      <c r="M27" s="88"/>
-      <c r="N27" s="89"/>
-      <c r="O27" s="82"/>
-      <c r="P27" s="83"/>
-      <c r="Q27" s="83"/>
-      <c r="R27" s="84"/>
+      <c r="M27" s="63"/>
+      <c r="N27" s="64"/>
+      <c r="O27" s="110"/>
+      <c r="P27" s="111"/>
+      <c r="Q27" s="111"/>
+      <c r="R27" s="112"/>
     </row>
     <row r="28" spans="1:18" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="49"/>
-      <c r="B28" s="50"/>
-      <c r="C28" s="50"/>
+      <c r="A28" s="85"/>
+      <c r="B28" s="86"/>
+      <c r="C28" s="86"/>
       <c r="D28" s="7"/>
       <c r="E28" s="6"/>
       <c r="F28" s="6"/>
@@ -2233,346 +2233,346 @@
       <c r="J28" s="6"/>
       <c r="K28" s="6"/>
       <c r="L28" s="5"/>
-      <c r="M28" s="90"/>
-      <c r="N28" s="91"/>
-      <c r="O28" s="85"/>
-      <c r="P28" s="86"/>
-      <c r="Q28" s="86"/>
-      <c r="R28" s="87"/>
+      <c r="M28" s="65"/>
+      <c r="N28" s="66"/>
+      <c r="O28" s="113"/>
+      <c r="P28" s="114"/>
+      <c r="Q28" s="114"/>
+      <c r="R28" s="115"/>
     </row>
     <row r="29" spans="1:18" ht="12.75" thickTop="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="1:18" ht="12.75" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="31" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="57" t="s">
+      <c r="A31" s="87" t="s">
         <v>6</v>
       </c>
-      <c r="B31" s="46"/>
-      <c r="C31" s="46"/>
-      <c r="D31" s="40"/>
-      <c r="E31" s="40"/>
-      <c r="F31" s="40"/>
-      <c r="G31" s="40"/>
-      <c r="H31" s="40"/>
-      <c r="I31" s="40"/>
-      <c r="J31" s="46" t="s">
+      <c r="B31" s="33"/>
+      <c r="C31" s="33"/>
+      <c r="D31" s="96"/>
+      <c r="E31" s="96"/>
+      <c r="F31" s="96"/>
+      <c r="G31" s="96"/>
+      <c r="H31" s="96"/>
+      <c r="I31" s="96"/>
+      <c r="J31" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="K31" s="46"/>
-      <c r="L31" s="46"/>
-      <c r="M31" s="40"/>
-      <c r="N31" s="40"/>
-      <c r="O31" s="40"/>
-      <c r="P31" s="40"/>
-      <c r="Q31" s="40"/>
-      <c r="R31" s="41"/>
+      <c r="K31" s="33"/>
+      <c r="L31" s="33"/>
+      <c r="M31" s="96"/>
+      <c r="N31" s="96"/>
+      <c r="O31" s="96"/>
+      <c r="P31" s="96"/>
+      <c r="Q31" s="96"/>
+      <c r="R31" s="126"/>
     </row>
     <row r="32" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="44"/>
-      <c r="B32" s="45"/>
-      <c r="C32" s="45"/>
-      <c r="D32" s="42"/>
-      <c r="E32" s="42"/>
-      <c r="F32" s="42"/>
-      <c r="G32" s="42"/>
-      <c r="H32" s="42"/>
-      <c r="I32" s="42"/>
-      <c r="J32" s="45"/>
-      <c r="K32" s="45"/>
-      <c r="L32" s="45"/>
-      <c r="M32" s="42"/>
-      <c r="N32" s="42"/>
-      <c r="O32" s="42"/>
-      <c r="P32" s="42"/>
-      <c r="Q32" s="42"/>
-      <c r="R32" s="43"/>
+      <c r="A32" s="84"/>
+      <c r="B32" s="35"/>
+      <c r="C32" s="35"/>
+      <c r="D32" s="97"/>
+      <c r="E32" s="97"/>
+      <c r="F32" s="97"/>
+      <c r="G32" s="97"/>
+      <c r="H32" s="97"/>
+      <c r="I32" s="97"/>
+      <c r="J32" s="35"/>
+      <c r="K32" s="35"/>
+      <c r="L32" s="35"/>
+      <c r="M32" s="97"/>
+      <c r="N32" s="97"/>
+      <c r="O32" s="97"/>
+      <c r="P32" s="97"/>
+      <c r="Q32" s="97"/>
+      <c r="R32" s="127"/>
     </row>
     <row r="33" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="44" t="s">
+      <c r="A33" s="84" t="s">
         <v>8</v>
       </c>
-      <c r="B33" s="45"/>
-      <c r="C33" s="45"/>
-      <c r="D33" s="42"/>
-      <c r="E33" s="42"/>
-      <c r="F33" s="42"/>
-      <c r="G33" s="42"/>
-      <c r="H33" s="42"/>
-      <c r="I33" s="42"/>
-      <c r="J33" s="45" t="s">
+      <c r="B33" s="35"/>
+      <c r="C33" s="35"/>
+      <c r="D33" s="97"/>
+      <c r="E33" s="97"/>
+      <c r="F33" s="97"/>
+      <c r="G33" s="97"/>
+      <c r="H33" s="97"/>
+      <c r="I33" s="97"/>
+      <c r="J33" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="K33" s="45"/>
-      <c r="L33" s="45"/>
-      <c r="M33" s="42"/>
-      <c r="N33" s="42"/>
-      <c r="O33" s="42"/>
-      <c r="P33" s="42"/>
-      <c r="Q33" s="42"/>
-      <c r="R33" s="43"/>
+      <c r="K33" s="35"/>
+      <c r="L33" s="35"/>
+      <c r="M33" s="97"/>
+      <c r="N33" s="97"/>
+      <c r="O33" s="97"/>
+      <c r="P33" s="97"/>
+      <c r="Q33" s="97"/>
+      <c r="R33" s="127"/>
     </row>
     <row r="34" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="44"/>
-      <c r="B34" s="45"/>
-      <c r="C34" s="45"/>
-      <c r="D34" s="42"/>
-      <c r="E34" s="42"/>
-      <c r="F34" s="42"/>
-      <c r="G34" s="42"/>
-      <c r="H34" s="42"/>
-      <c r="I34" s="42"/>
-      <c r="J34" s="45"/>
-      <c r="K34" s="45"/>
-      <c r="L34" s="45"/>
-      <c r="M34" s="42"/>
-      <c r="N34" s="42"/>
-      <c r="O34" s="42"/>
-      <c r="P34" s="42"/>
-      <c r="Q34" s="42"/>
-      <c r="R34" s="43"/>
+      <c r="A34" s="84"/>
+      <c r="B34" s="35"/>
+      <c r="C34" s="35"/>
+      <c r="D34" s="97"/>
+      <c r="E34" s="97"/>
+      <c r="F34" s="97"/>
+      <c r="G34" s="97"/>
+      <c r="H34" s="97"/>
+      <c r="I34" s="97"/>
+      <c r="J34" s="35"/>
+      <c r="K34" s="35"/>
+      <c r="L34" s="35"/>
+      <c r="M34" s="97"/>
+      <c r="N34" s="97"/>
+      <c r="O34" s="97"/>
+      <c r="P34" s="97"/>
+      <c r="Q34" s="97"/>
+      <c r="R34" s="127"/>
     </row>
     <row r="35" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="44" t="s">
+      <c r="A35" s="84" t="s">
         <v>10</v>
       </c>
-      <c r="B35" s="45"/>
-      <c r="C35" s="45"/>
-      <c r="D35" s="51"/>
-      <c r="E35" s="52"/>
-      <c r="F35" s="52"/>
-      <c r="G35" s="52"/>
-      <c r="H35" s="52"/>
-      <c r="I35" s="52"/>
-      <c r="J35" s="52"/>
-      <c r="K35" s="52"/>
-      <c r="L35" s="52"/>
-      <c r="M35" s="52"/>
-      <c r="N35" s="52"/>
-      <c r="O35" s="52"/>
-      <c r="P35" s="52"/>
-      <c r="Q35" s="52"/>
-      <c r="R35" s="53"/>
+      <c r="B35" s="35"/>
+      <c r="C35" s="35"/>
+      <c r="D35" s="130"/>
+      <c r="E35" s="131"/>
+      <c r="F35" s="131"/>
+      <c r="G35" s="131"/>
+      <c r="H35" s="131"/>
+      <c r="I35" s="131"/>
+      <c r="J35" s="131"/>
+      <c r="K35" s="131"/>
+      <c r="L35" s="131"/>
+      <c r="M35" s="131"/>
+      <c r="N35" s="131"/>
+      <c r="O35" s="131"/>
+      <c r="P35" s="131"/>
+      <c r="Q35" s="131"/>
+      <c r="R35" s="132"/>
     </row>
     <row r="36" spans="1:18" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A36" s="49"/>
-      <c r="B36" s="50"/>
-      <c r="C36" s="50"/>
-      <c r="D36" s="54"/>
-      <c r="E36" s="55"/>
-      <c r="F36" s="55"/>
-      <c r="G36" s="55"/>
-      <c r="H36" s="55"/>
-      <c r="I36" s="55"/>
-      <c r="J36" s="55"/>
-      <c r="K36" s="55"/>
-      <c r="L36" s="55"/>
-      <c r="M36" s="55"/>
-      <c r="N36" s="55"/>
-      <c r="O36" s="55"/>
-      <c r="P36" s="55"/>
-      <c r="Q36" s="55"/>
-      <c r="R36" s="56"/>
+      <c r="A36" s="85"/>
+      <c r="B36" s="86"/>
+      <c r="C36" s="86"/>
+      <c r="D36" s="133"/>
+      <c r="E36" s="134"/>
+      <c r="F36" s="134"/>
+      <c r="G36" s="134"/>
+      <c r="H36" s="134"/>
+      <c r="I36" s="134"/>
+      <c r="J36" s="134"/>
+      <c r="K36" s="134"/>
+      <c r="L36" s="134"/>
+      <c r="M36" s="134"/>
+      <c r="N36" s="134"/>
+      <c r="O36" s="134"/>
+      <c r="P36" s="134"/>
+      <c r="Q36" s="134"/>
+      <c r="R36" s="135"/>
     </row>
     <row r="37" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="68"/>
-      <c r="B37" s="69"/>
-      <c r="C37" s="69"/>
-      <c r="D37" s="69"/>
-      <c r="E37" s="69"/>
-      <c r="F37" s="69"/>
-      <c r="G37" s="69"/>
-      <c r="H37" s="69"/>
-      <c r="I37" s="69"/>
-      <c r="J37" s="69"/>
-      <c r="K37" s="69"/>
-      <c r="L37" s="69"/>
-      <c r="M37" s="69"/>
-      <c r="N37" s="69"/>
-      <c r="O37" s="69"/>
-      <c r="P37" s="69"/>
-      <c r="Q37" s="69"/>
-      <c r="R37" s="69"/>
+      <c r="A37" s="98"/>
+      <c r="B37" s="99"/>
+      <c r="C37" s="99"/>
+      <c r="D37" s="99"/>
+      <c r="E37" s="99"/>
+      <c r="F37" s="99"/>
+      <c r="G37" s="99"/>
+      <c r="H37" s="99"/>
+      <c r="I37" s="99"/>
+      <c r="J37" s="99"/>
+      <c r="K37" s="99"/>
+      <c r="L37" s="99"/>
+      <c r="M37" s="99"/>
+      <c r="N37" s="99"/>
+      <c r="O37" s="99"/>
+      <c r="P37" s="99"/>
+      <c r="Q37" s="99"/>
+      <c r="R37" s="99"/>
     </row>
     <row r="38" spans="1:18" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="70"/>
-      <c r="B38" s="70"/>
-      <c r="C38" s="70"/>
-      <c r="D38" s="70"/>
-      <c r="E38" s="70"/>
-      <c r="F38" s="70"/>
-      <c r="G38" s="70"/>
-      <c r="H38" s="70"/>
-      <c r="I38" s="70"/>
-      <c r="J38" s="70"/>
-      <c r="K38" s="70"/>
-      <c r="L38" s="70"/>
-      <c r="M38" s="70"/>
-      <c r="N38" s="70"/>
-      <c r="O38" s="70"/>
-      <c r="P38" s="70"/>
-      <c r="Q38" s="70"/>
-      <c r="R38" s="70"/>
+      <c r="A38" s="100"/>
+      <c r="B38" s="100"/>
+      <c r="C38" s="100"/>
+      <c r="D38" s="100"/>
+      <c r="E38" s="100"/>
+      <c r="F38" s="100"/>
+      <c r="G38" s="100"/>
+      <c r="H38" s="100"/>
+      <c r="I38" s="100"/>
+      <c r="J38" s="100"/>
+      <c r="K38" s="100"/>
+      <c r="L38" s="100"/>
+      <c r="M38" s="100"/>
+      <c r="N38" s="100"/>
+      <c r="O38" s="100"/>
+      <c r="P38" s="100"/>
+      <c r="Q38" s="100"/>
+      <c r="R38" s="100"/>
     </row>
     <row r="39" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="57" t="s">
+      <c r="A39" s="87" t="s">
         <v>11</v>
       </c>
-      <c r="B39" s="46"/>
-      <c r="C39" s="46"/>
-      <c r="D39" s="46" t="s">
+      <c r="B39" s="33"/>
+      <c r="C39" s="33"/>
+      <c r="D39" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="E39" s="46"/>
-      <c r="F39" s="46"/>
-      <c r="G39" s="71"/>
-      <c r="H39" s="46" t="s">
+      <c r="E39" s="33"/>
+      <c r="F39" s="33"/>
+      <c r="G39" s="34"/>
+      <c r="H39" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="I39" s="46"/>
-      <c r="J39" s="46"/>
-      <c r="K39" s="46" t="s">
+      <c r="I39" s="33"/>
+      <c r="J39" s="33"/>
+      <c r="K39" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="L39" s="46"/>
-      <c r="M39" s="46"/>
-      <c r="N39" s="71"/>
-      <c r="O39" s="46" t="s">
+      <c r="L39" s="33"/>
+      <c r="M39" s="33"/>
+      <c r="N39" s="34"/>
+      <c r="O39" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="P39" s="46"/>
-      <c r="Q39" s="46"/>
-      <c r="R39" s="47"/>
+      <c r="P39" s="33"/>
+      <c r="Q39" s="33"/>
+      <c r="R39" s="128"/>
     </row>
     <row r="40" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="44"/>
-      <c r="B40" s="45"/>
-      <c r="C40" s="45"/>
-      <c r="D40" s="45"/>
-      <c r="E40" s="45"/>
-      <c r="F40" s="45"/>
-      <c r="G40" s="72"/>
-      <c r="H40" s="45"/>
-      <c r="I40" s="45"/>
-      <c r="J40" s="45"/>
-      <c r="K40" s="45"/>
-      <c r="L40" s="45"/>
-      <c r="M40" s="45"/>
-      <c r="N40" s="72"/>
-      <c r="O40" s="45"/>
-      <c r="P40" s="45"/>
-      <c r="Q40" s="45"/>
-      <c r="R40" s="48"/>
+      <c r="A40" s="84"/>
+      <c r="B40" s="35"/>
+      <c r="C40" s="35"/>
+      <c r="D40" s="35"/>
+      <c r="E40" s="35"/>
+      <c r="F40" s="35"/>
+      <c r="G40" s="36"/>
+      <c r="H40" s="35"/>
+      <c r="I40" s="35"/>
+      <c r="J40" s="35"/>
+      <c r="K40" s="35"/>
+      <c r="L40" s="35"/>
+      <c r="M40" s="35"/>
+      <c r="N40" s="36"/>
+      <c r="O40" s="35"/>
+      <c r="P40" s="35"/>
+      <c r="Q40" s="35"/>
+      <c r="R40" s="129"/>
     </row>
     <row r="41" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="110" t="s">
+      <c r="A41" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="B41" s="111"/>
-      <c r="C41" s="112"/>
-      <c r="D41" s="94"/>
-      <c r="E41" s="95"/>
-      <c r="F41" s="95"/>
-      <c r="G41" s="96"/>
-      <c r="H41" s="100" t="s">
+      <c r="B41" s="28"/>
+      <c r="C41" s="29"/>
+      <c r="D41" s="55"/>
+      <c r="E41" s="56"/>
+      <c r="F41" s="56"/>
+      <c r="G41" s="57"/>
+      <c r="H41" s="69" t="s">
         <v>14</v>
       </c>
-      <c r="I41" s="101"/>
-      <c r="J41" s="102"/>
-      <c r="K41" s="94"/>
-      <c r="L41" s="95"/>
-      <c r="M41" s="95"/>
-      <c r="N41" s="96"/>
-      <c r="O41" s="106"/>
-      <c r="P41" s="106"/>
-      <c r="Q41" s="106"/>
-      <c r="R41" s="107"/>
+      <c r="I41" s="70"/>
+      <c r="J41" s="71"/>
+      <c r="K41" s="55"/>
+      <c r="L41" s="56"/>
+      <c r="M41" s="56"/>
+      <c r="N41" s="57"/>
+      <c r="O41" s="75"/>
+      <c r="P41" s="75"/>
+      <c r="Q41" s="75"/>
+      <c r="R41" s="76"/>
     </row>
     <row r="42" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="113"/>
-      <c r="B42" s="114"/>
-      <c r="C42" s="115"/>
-      <c r="D42" s="97"/>
-      <c r="E42" s="98"/>
-      <c r="F42" s="98"/>
-      <c r="G42" s="99"/>
-      <c r="H42" s="103"/>
-      <c r="I42" s="104"/>
-      <c r="J42" s="105"/>
-      <c r="K42" s="97"/>
-      <c r="L42" s="98"/>
-      <c r="M42" s="98"/>
-      <c r="N42" s="99"/>
-      <c r="O42" s="106"/>
-      <c r="P42" s="106"/>
-      <c r="Q42" s="106"/>
-      <c r="R42" s="107"/>
+      <c r="A42" s="30"/>
+      <c r="B42" s="31"/>
+      <c r="C42" s="32"/>
+      <c r="D42" s="58"/>
+      <c r="E42" s="59"/>
+      <c r="F42" s="59"/>
+      <c r="G42" s="60"/>
+      <c r="H42" s="72"/>
+      <c r="I42" s="73"/>
+      <c r="J42" s="74"/>
+      <c r="K42" s="58"/>
+      <c r="L42" s="59"/>
+      <c r="M42" s="59"/>
+      <c r="N42" s="60"/>
+      <c r="O42" s="75"/>
+      <c r="P42" s="75"/>
+      <c r="Q42" s="75"/>
+      <c r="R42" s="76"/>
     </row>
     <row r="43" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="110" t="s">
+      <c r="A43" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="B43" s="111"/>
-      <c r="C43" s="112"/>
-      <c r="D43" s="94"/>
-      <c r="E43" s="95"/>
-      <c r="F43" s="95"/>
-      <c r="G43" s="96"/>
-      <c r="H43" s="128" t="s">
+      <c r="B43" s="28"/>
+      <c r="C43" s="29"/>
+      <c r="D43" s="55"/>
+      <c r="E43" s="56"/>
+      <c r="F43" s="56"/>
+      <c r="G43" s="57"/>
+      <c r="H43" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="I43" s="111"/>
-      <c r="J43" s="112"/>
-      <c r="K43" s="94"/>
-      <c r="L43" s="95"/>
-      <c r="M43" s="95"/>
-      <c r="N43" s="96"/>
-      <c r="O43" s="106"/>
-      <c r="P43" s="106"/>
-      <c r="Q43" s="106"/>
-      <c r="R43" s="107"/>
+      <c r="I43" s="28"/>
+      <c r="J43" s="29"/>
+      <c r="K43" s="55"/>
+      <c r="L43" s="56"/>
+      <c r="M43" s="56"/>
+      <c r="N43" s="57"/>
+      <c r="O43" s="75"/>
+      <c r="P43" s="75"/>
+      <c r="Q43" s="75"/>
+      <c r="R43" s="76"/>
     </row>
     <row r="44" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="113"/>
-      <c r="B44" s="114"/>
-      <c r="C44" s="115"/>
-      <c r="D44" s="97"/>
-      <c r="E44" s="98"/>
-      <c r="F44" s="98"/>
-      <c r="G44" s="99"/>
-      <c r="H44" s="129"/>
-      <c r="I44" s="114"/>
-      <c r="J44" s="115"/>
-      <c r="K44" s="97"/>
-      <c r="L44" s="98"/>
-      <c r="M44" s="98"/>
-      <c r="N44" s="99"/>
-      <c r="O44" s="106"/>
-      <c r="P44" s="106"/>
-      <c r="Q44" s="106"/>
-      <c r="R44" s="107"/>
+      <c r="A44" s="30"/>
+      <c r="B44" s="31"/>
+      <c r="C44" s="32"/>
+      <c r="D44" s="58"/>
+      <c r="E44" s="59"/>
+      <c r="F44" s="59"/>
+      <c r="G44" s="60"/>
+      <c r="H44" s="62"/>
+      <c r="I44" s="31"/>
+      <c r="J44" s="32"/>
+      <c r="K44" s="58"/>
+      <c r="L44" s="59"/>
+      <c r="M44" s="59"/>
+      <c r="N44" s="60"/>
+      <c r="O44" s="75"/>
+      <c r="P44" s="75"/>
+      <c r="Q44" s="75"/>
+      <c r="R44" s="76"/>
     </row>
     <row r="45" spans="1:18" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A45" s="126" t="s">
+      <c r="A45" s="53" t="s">
         <v>17</v>
       </c>
-      <c r="B45" s="127"/>
-      <c r="C45" s="127"/>
-      <c r="D45" s="92"/>
-      <c r="E45" s="92"/>
-      <c r="F45" s="92"/>
-      <c r="G45" s="93"/>
-      <c r="H45" s="127" t="s">
+      <c r="B45" s="54"/>
+      <c r="C45" s="54"/>
+      <c r="D45" s="148"/>
+      <c r="E45" s="148"/>
+      <c r="F45" s="148"/>
+      <c r="G45" s="149"/>
+      <c r="H45" s="54" t="s">
         <v>17</v>
       </c>
-      <c r="I45" s="127"/>
-      <c r="J45" s="127"/>
-      <c r="K45" s="92"/>
-      <c r="L45" s="92"/>
-      <c r="M45" s="92"/>
-      <c r="N45" s="93"/>
-      <c r="O45" s="108"/>
-      <c r="P45" s="108"/>
-      <c r="Q45" s="108"/>
-      <c r="R45" s="109"/>
+      <c r="I45" s="54"/>
+      <c r="J45" s="54"/>
+      <c r="K45" s="148"/>
+      <c r="L45" s="148"/>
+      <c r="M45" s="148"/>
+      <c r="N45" s="149"/>
+      <c r="O45" s="77"/>
+      <c r="P45" s="77"/>
+      <c r="Q45" s="77"/>
+      <c r="R45" s="78"/>
     </row>
     <row r="46" spans="1:18" ht="20.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.4"/>
     <row r="47" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -2584,128 +2584,128 @@
       </c>
     </row>
     <row r="49" spans="1:18" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="120"/>
-      <c r="B49" s="121"/>
-      <c r="C49" s="122"/>
-      <c r="D49" s="142"/>
-      <c r="E49" s="143"/>
-      <c r="F49" s="143"/>
-      <c r="G49" s="143"/>
-      <c r="H49" s="144"/>
-      <c r="I49" s="142"/>
-      <c r="J49" s="143"/>
-      <c r="K49" s="143"/>
-      <c r="L49" s="143"/>
-      <c r="M49" s="144"/>
-      <c r="N49" s="142"/>
-      <c r="O49" s="143"/>
-      <c r="P49" s="143"/>
-      <c r="Q49" s="143"/>
-      <c r="R49" s="145"/>
+      <c r="A49" s="41"/>
+      <c r="B49" s="42"/>
+      <c r="C49" s="43"/>
+      <c r="D49" s="47"/>
+      <c r="E49" s="48"/>
+      <c r="F49" s="48"/>
+      <c r="G49" s="48"/>
+      <c r="H49" s="49"/>
+      <c r="I49" s="47"/>
+      <c r="J49" s="48"/>
+      <c r="K49" s="48"/>
+      <c r="L49" s="48"/>
+      <c r="M49" s="49"/>
+      <c r="N49" s="47"/>
+      <c r="O49" s="48"/>
+      <c r="P49" s="48"/>
+      <c r="Q49" s="48"/>
+      <c r="R49" s="67"/>
     </row>
     <row r="50" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="123"/>
-      <c r="B50" s="124"/>
-      <c r="C50" s="125"/>
-      <c r="D50" s="146"/>
-      <c r="E50" s="147"/>
-      <c r="F50" s="147"/>
-      <c r="G50" s="147"/>
-      <c r="H50" s="148"/>
-      <c r="I50" s="146"/>
-      <c r="J50" s="147"/>
-      <c r="K50" s="147"/>
-      <c r="L50" s="147"/>
-      <c r="M50" s="148"/>
-      <c r="N50" s="146"/>
-      <c r="O50" s="147"/>
-      <c r="P50" s="147"/>
-      <c r="Q50" s="147"/>
-      <c r="R50" s="149"/>
+      <c r="A50" s="44"/>
+      <c r="B50" s="45"/>
+      <c r="C50" s="46"/>
+      <c r="D50" s="50"/>
+      <c r="E50" s="51"/>
+      <c r="F50" s="51"/>
+      <c r="G50" s="51"/>
+      <c r="H50" s="52"/>
+      <c r="I50" s="50"/>
+      <c r="J50" s="51"/>
+      <c r="K50" s="51"/>
+      <c r="L50" s="51"/>
+      <c r="M50" s="52"/>
+      <c r="N50" s="50"/>
+      <c r="O50" s="51"/>
+      <c r="P50" s="51"/>
+      <c r="Q50" s="51"/>
+      <c r="R50" s="68"/>
     </row>
     <row r="51" spans="1:18" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A51" s="30" t="s">
+      <c r="A51" s="118" t="s">
         <v>19</v>
       </c>
-      <c r="B51" s="31"/>
-      <c r="C51" s="32"/>
-      <c r="D51" s="28"/>
-      <c r="E51" s="28"/>
-      <c r="F51" s="28"/>
-      <c r="G51" s="28"/>
-      <c r="H51" s="28"/>
-      <c r="I51" s="28"/>
-      <c r="J51" s="28"/>
-      <c r="K51" s="28"/>
-      <c r="L51" s="28"/>
-      <c r="M51" s="28"/>
-      <c r="N51" s="28"/>
-      <c r="O51" s="28"/>
-      <c r="P51" s="28"/>
-      <c r="Q51" s="28"/>
-      <c r="R51" s="29"/>
+      <c r="B51" s="119"/>
+      <c r="C51" s="120"/>
+      <c r="D51" s="81"/>
+      <c r="E51" s="81"/>
+      <c r="F51" s="81"/>
+      <c r="G51" s="81"/>
+      <c r="H51" s="81"/>
+      <c r="I51" s="81"/>
+      <c r="J51" s="81"/>
+      <c r="K51" s="81"/>
+      <c r="L51" s="81"/>
+      <c r="M51" s="81"/>
+      <c r="N51" s="81"/>
+      <c r="O51" s="81"/>
+      <c r="P51" s="81"/>
+      <c r="Q51" s="81"/>
+      <c r="R51" s="117"/>
     </row>
     <row r="52" spans="1:18" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A52" s="33"/>
-      <c r="B52" s="34"/>
-      <c r="C52" s="35"/>
-      <c r="D52" s="28"/>
-      <c r="E52" s="28"/>
-      <c r="F52" s="28"/>
-      <c r="G52" s="28"/>
-      <c r="H52" s="28"/>
-      <c r="I52" s="28"/>
-      <c r="J52" s="28"/>
-      <c r="K52" s="28"/>
-      <c r="L52" s="28"/>
-      <c r="M52" s="28"/>
-      <c r="N52" s="28"/>
-      <c r="O52" s="28"/>
-      <c r="P52" s="28"/>
-      <c r="Q52" s="28"/>
-      <c r="R52" s="29"/>
+      <c r="A52" s="121"/>
+      <c r="B52" s="122"/>
+      <c r="C52" s="123"/>
+      <c r="D52" s="81"/>
+      <c r="E52" s="81"/>
+      <c r="F52" s="81"/>
+      <c r="G52" s="81"/>
+      <c r="H52" s="81"/>
+      <c r="I52" s="81"/>
+      <c r="J52" s="81"/>
+      <c r="K52" s="81"/>
+      <c r="L52" s="81"/>
+      <c r="M52" s="81"/>
+      <c r="N52" s="81"/>
+      <c r="O52" s="81"/>
+      <c r="P52" s="81"/>
+      <c r="Q52" s="81"/>
+      <c r="R52" s="117"/>
     </row>
     <row r="53" spans="1:18" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A53" s="73" t="s">
+      <c r="A53" s="101" t="s">
         <v>20</v>
       </c>
-      <c r="B53" s="74"/>
-      <c r="C53" s="75"/>
-      <c r="D53" s="36"/>
-      <c r="E53" s="36"/>
-      <c r="F53" s="36"/>
-      <c r="G53" s="36"/>
-      <c r="H53" s="36"/>
-      <c r="I53" s="36"/>
-      <c r="J53" s="36"/>
-      <c r="K53" s="36"/>
-      <c r="L53" s="36"/>
-      <c r="M53" s="36"/>
-      <c r="N53" s="36"/>
-      <c r="O53" s="36"/>
-      <c r="P53" s="36"/>
-      <c r="Q53" s="36"/>
-      <c r="R53" s="37"/>
+      <c r="B53" s="102"/>
+      <c r="C53" s="103"/>
+      <c r="D53" s="79"/>
+      <c r="E53" s="79"/>
+      <c r="F53" s="79"/>
+      <c r="G53" s="79"/>
+      <c r="H53" s="79"/>
+      <c r="I53" s="79"/>
+      <c r="J53" s="79"/>
+      <c r="K53" s="79"/>
+      <c r="L53" s="79"/>
+      <c r="M53" s="79"/>
+      <c r="N53" s="79"/>
+      <c r="O53" s="79"/>
+      <c r="P53" s="79"/>
+      <c r="Q53" s="79"/>
+      <c r="R53" s="124"/>
     </row>
     <row r="54" spans="1:18" s="2" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="76"/>
-      <c r="B54" s="77"/>
-      <c r="C54" s="78"/>
-      <c r="D54" s="38"/>
-      <c r="E54" s="38"/>
-      <c r="F54" s="38"/>
-      <c r="G54" s="38"/>
-      <c r="H54" s="38"/>
-      <c r="I54" s="38"/>
-      <c r="J54" s="38"/>
-      <c r="K54" s="38"/>
-      <c r="L54" s="38"/>
-      <c r="M54" s="38"/>
-      <c r="N54" s="38"/>
-      <c r="O54" s="38"/>
-      <c r="P54" s="38"/>
-      <c r="Q54" s="38"/>
-      <c r="R54" s="39"/>
+      <c r="A54" s="104"/>
+      <c r="B54" s="105"/>
+      <c r="C54" s="106"/>
+      <c r="D54" s="80"/>
+      <c r="E54" s="80"/>
+      <c r="F54" s="80"/>
+      <c r="G54" s="80"/>
+      <c r="H54" s="80"/>
+      <c r="I54" s="80"/>
+      <c r="J54" s="80"/>
+      <c r="K54" s="80"/>
+      <c r="L54" s="80"/>
+      <c r="M54" s="80"/>
+      <c r="N54" s="80"/>
+      <c r="O54" s="80"/>
+      <c r="P54" s="80"/>
+      <c r="Q54" s="80"/>
+      <c r="R54" s="125"/>
     </row>
     <row r="55" spans="1:18" s="2" customFormat="1" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.15"/>
     <row r="56" spans="1:18" s="2" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -2720,26 +2720,22 @@
   </sheetData>
   <sheetProtection formatCells="0"/>
   <mergeCells count="52">
-    <mergeCell ref="A43:C44"/>
-    <mergeCell ref="D39:G40"/>
-    <mergeCell ref="D23:L25"/>
-    <mergeCell ref="A49:C50"/>
-    <mergeCell ref="D49:H50"/>
-    <mergeCell ref="A45:C45"/>
-    <mergeCell ref="H45:J45"/>
-    <mergeCell ref="A41:C42"/>
-    <mergeCell ref="D43:G44"/>
-    <mergeCell ref="H43:J44"/>
-    <mergeCell ref="M22:N28"/>
-    <mergeCell ref="N49:R50"/>
-    <mergeCell ref="I49:M50"/>
-    <mergeCell ref="D45:G45"/>
-    <mergeCell ref="D41:G42"/>
-    <mergeCell ref="H41:J42"/>
-    <mergeCell ref="K41:N42"/>
-    <mergeCell ref="O41:R45"/>
-    <mergeCell ref="K43:N44"/>
-    <mergeCell ref="K45:N45"/>
+    <mergeCell ref="O3:R4"/>
+    <mergeCell ref="D51:H52"/>
+    <mergeCell ref="N51:R52"/>
+    <mergeCell ref="A51:C52"/>
+    <mergeCell ref="N53:R54"/>
+    <mergeCell ref="M31:R32"/>
+    <mergeCell ref="M33:R34"/>
+    <mergeCell ref="A33:C34"/>
+    <mergeCell ref="O39:R40"/>
+    <mergeCell ref="A35:C36"/>
+    <mergeCell ref="D33:I34"/>
+    <mergeCell ref="J33:L34"/>
+    <mergeCell ref="D35:R36"/>
+    <mergeCell ref="A31:C32"/>
+    <mergeCell ref="J31:L32"/>
+    <mergeCell ref="D53:H54"/>
     <mergeCell ref="I53:M54"/>
     <mergeCell ref="I51:M52"/>
     <mergeCell ref="O1:R1"/>
@@ -2756,22 +2752,26 @@
     <mergeCell ref="K39:N40"/>
     <mergeCell ref="A53:C54"/>
     <mergeCell ref="O22:R28"/>
-    <mergeCell ref="O3:R4"/>
-    <mergeCell ref="D51:H52"/>
-    <mergeCell ref="N51:R52"/>
-    <mergeCell ref="A51:C52"/>
-    <mergeCell ref="N53:R54"/>
-    <mergeCell ref="M31:R32"/>
-    <mergeCell ref="M33:R34"/>
-    <mergeCell ref="A33:C34"/>
-    <mergeCell ref="O39:R40"/>
-    <mergeCell ref="A35:C36"/>
-    <mergeCell ref="D33:I34"/>
-    <mergeCell ref="J33:L34"/>
-    <mergeCell ref="D35:R36"/>
-    <mergeCell ref="A31:C32"/>
-    <mergeCell ref="J31:L32"/>
-    <mergeCell ref="D53:H54"/>
+    <mergeCell ref="M22:N28"/>
+    <mergeCell ref="N49:R50"/>
+    <mergeCell ref="I49:M50"/>
+    <mergeCell ref="D45:G45"/>
+    <mergeCell ref="D41:G42"/>
+    <mergeCell ref="H41:J42"/>
+    <mergeCell ref="K41:N42"/>
+    <mergeCell ref="O41:R45"/>
+    <mergeCell ref="K43:N44"/>
+    <mergeCell ref="K45:N45"/>
+    <mergeCell ref="A43:C44"/>
+    <mergeCell ref="D39:G40"/>
+    <mergeCell ref="D23:L25"/>
+    <mergeCell ref="A49:C50"/>
+    <mergeCell ref="D49:H50"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="H45:J45"/>
+    <mergeCell ref="A41:C42"/>
+    <mergeCell ref="D43:G44"/>
+    <mergeCell ref="H43:J44"/>
   </mergeCells>
   <phoneticPr fontId="20"/>
   <printOptions horizontalCentered="1"/>
@@ -2799,62 +2799,62 @@
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="132" t="s">
+      <c r="E2" s="146" t="s">
         <v>22</v>
       </c>
-      <c r="F2" s="132"/>
-      <c r="G2" s="132" t="s">
+      <c r="F2" s="146"/>
+      <c r="G2" s="146" t="s">
         <v>23</v>
       </c>
-      <c r="H2" s="132"/>
-      <c r="I2" s="132" t="s">
+      <c r="H2" s="146"/>
+      <c r="I2" s="146" t="s">
         <v>24</v>
       </c>
-      <c r="J2" s="132"/>
-      <c r="K2" s="132" t="s">
+      <c r="J2" s="146"/>
+      <c r="K2" s="146" t="s">
         <v>25</v>
       </c>
-      <c r="L2" s="132"/>
-      <c r="M2" s="132" t="s">
+      <c r="L2" s="146"/>
+      <c r="M2" s="146" t="s">
         <v>26</v>
       </c>
-      <c r="N2" s="132"/>
+      <c r="N2" s="146"/>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B3" s="130" t="s">
+      <c r="B3" s="143" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="130"/>
+      <c r="C3" s="143"/>
       <c r="D3" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="130"/>
-      <c r="F3" s="130"/>
-      <c r="G3" s="131"/>
-      <c r="H3" s="131"/>
-      <c r="I3" s="130"/>
-      <c r="J3" s="130"/>
-      <c r="K3" s="130"/>
-      <c r="L3" s="130"/>
-      <c r="M3" s="130"/>
-      <c r="N3" s="130"/>
+      <c r="E3" s="143"/>
+      <c r="F3" s="143"/>
+      <c r="G3" s="147"/>
+      <c r="H3" s="147"/>
+      <c r="I3" s="143"/>
+      <c r="J3" s="143"/>
+      <c r="K3" s="143"/>
+      <c r="L3" s="143"/>
+      <c r="M3" s="143"/>
+      <c r="N3" s="143"/>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B4" s="130"/>
-      <c r="C4" s="130"/>
+      <c r="B4" s="143"/>
+      <c r="C4" s="143"/>
       <c r="D4" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="130"/>
-      <c r="F4" s="130"/>
-      <c r="G4" s="130"/>
-      <c r="H4" s="130"/>
-      <c r="I4" s="130"/>
-      <c r="J4" s="130"/>
-      <c r="K4" s="130"/>
-      <c r="L4" s="130"/>
-      <c r="M4" s="130"/>
-      <c r="N4" s="130"/>
+      <c r="E4" s="143"/>
+      <c r="F4" s="143"/>
+      <c r="G4" s="143"/>
+      <c r="H4" s="143"/>
+      <c r="I4" s="143"/>
+      <c r="J4" s="143"/>
+      <c r="K4" s="143"/>
+      <c r="L4" s="143"/>
+      <c r="M4" s="143"/>
+      <c r="N4" s="143"/>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B5" s="1"/>
@@ -2875,62 +2875,62 @@
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
-      <c r="E6" s="137" t="s">
+      <c r="E6" s="141" t="s">
         <v>22</v>
       </c>
-      <c r="F6" s="138"/>
-      <c r="G6" s="137" t="s">
+      <c r="F6" s="142"/>
+      <c r="G6" s="141" t="s">
         <v>23</v>
       </c>
-      <c r="H6" s="138"/>
-      <c r="I6" s="137" t="s">
+      <c r="H6" s="142"/>
+      <c r="I6" s="141" t="s">
         <v>24</v>
       </c>
-      <c r="J6" s="138"/>
-      <c r="K6" s="137" t="s">
+      <c r="J6" s="142"/>
+      <c r="K6" s="141" t="s">
         <v>25</v>
       </c>
-      <c r="L6" s="138"/>
-      <c r="M6" s="137" t="s">
+      <c r="L6" s="142"/>
+      <c r="M6" s="141" t="s">
         <v>26</v>
       </c>
-      <c r="N6" s="138"/>
+      <c r="N6" s="142"/>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B7" s="130" t="s">
+      <c r="B7" s="143" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="130"/>
+      <c r="C7" s="143"/>
       <c r="D7" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="E7" s="133"/>
-      <c r="F7" s="134"/>
-      <c r="G7" s="135"/>
-      <c r="H7" s="136"/>
-      <c r="I7" s="133"/>
-      <c r="J7" s="134"/>
-      <c r="K7" s="133"/>
-      <c r="L7" s="134"/>
-      <c r="M7" s="133"/>
-      <c r="N7" s="134"/>
+      <c r="E7" s="139"/>
+      <c r="F7" s="140"/>
+      <c r="G7" s="144"/>
+      <c r="H7" s="145"/>
+      <c r="I7" s="139"/>
+      <c r="J7" s="140"/>
+      <c r="K7" s="139"/>
+      <c r="L7" s="140"/>
+      <c r="M7" s="139"/>
+      <c r="N7" s="140"/>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B8" s="130"/>
-      <c r="C8" s="130"/>
+      <c r="B8" s="143"/>
+      <c r="C8" s="143"/>
       <c r="D8" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="E8" s="133"/>
-      <c r="F8" s="134"/>
-      <c r="G8" s="133"/>
-      <c r="H8" s="134"/>
-      <c r="I8" s="133"/>
-      <c r="J8" s="134"/>
-      <c r="K8" s="133"/>
-      <c r="L8" s="134"/>
-      <c r="M8" s="133"/>
-      <c r="N8" s="134"/>
+      <c r="E8" s="139"/>
+      <c r="F8" s="140"/>
+      <c r="G8" s="139"/>
+      <c r="H8" s="140"/>
+      <c r="I8" s="139"/>
+      <c r="J8" s="140"/>
+      <c r="K8" s="139"/>
+      <c r="L8" s="140"/>
+      <c r="M8" s="139"/>
+      <c r="N8" s="140"/>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B9" s="1"/>
@@ -2951,62 +2951,62 @@
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
-      <c r="E10" s="137" t="s">
+      <c r="E10" s="141" t="s">
         <v>22</v>
       </c>
-      <c r="F10" s="138"/>
-      <c r="G10" s="137" t="s">
+      <c r="F10" s="142"/>
+      <c r="G10" s="141" t="s">
         <v>23</v>
       </c>
-      <c r="H10" s="138"/>
-      <c r="I10" s="137" t="s">
+      <c r="H10" s="142"/>
+      <c r="I10" s="141" t="s">
         <v>24</v>
       </c>
-      <c r="J10" s="138"/>
-      <c r="K10" s="137" t="s">
+      <c r="J10" s="142"/>
+      <c r="K10" s="141" t="s">
         <v>25</v>
       </c>
-      <c r="L10" s="138"/>
-      <c r="M10" s="137" t="s">
+      <c r="L10" s="142"/>
+      <c r="M10" s="141" t="s">
         <v>26</v>
       </c>
-      <c r="N10" s="138"/>
+      <c r="N10" s="142"/>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B11" s="130" t="s">
+      <c r="B11" s="143" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="130"/>
+      <c r="C11" s="143"/>
       <c r="D11" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="E11" s="133"/>
-      <c r="F11" s="134"/>
-      <c r="G11" s="135"/>
-      <c r="H11" s="136"/>
-      <c r="I11" s="133"/>
-      <c r="J11" s="134"/>
-      <c r="K11" s="133"/>
-      <c r="L11" s="134"/>
-      <c r="M11" s="133"/>
-      <c r="N11" s="134"/>
+      <c r="E11" s="139"/>
+      <c r="F11" s="140"/>
+      <c r="G11" s="144"/>
+      <c r="H11" s="145"/>
+      <c r="I11" s="139"/>
+      <c r="J11" s="140"/>
+      <c r="K11" s="139"/>
+      <c r="L11" s="140"/>
+      <c r="M11" s="139"/>
+      <c r="N11" s="140"/>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B12" s="130"/>
-      <c r="C12" s="130"/>
+      <c r="B12" s="143"/>
+      <c r="C12" s="143"/>
       <c r="D12" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="E12" s="133"/>
-      <c r="F12" s="134"/>
-      <c r="G12" s="133"/>
-      <c r="H12" s="134"/>
-      <c r="I12" s="133"/>
-      <c r="J12" s="134"/>
-      <c r="K12" s="133"/>
-      <c r="L12" s="134"/>
-      <c r="M12" s="133"/>
-      <c r="N12" s="134"/>
+      <c r="E12" s="139"/>
+      <c r="F12" s="140"/>
+      <c r="G12" s="139"/>
+      <c r="H12" s="140"/>
+      <c r="I12" s="139"/>
+      <c r="J12" s="140"/>
+      <c r="K12" s="139"/>
+      <c r="L12" s="140"/>
+      <c r="M12" s="139"/>
+      <c r="N12" s="140"/>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B13" s="1"/>
@@ -3042,155 +3042,231 @@
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
-      <c r="E15" s="137" t="s">
+      <c r="E15" s="141" t="s">
         <v>22</v>
       </c>
-      <c r="F15" s="138"/>
-      <c r="G15" s="137" t="s">
+      <c r="F15" s="142"/>
+      <c r="G15" s="141" t="s">
         <v>23</v>
       </c>
-      <c r="H15" s="138"/>
-      <c r="I15" s="137" t="s">
+      <c r="H15" s="142"/>
+      <c r="I15" s="141" t="s">
         <v>24</v>
       </c>
-      <c r="J15" s="138"/>
-      <c r="K15" s="137" t="s">
+      <c r="J15" s="142"/>
+      <c r="K15" s="141" t="s">
         <v>25</v>
       </c>
-      <c r="L15" s="138"/>
-      <c r="M15" s="137" t="s">
+      <c r="L15" s="142"/>
+      <c r="M15" s="141" t="s">
         <v>26</v>
       </c>
-      <c r="N15" s="138"/>
+      <c r="N15" s="142"/>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B16" s="130" t="s">
+      <c r="B16" s="143" t="s">
         <v>32</v>
       </c>
-      <c r="C16" s="130"/>
+      <c r="C16" s="143"/>
       <c r="D16" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="E16" s="133"/>
-      <c r="F16" s="134"/>
-      <c r="G16" s="135"/>
-      <c r="H16" s="136"/>
-      <c r="I16" s="133"/>
-      <c r="J16" s="134"/>
-      <c r="K16" s="133"/>
-      <c r="L16" s="134"/>
-      <c r="M16" s="133"/>
-      <c r="N16" s="134"/>
+      <c r="E16" s="139"/>
+      <c r="F16" s="140"/>
+      <c r="G16" s="144"/>
+      <c r="H16" s="145"/>
+      <c r="I16" s="139"/>
+      <c r="J16" s="140"/>
+      <c r="K16" s="139"/>
+      <c r="L16" s="140"/>
+      <c r="M16" s="139"/>
+      <c r="N16" s="140"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B17" s="130"/>
-      <c r="C17" s="130"/>
+      <c r="B17" s="143"/>
+      <c r="C17" s="143"/>
       <c r="D17" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="E17" s="133"/>
-      <c r="F17" s="134"/>
-      <c r="G17" s="133"/>
-      <c r="H17" s="134"/>
-      <c r="I17" s="133"/>
-      <c r="J17" s="134"/>
-      <c r="K17" s="133"/>
-      <c r="L17" s="134"/>
-      <c r="M17" s="133"/>
-      <c r="N17" s="134"/>
+      <c r="E17" s="139"/>
+      <c r="F17" s="140"/>
+      <c r="G17" s="139"/>
+      <c r="H17" s="140"/>
+      <c r="I17" s="139"/>
+      <c r="J17" s="140"/>
+      <c r="K17" s="139"/>
+      <c r="L17" s="140"/>
+      <c r="M17" s="139"/>
+      <c r="N17" s="140"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B20" s="139"/>
-      <c r="C20" s="139"/>
-      <c r="D20" s="139"/>
-      <c r="E20" s="139" t="s">
+      <c r="B20" s="136"/>
+      <c r="C20" s="136"/>
+      <c r="D20" s="136"/>
+      <c r="E20" s="136" t="s">
         <v>33</v>
       </c>
-      <c r="F20" s="139"/>
+      <c r="F20" s="136"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B21" s="139" t="s">
+      <c r="B21" s="136" t="s">
         <v>34</v>
       </c>
-      <c r="C21" s="139"/>
-      <c r="D21" s="139"/>
-      <c r="E21" s="140"/>
-      <c r="F21" s="140"/>
+      <c r="C21" s="136"/>
+      <c r="D21" s="136"/>
+      <c r="E21" s="137"/>
+      <c r="F21" s="137"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B22" s="139" t="s">
+      <c r="B22" s="136" t="s">
         <v>35</v>
       </c>
-      <c r="C22" s="139"/>
-      <c r="D22" s="139"/>
-      <c r="E22" s="140"/>
-      <c r="F22" s="140"/>
+      <c r="C22" s="136"/>
+      <c r="D22" s="136"/>
+      <c r="E22" s="137"/>
+      <c r="F22" s="137"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B23" s="139" t="s">
+      <c r="B23" s="136" t="s">
         <v>36</v>
       </c>
-      <c r="C23" s="139"/>
-      <c r="D23" s="139"/>
-      <c r="E23" s="140"/>
-      <c r="F23" s="140"/>
+      <c r="C23" s="136"/>
+      <c r="D23" s="136"/>
+      <c r="E23" s="137"/>
+      <c r="F23" s="137"/>
     </row>
     <row r="24" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B24" s="139" t="s">
+      <c r="B24" s="136" t="s">
         <v>37</v>
       </c>
-      <c r="C24" s="139"/>
-      <c r="D24" s="139"/>
-      <c r="E24" s="140"/>
-      <c r="F24" s="140"/>
+      <c r="C24" s="136"/>
+      <c r="D24" s="136"/>
+      <c r="E24" s="137"/>
+      <c r="F24" s="137"/>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B25" s="139" t="s">
+      <c r="B25" s="136" t="s">
         <v>38</v>
       </c>
-      <c r="C25" s="139"/>
-      <c r="D25" s="139"/>
-      <c r="E25" s="140"/>
-      <c r="F25" s="140"/>
+      <c r="C25" s="136"/>
+      <c r="D25" s="136"/>
+      <c r="E25" s="137"/>
+      <c r="F25" s="137"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B26" s="139" t="s">
+      <c r="B26" s="136" t="s">
         <v>39</v>
       </c>
-      <c r="C26" s="139"/>
-      <c r="D26" s="139"/>
-      <c r="E26" s="140"/>
-      <c r="F26" s="140"/>
+      <c r="C26" s="136"/>
+      <c r="D26" s="136"/>
+      <c r="E26" s="137"/>
+      <c r="F26" s="137"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B27" s="139" t="s">
+      <c r="B27" s="136" t="s">
         <v>40</v>
       </c>
-      <c r="C27" s="139"/>
-      <c r="D27" s="139"/>
-      <c r="E27" s="141"/>
-      <c r="F27" s="141"/>
+      <c r="C27" s="136"/>
+      <c r="D27" s="136"/>
+      <c r="E27" s="138"/>
+      <c r="F27" s="138"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B28" s="139" t="s">
+      <c r="B28" s="136" t="s">
         <v>41</v>
       </c>
-      <c r="C28" s="139"/>
-      <c r="D28" s="139"/>
-      <c r="E28" s="140"/>
-      <c r="F28" s="140"/>
+      <c r="C28" s="136"/>
+      <c r="D28" s="136"/>
+      <c r="E28" s="137"/>
+      <c r="F28" s="137"/>
     </row>
     <row r="29" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B29" s="139" t="s">
+      <c r="B29" s="136" t="s">
         <v>42</v>
       </c>
-      <c r="C29" s="139"/>
-      <c r="D29" s="139"/>
-      <c r="E29" s="140"/>
-      <c r="F29" s="140"/>
+      <c r="C29" s="136"/>
+      <c r="D29" s="136"/>
+      <c r="E29" s="137"/>
+      <c r="F29" s="137"/>
     </row>
   </sheetData>
   <mergeCells count="84">
+    <mergeCell ref="B3:C4"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="B7:C8"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="M8:N8"/>
+    <mergeCell ref="B11:C12"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="B16:C17"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="K16:L16"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="E25:F25"/>
     <mergeCell ref="B29:D29"/>
     <mergeCell ref="E29:F29"/>
     <mergeCell ref="B26:D26"/>
@@ -3199,82 +3275,6 @@
     <mergeCell ref="E27:F27"/>
     <mergeCell ref="B28:D28"/>
     <mergeCell ref="E28:F28"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="K15:L15"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="B16:C17"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="K16:L16"/>
-    <mergeCell ref="M11:N11"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="M10:N10"/>
-    <mergeCell ref="B11:C12"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="M7:N7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="M8:N8"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="B7:C8"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="B3:C4"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="K3:L3"/>
   </mergeCells>
   <phoneticPr fontId="20"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/storage/app/estimateTemplate/comprehensiveOfRecommend.xlsx
+++ b/storage/app/estimateTemplate/comprehensiveOfRecommend.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yokoyama\Desktop\修正用ふぉうるだ\a\estimateTemplate\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.100.1\エルフル事務局\yokoyama\火災見積システム(mitumo)\新mitumo\見積書Excelテンプレート\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FF07D3A-2562-479A-B078-DD902561999F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94244D05-6C41-4339-A452-ACE45285D55E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30" yWindow="90" windowWidth="28770" windowHeight="15435" xr2:uid="{0E9C5CA5-184F-4C06-AA15-1AF55B55AFB9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{0E9C5CA5-184F-4C06-AA15-1AF55B55AFB9}"/>
   </bookViews>
   <sheets>
     <sheet name="おすすめ(総合)" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="44">
   <si>
     <t>御　　見　　積　　書</t>
     <rPh sb="0" eb="1">
@@ -438,6 +438,19 @@
     </rPh>
     <rPh sb="3" eb="5">
       <t>ケイスウ</t>
+    </rPh>
+    <phoneticPr fontId="20"/>
+  </si>
+  <si>
+    <t>長期年払割引</t>
+    <rPh sb="0" eb="2">
+      <t>チョウキ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ネンハラ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ワリビキ</t>
     </rPh>
     <phoneticPr fontId="20"/>
   </si>
@@ -1165,169 +1178,97 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="18" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="18" fillId="0" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="9" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="9" fillId="0" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="9" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="9" fillId="0" borderId="29" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="24" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="26" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="8" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="28" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="16" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="16" fillId="0" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="16" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="16" fillId="0" borderId="29" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="9" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="9" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="58" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -1337,18 +1278,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -1373,12 +1302,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1388,6 +1311,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="2" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1433,100 +1362,40 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="181" fontId="9" fillId="0" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="9" fillId="0" borderId="29" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="24" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="33" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="34" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="35" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="179" fontId="9" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1534,6 +1403,150 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="26" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="8" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="28" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="16" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="16" fillId="0" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="16" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="16" fillId="0" borderId="29" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="35" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="33" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="34" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1911,10 +1924,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="O1" s="82"/>
-      <c r="P1" s="82"/>
-      <c r="Q1" s="82"/>
-      <c r="R1" s="82"/>
+      <c r="O1" s="58"/>
+      <c r="P1" s="58"/>
+      <c r="Q1" s="58"/>
+      <c r="R1" s="58"/>
     </row>
     <row r="2" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="O2" s="25"/>
@@ -1924,16 +1937,16 @@
     </row>
     <row r="3" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A3" s="3"/>
-      <c r="O3" s="116"/>
-      <c r="P3" s="116"/>
-      <c r="Q3" s="116"/>
-      <c r="R3" s="116"/>
+      <c r="O3" s="27"/>
+      <c r="P3" s="27"/>
+      <c r="Q3" s="27"/>
+      <c r="R3" s="27"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="O4" s="116"/>
-      <c r="P4" s="116"/>
-      <c r="Q4" s="116"/>
-      <c r="R4" s="116"/>
+      <c r="O4" s="27"/>
+      <c r="P4" s="27"/>
+      <c r="Q4" s="27"/>
+      <c r="R4" s="27"/>
     </row>
     <row r="5" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="N5" s="24"/>
@@ -1996,196 +2009,196 @@
       <c r="R10" s="20"/>
     </row>
     <row r="11" spans="1:18" ht="21" x14ac:dyDescent="0.4">
-      <c r="A11" s="83" t="s">
+      <c r="A11" s="59" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="83"/>
-      <c r="C11" s="83"/>
-      <c r="D11" s="83"/>
-      <c r="E11" s="83"/>
-      <c r="F11" s="83"/>
-      <c r="G11" s="83"/>
-      <c r="H11" s="83"/>
-      <c r="I11" s="83"/>
-      <c r="J11" s="83"/>
-      <c r="K11" s="83"/>
-      <c r="L11" s="83"/>
-      <c r="M11" s="83"/>
-      <c r="N11" s="83"/>
-      <c r="O11" s="83"/>
-      <c r="P11" s="83"/>
-      <c r="Q11" s="83"/>
-      <c r="R11" s="83"/>
+      <c r="B11" s="59"/>
+      <c r="C11" s="59"/>
+      <c r="D11" s="59"/>
+      <c r="E11" s="59"/>
+      <c r="F11" s="59"/>
+      <c r="G11" s="59"/>
+      <c r="H11" s="59"/>
+      <c r="I11" s="59"/>
+      <c r="J11" s="59"/>
+      <c r="K11" s="59"/>
+      <c r="L11" s="59"/>
+      <c r="M11" s="59"/>
+      <c r="N11" s="59"/>
+      <c r="O11" s="59"/>
+      <c r="P11" s="59"/>
+      <c r="Q11" s="59"/>
+      <c r="R11" s="59"/>
     </row>
     <row r="14" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="15" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
-      <c r="A15" s="94" t="s">
+      <c r="A15" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="B15" s="94"/>
-      <c r="C15" s="94"/>
-      <c r="D15" s="94"/>
-      <c r="E15" s="94"/>
-      <c r="F15" s="94"/>
-      <c r="G15" s="94"/>
-      <c r="H15" s="94"/>
-      <c r="I15" s="94"/>
-      <c r="J15" s="94"/>
-      <c r="K15" s="94"/>
-      <c r="L15" s="94"/>
-      <c r="M15" s="94"/>
-      <c r="N15" s="94"/>
-      <c r="O15" s="94"/>
-      <c r="P15" s="94"/>
-      <c r="Q15" s="94"/>
-      <c r="R15" s="94"/>
+      <c r="B15" s="66"/>
+      <c r="C15" s="66"/>
+      <c r="D15" s="66"/>
+      <c r="E15" s="66"/>
+      <c r="F15" s="66"/>
+      <c r="G15" s="66"/>
+      <c r="H15" s="66"/>
+      <c r="I15" s="66"/>
+      <c r="J15" s="66"/>
+      <c r="K15" s="66"/>
+      <c r="L15" s="66"/>
+      <c r="M15" s="66"/>
+      <c r="N15" s="66"/>
+      <c r="O15" s="66"/>
+      <c r="P15" s="66"/>
+      <c r="Q15" s="66"/>
+      <c r="R15" s="66"/>
     </row>
     <row r="18" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
-      <c r="A18" s="95" t="s">
+      <c r="A18" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="B18" s="95"/>
-      <c r="C18" s="95"/>
-      <c r="D18" s="95"/>
-      <c r="E18" s="95"/>
-      <c r="F18" s="95"/>
-      <c r="G18" s="95"/>
-      <c r="H18" s="95"/>
-      <c r="I18" s="95"/>
-      <c r="J18" s="95"/>
-      <c r="K18" s="95"/>
-      <c r="L18" s="95"/>
-      <c r="M18" s="95"/>
-      <c r="N18" s="95"/>
-      <c r="O18" s="95"/>
-      <c r="P18" s="95"/>
-      <c r="Q18" s="95"/>
-      <c r="R18" s="95"/>
+      <c r="B18" s="67"/>
+      <c r="C18" s="67"/>
+      <c r="D18" s="67"/>
+      <c r="E18" s="67"/>
+      <c r="F18" s="67"/>
+      <c r="G18" s="67"/>
+      <c r="H18" s="67"/>
+      <c r="I18" s="67"/>
+      <c r="J18" s="67"/>
+      <c r="K18" s="67"/>
+      <c r="L18" s="67"/>
+      <c r="M18" s="67"/>
+      <c r="N18" s="67"/>
+      <c r="O18" s="67"/>
+      <c r="P18" s="67"/>
+      <c r="Q18" s="67"/>
+      <c r="R18" s="67"/>
     </row>
     <row r="19" spans="1:18" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="20" spans="1:18" ht="12.75" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="87" t="s">
+      <c r="A20" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="B20" s="33"/>
-      <c r="C20" s="33"/>
-      <c r="D20" s="88"/>
-      <c r="E20" s="89"/>
-      <c r="F20" s="89"/>
-      <c r="G20" s="89"/>
-      <c r="H20" s="89"/>
-      <c r="I20" s="89"/>
-      <c r="J20" s="89"/>
-      <c r="K20" s="89"/>
-      <c r="L20" s="89"/>
-      <c r="M20" s="89"/>
-      <c r="N20" s="89"/>
-      <c r="O20" s="89"/>
-      <c r="P20" s="89"/>
-      <c r="Q20" s="89"/>
-      <c r="R20" s="90"/>
+      <c r="B20" s="46"/>
+      <c r="C20" s="46"/>
+      <c r="D20" s="60"/>
+      <c r="E20" s="61"/>
+      <c r="F20" s="61"/>
+      <c r="G20" s="61"/>
+      <c r="H20" s="61"/>
+      <c r="I20" s="61"/>
+      <c r="J20" s="61"/>
+      <c r="K20" s="61"/>
+      <c r="L20" s="61"/>
+      <c r="M20" s="61"/>
+      <c r="N20" s="61"/>
+      <c r="O20" s="61"/>
+      <c r="P20" s="61"/>
+      <c r="Q20" s="61"/>
+      <c r="R20" s="62"/>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A21" s="84"/>
-      <c r="B21" s="35"/>
-      <c r="C21" s="35"/>
-      <c r="D21" s="91"/>
-      <c r="E21" s="92"/>
-      <c r="F21" s="92"/>
-      <c r="G21" s="92"/>
-      <c r="H21" s="92"/>
-      <c r="I21" s="92"/>
-      <c r="J21" s="92"/>
-      <c r="K21" s="92"/>
-      <c r="L21" s="92"/>
-      <c r="M21" s="92"/>
-      <c r="N21" s="92"/>
-      <c r="O21" s="92"/>
-      <c r="P21" s="92"/>
-      <c r="Q21" s="92"/>
-      <c r="R21" s="93"/>
+      <c r="A21" s="44"/>
+      <c r="B21" s="45"/>
+      <c r="C21" s="45"/>
+      <c r="D21" s="63"/>
+      <c r="E21" s="64"/>
+      <c r="F21" s="64"/>
+      <c r="G21" s="64"/>
+      <c r="H21" s="64"/>
+      <c r="I21" s="64"/>
+      <c r="J21" s="64"/>
+      <c r="K21" s="64"/>
+      <c r="L21" s="64"/>
+      <c r="M21" s="64"/>
+      <c r="N21" s="64"/>
+      <c r="O21" s="64"/>
+      <c r="P21" s="64"/>
+      <c r="Q21" s="64"/>
+      <c r="R21" s="65"/>
     </row>
     <row r="22" spans="1:18" ht="5.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="84" t="s">
+      <c r="A22" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="B22" s="35"/>
-      <c r="C22" s="35"/>
+      <c r="B22" s="45"/>
+      <c r="C22" s="45"/>
       <c r="D22" s="19"/>
       <c r="L22" s="18"/>
-      <c r="M22" s="63" t="s">
+      <c r="M22" s="88" t="s">
         <v>5</v>
       </c>
-      <c r="N22" s="64"/>
-      <c r="O22" s="107"/>
-      <c r="P22" s="108"/>
-      <c r="Q22" s="108"/>
-      <c r="R22" s="109"/>
+      <c r="N22" s="89"/>
+      <c r="O22" s="79"/>
+      <c r="P22" s="80"/>
+      <c r="Q22" s="80"/>
+      <c r="R22" s="81"/>
     </row>
     <row r="23" spans="1:18" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="84"/>
-      <c r="B23" s="35"/>
-      <c r="C23" s="35"/>
-      <c r="D23" s="37"/>
-      <c r="E23" s="38"/>
-      <c r="F23" s="38"/>
-      <c r="G23" s="38"/>
-      <c r="H23" s="38"/>
-      <c r="I23" s="38"/>
-      <c r="J23" s="38"/>
-      <c r="K23" s="38"/>
-      <c r="L23" s="39"/>
-      <c r="M23" s="63"/>
-      <c r="N23" s="64"/>
-      <c r="O23" s="110"/>
-      <c r="P23" s="111"/>
-      <c r="Q23" s="111"/>
-      <c r="R23" s="112"/>
+      <c r="A23" s="44"/>
+      <c r="B23" s="45"/>
+      <c r="C23" s="45"/>
+      <c r="D23" s="124"/>
+      <c r="E23" s="125"/>
+      <c r="F23" s="125"/>
+      <c r="G23" s="125"/>
+      <c r="H23" s="125"/>
+      <c r="I23" s="125"/>
+      <c r="J23" s="125"/>
+      <c r="K23" s="125"/>
+      <c r="L23" s="126"/>
+      <c r="M23" s="88"/>
+      <c r="N23" s="89"/>
+      <c r="O23" s="82"/>
+      <c r="P23" s="83"/>
+      <c r="Q23" s="83"/>
+      <c r="R23" s="84"/>
     </row>
     <row r="24" spans="1:18" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="84"/>
-      <c r="B24" s="35"/>
-      <c r="C24" s="35"/>
-      <c r="D24" s="40"/>
-      <c r="E24" s="38"/>
-      <c r="F24" s="38"/>
-      <c r="G24" s="38"/>
-      <c r="H24" s="38"/>
-      <c r="I24" s="38"/>
-      <c r="J24" s="38"/>
-      <c r="K24" s="38"/>
-      <c r="L24" s="39"/>
-      <c r="M24" s="63"/>
-      <c r="N24" s="64"/>
-      <c r="O24" s="110"/>
-      <c r="P24" s="111"/>
-      <c r="Q24" s="111"/>
-      <c r="R24" s="112"/>
+      <c r="A24" s="44"/>
+      <c r="B24" s="45"/>
+      <c r="C24" s="45"/>
+      <c r="D24" s="127"/>
+      <c r="E24" s="125"/>
+      <c r="F24" s="125"/>
+      <c r="G24" s="125"/>
+      <c r="H24" s="125"/>
+      <c r="I24" s="125"/>
+      <c r="J24" s="125"/>
+      <c r="K24" s="125"/>
+      <c r="L24" s="126"/>
+      <c r="M24" s="88"/>
+      <c r="N24" s="89"/>
+      <c r="O24" s="82"/>
+      <c r="P24" s="83"/>
+      <c r="Q24" s="83"/>
+      <c r="R24" s="84"/>
     </row>
     <row r="25" spans="1:18" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="84"/>
-      <c r="B25" s="35"/>
-      <c r="C25" s="35"/>
-      <c r="D25" s="40"/>
-      <c r="E25" s="38"/>
-      <c r="F25" s="38"/>
-      <c r="G25" s="38"/>
-      <c r="H25" s="38"/>
-      <c r="I25" s="38"/>
-      <c r="J25" s="38"/>
-      <c r="K25" s="38"/>
-      <c r="L25" s="39"/>
-      <c r="M25" s="63"/>
-      <c r="N25" s="64"/>
-      <c r="O25" s="110"/>
-      <c r="P25" s="111"/>
-      <c r="Q25" s="111"/>
-      <c r="R25" s="112"/>
+      <c r="A25" s="44"/>
+      <c r="B25" s="45"/>
+      <c r="C25" s="45"/>
+      <c r="D25" s="127"/>
+      <c r="E25" s="125"/>
+      <c r="F25" s="125"/>
+      <c r="G25" s="125"/>
+      <c r="H25" s="125"/>
+      <c r="I25" s="125"/>
+      <c r="J25" s="125"/>
+      <c r="K25" s="125"/>
+      <c r="L25" s="126"/>
+      <c r="M25" s="88"/>
+      <c r="N25" s="89"/>
+      <c r="O25" s="82"/>
+      <c r="P25" s="83"/>
+      <c r="Q25" s="83"/>
+      <c r="R25" s="84"/>
     </row>
     <row r="26" spans="1:18" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="84"/>
-      <c r="B26" s="35"/>
-      <c r="C26" s="35"/>
+      <c r="A26" s="44"/>
+      <c r="B26" s="45"/>
+      <c r="C26" s="45"/>
       <c r="D26" s="17"/>
       <c r="E26" s="16"/>
       <c r="F26" s="15"/>
@@ -2195,17 +2208,17 @@
       <c r="J26" s="14"/>
       <c r="K26" s="14"/>
       <c r="L26" s="13"/>
-      <c r="M26" s="63"/>
-      <c r="N26" s="64"/>
-      <c r="O26" s="110"/>
-      <c r="P26" s="111"/>
-      <c r="Q26" s="111"/>
-      <c r="R26" s="112"/>
+      <c r="M26" s="88"/>
+      <c r="N26" s="89"/>
+      <c r="O26" s="82"/>
+      <c r="P26" s="83"/>
+      <c r="Q26" s="83"/>
+      <c r="R26" s="84"/>
     </row>
     <row r="27" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="84"/>
-      <c r="B27" s="35"/>
-      <c r="C27" s="35"/>
+      <c r="A27" s="44"/>
+      <c r="B27" s="45"/>
+      <c r="C27" s="45"/>
       <c r="D27" s="12"/>
       <c r="F27" s="10"/>
       <c r="G27" s="11"/>
@@ -2213,17 +2226,17 @@
       <c r="I27" s="9"/>
       <c r="J27" s="9"/>
       <c r="L27" s="8"/>
-      <c r="M27" s="63"/>
-      <c r="N27" s="64"/>
-      <c r="O27" s="110"/>
-      <c r="P27" s="111"/>
-      <c r="Q27" s="111"/>
-      <c r="R27" s="112"/>
+      <c r="M27" s="88"/>
+      <c r="N27" s="89"/>
+      <c r="O27" s="82"/>
+      <c r="P27" s="83"/>
+      <c r="Q27" s="83"/>
+      <c r="R27" s="84"/>
     </row>
     <row r="28" spans="1:18" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="85"/>
-      <c r="B28" s="86"/>
-      <c r="C28" s="86"/>
+      <c r="A28" s="49"/>
+      <c r="B28" s="50"/>
+      <c r="C28" s="50"/>
       <c r="D28" s="7"/>
       <c r="E28" s="6"/>
       <c r="F28" s="6"/>
@@ -2233,346 +2246,346 @@
       <c r="J28" s="6"/>
       <c r="K28" s="6"/>
       <c r="L28" s="5"/>
-      <c r="M28" s="65"/>
-      <c r="N28" s="66"/>
-      <c r="O28" s="113"/>
-      <c r="P28" s="114"/>
-      <c r="Q28" s="114"/>
-      <c r="R28" s="115"/>
+      <c r="M28" s="90"/>
+      <c r="N28" s="91"/>
+      <c r="O28" s="85"/>
+      <c r="P28" s="86"/>
+      <c r="Q28" s="86"/>
+      <c r="R28" s="87"/>
     </row>
     <row r="29" spans="1:18" ht="12.75" thickTop="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="1:18" ht="12.75" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="31" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="87" t="s">
+      <c r="A31" s="57" t="s">
         <v>6</v>
       </c>
-      <c r="B31" s="33"/>
-      <c r="C31" s="33"/>
-      <c r="D31" s="96"/>
-      <c r="E31" s="96"/>
-      <c r="F31" s="96"/>
-      <c r="G31" s="96"/>
-      <c r="H31" s="96"/>
-      <c r="I31" s="96"/>
-      <c r="J31" s="33" t="s">
+      <c r="B31" s="46"/>
+      <c r="C31" s="46"/>
+      <c r="D31" s="40"/>
+      <c r="E31" s="40"/>
+      <c r="F31" s="40"/>
+      <c r="G31" s="40"/>
+      <c r="H31" s="40"/>
+      <c r="I31" s="40"/>
+      <c r="J31" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="K31" s="33"/>
-      <c r="L31" s="33"/>
-      <c r="M31" s="96"/>
-      <c r="N31" s="96"/>
-      <c r="O31" s="96"/>
-      <c r="P31" s="96"/>
-      <c r="Q31" s="96"/>
-      <c r="R31" s="126"/>
+      <c r="K31" s="46"/>
+      <c r="L31" s="46"/>
+      <c r="M31" s="40"/>
+      <c r="N31" s="40"/>
+      <c r="O31" s="40"/>
+      <c r="P31" s="40"/>
+      <c r="Q31" s="40"/>
+      <c r="R31" s="41"/>
     </row>
     <row r="32" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="84"/>
-      <c r="B32" s="35"/>
-      <c r="C32" s="35"/>
-      <c r="D32" s="97"/>
-      <c r="E32" s="97"/>
-      <c r="F32" s="97"/>
-      <c r="G32" s="97"/>
-      <c r="H32" s="97"/>
-      <c r="I32" s="97"/>
-      <c r="J32" s="35"/>
-      <c r="K32" s="35"/>
-      <c r="L32" s="35"/>
-      <c r="M32" s="97"/>
-      <c r="N32" s="97"/>
-      <c r="O32" s="97"/>
-      <c r="P32" s="97"/>
-      <c r="Q32" s="97"/>
-      <c r="R32" s="127"/>
+      <c r="A32" s="44"/>
+      <c r="B32" s="45"/>
+      <c r="C32" s="45"/>
+      <c r="D32" s="42"/>
+      <c r="E32" s="42"/>
+      <c r="F32" s="42"/>
+      <c r="G32" s="42"/>
+      <c r="H32" s="42"/>
+      <c r="I32" s="42"/>
+      <c r="J32" s="45"/>
+      <c r="K32" s="45"/>
+      <c r="L32" s="45"/>
+      <c r="M32" s="42"/>
+      <c r="N32" s="42"/>
+      <c r="O32" s="42"/>
+      <c r="P32" s="42"/>
+      <c r="Q32" s="42"/>
+      <c r="R32" s="43"/>
     </row>
     <row r="33" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="84" t="s">
+      <c r="A33" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="B33" s="35"/>
-      <c r="C33" s="35"/>
-      <c r="D33" s="97"/>
-      <c r="E33" s="97"/>
-      <c r="F33" s="97"/>
-      <c r="G33" s="97"/>
-      <c r="H33" s="97"/>
-      <c r="I33" s="97"/>
-      <c r="J33" s="35" t="s">
+      <c r="B33" s="45"/>
+      <c r="C33" s="45"/>
+      <c r="D33" s="42"/>
+      <c r="E33" s="42"/>
+      <c r="F33" s="42"/>
+      <c r="G33" s="42"/>
+      <c r="H33" s="42"/>
+      <c r="I33" s="42"/>
+      <c r="J33" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="K33" s="35"/>
-      <c r="L33" s="35"/>
-      <c r="M33" s="97"/>
-      <c r="N33" s="97"/>
-      <c r="O33" s="97"/>
-      <c r="P33" s="97"/>
-      <c r="Q33" s="97"/>
-      <c r="R33" s="127"/>
+      <c r="K33" s="45"/>
+      <c r="L33" s="45"/>
+      <c r="M33" s="42"/>
+      <c r="N33" s="42"/>
+      <c r="O33" s="42"/>
+      <c r="P33" s="42"/>
+      <c r="Q33" s="42"/>
+      <c r="R33" s="43"/>
     </row>
     <row r="34" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="84"/>
-      <c r="B34" s="35"/>
-      <c r="C34" s="35"/>
-      <c r="D34" s="97"/>
-      <c r="E34" s="97"/>
-      <c r="F34" s="97"/>
-      <c r="G34" s="97"/>
-      <c r="H34" s="97"/>
-      <c r="I34" s="97"/>
-      <c r="J34" s="35"/>
-      <c r="K34" s="35"/>
-      <c r="L34" s="35"/>
-      <c r="M34" s="97"/>
-      <c r="N34" s="97"/>
-      <c r="O34" s="97"/>
-      <c r="P34" s="97"/>
-      <c r="Q34" s="97"/>
-      <c r="R34" s="127"/>
+      <c r="A34" s="44"/>
+      <c r="B34" s="45"/>
+      <c r="C34" s="45"/>
+      <c r="D34" s="42"/>
+      <c r="E34" s="42"/>
+      <c r="F34" s="42"/>
+      <c r="G34" s="42"/>
+      <c r="H34" s="42"/>
+      <c r="I34" s="42"/>
+      <c r="J34" s="45"/>
+      <c r="K34" s="45"/>
+      <c r="L34" s="45"/>
+      <c r="M34" s="42"/>
+      <c r="N34" s="42"/>
+      <c r="O34" s="42"/>
+      <c r="P34" s="42"/>
+      <c r="Q34" s="42"/>
+      <c r="R34" s="43"/>
     </row>
     <row r="35" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="84" t="s">
+      <c r="A35" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="B35" s="35"/>
-      <c r="C35" s="35"/>
-      <c r="D35" s="130"/>
-      <c r="E35" s="131"/>
-      <c r="F35" s="131"/>
-      <c r="G35" s="131"/>
-      <c r="H35" s="131"/>
-      <c r="I35" s="131"/>
-      <c r="J35" s="131"/>
-      <c r="K35" s="131"/>
-      <c r="L35" s="131"/>
-      <c r="M35" s="131"/>
-      <c r="N35" s="131"/>
-      <c r="O35" s="131"/>
-      <c r="P35" s="131"/>
-      <c r="Q35" s="131"/>
-      <c r="R35" s="132"/>
+      <c r="B35" s="45"/>
+      <c r="C35" s="45"/>
+      <c r="D35" s="51"/>
+      <c r="E35" s="52"/>
+      <c r="F35" s="52"/>
+      <c r="G35" s="52"/>
+      <c r="H35" s="52"/>
+      <c r="I35" s="52"/>
+      <c r="J35" s="52"/>
+      <c r="K35" s="52"/>
+      <c r="L35" s="52"/>
+      <c r="M35" s="52"/>
+      <c r="N35" s="52"/>
+      <c r="O35" s="52"/>
+      <c r="P35" s="52"/>
+      <c r="Q35" s="52"/>
+      <c r="R35" s="53"/>
     </row>
     <row r="36" spans="1:18" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A36" s="85"/>
-      <c r="B36" s="86"/>
-      <c r="C36" s="86"/>
-      <c r="D36" s="133"/>
-      <c r="E36" s="134"/>
-      <c r="F36" s="134"/>
-      <c r="G36" s="134"/>
-      <c r="H36" s="134"/>
-      <c r="I36" s="134"/>
-      <c r="J36" s="134"/>
-      <c r="K36" s="134"/>
-      <c r="L36" s="134"/>
-      <c r="M36" s="134"/>
-      <c r="N36" s="134"/>
-      <c r="O36" s="134"/>
-      <c r="P36" s="134"/>
-      <c r="Q36" s="134"/>
-      <c r="R36" s="135"/>
+      <c r="A36" s="49"/>
+      <c r="B36" s="50"/>
+      <c r="C36" s="50"/>
+      <c r="D36" s="54"/>
+      <c r="E36" s="55"/>
+      <c r="F36" s="55"/>
+      <c r="G36" s="55"/>
+      <c r="H36" s="55"/>
+      <c r="I36" s="55"/>
+      <c r="J36" s="55"/>
+      <c r="K36" s="55"/>
+      <c r="L36" s="55"/>
+      <c r="M36" s="55"/>
+      <c r="N36" s="55"/>
+      <c r="O36" s="55"/>
+      <c r="P36" s="55"/>
+      <c r="Q36" s="55"/>
+      <c r="R36" s="56"/>
     </row>
     <row r="37" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="98"/>
-      <c r="B37" s="99"/>
-      <c r="C37" s="99"/>
-      <c r="D37" s="99"/>
-      <c r="E37" s="99"/>
-      <c r="F37" s="99"/>
-      <c r="G37" s="99"/>
-      <c r="H37" s="99"/>
-      <c r="I37" s="99"/>
-      <c r="J37" s="99"/>
-      <c r="K37" s="99"/>
-      <c r="L37" s="99"/>
-      <c r="M37" s="99"/>
-      <c r="N37" s="99"/>
-      <c r="O37" s="99"/>
-      <c r="P37" s="99"/>
-      <c r="Q37" s="99"/>
-      <c r="R37" s="99"/>
+      <c r="A37" s="68"/>
+      <c r="B37" s="69"/>
+      <c r="C37" s="69"/>
+      <c r="D37" s="69"/>
+      <c r="E37" s="69"/>
+      <c r="F37" s="69"/>
+      <c r="G37" s="69"/>
+      <c r="H37" s="69"/>
+      <c r="I37" s="69"/>
+      <c r="J37" s="69"/>
+      <c r="K37" s="69"/>
+      <c r="L37" s="69"/>
+      <c r="M37" s="69"/>
+      <c r="N37" s="69"/>
+      <c r="O37" s="69"/>
+      <c r="P37" s="69"/>
+      <c r="Q37" s="69"/>
+      <c r="R37" s="69"/>
     </row>
     <row r="38" spans="1:18" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="100"/>
-      <c r="B38" s="100"/>
-      <c r="C38" s="100"/>
-      <c r="D38" s="100"/>
-      <c r="E38" s="100"/>
-      <c r="F38" s="100"/>
-      <c r="G38" s="100"/>
-      <c r="H38" s="100"/>
-      <c r="I38" s="100"/>
-      <c r="J38" s="100"/>
-      <c r="K38" s="100"/>
-      <c r="L38" s="100"/>
-      <c r="M38" s="100"/>
-      <c r="N38" s="100"/>
-      <c r="O38" s="100"/>
-      <c r="P38" s="100"/>
-      <c r="Q38" s="100"/>
-      <c r="R38" s="100"/>
+      <c r="A38" s="70"/>
+      <c r="B38" s="70"/>
+      <c r="C38" s="70"/>
+      <c r="D38" s="70"/>
+      <c r="E38" s="70"/>
+      <c r="F38" s="70"/>
+      <c r="G38" s="70"/>
+      <c r="H38" s="70"/>
+      <c r="I38" s="70"/>
+      <c r="J38" s="70"/>
+      <c r="K38" s="70"/>
+      <c r="L38" s="70"/>
+      <c r="M38" s="70"/>
+      <c r="N38" s="70"/>
+      <c r="O38" s="70"/>
+      <c r="P38" s="70"/>
+      <c r="Q38" s="70"/>
+      <c r="R38" s="70"/>
     </row>
     <row r="39" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="87" t="s">
+      <c r="A39" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="B39" s="33"/>
-      <c r="C39" s="33"/>
-      <c r="D39" s="33" t="s">
+      <c r="B39" s="46"/>
+      <c r="C39" s="46"/>
+      <c r="D39" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="E39" s="33"/>
-      <c r="F39" s="33"/>
-      <c r="G39" s="34"/>
-      <c r="H39" s="33" t="s">
+      <c r="E39" s="46"/>
+      <c r="F39" s="46"/>
+      <c r="G39" s="71"/>
+      <c r="H39" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="I39" s="33"/>
-      <c r="J39" s="33"/>
-      <c r="K39" s="33" t="s">
+      <c r="I39" s="46"/>
+      <c r="J39" s="46"/>
+      <c r="K39" s="46" t="s">
         <v>12</v>
       </c>
-      <c r="L39" s="33"/>
-      <c r="M39" s="33"/>
-      <c r="N39" s="34"/>
-      <c r="O39" s="33" t="s">
+      <c r="L39" s="46"/>
+      <c r="M39" s="46"/>
+      <c r="N39" s="71"/>
+      <c r="O39" s="46" t="s">
         <v>21</v>
       </c>
-      <c r="P39" s="33"/>
-      <c r="Q39" s="33"/>
-      <c r="R39" s="128"/>
+      <c r="P39" s="46"/>
+      <c r="Q39" s="46"/>
+      <c r="R39" s="47"/>
     </row>
     <row r="40" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="84"/>
-      <c r="B40" s="35"/>
-      <c r="C40" s="35"/>
-      <c r="D40" s="35"/>
-      <c r="E40" s="35"/>
-      <c r="F40" s="35"/>
-      <c r="G40" s="36"/>
-      <c r="H40" s="35"/>
-      <c r="I40" s="35"/>
-      <c r="J40" s="35"/>
-      <c r="K40" s="35"/>
-      <c r="L40" s="35"/>
-      <c r="M40" s="35"/>
-      <c r="N40" s="36"/>
-      <c r="O40" s="35"/>
-      <c r="P40" s="35"/>
-      <c r="Q40" s="35"/>
-      <c r="R40" s="129"/>
+      <c r="A40" s="44"/>
+      <c r="B40" s="45"/>
+      <c r="C40" s="45"/>
+      <c r="D40" s="45"/>
+      <c r="E40" s="45"/>
+      <c r="F40" s="45"/>
+      <c r="G40" s="72"/>
+      <c r="H40" s="45"/>
+      <c r="I40" s="45"/>
+      <c r="J40" s="45"/>
+      <c r="K40" s="45"/>
+      <c r="L40" s="45"/>
+      <c r="M40" s="45"/>
+      <c r="N40" s="72"/>
+      <c r="O40" s="45"/>
+      <c r="P40" s="45"/>
+      <c r="Q40" s="45"/>
+      <c r="R40" s="48"/>
     </row>
     <row r="41" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="27" t="s">
+      <c r="A41" s="118" t="s">
         <v>13</v>
       </c>
-      <c r="B41" s="28"/>
-      <c r="C41" s="29"/>
-      <c r="D41" s="55"/>
-      <c r="E41" s="56"/>
-      <c r="F41" s="56"/>
-      <c r="G41" s="57"/>
-      <c r="H41" s="69" t="s">
+      <c r="B41" s="119"/>
+      <c r="C41" s="120"/>
+      <c r="D41" s="102"/>
+      <c r="E41" s="103"/>
+      <c r="F41" s="103"/>
+      <c r="G41" s="104"/>
+      <c r="H41" s="108" t="s">
         <v>14</v>
       </c>
-      <c r="I41" s="70"/>
-      <c r="J41" s="71"/>
-      <c r="K41" s="55"/>
-      <c r="L41" s="56"/>
-      <c r="M41" s="56"/>
-      <c r="N41" s="57"/>
-      <c r="O41" s="75"/>
-      <c r="P41" s="75"/>
-      <c r="Q41" s="75"/>
-      <c r="R41" s="76"/>
+      <c r="I41" s="109"/>
+      <c r="J41" s="110"/>
+      <c r="K41" s="102"/>
+      <c r="L41" s="103"/>
+      <c r="M41" s="103"/>
+      <c r="N41" s="104"/>
+      <c r="O41" s="114"/>
+      <c r="P41" s="114"/>
+      <c r="Q41" s="114"/>
+      <c r="R41" s="115"/>
     </row>
     <row r="42" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="30"/>
-      <c r="B42" s="31"/>
-      <c r="C42" s="32"/>
-      <c r="D42" s="58"/>
-      <c r="E42" s="59"/>
-      <c r="F42" s="59"/>
-      <c r="G42" s="60"/>
-      <c r="H42" s="72"/>
-      <c r="I42" s="73"/>
-      <c r="J42" s="74"/>
-      <c r="K42" s="58"/>
-      <c r="L42" s="59"/>
-      <c r="M42" s="59"/>
-      <c r="N42" s="60"/>
-      <c r="O42" s="75"/>
-      <c r="P42" s="75"/>
-      <c r="Q42" s="75"/>
-      <c r="R42" s="76"/>
+      <c r="A42" s="121"/>
+      <c r="B42" s="122"/>
+      <c r="C42" s="123"/>
+      <c r="D42" s="105"/>
+      <c r="E42" s="106"/>
+      <c r="F42" s="106"/>
+      <c r="G42" s="107"/>
+      <c r="H42" s="111"/>
+      <c r="I42" s="112"/>
+      <c r="J42" s="113"/>
+      <c r="K42" s="105"/>
+      <c r="L42" s="106"/>
+      <c r="M42" s="106"/>
+      <c r="N42" s="107"/>
+      <c r="O42" s="114"/>
+      <c r="P42" s="114"/>
+      <c r="Q42" s="114"/>
+      <c r="R42" s="115"/>
     </row>
     <row r="43" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="27" t="s">
+      <c r="A43" s="118" t="s">
         <v>15</v>
       </c>
-      <c r="B43" s="28"/>
-      <c r="C43" s="29"/>
-      <c r="D43" s="55"/>
-      <c r="E43" s="56"/>
-      <c r="F43" s="56"/>
-      <c r="G43" s="57"/>
-      <c r="H43" s="61" t="s">
+      <c r="B43" s="119"/>
+      <c r="C43" s="120"/>
+      <c r="D43" s="102"/>
+      <c r="E43" s="103"/>
+      <c r="F43" s="103"/>
+      <c r="G43" s="104"/>
+      <c r="H43" s="136" t="s">
         <v>16</v>
       </c>
-      <c r="I43" s="28"/>
-      <c r="J43" s="29"/>
-      <c r="K43" s="55"/>
-      <c r="L43" s="56"/>
-      <c r="M43" s="56"/>
-      <c r="N43" s="57"/>
-      <c r="O43" s="75"/>
-      <c r="P43" s="75"/>
-      <c r="Q43" s="75"/>
-      <c r="R43" s="76"/>
+      <c r="I43" s="119"/>
+      <c r="J43" s="120"/>
+      <c r="K43" s="102"/>
+      <c r="L43" s="103"/>
+      <c r="M43" s="103"/>
+      <c r="N43" s="104"/>
+      <c r="O43" s="114"/>
+      <c r="P43" s="114"/>
+      <c r="Q43" s="114"/>
+      <c r="R43" s="115"/>
     </row>
     <row r="44" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="30"/>
-      <c r="B44" s="31"/>
-      <c r="C44" s="32"/>
-      <c r="D44" s="58"/>
-      <c r="E44" s="59"/>
-      <c r="F44" s="59"/>
-      <c r="G44" s="60"/>
-      <c r="H44" s="62"/>
-      <c r="I44" s="31"/>
-      <c r="J44" s="32"/>
-      <c r="K44" s="58"/>
-      <c r="L44" s="59"/>
-      <c r="M44" s="59"/>
-      <c r="N44" s="60"/>
-      <c r="O44" s="75"/>
-      <c r="P44" s="75"/>
-      <c r="Q44" s="75"/>
-      <c r="R44" s="76"/>
+      <c r="A44" s="121"/>
+      <c r="B44" s="122"/>
+      <c r="C44" s="123"/>
+      <c r="D44" s="105"/>
+      <c r="E44" s="106"/>
+      <c r="F44" s="106"/>
+      <c r="G44" s="107"/>
+      <c r="H44" s="137"/>
+      <c r="I44" s="122"/>
+      <c r="J44" s="123"/>
+      <c r="K44" s="105"/>
+      <c r="L44" s="106"/>
+      <c r="M44" s="106"/>
+      <c r="N44" s="107"/>
+      <c r="O44" s="114"/>
+      <c r="P44" s="114"/>
+      <c r="Q44" s="114"/>
+      <c r="R44" s="115"/>
     </row>
     <row r="45" spans="1:18" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A45" s="53" t="s">
+      <c r="A45" s="134" t="s">
         <v>17</v>
       </c>
-      <c r="B45" s="54"/>
-      <c r="C45" s="54"/>
-      <c r="D45" s="148"/>
-      <c r="E45" s="148"/>
-      <c r="F45" s="148"/>
-      <c r="G45" s="149"/>
-      <c r="H45" s="54" t="s">
+      <c r="B45" s="135"/>
+      <c r="C45" s="135"/>
+      <c r="D45" s="100"/>
+      <c r="E45" s="100"/>
+      <c r="F45" s="100"/>
+      <c r="G45" s="101"/>
+      <c r="H45" s="135" t="s">
         <v>17</v>
       </c>
-      <c r="I45" s="54"/>
-      <c r="J45" s="54"/>
-      <c r="K45" s="148"/>
-      <c r="L45" s="148"/>
-      <c r="M45" s="148"/>
-      <c r="N45" s="149"/>
-      <c r="O45" s="77"/>
-      <c r="P45" s="77"/>
-      <c r="Q45" s="77"/>
-      <c r="R45" s="78"/>
+      <c r="I45" s="135"/>
+      <c r="J45" s="135"/>
+      <c r="K45" s="100"/>
+      <c r="L45" s="100"/>
+      <c r="M45" s="100"/>
+      <c r="N45" s="101"/>
+      <c r="O45" s="116"/>
+      <c r="P45" s="116"/>
+      <c r="Q45" s="116"/>
+      <c r="R45" s="117"/>
     </row>
     <row r="46" spans="1:18" ht="20.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.4"/>
     <row r="47" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -2584,128 +2597,128 @@
       </c>
     </row>
     <row r="49" spans="1:18" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="41"/>
-      <c r="B49" s="42"/>
-      <c r="C49" s="43"/>
-      <c r="D49" s="47"/>
-      <c r="E49" s="48"/>
-      <c r="F49" s="48"/>
-      <c r="G49" s="48"/>
-      <c r="H49" s="49"/>
-      <c r="I49" s="47"/>
-      <c r="J49" s="48"/>
-      <c r="K49" s="48"/>
-      <c r="L49" s="48"/>
-      <c r="M49" s="49"/>
-      <c r="N49" s="47"/>
-      <c r="O49" s="48"/>
-      <c r="P49" s="48"/>
-      <c r="Q49" s="48"/>
-      <c r="R49" s="67"/>
+      <c r="A49" s="128"/>
+      <c r="B49" s="129"/>
+      <c r="C49" s="130"/>
+      <c r="D49" s="92"/>
+      <c r="E49" s="93"/>
+      <c r="F49" s="93"/>
+      <c r="G49" s="93"/>
+      <c r="H49" s="98"/>
+      <c r="I49" s="92"/>
+      <c r="J49" s="93"/>
+      <c r="K49" s="93"/>
+      <c r="L49" s="93"/>
+      <c r="M49" s="98"/>
+      <c r="N49" s="92"/>
+      <c r="O49" s="93"/>
+      <c r="P49" s="93"/>
+      <c r="Q49" s="93"/>
+      <c r="R49" s="94"/>
     </row>
     <row r="50" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="44"/>
-      <c r="B50" s="45"/>
-      <c r="C50" s="46"/>
-      <c r="D50" s="50"/>
-      <c r="E50" s="51"/>
-      <c r="F50" s="51"/>
-      <c r="G50" s="51"/>
-      <c r="H50" s="52"/>
-      <c r="I50" s="50"/>
-      <c r="J50" s="51"/>
-      <c r="K50" s="51"/>
-      <c r="L50" s="51"/>
-      <c r="M50" s="52"/>
-      <c r="N50" s="50"/>
-      <c r="O50" s="51"/>
-      <c r="P50" s="51"/>
-      <c r="Q50" s="51"/>
-      <c r="R50" s="68"/>
+      <c r="A50" s="131"/>
+      <c r="B50" s="132"/>
+      <c r="C50" s="133"/>
+      <c r="D50" s="95"/>
+      <c r="E50" s="96"/>
+      <c r="F50" s="96"/>
+      <c r="G50" s="96"/>
+      <c r="H50" s="99"/>
+      <c r="I50" s="95"/>
+      <c r="J50" s="96"/>
+      <c r="K50" s="96"/>
+      <c r="L50" s="96"/>
+      <c r="M50" s="99"/>
+      <c r="N50" s="95"/>
+      <c r="O50" s="96"/>
+      <c r="P50" s="96"/>
+      <c r="Q50" s="96"/>
+      <c r="R50" s="97"/>
     </row>
     <row r="51" spans="1:18" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A51" s="118" t="s">
+      <c r="A51" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="B51" s="119"/>
-      <c r="C51" s="120"/>
-      <c r="D51" s="81"/>
-      <c r="E51" s="81"/>
-      <c r="F51" s="81"/>
-      <c r="G51" s="81"/>
-      <c r="H51" s="81"/>
-      <c r="I51" s="81"/>
-      <c r="J51" s="81"/>
-      <c r="K51" s="81"/>
-      <c r="L51" s="81"/>
-      <c r="M51" s="81"/>
-      <c r="N51" s="81"/>
-      <c r="O51" s="81"/>
-      <c r="P51" s="81"/>
-      <c r="Q51" s="81"/>
-      <c r="R51" s="117"/>
+      <c r="B51" s="31"/>
+      <c r="C51" s="32"/>
+      <c r="D51" s="28"/>
+      <c r="E51" s="28"/>
+      <c r="F51" s="28"/>
+      <c r="G51" s="28"/>
+      <c r="H51" s="28"/>
+      <c r="I51" s="28"/>
+      <c r="J51" s="28"/>
+      <c r="K51" s="28"/>
+      <c r="L51" s="28"/>
+      <c r="M51" s="28"/>
+      <c r="N51" s="28"/>
+      <c r="O51" s="28"/>
+      <c r="P51" s="28"/>
+      <c r="Q51" s="28"/>
+      <c r="R51" s="29"/>
     </row>
     <row r="52" spans="1:18" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A52" s="121"/>
-      <c r="B52" s="122"/>
-      <c r="C52" s="123"/>
-      <c r="D52" s="81"/>
-      <c r="E52" s="81"/>
-      <c r="F52" s="81"/>
-      <c r="G52" s="81"/>
-      <c r="H52" s="81"/>
-      <c r="I52" s="81"/>
-      <c r="J52" s="81"/>
-      <c r="K52" s="81"/>
-      <c r="L52" s="81"/>
-      <c r="M52" s="81"/>
-      <c r="N52" s="81"/>
-      <c r="O52" s="81"/>
-      <c r="P52" s="81"/>
-      <c r="Q52" s="81"/>
-      <c r="R52" s="117"/>
+      <c r="A52" s="33"/>
+      <c r="B52" s="34"/>
+      <c r="C52" s="35"/>
+      <c r="D52" s="28"/>
+      <c r="E52" s="28"/>
+      <c r="F52" s="28"/>
+      <c r="G52" s="28"/>
+      <c r="H52" s="28"/>
+      <c r="I52" s="28"/>
+      <c r="J52" s="28"/>
+      <c r="K52" s="28"/>
+      <c r="L52" s="28"/>
+      <c r="M52" s="28"/>
+      <c r="N52" s="28"/>
+      <c r="O52" s="28"/>
+      <c r="P52" s="28"/>
+      <c r="Q52" s="28"/>
+      <c r="R52" s="29"/>
     </row>
     <row r="53" spans="1:18" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A53" s="101" t="s">
+      <c r="A53" s="73" t="s">
         <v>20</v>
       </c>
-      <c r="B53" s="102"/>
-      <c r="C53" s="103"/>
-      <c r="D53" s="79"/>
-      <c r="E53" s="79"/>
-      <c r="F53" s="79"/>
-      <c r="G53" s="79"/>
-      <c r="H53" s="79"/>
-      <c r="I53" s="79"/>
-      <c r="J53" s="79"/>
-      <c r="K53" s="79"/>
-      <c r="L53" s="79"/>
-      <c r="M53" s="79"/>
-      <c r="N53" s="79"/>
-      <c r="O53" s="79"/>
-      <c r="P53" s="79"/>
-      <c r="Q53" s="79"/>
-      <c r="R53" s="124"/>
+      <c r="B53" s="74"/>
+      <c r="C53" s="75"/>
+      <c r="D53" s="36"/>
+      <c r="E53" s="36"/>
+      <c r="F53" s="36"/>
+      <c r="G53" s="36"/>
+      <c r="H53" s="36"/>
+      <c r="I53" s="36"/>
+      <c r="J53" s="36"/>
+      <c r="K53" s="36"/>
+      <c r="L53" s="36"/>
+      <c r="M53" s="36"/>
+      <c r="N53" s="36"/>
+      <c r="O53" s="36"/>
+      <c r="P53" s="36"/>
+      <c r="Q53" s="36"/>
+      <c r="R53" s="37"/>
     </row>
     <row r="54" spans="1:18" s="2" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="104"/>
-      <c r="B54" s="105"/>
-      <c r="C54" s="106"/>
-      <c r="D54" s="80"/>
-      <c r="E54" s="80"/>
-      <c r="F54" s="80"/>
-      <c r="G54" s="80"/>
-      <c r="H54" s="80"/>
-      <c r="I54" s="80"/>
-      <c r="J54" s="80"/>
-      <c r="K54" s="80"/>
-      <c r="L54" s="80"/>
-      <c r="M54" s="80"/>
-      <c r="N54" s="80"/>
-      <c r="O54" s="80"/>
-      <c r="P54" s="80"/>
-      <c r="Q54" s="80"/>
-      <c r="R54" s="125"/>
+      <c r="A54" s="76"/>
+      <c r="B54" s="77"/>
+      <c r="C54" s="78"/>
+      <c r="D54" s="38"/>
+      <c r="E54" s="38"/>
+      <c r="F54" s="38"/>
+      <c r="G54" s="38"/>
+      <c r="H54" s="38"/>
+      <c r="I54" s="38"/>
+      <c r="J54" s="38"/>
+      <c r="K54" s="38"/>
+      <c r="L54" s="38"/>
+      <c r="M54" s="38"/>
+      <c r="N54" s="38"/>
+      <c r="O54" s="38"/>
+      <c r="P54" s="38"/>
+      <c r="Q54" s="38"/>
+      <c r="R54" s="39"/>
     </row>
     <row r="55" spans="1:18" s="2" customFormat="1" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.15"/>
     <row r="56" spans="1:18" s="2" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -2720,6 +2733,42 @@
   </sheetData>
   <sheetProtection formatCells="0"/>
   <mergeCells count="52">
+    <mergeCell ref="A43:C44"/>
+    <mergeCell ref="D39:G40"/>
+    <mergeCell ref="D23:L25"/>
+    <mergeCell ref="A49:C50"/>
+    <mergeCell ref="D49:H50"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="H45:J45"/>
+    <mergeCell ref="A41:C42"/>
+    <mergeCell ref="D43:G44"/>
+    <mergeCell ref="H43:J44"/>
+    <mergeCell ref="M22:N28"/>
+    <mergeCell ref="N49:R50"/>
+    <mergeCell ref="I49:M50"/>
+    <mergeCell ref="D45:G45"/>
+    <mergeCell ref="D41:G42"/>
+    <mergeCell ref="H41:J42"/>
+    <mergeCell ref="K41:N42"/>
+    <mergeCell ref="O41:R45"/>
+    <mergeCell ref="K43:N44"/>
+    <mergeCell ref="K45:N45"/>
+    <mergeCell ref="I53:M54"/>
+    <mergeCell ref="I51:M52"/>
+    <mergeCell ref="O1:R1"/>
+    <mergeCell ref="A11:R11"/>
+    <mergeCell ref="A22:C28"/>
+    <mergeCell ref="A20:C21"/>
+    <mergeCell ref="D20:R21"/>
+    <mergeCell ref="A15:R15"/>
+    <mergeCell ref="A18:R18"/>
+    <mergeCell ref="D31:I32"/>
+    <mergeCell ref="A37:R38"/>
+    <mergeCell ref="H39:J40"/>
+    <mergeCell ref="A39:C40"/>
+    <mergeCell ref="K39:N40"/>
+    <mergeCell ref="A53:C54"/>
+    <mergeCell ref="O22:R28"/>
     <mergeCell ref="O3:R4"/>
     <mergeCell ref="D51:H52"/>
     <mergeCell ref="N51:R52"/>
@@ -2736,42 +2785,6 @@
     <mergeCell ref="A31:C32"/>
     <mergeCell ref="J31:L32"/>
     <mergeCell ref="D53:H54"/>
-    <mergeCell ref="I53:M54"/>
-    <mergeCell ref="I51:M52"/>
-    <mergeCell ref="O1:R1"/>
-    <mergeCell ref="A11:R11"/>
-    <mergeCell ref="A22:C28"/>
-    <mergeCell ref="A20:C21"/>
-    <mergeCell ref="D20:R21"/>
-    <mergeCell ref="A15:R15"/>
-    <mergeCell ref="A18:R18"/>
-    <mergeCell ref="D31:I32"/>
-    <mergeCell ref="A37:R38"/>
-    <mergeCell ref="H39:J40"/>
-    <mergeCell ref="A39:C40"/>
-    <mergeCell ref="K39:N40"/>
-    <mergeCell ref="A53:C54"/>
-    <mergeCell ref="O22:R28"/>
-    <mergeCell ref="M22:N28"/>
-    <mergeCell ref="N49:R50"/>
-    <mergeCell ref="I49:M50"/>
-    <mergeCell ref="D45:G45"/>
-    <mergeCell ref="D41:G42"/>
-    <mergeCell ref="H41:J42"/>
-    <mergeCell ref="K41:N42"/>
-    <mergeCell ref="O41:R45"/>
-    <mergeCell ref="K43:N44"/>
-    <mergeCell ref="K45:N45"/>
-    <mergeCell ref="A43:C44"/>
-    <mergeCell ref="D39:G40"/>
-    <mergeCell ref="D23:L25"/>
-    <mergeCell ref="A49:C50"/>
-    <mergeCell ref="D49:H50"/>
-    <mergeCell ref="A45:C45"/>
-    <mergeCell ref="H45:J45"/>
-    <mergeCell ref="A41:C42"/>
-    <mergeCell ref="D43:G44"/>
-    <mergeCell ref="H43:J44"/>
   </mergeCells>
   <phoneticPr fontId="20"/>
   <printOptions horizontalCentered="1"/>
@@ -2789,7 +2802,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{980EFC93-3554-4863-A81F-3ECF9A45AFCC}">
-  <dimension ref="B2:N29"/>
+  <dimension ref="B2:N30"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="15" width="4.625" customWidth="1"/>
@@ -2799,62 +2812,62 @@
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="146" t="s">
+      <c r="E2" s="140" t="s">
         <v>22</v>
       </c>
-      <c r="F2" s="146"/>
-      <c r="G2" s="146" t="s">
+      <c r="F2" s="140"/>
+      <c r="G2" s="140" t="s">
         <v>23</v>
       </c>
-      <c r="H2" s="146"/>
-      <c r="I2" s="146" t="s">
+      <c r="H2" s="140"/>
+      <c r="I2" s="140" t="s">
         <v>24</v>
       </c>
-      <c r="J2" s="146"/>
-      <c r="K2" s="146" t="s">
+      <c r="J2" s="140"/>
+      <c r="K2" s="140" t="s">
         <v>25</v>
       </c>
-      <c r="L2" s="146"/>
-      <c r="M2" s="146" t="s">
+      <c r="L2" s="140"/>
+      <c r="M2" s="140" t="s">
         <v>26</v>
       </c>
-      <c r="N2" s="146"/>
+      <c r="N2" s="140"/>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B3" s="143" t="s">
+      <c r="B3" s="138" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="143"/>
+      <c r="C3" s="138"/>
       <c r="D3" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="143"/>
-      <c r="F3" s="143"/>
-      <c r="G3" s="147"/>
-      <c r="H3" s="147"/>
-      <c r="I3" s="143"/>
-      <c r="J3" s="143"/>
-      <c r="K3" s="143"/>
-      <c r="L3" s="143"/>
-      <c r="M3" s="143"/>
-      <c r="N3" s="143"/>
+      <c r="E3" s="138"/>
+      <c r="F3" s="138"/>
+      <c r="G3" s="139"/>
+      <c r="H3" s="139"/>
+      <c r="I3" s="138"/>
+      <c r="J3" s="138"/>
+      <c r="K3" s="138"/>
+      <c r="L3" s="138"/>
+      <c r="M3" s="138"/>
+      <c r="N3" s="138"/>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B4" s="143"/>
-      <c r="C4" s="143"/>
+      <c r="B4" s="138"/>
+      <c r="C4" s="138"/>
       <c r="D4" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="143"/>
-      <c r="F4" s="143"/>
-      <c r="G4" s="143"/>
-      <c r="H4" s="143"/>
-      <c r="I4" s="143"/>
-      <c r="J4" s="143"/>
-      <c r="K4" s="143"/>
-      <c r="L4" s="143"/>
-      <c r="M4" s="143"/>
-      <c r="N4" s="143"/>
+      <c r="E4" s="138"/>
+      <c r="F4" s="138"/>
+      <c r="G4" s="138"/>
+      <c r="H4" s="138"/>
+      <c r="I4" s="138"/>
+      <c r="J4" s="138"/>
+      <c r="K4" s="138"/>
+      <c r="L4" s="138"/>
+      <c r="M4" s="138"/>
+      <c r="N4" s="138"/>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B5" s="1"/>
@@ -2875,62 +2888,62 @@
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
-      <c r="E6" s="141" t="s">
+      <c r="E6" s="145" t="s">
         <v>22</v>
       </c>
-      <c r="F6" s="142"/>
-      <c r="G6" s="141" t="s">
+      <c r="F6" s="146"/>
+      <c r="G6" s="145" t="s">
         <v>23</v>
       </c>
-      <c r="H6" s="142"/>
-      <c r="I6" s="141" t="s">
+      <c r="H6" s="146"/>
+      <c r="I6" s="145" t="s">
         <v>24</v>
       </c>
-      <c r="J6" s="142"/>
-      <c r="K6" s="141" t="s">
+      <c r="J6" s="146"/>
+      <c r="K6" s="145" t="s">
         <v>25</v>
       </c>
-      <c r="L6" s="142"/>
-      <c r="M6" s="141" t="s">
+      <c r="L6" s="146"/>
+      <c r="M6" s="145" t="s">
         <v>26</v>
       </c>
-      <c r="N6" s="142"/>
+      <c r="N6" s="146"/>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B7" s="143" t="s">
+      <c r="B7" s="138" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="143"/>
+      <c r="C7" s="138"/>
       <c r="D7" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="E7" s="139"/>
-      <c r="F7" s="140"/>
-      <c r="G7" s="144"/>
-      <c r="H7" s="145"/>
-      <c r="I7" s="139"/>
-      <c r="J7" s="140"/>
-      <c r="K7" s="139"/>
-      <c r="L7" s="140"/>
-      <c r="M7" s="139"/>
-      <c r="N7" s="140"/>
+      <c r="E7" s="141"/>
+      <c r="F7" s="142"/>
+      <c r="G7" s="143"/>
+      <c r="H7" s="144"/>
+      <c r="I7" s="141"/>
+      <c r="J7" s="142"/>
+      <c r="K7" s="141"/>
+      <c r="L7" s="142"/>
+      <c r="M7" s="141"/>
+      <c r="N7" s="142"/>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B8" s="143"/>
-      <c r="C8" s="143"/>
+      <c r="B8" s="138"/>
+      <c r="C8" s="138"/>
       <c r="D8" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="E8" s="139"/>
-      <c r="F8" s="140"/>
-      <c r="G8" s="139"/>
-      <c r="H8" s="140"/>
-      <c r="I8" s="139"/>
-      <c r="J8" s="140"/>
-      <c r="K8" s="139"/>
-      <c r="L8" s="140"/>
-      <c r="M8" s="139"/>
-      <c r="N8" s="140"/>
+      <c r="E8" s="141"/>
+      <c r="F8" s="142"/>
+      <c r="G8" s="141"/>
+      <c r="H8" s="142"/>
+      <c r="I8" s="141"/>
+      <c r="J8" s="142"/>
+      <c r="K8" s="141"/>
+      <c r="L8" s="142"/>
+      <c r="M8" s="141"/>
+      <c r="N8" s="142"/>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B9" s="1"/>
@@ -2951,62 +2964,62 @@
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
-      <c r="E10" s="141" t="s">
+      <c r="E10" s="145" t="s">
         <v>22</v>
       </c>
-      <c r="F10" s="142"/>
-      <c r="G10" s="141" t="s">
+      <c r="F10" s="146"/>
+      <c r="G10" s="145" t="s">
         <v>23</v>
       </c>
-      <c r="H10" s="142"/>
-      <c r="I10" s="141" t="s">
+      <c r="H10" s="146"/>
+      <c r="I10" s="145" t="s">
         <v>24</v>
       </c>
-      <c r="J10" s="142"/>
-      <c r="K10" s="141" t="s">
+      <c r="J10" s="146"/>
+      <c r="K10" s="145" t="s">
         <v>25</v>
       </c>
-      <c r="L10" s="142"/>
-      <c r="M10" s="141" t="s">
+      <c r="L10" s="146"/>
+      <c r="M10" s="145" t="s">
         <v>26</v>
       </c>
-      <c r="N10" s="142"/>
+      <c r="N10" s="146"/>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B11" s="143" t="s">
+      <c r="B11" s="138" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="143"/>
+      <c r="C11" s="138"/>
       <c r="D11" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="E11" s="139"/>
-      <c r="F11" s="140"/>
-      <c r="G11" s="144"/>
-      <c r="H11" s="145"/>
-      <c r="I11" s="139"/>
-      <c r="J11" s="140"/>
-      <c r="K11" s="139"/>
-      <c r="L11" s="140"/>
-      <c r="M11" s="139"/>
-      <c r="N11" s="140"/>
+      <c r="E11" s="141"/>
+      <c r="F11" s="142"/>
+      <c r="G11" s="143"/>
+      <c r="H11" s="144"/>
+      <c r="I11" s="141"/>
+      <c r="J11" s="142"/>
+      <c r="K11" s="141"/>
+      <c r="L11" s="142"/>
+      <c r="M11" s="141"/>
+      <c r="N11" s="142"/>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B12" s="143"/>
-      <c r="C12" s="143"/>
+      <c r="B12" s="138"/>
+      <c r="C12" s="138"/>
       <c r="D12" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="E12" s="139"/>
-      <c r="F12" s="140"/>
-      <c r="G12" s="139"/>
-      <c r="H12" s="140"/>
-      <c r="I12" s="139"/>
-      <c r="J12" s="140"/>
-      <c r="K12" s="139"/>
-      <c r="L12" s="140"/>
-      <c r="M12" s="139"/>
-      <c r="N12" s="140"/>
+      <c r="E12" s="141"/>
+      <c r="F12" s="142"/>
+      <c r="G12" s="141"/>
+      <c r="H12" s="142"/>
+      <c r="I12" s="141"/>
+      <c r="J12" s="142"/>
+      <c r="K12" s="141"/>
+      <c r="L12" s="142"/>
+      <c r="M12" s="141"/>
+      <c r="N12" s="142"/>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B13" s="1"/>
@@ -3042,231 +3055,166 @@
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
-      <c r="E15" s="141" t="s">
+      <c r="E15" s="145" t="s">
         <v>22</v>
       </c>
-      <c r="F15" s="142"/>
-      <c r="G15" s="141" t="s">
+      <c r="F15" s="146"/>
+      <c r="G15" s="145" t="s">
         <v>23</v>
       </c>
-      <c r="H15" s="142"/>
-      <c r="I15" s="141" t="s">
+      <c r="H15" s="146"/>
+      <c r="I15" s="145" t="s">
         <v>24</v>
       </c>
-      <c r="J15" s="142"/>
-      <c r="K15" s="141" t="s">
+      <c r="J15" s="146"/>
+      <c r="K15" s="145" t="s">
         <v>25</v>
       </c>
-      <c r="L15" s="142"/>
-      <c r="M15" s="141" t="s">
+      <c r="L15" s="146"/>
+      <c r="M15" s="145" t="s">
         <v>26</v>
       </c>
-      <c r="N15" s="142"/>
+      <c r="N15" s="146"/>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B16" s="143" t="s">
+      <c r="B16" s="138" t="s">
         <v>32</v>
       </c>
-      <c r="C16" s="143"/>
+      <c r="C16" s="138"/>
       <c r="D16" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="E16" s="139"/>
-      <c r="F16" s="140"/>
-      <c r="G16" s="144"/>
-      <c r="H16" s="145"/>
-      <c r="I16" s="139"/>
-      <c r="J16" s="140"/>
-      <c r="K16" s="139"/>
-      <c r="L16" s="140"/>
-      <c r="M16" s="139"/>
-      <c r="N16" s="140"/>
+      <c r="E16" s="141"/>
+      <c r="F16" s="142"/>
+      <c r="G16" s="143"/>
+      <c r="H16" s="144"/>
+      <c r="I16" s="141"/>
+      <c r="J16" s="142"/>
+      <c r="K16" s="141"/>
+      <c r="L16" s="142"/>
+      <c r="M16" s="141"/>
+      <c r="N16" s="142"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B17" s="143"/>
-      <c r="C17" s="143"/>
+      <c r="B17" s="138"/>
+      <c r="C17" s="138"/>
       <c r="D17" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="E17" s="139"/>
-      <c r="F17" s="140"/>
-      <c r="G17" s="139"/>
-      <c r="H17" s="140"/>
-      <c r="I17" s="139"/>
-      <c r="J17" s="140"/>
-      <c r="K17" s="139"/>
-      <c r="L17" s="140"/>
-      <c r="M17" s="139"/>
-      <c r="N17" s="140"/>
+      <c r="E17" s="141"/>
+      <c r="F17" s="142"/>
+      <c r="G17" s="141"/>
+      <c r="H17" s="142"/>
+      <c r="I17" s="141"/>
+      <c r="J17" s="142"/>
+      <c r="K17" s="141"/>
+      <c r="L17" s="142"/>
+      <c r="M17" s="141"/>
+      <c r="N17" s="142"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B20" s="136"/>
-      <c r="C20" s="136"/>
-      <c r="D20" s="136"/>
-      <c r="E20" s="136" t="s">
+      <c r="B20" s="147"/>
+      <c r="C20" s="147"/>
+      <c r="D20" s="147"/>
+      <c r="E20" s="147" t="s">
         <v>33</v>
       </c>
-      <c r="F20" s="136"/>
+      <c r="F20" s="147"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B21" s="136" t="s">
+      <c r="B21" s="147" t="s">
         <v>34</v>
       </c>
-      <c r="C21" s="136"/>
-      <c r="D21" s="136"/>
-      <c r="E21" s="137"/>
-      <c r="F21" s="137"/>
+      <c r="C21" s="147"/>
+      <c r="D21" s="147"/>
+      <c r="E21" s="148"/>
+      <c r="F21" s="148"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B22" s="136" t="s">
+      <c r="B22" s="147" t="s">
         <v>35</v>
       </c>
-      <c r="C22" s="136"/>
-      <c r="D22" s="136"/>
-      <c r="E22" s="137"/>
-      <c r="F22" s="137"/>
+      <c r="C22" s="147"/>
+      <c r="D22" s="147"/>
+      <c r="E22" s="148"/>
+      <c r="F22" s="148"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B23" s="136" t="s">
+      <c r="B23" s="147" t="s">
         <v>36</v>
       </c>
-      <c r="C23" s="136"/>
-      <c r="D23" s="136"/>
-      <c r="E23" s="137"/>
-      <c r="F23" s="137"/>
+      <c r="C23" s="147"/>
+      <c r="D23" s="147"/>
+      <c r="E23" s="148"/>
+      <c r="F23" s="148"/>
     </row>
     <row r="24" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B24" s="136" t="s">
+      <c r="B24" s="147" t="s">
         <v>37</v>
       </c>
-      <c r="C24" s="136"/>
-      <c r="D24" s="136"/>
-      <c r="E24" s="137"/>
-      <c r="F24" s="137"/>
+      <c r="C24" s="147"/>
+      <c r="D24" s="147"/>
+      <c r="E24" s="148"/>
+      <c r="F24" s="148"/>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B25" s="136" t="s">
+      <c r="B25" s="147" t="s">
         <v>38</v>
       </c>
-      <c r="C25" s="136"/>
-      <c r="D25" s="136"/>
-      <c r="E25" s="137"/>
-      <c r="F25" s="137"/>
+      <c r="C25" s="147"/>
+      <c r="D25" s="147"/>
+      <c r="E25" s="148"/>
+      <c r="F25" s="148"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B26" s="136" t="s">
+      <c r="B26" s="147" t="s">
         <v>39</v>
       </c>
-      <c r="C26" s="136"/>
-      <c r="D26" s="136"/>
-      <c r="E26" s="137"/>
-      <c r="F26" s="137"/>
+      <c r="C26" s="147"/>
+      <c r="D26" s="147"/>
+      <c r="E26" s="148"/>
+      <c r="F26" s="148"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B27" s="136" t="s">
+      <c r="B27" s="147" t="s">
         <v>40</v>
       </c>
-      <c r="C27" s="136"/>
-      <c r="D27" s="136"/>
-      <c r="E27" s="138"/>
-      <c r="F27" s="138"/>
+      <c r="C27" s="147"/>
+      <c r="D27" s="147"/>
+      <c r="E27" s="149"/>
+      <c r="F27" s="149"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B28" s="136" t="s">
+      <c r="B28" s="147" t="s">
         <v>41</v>
       </c>
-      <c r="C28" s="136"/>
-      <c r="D28" s="136"/>
-      <c r="E28" s="137"/>
-      <c r="F28" s="137"/>
+      <c r="C28" s="147"/>
+      <c r="D28" s="147"/>
+      <c r="E28" s="148"/>
+      <c r="F28" s="148"/>
     </row>
     <row r="29" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B29" s="136" t="s">
+      <c r="B29" s="147" t="s">
         <v>42</v>
       </c>
-      <c r="C29" s="136"/>
-      <c r="D29" s="136"/>
-      <c r="E29" s="137"/>
-      <c r="F29" s="137"/>
+      <c r="C29" s="147"/>
+      <c r="D29" s="147"/>
+      <c r="E29" s="148"/>
+      <c r="F29" s="148"/>
+    </row>
+    <row r="30" spans="2:14" x14ac:dyDescent="0.4">
+      <c r="B30" s="147" t="s">
+        <v>43</v>
+      </c>
+      <c r="C30" s="147"/>
+      <c r="D30" s="147"/>
+      <c r="E30" s="148"/>
+      <c r="F30" s="148"/>
     </row>
   </sheetData>
-  <mergeCells count="84">
-    <mergeCell ref="B3:C4"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="B7:C8"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="M7:N7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="M8:N8"/>
-    <mergeCell ref="B11:C12"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="M10:N10"/>
-    <mergeCell ref="M11:N11"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="B16:C17"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="K16:L16"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="K15:L15"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="E25:F25"/>
+  <mergeCells count="86">
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="E30:F30"/>
     <mergeCell ref="B29:D29"/>
     <mergeCell ref="E29:F29"/>
     <mergeCell ref="B26:D26"/>
@@ -3275,6 +3223,82 @@
     <mergeCell ref="E27:F27"/>
     <mergeCell ref="B28:D28"/>
     <mergeCell ref="E28:F28"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="B16:C17"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="K16:L16"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="B11:C12"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="M8:N8"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="B7:C8"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="B3:C4"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="K3:L3"/>
   </mergeCells>
   <phoneticPr fontId="20"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/storage/app/estimateTemplate/comprehensiveOfRecommend.xlsx
+++ b/storage/app/estimateTemplate/comprehensiveOfRecommend.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.100.1\エルフル事務局\yokoyama\火災見積システム(mitumo)\新mitumo\見積書Excelテンプレート\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94244D05-6C41-4339-A452-ACE45285D55E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72482295-0CEA-42C7-90FB-7D7865C33016}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{0E9C5CA5-184F-4C06-AA15-1AF55B55AFB9}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="48">
   <si>
     <t>御　　見　　積　　書</t>
     <rPh sb="0" eb="1">
@@ -450,6 +450,49 @@
       <t>ネンハラ</t>
     </rPh>
     <rPh sb="4" eb="6">
+      <t>ワリビキ</t>
+    </rPh>
+    <phoneticPr fontId="20"/>
+  </si>
+  <si>
+    <t>消火設備割引</t>
+    <rPh sb="0" eb="4">
+      <t>ショウカセツビ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ワリビキ</t>
+    </rPh>
+    <phoneticPr fontId="20"/>
+  </si>
+  <si>
+    <t>セキュリティ割引</t>
+    <rPh sb="6" eb="8">
+      <t>ワリビキ</t>
+    </rPh>
+    <phoneticPr fontId="20"/>
+  </si>
+  <si>
+    <t>公有物件等割引</t>
+    <rPh sb="0" eb="2">
+      <t>コウユウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ブッケン</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>トウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ワリビキ</t>
+    </rPh>
+    <phoneticPr fontId="20"/>
+  </si>
+  <si>
+    <t>リスク評価割引</t>
+    <rPh sb="3" eb="5">
+      <t>ヒョウカ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
       <t>ワリビキ</t>
     </rPh>
     <phoneticPr fontId="20"/>
@@ -1178,97 +1221,175 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="26" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="8" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="28" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="16" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="16" fillId="0" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="16" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="16" fillId="0" borderId="29" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="9" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="9" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="180" fontId="18" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="181" fontId="9" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="9" fillId="0" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="9" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="9" fillId="0" borderId="29" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="24" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="58" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -1278,6 +1399,18 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -1302,6 +1435,12 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1311,12 +1450,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="2" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1362,190 +1495,100 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="26" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="8" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="28" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="16" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="16" fillId="0" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="16" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="16" fillId="0" borderId="29" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="18" fillId="0" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="9" fillId="0" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="9" fillId="0" borderId="29" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="24" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="33" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="34" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="35" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="33" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="34" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1924,10 +1967,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="O1" s="58"/>
-      <c r="P1" s="58"/>
-      <c r="Q1" s="58"/>
-      <c r="R1" s="58"/>
+      <c r="O1" s="84"/>
+      <c r="P1" s="84"/>
+      <c r="Q1" s="84"/>
+      <c r="R1" s="84"/>
     </row>
     <row r="2" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="O2" s="25"/>
@@ -1937,16 +1980,16 @@
     </row>
     <row r="3" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A3" s="3"/>
-      <c r="O3" s="27"/>
-      <c r="P3" s="27"/>
-      <c r="Q3" s="27"/>
-      <c r="R3" s="27"/>
+      <c r="O3" s="118"/>
+      <c r="P3" s="118"/>
+      <c r="Q3" s="118"/>
+      <c r="R3" s="118"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="O4" s="27"/>
-      <c r="P4" s="27"/>
-      <c r="Q4" s="27"/>
-      <c r="R4" s="27"/>
+      <c r="O4" s="118"/>
+      <c r="P4" s="118"/>
+      <c r="Q4" s="118"/>
+      <c r="R4" s="118"/>
     </row>
     <row r="5" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="N5" s="24"/>
@@ -2009,196 +2052,196 @@
       <c r="R10" s="20"/>
     </row>
     <row r="11" spans="1:18" ht="21" x14ac:dyDescent="0.4">
-      <c r="A11" s="59" t="s">
+      <c r="A11" s="85" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="59"/>
-      <c r="C11" s="59"/>
-      <c r="D11" s="59"/>
-      <c r="E11" s="59"/>
-      <c r="F11" s="59"/>
-      <c r="G11" s="59"/>
-      <c r="H11" s="59"/>
-      <c r="I11" s="59"/>
-      <c r="J11" s="59"/>
-      <c r="K11" s="59"/>
-      <c r="L11" s="59"/>
-      <c r="M11" s="59"/>
-      <c r="N11" s="59"/>
-      <c r="O11" s="59"/>
-      <c r="P11" s="59"/>
-      <c r="Q11" s="59"/>
-      <c r="R11" s="59"/>
+      <c r="B11" s="85"/>
+      <c r="C11" s="85"/>
+      <c r="D11" s="85"/>
+      <c r="E11" s="85"/>
+      <c r="F11" s="85"/>
+      <c r="G11" s="85"/>
+      <c r="H11" s="85"/>
+      <c r="I11" s="85"/>
+      <c r="J11" s="85"/>
+      <c r="K11" s="85"/>
+      <c r="L11" s="85"/>
+      <c r="M11" s="85"/>
+      <c r="N11" s="85"/>
+      <c r="O11" s="85"/>
+      <c r="P11" s="85"/>
+      <c r="Q11" s="85"/>
+      <c r="R11" s="85"/>
     </row>
     <row r="14" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="15" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
-      <c r="A15" s="66" t="s">
+      <c r="A15" s="96" t="s">
         <v>1</v>
       </c>
-      <c r="B15" s="66"/>
-      <c r="C15" s="66"/>
-      <c r="D15" s="66"/>
-      <c r="E15" s="66"/>
-      <c r="F15" s="66"/>
-      <c r="G15" s="66"/>
-      <c r="H15" s="66"/>
-      <c r="I15" s="66"/>
-      <c r="J15" s="66"/>
-      <c r="K15" s="66"/>
-      <c r="L15" s="66"/>
-      <c r="M15" s="66"/>
-      <c r="N15" s="66"/>
-      <c r="O15" s="66"/>
-      <c r="P15" s="66"/>
-      <c r="Q15" s="66"/>
-      <c r="R15" s="66"/>
+      <c r="B15" s="96"/>
+      <c r="C15" s="96"/>
+      <c r="D15" s="96"/>
+      <c r="E15" s="96"/>
+      <c r="F15" s="96"/>
+      <c r="G15" s="96"/>
+      <c r="H15" s="96"/>
+      <c r="I15" s="96"/>
+      <c r="J15" s="96"/>
+      <c r="K15" s="96"/>
+      <c r="L15" s="96"/>
+      <c r="M15" s="96"/>
+      <c r="N15" s="96"/>
+      <c r="O15" s="96"/>
+      <c r="P15" s="96"/>
+      <c r="Q15" s="96"/>
+      <c r="R15" s="96"/>
     </row>
     <row r="18" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
-      <c r="A18" s="67" t="s">
+      <c r="A18" s="97" t="s">
         <v>2</v>
       </c>
-      <c r="B18" s="67"/>
-      <c r="C18" s="67"/>
-      <c r="D18" s="67"/>
-      <c r="E18" s="67"/>
-      <c r="F18" s="67"/>
-      <c r="G18" s="67"/>
-      <c r="H18" s="67"/>
-      <c r="I18" s="67"/>
-      <c r="J18" s="67"/>
-      <c r="K18" s="67"/>
-      <c r="L18" s="67"/>
-      <c r="M18" s="67"/>
-      <c r="N18" s="67"/>
-      <c r="O18" s="67"/>
-      <c r="P18" s="67"/>
-      <c r="Q18" s="67"/>
-      <c r="R18" s="67"/>
+      <c r="B18" s="97"/>
+      <c r="C18" s="97"/>
+      <c r="D18" s="97"/>
+      <c r="E18" s="97"/>
+      <c r="F18" s="97"/>
+      <c r="G18" s="97"/>
+      <c r="H18" s="97"/>
+      <c r="I18" s="97"/>
+      <c r="J18" s="97"/>
+      <c r="K18" s="97"/>
+      <c r="L18" s="97"/>
+      <c r="M18" s="97"/>
+      <c r="N18" s="97"/>
+      <c r="O18" s="97"/>
+      <c r="P18" s="97"/>
+      <c r="Q18" s="97"/>
+      <c r="R18" s="97"/>
     </row>
     <row r="19" spans="1:18" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="20" spans="1:18" ht="12.75" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="57" t="s">
+      <c r="A20" s="89" t="s">
         <v>3</v>
       </c>
-      <c r="B20" s="46"/>
-      <c r="C20" s="46"/>
-      <c r="D20" s="60"/>
-      <c r="E20" s="61"/>
-      <c r="F20" s="61"/>
-      <c r="G20" s="61"/>
-      <c r="H20" s="61"/>
-      <c r="I20" s="61"/>
-      <c r="J20" s="61"/>
-      <c r="K20" s="61"/>
-      <c r="L20" s="61"/>
-      <c r="M20" s="61"/>
-      <c r="N20" s="61"/>
-      <c r="O20" s="61"/>
-      <c r="P20" s="61"/>
-      <c r="Q20" s="61"/>
-      <c r="R20" s="62"/>
+      <c r="B20" s="33"/>
+      <c r="C20" s="33"/>
+      <c r="D20" s="90"/>
+      <c r="E20" s="91"/>
+      <c r="F20" s="91"/>
+      <c r="G20" s="91"/>
+      <c r="H20" s="91"/>
+      <c r="I20" s="91"/>
+      <c r="J20" s="91"/>
+      <c r="K20" s="91"/>
+      <c r="L20" s="91"/>
+      <c r="M20" s="91"/>
+      <c r="N20" s="91"/>
+      <c r="O20" s="91"/>
+      <c r="P20" s="91"/>
+      <c r="Q20" s="91"/>
+      <c r="R20" s="92"/>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A21" s="44"/>
-      <c r="B21" s="45"/>
-      <c r="C21" s="45"/>
-      <c r="D21" s="63"/>
-      <c r="E21" s="64"/>
-      <c r="F21" s="64"/>
-      <c r="G21" s="64"/>
-      <c r="H21" s="64"/>
-      <c r="I21" s="64"/>
-      <c r="J21" s="64"/>
-      <c r="K21" s="64"/>
-      <c r="L21" s="64"/>
-      <c r="M21" s="64"/>
-      <c r="N21" s="64"/>
-      <c r="O21" s="64"/>
-      <c r="P21" s="64"/>
-      <c r="Q21" s="64"/>
-      <c r="R21" s="65"/>
+      <c r="A21" s="86"/>
+      <c r="B21" s="35"/>
+      <c r="C21" s="35"/>
+      <c r="D21" s="93"/>
+      <c r="E21" s="94"/>
+      <c r="F21" s="94"/>
+      <c r="G21" s="94"/>
+      <c r="H21" s="94"/>
+      <c r="I21" s="94"/>
+      <c r="J21" s="94"/>
+      <c r="K21" s="94"/>
+      <c r="L21" s="94"/>
+      <c r="M21" s="94"/>
+      <c r="N21" s="94"/>
+      <c r="O21" s="94"/>
+      <c r="P21" s="94"/>
+      <c r="Q21" s="94"/>
+      <c r="R21" s="95"/>
     </row>
     <row r="22" spans="1:18" ht="5.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="44" t="s">
+      <c r="A22" s="86" t="s">
         <v>4</v>
       </c>
-      <c r="B22" s="45"/>
-      <c r="C22" s="45"/>
+      <c r="B22" s="35"/>
+      <c r="C22" s="35"/>
       <c r="D22" s="19"/>
       <c r="L22" s="18"/>
-      <c r="M22" s="88" t="s">
+      <c r="M22" s="63" t="s">
         <v>5</v>
       </c>
-      <c r="N22" s="89"/>
-      <c r="O22" s="79"/>
-      <c r="P22" s="80"/>
-      <c r="Q22" s="80"/>
-      <c r="R22" s="81"/>
+      <c r="N22" s="64"/>
+      <c r="O22" s="109"/>
+      <c r="P22" s="110"/>
+      <c r="Q22" s="110"/>
+      <c r="R22" s="111"/>
     </row>
     <row r="23" spans="1:18" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="44"/>
-      <c r="B23" s="45"/>
-      <c r="C23" s="45"/>
-      <c r="D23" s="124"/>
-      <c r="E23" s="125"/>
-      <c r="F23" s="125"/>
-      <c r="G23" s="125"/>
-      <c r="H23" s="125"/>
-      <c r="I23" s="125"/>
-      <c r="J23" s="125"/>
-      <c r="K23" s="125"/>
-      <c r="L23" s="126"/>
-      <c r="M23" s="88"/>
-      <c r="N23" s="89"/>
-      <c r="O23" s="82"/>
-      <c r="P23" s="83"/>
-      <c r="Q23" s="83"/>
-      <c r="R23" s="84"/>
+      <c r="A23" s="86"/>
+      <c r="B23" s="35"/>
+      <c r="C23" s="35"/>
+      <c r="D23" s="37"/>
+      <c r="E23" s="38"/>
+      <c r="F23" s="38"/>
+      <c r="G23" s="38"/>
+      <c r="H23" s="38"/>
+      <c r="I23" s="38"/>
+      <c r="J23" s="38"/>
+      <c r="K23" s="38"/>
+      <c r="L23" s="39"/>
+      <c r="M23" s="63"/>
+      <c r="N23" s="64"/>
+      <c r="O23" s="112"/>
+      <c r="P23" s="113"/>
+      <c r="Q23" s="113"/>
+      <c r="R23" s="114"/>
     </row>
     <row r="24" spans="1:18" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="44"/>
-      <c r="B24" s="45"/>
-      <c r="C24" s="45"/>
-      <c r="D24" s="127"/>
-      <c r="E24" s="125"/>
-      <c r="F24" s="125"/>
-      <c r="G24" s="125"/>
-      <c r="H24" s="125"/>
-      <c r="I24" s="125"/>
-      <c r="J24" s="125"/>
-      <c r="K24" s="125"/>
-      <c r="L24" s="126"/>
-      <c r="M24" s="88"/>
-      <c r="N24" s="89"/>
-      <c r="O24" s="82"/>
-      <c r="P24" s="83"/>
-      <c r="Q24" s="83"/>
-      <c r="R24" s="84"/>
+      <c r="A24" s="86"/>
+      <c r="B24" s="35"/>
+      <c r="C24" s="35"/>
+      <c r="D24" s="40"/>
+      <c r="E24" s="38"/>
+      <c r="F24" s="38"/>
+      <c r="G24" s="38"/>
+      <c r="H24" s="38"/>
+      <c r="I24" s="38"/>
+      <c r="J24" s="38"/>
+      <c r="K24" s="38"/>
+      <c r="L24" s="39"/>
+      <c r="M24" s="63"/>
+      <c r="N24" s="64"/>
+      <c r="O24" s="112"/>
+      <c r="P24" s="113"/>
+      <c r="Q24" s="113"/>
+      <c r="R24" s="114"/>
     </row>
     <row r="25" spans="1:18" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="44"/>
-      <c r="B25" s="45"/>
-      <c r="C25" s="45"/>
-      <c r="D25" s="127"/>
-      <c r="E25" s="125"/>
-      <c r="F25" s="125"/>
-      <c r="G25" s="125"/>
-      <c r="H25" s="125"/>
-      <c r="I25" s="125"/>
-      <c r="J25" s="125"/>
-      <c r="K25" s="125"/>
-      <c r="L25" s="126"/>
-      <c r="M25" s="88"/>
-      <c r="N25" s="89"/>
-      <c r="O25" s="82"/>
-      <c r="P25" s="83"/>
-      <c r="Q25" s="83"/>
-      <c r="R25" s="84"/>
+      <c r="A25" s="86"/>
+      <c r="B25" s="35"/>
+      <c r="C25" s="35"/>
+      <c r="D25" s="40"/>
+      <c r="E25" s="38"/>
+      <c r="F25" s="38"/>
+      <c r="G25" s="38"/>
+      <c r="H25" s="38"/>
+      <c r="I25" s="38"/>
+      <c r="J25" s="38"/>
+      <c r="K25" s="38"/>
+      <c r="L25" s="39"/>
+      <c r="M25" s="63"/>
+      <c r="N25" s="64"/>
+      <c r="O25" s="112"/>
+      <c r="P25" s="113"/>
+      <c r="Q25" s="113"/>
+      <c r="R25" s="114"/>
     </row>
     <row r="26" spans="1:18" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="44"/>
-      <c r="B26" s="45"/>
-      <c r="C26" s="45"/>
+      <c r="A26" s="86"/>
+      <c r="B26" s="35"/>
+      <c r="C26" s="35"/>
       <c r="D26" s="17"/>
       <c r="E26" s="16"/>
       <c r="F26" s="15"/>
@@ -2208,17 +2251,17 @@
       <c r="J26" s="14"/>
       <c r="K26" s="14"/>
       <c r="L26" s="13"/>
-      <c r="M26" s="88"/>
-      <c r="N26" s="89"/>
-      <c r="O26" s="82"/>
-      <c r="P26" s="83"/>
-      <c r="Q26" s="83"/>
-      <c r="R26" s="84"/>
+      <c r="M26" s="63"/>
+      <c r="N26" s="64"/>
+      <c r="O26" s="112"/>
+      <c r="P26" s="113"/>
+      <c r="Q26" s="113"/>
+      <c r="R26" s="114"/>
     </row>
     <row r="27" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="44"/>
-      <c r="B27" s="45"/>
-      <c r="C27" s="45"/>
+      <c r="A27" s="86"/>
+      <c r="B27" s="35"/>
+      <c r="C27" s="35"/>
       <c r="D27" s="12"/>
       <c r="F27" s="10"/>
       <c r="G27" s="11"/>
@@ -2226,17 +2269,17 @@
       <c r="I27" s="9"/>
       <c r="J27" s="9"/>
       <c r="L27" s="8"/>
-      <c r="M27" s="88"/>
-      <c r="N27" s="89"/>
-      <c r="O27" s="82"/>
-      <c r="P27" s="83"/>
-      <c r="Q27" s="83"/>
-      <c r="R27" s="84"/>
+      <c r="M27" s="63"/>
+      <c r="N27" s="64"/>
+      <c r="O27" s="112"/>
+      <c r="P27" s="113"/>
+      <c r="Q27" s="113"/>
+      <c r="R27" s="114"/>
     </row>
     <row r="28" spans="1:18" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="49"/>
-      <c r="B28" s="50"/>
-      <c r="C28" s="50"/>
+      <c r="A28" s="87"/>
+      <c r="B28" s="88"/>
+      <c r="C28" s="88"/>
       <c r="D28" s="7"/>
       <c r="E28" s="6"/>
       <c r="F28" s="6"/>
@@ -2246,346 +2289,346 @@
       <c r="J28" s="6"/>
       <c r="K28" s="6"/>
       <c r="L28" s="5"/>
-      <c r="M28" s="90"/>
-      <c r="N28" s="91"/>
-      <c r="O28" s="85"/>
-      <c r="P28" s="86"/>
-      <c r="Q28" s="86"/>
-      <c r="R28" s="87"/>
+      <c r="M28" s="65"/>
+      <c r="N28" s="66"/>
+      <c r="O28" s="115"/>
+      <c r="P28" s="116"/>
+      <c r="Q28" s="116"/>
+      <c r="R28" s="117"/>
     </row>
     <row r="29" spans="1:18" ht="12.75" thickTop="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="1:18" ht="12.75" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="31" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="57" t="s">
+      <c r="A31" s="89" t="s">
         <v>6</v>
       </c>
-      <c r="B31" s="46"/>
-      <c r="C31" s="46"/>
-      <c r="D31" s="40"/>
-      <c r="E31" s="40"/>
-      <c r="F31" s="40"/>
-      <c r="G31" s="40"/>
-      <c r="H31" s="40"/>
-      <c r="I31" s="40"/>
-      <c r="J31" s="46" t="s">
+      <c r="B31" s="33"/>
+      <c r="C31" s="33"/>
+      <c r="D31" s="98"/>
+      <c r="E31" s="98"/>
+      <c r="F31" s="98"/>
+      <c r="G31" s="98"/>
+      <c r="H31" s="98"/>
+      <c r="I31" s="98"/>
+      <c r="J31" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="K31" s="46"/>
-      <c r="L31" s="46"/>
-      <c r="M31" s="40"/>
-      <c r="N31" s="40"/>
-      <c r="O31" s="40"/>
-      <c r="P31" s="40"/>
-      <c r="Q31" s="40"/>
-      <c r="R31" s="41"/>
+      <c r="K31" s="33"/>
+      <c r="L31" s="33"/>
+      <c r="M31" s="98"/>
+      <c r="N31" s="98"/>
+      <c r="O31" s="98"/>
+      <c r="P31" s="98"/>
+      <c r="Q31" s="98"/>
+      <c r="R31" s="128"/>
     </row>
     <row r="32" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="44"/>
-      <c r="B32" s="45"/>
-      <c r="C32" s="45"/>
-      <c r="D32" s="42"/>
-      <c r="E32" s="42"/>
-      <c r="F32" s="42"/>
-      <c r="G32" s="42"/>
-      <c r="H32" s="42"/>
-      <c r="I32" s="42"/>
-      <c r="J32" s="45"/>
-      <c r="K32" s="45"/>
-      <c r="L32" s="45"/>
-      <c r="M32" s="42"/>
-      <c r="N32" s="42"/>
-      <c r="O32" s="42"/>
-      <c r="P32" s="42"/>
-      <c r="Q32" s="42"/>
-      <c r="R32" s="43"/>
+      <c r="A32" s="86"/>
+      <c r="B32" s="35"/>
+      <c r="C32" s="35"/>
+      <c r="D32" s="99"/>
+      <c r="E32" s="99"/>
+      <c r="F32" s="99"/>
+      <c r="G32" s="99"/>
+      <c r="H32" s="99"/>
+      <c r="I32" s="99"/>
+      <c r="J32" s="35"/>
+      <c r="K32" s="35"/>
+      <c r="L32" s="35"/>
+      <c r="M32" s="99"/>
+      <c r="N32" s="99"/>
+      <c r="O32" s="99"/>
+      <c r="P32" s="99"/>
+      <c r="Q32" s="99"/>
+      <c r="R32" s="129"/>
     </row>
     <row r="33" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="44" t="s">
+      <c r="A33" s="86" t="s">
         <v>8</v>
       </c>
-      <c r="B33" s="45"/>
-      <c r="C33" s="45"/>
-      <c r="D33" s="42"/>
-      <c r="E33" s="42"/>
-      <c r="F33" s="42"/>
-      <c r="G33" s="42"/>
-      <c r="H33" s="42"/>
-      <c r="I33" s="42"/>
-      <c r="J33" s="45" t="s">
+      <c r="B33" s="35"/>
+      <c r="C33" s="35"/>
+      <c r="D33" s="99"/>
+      <c r="E33" s="99"/>
+      <c r="F33" s="99"/>
+      <c r="G33" s="99"/>
+      <c r="H33" s="99"/>
+      <c r="I33" s="99"/>
+      <c r="J33" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="K33" s="45"/>
-      <c r="L33" s="45"/>
-      <c r="M33" s="42"/>
-      <c r="N33" s="42"/>
-      <c r="O33" s="42"/>
-      <c r="P33" s="42"/>
-      <c r="Q33" s="42"/>
-      <c r="R33" s="43"/>
+      <c r="K33" s="35"/>
+      <c r="L33" s="35"/>
+      <c r="M33" s="99"/>
+      <c r="N33" s="99"/>
+      <c r="O33" s="99"/>
+      <c r="P33" s="99"/>
+      <c r="Q33" s="99"/>
+      <c r="R33" s="129"/>
     </row>
     <row r="34" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="44"/>
-      <c r="B34" s="45"/>
-      <c r="C34" s="45"/>
-      <c r="D34" s="42"/>
-      <c r="E34" s="42"/>
-      <c r="F34" s="42"/>
-      <c r="G34" s="42"/>
-      <c r="H34" s="42"/>
-      <c r="I34" s="42"/>
-      <c r="J34" s="45"/>
-      <c r="K34" s="45"/>
-      <c r="L34" s="45"/>
-      <c r="M34" s="42"/>
-      <c r="N34" s="42"/>
-      <c r="O34" s="42"/>
-      <c r="P34" s="42"/>
-      <c r="Q34" s="42"/>
-      <c r="R34" s="43"/>
+      <c r="A34" s="86"/>
+      <c r="B34" s="35"/>
+      <c r="C34" s="35"/>
+      <c r="D34" s="99"/>
+      <c r="E34" s="99"/>
+      <c r="F34" s="99"/>
+      <c r="G34" s="99"/>
+      <c r="H34" s="99"/>
+      <c r="I34" s="99"/>
+      <c r="J34" s="35"/>
+      <c r="K34" s="35"/>
+      <c r="L34" s="35"/>
+      <c r="M34" s="99"/>
+      <c r="N34" s="99"/>
+      <c r="O34" s="99"/>
+      <c r="P34" s="99"/>
+      <c r="Q34" s="99"/>
+      <c r="R34" s="129"/>
     </row>
     <row r="35" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="44" t="s">
+      <c r="A35" s="86" t="s">
         <v>10</v>
       </c>
-      <c r="B35" s="45"/>
-      <c r="C35" s="45"/>
-      <c r="D35" s="51"/>
-      <c r="E35" s="52"/>
-      <c r="F35" s="52"/>
-      <c r="G35" s="52"/>
-      <c r="H35" s="52"/>
-      <c r="I35" s="52"/>
-      <c r="J35" s="52"/>
-      <c r="K35" s="52"/>
-      <c r="L35" s="52"/>
-      <c r="M35" s="52"/>
-      <c r="N35" s="52"/>
-      <c r="O35" s="52"/>
-      <c r="P35" s="52"/>
-      <c r="Q35" s="52"/>
-      <c r="R35" s="53"/>
+      <c r="B35" s="35"/>
+      <c r="C35" s="35"/>
+      <c r="D35" s="132"/>
+      <c r="E35" s="133"/>
+      <c r="F35" s="133"/>
+      <c r="G35" s="133"/>
+      <c r="H35" s="133"/>
+      <c r="I35" s="133"/>
+      <c r="J35" s="133"/>
+      <c r="K35" s="133"/>
+      <c r="L35" s="133"/>
+      <c r="M35" s="133"/>
+      <c r="N35" s="133"/>
+      <c r="O35" s="133"/>
+      <c r="P35" s="133"/>
+      <c r="Q35" s="133"/>
+      <c r="R35" s="134"/>
     </row>
     <row r="36" spans="1:18" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A36" s="49"/>
-      <c r="B36" s="50"/>
-      <c r="C36" s="50"/>
-      <c r="D36" s="54"/>
-      <c r="E36" s="55"/>
-      <c r="F36" s="55"/>
-      <c r="G36" s="55"/>
-      <c r="H36" s="55"/>
-      <c r="I36" s="55"/>
-      <c r="J36" s="55"/>
-      <c r="K36" s="55"/>
-      <c r="L36" s="55"/>
-      <c r="M36" s="55"/>
-      <c r="N36" s="55"/>
-      <c r="O36" s="55"/>
-      <c r="P36" s="55"/>
-      <c r="Q36" s="55"/>
-      <c r="R36" s="56"/>
+      <c r="A36" s="87"/>
+      <c r="B36" s="88"/>
+      <c r="C36" s="88"/>
+      <c r="D36" s="135"/>
+      <c r="E36" s="136"/>
+      <c r="F36" s="136"/>
+      <c r="G36" s="136"/>
+      <c r="H36" s="136"/>
+      <c r="I36" s="136"/>
+      <c r="J36" s="136"/>
+      <c r="K36" s="136"/>
+      <c r="L36" s="136"/>
+      <c r="M36" s="136"/>
+      <c r="N36" s="136"/>
+      <c r="O36" s="136"/>
+      <c r="P36" s="136"/>
+      <c r="Q36" s="136"/>
+      <c r="R36" s="137"/>
     </row>
     <row r="37" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="68"/>
-      <c r="B37" s="69"/>
-      <c r="C37" s="69"/>
-      <c r="D37" s="69"/>
-      <c r="E37" s="69"/>
-      <c r="F37" s="69"/>
-      <c r="G37" s="69"/>
-      <c r="H37" s="69"/>
-      <c r="I37" s="69"/>
-      <c r="J37" s="69"/>
-      <c r="K37" s="69"/>
-      <c r="L37" s="69"/>
-      <c r="M37" s="69"/>
-      <c r="N37" s="69"/>
-      <c r="O37" s="69"/>
-      <c r="P37" s="69"/>
-      <c r="Q37" s="69"/>
-      <c r="R37" s="69"/>
+      <c r="A37" s="100"/>
+      <c r="B37" s="101"/>
+      <c r="C37" s="101"/>
+      <c r="D37" s="101"/>
+      <c r="E37" s="101"/>
+      <c r="F37" s="101"/>
+      <c r="G37" s="101"/>
+      <c r="H37" s="101"/>
+      <c r="I37" s="101"/>
+      <c r="J37" s="101"/>
+      <c r="K37" s="101"/>
+      <c r="L37" s="101"/>
+      <c r="M37" s="101"/>
+      <c r="N37" s="101"/>
+      <c r="O37" s="101"/>
+      <c r="P37" s="101"/>
+      <c r="Q37" s="101"/>
+      <c r="R37" s="101"/>
     </row>
     <row r="38" spans="1:18" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="70"/>
-      <c r="B38" s="70"/>
-      <c r="C38" s="70"/>
-      <c r="D38" s="70"/>
-      <c r="E38" s="70"/>
-      <c r="F38" s="70"/>
-      <c r="G38" s="70"/>
-      <c r="H38" s="70"/>
-      <c r="I38" s="70"/>
-      <c r="J38" s="70"/>
-      <c r="K38" s="70"/>
-      <c r="L38" s="70"/>
-      <c r="M38" s="70"/>
-      <c r="N38" s="70"/>
-      <c r="O38" s="70"/>
-      <c r="P38" s="70"/>
-      <c r="Q38" s="70"/>
-      <c r="R38" s="70"/>
+      <c r="A38" s="102"/>
+      <c r="B38" s="102"/>
+      <c r="C38" s="102"/>
+      <c r="D38" s="102"/>
+      <c r="E38" s="102"/>
+      <c r="F38" s="102"/>
+      <c r="G38" s="102"/>
+      <c r="H38" s="102"/>
+      <c r="I38" s="102"/>
+      <c r="J38" s="102"/>
+      <c r="K38" s="102"/>
+      <c r="L38" s="102"/>
+      <c r="M38" s="102"/>
+      <c r="N38" s="102"/>
+      <c r="O38" s="102"/>
+      <c r="P38" s="102"/>
+      <c r="Q38" s="102"/>
+      <c r="R38" s="102"/>
     </row>
     <row r="39" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="57" t="s">
+      <c r="A39" s="89" t="s">
         <v>11</v>
       </c>
-      <c r="B39" s="46"/>
-      <c r="C39" s="46"/>
-      <c r="D39" s="46" t="s">
+      <c r="B39" s="33"/>
+      <c r="C39" s="33"/>
+      <c r="D39" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="E39" s="46"/>
-      <c r="F39" s="46"/>
-      <c r="G39" s="71"/>
-      <c r="H39" s="46" t="s">
+      <c r="E39" s="33"/>
+      <c r="F39" s="33"/>
+      <c r="G39" s="34"/>
+      <c r="H39" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="I39" s="46"/>
-      <c r="J39" s="46"/>
-      <c r="K39" s="46" t="s">
+      <c r="I39" s="33"/>
+      <c r="J39" s="33"/>
+      <c r="K39" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="L39" s="46"/>
-      <c r="M39" s="46"/>
-      <c r="N39" s="71"/>
-      <c r="O39" s="46" t="s">
+      <c r="L39" s="33"/>
+      <c r="M39" s="33"/>
+      <c r="N39" s="34"/>
+      <c r="O39" s="33" t="s">
         <v>21</v>
       </c>
-      <c r="P39" s="46"/>
-      <c r="Q39" s="46"/>
-      <c r="R39" s="47"/>
+      <c r="P39" s="33"/>
+      <c r="Q39" s="33"/>
+      <c r="R39" s="130"/>
     </row>
     <row r="40" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="44"/>
-      <c r="B40" s="45"/>
-      <c r="C40" s="45"/>
-      <c r="D40" s="45"/>
-      <c r="E40" s="45"/>
-      <c r="F40" s="45"/>
-      <c r="G40" s="72"/>
-      <c r="H40" s="45"/>
-      <c r="I40" s="45"/>
-      <c r="J40" s="45"/>
-      <c r="K40" s="45"/>
-      <c r="L40" s="45"/>
-      <c r="M40" s="45"/>
-      <c r="N40" s="72"/>
-      <c r="O40" s="45"/>
-      <c r="P40" s="45"/>
-      <c r="Q40" s="45"/>
-      <c r="R40" s="48"/>
+      <c r="A40" s="86"/>
+      <c r="B40" s="35"/>
+      <c r="C40" s="35"/>
+      <c r="D40" s="35"/>
+      <c r="E40" s="35"/>
+      <c r="F40" s="35"/>
+      <c r="G40" s="36"/>
+      <c r="H40" s="35"/>
+      <c r="I40" s="35"/>
+      <c r="J40" s="35"/>
+      <c r="K40" s="35"/>
+      <c r="L40" s="35"/>
+      <c r="M40" s="35"/>
+      <c r="N40" s="36"/>
+      <c r="O40" s="35"/>
+      <c r="P40" s="35"/>
+      <c r="Q40" s="35"/>
+      <c r="R40" s="131"/>
     </row>
     <row r="41" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="118" t="s">
+      <c r="A41" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="B41" s="119"/>
-      <c r="C41" s="120"/>
-      <c r="D41" s="102"/>
-      <c r="E41" s="103"/>
-      <c r="F41" s="103"/>
-      <c r="G41" s="104"/>
-      <c r="H41" s="108" t="s">
+      <c r="B41" s="28"/>
+      <c r="C41" s="29"/>
+      <c r="D41" s="55"/>
+      <c r="E41" s="56"/>
+      <c r="F41" s="56"/>
+      <c r="G41" s="57"/>
+      <c r="H41" s="71" t="s">
         <v>14</v>
       </c>
-      <c r="I41" s="109"/>
-      <c r="J41" s="110"/>
-      <c r="K41" s="102"/>
-      <c r="L41" s="103"/>
-      <c r="M41" s="103"/>
-      <c r="N41" s="104"/>
-      <c r="O41" s="114"/>
-      <c r="P41" s="114"/>
-      <c r="Q41" s="114"/>
-      <c r="R41" s="115"/>
+      <c r="I41" s="72"/>
+      <c r="J41" s="73"/>
+      <c r="K41" s="55"/>
+      <c r="L41" s="56"/>
+      <c r="M41" s="56"/>
+      <c r="N41" s="57"/>
+      <c r="O41" s="77"/>
+      <c r="P41" s="77"/>
+      <c r="Q41" s="77"/>
+      <c r="R41" s="78"/>
     </row>
     <row r="42" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="121"/>
-      <c r="B42" s="122"/>
-      <c r="C42" s="123"/>
-      <c r="D42" s="105"/>
-      <c r="E42" s="106"/>
-      <c r="F42" s="106"/>
-      <c r="G42" s="107"/>
-      <c r="H42" s="111"/>
-      <c r="I42" s="112"/>
-      <c r="J42" s="113"/>
-      <c r="K42" s="105"/>
-      <c r="L42" s="106"/>
-      <c r="M42" s="106"/>
-      <c r="N42" s="107"/>
-      <c r="O42" s="114"/>
-      <c r="P42" s="114"/>
-      <c r="Q42" s="114"/>
-      <c r="R42" s="115"/>
+      <c r="A42" s="30"/>
+      <c r="B42" s="31"/>
+      <c r="C42" s="32"/>
+      <c r="D42" s="58"/>
+      <c r="E42" s="59"/>
+      <c r="F42" s="59"/>
+      <c r="G42" s="60"/>
+      <c r="H42" s="74"/>
+      <c r="I42" s="75"/>
+      <c r="J42" s="76"/>
+      <c r="K42" s="58"/>
+      <c r="L42" s="59"/>
+      <c r="M42" s="59"/>
+      <c r="N42" s="60"/>
+      <c r="O42" s="77"/>
+      <c r="P42" s="77"/>
+      <c r="Q42" s="77"/>
+      <c r="R42" s="78"/>
     </row>
     <row r="43" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="118" t="s">
+      <c r="A43" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="B43" s="119"/>
-      <c r="C43" s="120"/>
-      <c r="D43" s="102"/>
-      <c r="E43" s="103"/>
-      <c r="F43" s="103"/>
-      <c r="G43" s="104"/>
-      <c r="H43" s="136" t="s">
+      <c r="B43" s="28"/>
+      <c r="C43" s="29"/>
+      <c r="D43" s="55"/>
+      <c r="E43" s="56"/>
+      <c r="F43" s="56"/>
+      <c r="G43" s="57"/>
+      <c r="H43" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="I43" s="119"/>
-      <c r="J43" s="120"/>
-      <c r="K43" s="102"/>
-      <c r="L43" s="103"/>
-      <c r="M43" s="103"/>
-      <c r="N43" s="104"/>
-      <c r="O43" s="114"/>
-      <c r="P43" s="114"/>
-      <c r="Q43" s="114"/>
-      <c r="R43" s="115"/>
+      <c r="I43" s="28"/>
+      <c r="J43" s="29"/>
+      <c r="K43" s="55"/>
+      <c r="L43" s="56"/>
+      <c r="M43" s="56"/>
+      <c r="N43" s="57"/>
+      <c r="O43" s="77"/>
+      <c r="P43" s="77"/>
+      <c r="Q43" s="77"/>
+      <c r="R43" s="78"/>
     </row>
     <row r="44" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="121"/>
-      <c r="B44" s="122"/>
-      <c r="C44" s="123"/>
-      <c r="D44" s="105"/>
-      <c r="E44" s="106"/>
-      <c r="F44" s="106"/>
-      <c r="G44" s="107"/>
-      <c r="H44" s="137"/>
-      <c r="I44" s="122"/>
-      <c r="J44" s="123"/>
-      <c r="K44" s="105"/>
-      <c r="L44" s="106"/>
-      <c r="M44" s="106"/>
-      <c r="N44" s="107"/>
-      <c r="O44" s="114"/>
-      <c r="P44" s="114"/>
-      <c r="Q44" s="114"/>
-      <c r="R44" s="115"/>
+      <c r="A44" s="30"/>
+      <c r="B44" s="31"/>
+      <c r="C44" s="32"/>
+      <c r="D44" s="58"/>
+      <c r="E44" s="59"/>
+      <c r="F44" s="59"/>
+      <c r="G44" s="60"/>
+      <c r="H44" s="62"/>
+      <c r="I44" s="31"/>
+      <c r="J44" s="32"/>
+      <c r="K44" s="58"/>
+      <c r="L44" s="59"/>
+      <c r="M44" s="59"/>
+      <c r="N44" s="60"/>
+      <c r="O44" s="77"/>
+      <c r="P44" s="77"/>
+      <c r="Q44" s="77"/>
+      <c r="R44" s="78"/>
     </row>
     <row r="45" spans="1:18" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A45" s="134" t="s">
+      <c r="A45" s="53" t="s">
         <v>17</v>
       </c>
-      <c r="B45" s="135"/>
-      <c r="C45" s="135"/>
-      <c r="D45" s="100"/>
-      <c r="E45" s="100"/>
-      <c r="F45" s="100"/>
-      <c r="G45" s="101"/>
-      <c r="H45" s="135" t="s">
+      <c r="B45" s="54"/>
+      <c r="C45" s="54"/>
+      <c r="D45" s="69"/>
+      <c r="E45" s="69"/>
+      <c r="F45" s="69"/>
+      <c r="G45" s="70"/>
+      <c r="H45" s="54" t="s">
         <v>17</v>
       </c>
-      <c r="I45" s="135"/>
-      <c r="J45" s="135"/>
-      <c r="K45" s="100"/>
-      <c r="L45" s="100"/>
-      <c r="M45" s="100"/>
-      <c r="N45" s="101"/>
-      <c r="O45" s="116"/>
-      <c r="P45" s="116"/>
-      <c r="Q45" s="116"/>
-      <c r="R45" s="117"/>
+      <c r="I45" s="54"/>
+      <c r="J45" s="54"/>
+      <c r="K45" s="69"/>
+      <c r="L45" s="69"/>
+      <c r="M45" s="69"/>
+      <c r="N45" s="70"/>
+      <c r="O45" s="79"/>
+      <c r="P45" s="79"/>
+      <c r="Q45" s="79"/>
+      <c r="R45" s="80"/>
     </row>
     <row r="46" spans="1:18" ht="20.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.4"/>
     <row r="47" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -2597,128 +2640,128 @@
       </c>
     </row>
     <row r="49" spans="1:18" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="128"/>
-      <c r="B49" s="129"/>
-      <c r="C49" s="130"/>
-      <c r="D49" s="92"/>
-      <c r="E49" s="93"/>
-      <c r="F49" s="93"/>
-      <c r="G49" s="93"/>
-      <c r="H49" s="98"/>
-      <c r="I49" s="92"/>
-      <c r="J49" s="93"/>
-      <c r="K49" s="93"/>
-      <c r="L49" s="93"/>
-      <c r="M49" s="98"/>
-      <c r="N49" s="92"/>
-      <c r="O49" s="93"/>
-      <c r="P49" s="93"/>
-      <c r="Q49" s="93"/>
-      <c r="R49" s="94"/>
+      <c r="A49" s="41"/>
+      <c r="B49" s="42"/>
+      <c r="C49" s="43"/>
+      <c r="D49" s="47"/>
+      <c r="E49" s="48"/>
+      <c r="F49" s="48"/>
+      <c r="G49" s="48"/>
+      <c r="H49" s="49"/>
+      <c r="I49" s="47"/>
+      <c r="J49" s="48"/>
+      <c r="K49" s="48"/>
+      <c r="L49" s="48"/>
+      <c r="M49" s="49"/>
+      <c r="N49" s="47"/>
+      <c r="O49" s="48"/>
+      <c r="P49" s="48"/>
+      <c r="Q49" s="48"/>
+      <c r="R49" s="67"/>
     </row>
     <row r="50" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="131"/>
-      <c r="B50" s="132"/>
-      <c r="C50" s="133"/>
-      <c r="D50" s="95"/>
-      <c r="E50" s="96"/>
-      <c r="F50" s="96"/>
-      <c r="G50" s="96"/>
-      <c r="H50" s="99"/>
-      <c r="I50" s="95"/>
-      <c r="J50" s="96"/>
-      <c r="K50" s="96"/>
-      <c r="L50" s="96"/>
-      <c r="M50" s="99"/>
-      <c r="N50" s="95"/>
-      <c r="O50" s="96"/>
-      <c r="P50" s="96"/>
-      <c r="Q50" s="96"/>
-      <c r="R50" s="97"/>
+      <c r="A50" s="44"/>
+      <c r="B50" s="45"/>
+      <c r="C50" s="46"/>
+      <c r="D50" s="50"/>
+      <c r="E50" s="51"/>
+      <c r="F50" s="51"/>
+      <c r="G50" s="51"/>
+      <c r="H50" s="52"/>
+      <c r="I50" s="50"/>
+      <c r="J50" s="51"/>
+      <c r="K50" s="51"/>
+      <c r="L50" s="51"/>
+      <c r="M50" s="52"/>
+      <c r="N50" s="50"/>
+      <c r="O50" s="51"/>
+      <c r="P50" s="51"/>
+      <c r="Q50" s="51"/>
+      <c r="R50" s="68"/>
     </row>
     <row r="51" spans="1:18" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A51" s="30" t="s">
+      <c r="A51" s="120" t="s">
         <v>19</v>
       </c>
-      <c r="B51" s="31"/>
-      <c r="C51" s="32"/>
-      <c r="D51" s="28"/>
-      <c r="E51" s="28"/>
-      <c r="F51" s="28"/>
-      <c r="G51" s="28"/>
-      <c r="H51" s="28"/>
-      <c r="I51" s="28"/>
-      <c r="J51" s="28"/>
-      <c r="K51" s="28"/>
-      <c r="L51" s="28"/>
-      <c r="M51" s="28"/>
-      <c r="N51" s="28"/>
-      <c r="O51" s="28"/>
-      <c r="P51" s="28"/>
-      <c r="Q51" s="28"/>
-      <c r="R51" s="29"/>
+      <c r="B51" s="121"/>
+      <c r="C51" s="122"/>
+      <c r="D51" s="83"/>
+      <c r="E51" s="83"/>
+      <c r="F51" s="83"/>
+      <c r="G51" s="83"/>
+      <c r="H51" s="83"/>
+      <c r="I51" s="83"/>
+      <c r="J51" s="83"/>
+      <c r="K51" s="83"/>
+      <c r="L51" s="83"/>
+      <c r="M51" s="83"/>
+      <c r="N51" s="83"/>
+      <c r="O51" s="83"/>
+      <c r="P51" s="83"/>
+      <c r="Q51" s="83"/>
+      <c r="R51" s="119"/>
     </row>
     <row r="52" spans="1:18" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A52" s="33"/>
-      <c r="B52" s="34"/>
-      <c r="C52" s="35"/>
-      <c r="D52" s="28"/>
-      <c r="E52" s="28"/>
-      <c r="F52" s="28"/>
-      <c r="G52" s="28"/>
-      <c r="H52" s="28"/>
-      <c r="I52" s="28"/>
-      <c r="J52" s="28"/>
-      <c r="K52" s="28"/>
-      <c r="L52" s="28"/>
-      <c r="M52" s="28"/>
-      <c r="N52" s="28"/>
-      <c r="O52" s="28"/>
-      <c r="P52" s="28"/>
-      <c r="Q52" s="28"/>
-      <c r="R52" s="29"/>
+      <c r="A52" s="123"/>
+      <c r="B52" s="124"/>
+      <c r="C52" s="125"/>
+      <c r="D52" s="83"/>
+      <c r="E52" s="83"/>
+      <c r="F52" s="83"/>
+      <c r="G52" s="83"/>
+      <c r="H52" s="83"/>
+      <c r="I52" s="83"/>
+      <c r="J52" s="83"/>
+      <c r="K52" s="83"/>
+      <c r="L52" s="83"/>
+      <c r="M52" s="83"/>
+      <c r="N52" s="83"/>
+      <c r="O52" s="83"/>
+      <c r="P52" s="83"/>
+      <c r="Q52" s="83"/>
+      <c r="R52" s="119"/>
     </row>
     <row r="53" spans="1:18" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A53" s="73" t="s">
+      <c r="A53" s="103" t="s">
         <v>20</v>
       </c>
-      <c r="B53" s="74"/>
-      <c r="C53" s="75"/>
-      <c r="D53" s="36"/>
-      <c r="E53" s="36"/>
-      <c r="F53" s="36"/>
-      <c r="G53" s="36"/>
-      <c r="H53" s="36"/>
-      <c r="I53" s="36"/>
-      <c r="J53" s="36"/>
-      <c r="K53" s="36"/>
-      <c r="L53" s="36"/>
-      <c r="M53" s="36"/>
-      <c r="N53" s="36"/>
-      <c r="O53" s="36"/>
-      <c r="P53" s="36"/>
-      <c r="Q53" s="36"/>
-      <c r="R53" s="37"/>
+      <c r="B53" s="104"/>
+      <c r="C53" s="105"/>
+      <c r="D53" s="81"/>
+      <c r="E53" s="81"/>
+      <c r="F53" s="81"/>
+      <c r="G53" s="81"/>
+      <c r="H53" s="81"/>
+      <c r="I53" s="81"/>
+      <c r="J53" s="81"/>
+      <c r="K53" s="81"/>
+      <c r="L53" s="81"/>
+      <c r="M53" s="81"/>
+      <c r="N53" s="81"/>
+      <c r="O53" s="81"/>
+      <c r="P53" s="81"/>
+      <c r="Q53" s="81"/>
+      <c r="R53" s="126"/>
     </row>
     <row r="54" spans="1:18" s="2" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="76"/>
-      <c r="B54" s="77"/>
-      <c r="C54" s="78"/>
-      <c r="D54" s="38"/>
-      <c r="E54" s="38"/>
-      <c r="F54" s="38"/>
-      <c r="G54" s="38"/>
-      <c r="H54" s="38"/>
-      <c r="I54" s="38"/>
-      <c r="J54" s="38"/>
-      <c r="K54" s="38"/>
-      <c r="L54" s="38"/>
-      <c r="M54" s="38"/>
-      <c r="N54" s="38"/>
-      <c r="O54" s="38"/>
-      <c r="P54" s="38"/>
-      <c r="Q54" s="38"/>
-      <c r="R54" s="39"/>
+      <c r="A54" s="106"/>
+      <c r="B54" s="107"/>
+      <c r="C54" s="108"/>
+      <c r="D54" s="82"/>
+      <c r="E54" s="82"/>
+      <c r="F54" s="82"/>
+      <c r="G54" s="82"/>
+      <c r="H54" s="82"/>
+      <c r="I54" s="82"/>
+      <c r="J54" s="82"/>
+      <c r="K54" s="82"/>
+      <c r="L54" s="82"/>
+      <c r="M54" s="82"/>
+      <c r="N54" s="82"/>
+      <c r="O54" s="82"/>
+      <c r="P54" s="82"/>
+      <c r="Q54" s="82"/>
+      <c r="R54" s="127"/>
     </row>
     <row r="55" spans="1:18" s="2" customFormat="1" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.15"/>
     <row r="56" spans="1:18" s="2" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -2733,26 +2776,22 @@
   </sheetData>
   <sheetProtection formatCells="0"/>
   <mergeCells count="52">
-    <mergeCell ref="A43:C44"/>
-    <mergeCell ref="D39:G40"/>
-    <mergeCell ref="D23:L25"/>
-    <mergeCell ref="A49:C50"/>
-    <mergeCell ref="D49:H50"/>
-    <mergeCell ref="A45:C45"/>
-    <mergeCell ref="H45:J45"/>
-    <mergeCell ref="A41:C42"/>
-    <mergeCell ref="D43:G44"/>
-    <mergeCell ref="H43:J44"/>
-    <mergeCell ref="M22:N28"/>
-    <mergeCell ref="N49:R50"/>
-    <mergeCell ref="I49:M50"/>
-    <mergeCell ref="D45:G45"/>
-    <mergeCell ref="D41:G42"/>
-    <mergeCell ref="H41:J42"/>
-    <mergeCell ref="K41:N42"/>
-    <mergeCell ref="O41:R45"/>
-    <mergeCell ref="K43:N44"/>
-    <mergeCell ref="K45:N45"/>
+    <mergeCell ref="O3:R4"/>
+    <mergeCell ref="D51:H52"/>
+    <mergeCell ref="N51:R52"/>
+    <mergeCell ref="A51:C52"/>
+    <mergeCell ref="N53:R54"/>
+    <mergeCell ref="M31:R32"/>
+    <mergeCell ref="M33:R34"/>
+    <mergeCell ref="A33:C34"/>
+    <mergeCell ref="O39:R40"/>
+    <mergeCell ref="A35:C36"/>
+    <mergeCell ref="D33:I34"/>
+    <mergeCell ref="J33:L34"/>
+    <mergeCell ref="D35:R36"/>
+    <mergeCell ref="A31:C32"/>
+    <mergeCell ref="J31:L32"/>
+    <mergeCell ref="D53:H54"/>
     <mergeCell ref="I53:M54"/>
     <mergeCell ref="I51:M52"/>
     <mergeCell ref="O1:R1"/>
@@ -2769,22 +2808,26 @@
     <mergeCell ref="K39:N40"/>
     <mergeCell ref="A53:C54"/>
     <mergeCell ref="O22:R28"/>
-    <mergeCell ref="O3:R4"/>
-    <mergeCell ref="D51:H52"/>
-    <mergeCell ref="N51:R52"/>
-    <mergeCell ref="A51:C52"/>
-    <mergeCell ref="N53:R54"/>
-    <mergeCell ref="M31:R32"/>
-    <mergeCell ref="M33:R34"/>
-    <mergeCell ref="A33:C34"/>
-    <mergeCell ref="O39:R40"/>
-    <mergeCell ref="A35:C36"/>
-    <mergeCell ref="D33:I34"/>
-    <mergeCell ref="J33:L34"/>
-    <mergeCell ref="D35:R36"/>
-    <mergeCell ref="A31:C32"/>
-    <mergeCell ref="J31:L32"/>
-    <mergeCell ref="D53:H54"/>
+    <mergeCell ref="M22:N28"/>
+    <mergeCell ref="N49:R50"/>
+    <mergeCell ref="I49:M50"/>
+    <mergeCell ref="D45:G45"/>
+    <mergeCell ref="D41:G42"/>
+    <mergeCell ref="H41:J42"/>
+    <mergeCell ref="K41:N42"/>
+    <mergeCell ref="O41:R45"/>
+    <mergeCell ref="K43:N44"/>
+    <mergeCell ref="K45:N45"/>
+    <mergeCell ref="A43:C44"/>
+    <mergeCell ref="D39:G40"/>
+    <mergeCell ref="D23:L25"/>
+    <mergeCell ref="A49:C50"/>
+    <mergeCell ref="D49:H50"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="H45:J45"/>
+    <mergeCell ref="A41:C42"/>
+    <mergeCell ref="D43:G44"/>
+    <mergeCell ref="H43:J44"/>
   </mergeCells>
   <phoneticPr fontId="20"/>
   <printOptions horizontalCentered="1"/>
@@ -2812,62 +2855,62 @@
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="140" t="s">
+      <c r="E2" s="148" t="s">
         <v>22</v>
       </c>
-      <c r="F2" s="140"/>
-      <c r="G2" s="140" t="s">
+      <c r="F2" s="148"/>
+      <c r="G2" s="148" t="s">
         <v>23</v>
       </c>
-      <c r="H2" s="140"/>
-      <c r="I2" s="140" t="s">
+      <c r="H2" s="148"/>
+      <c r="I2" s="148" t="s">
         <v>24</v>
       </c>
-      <c r="J2" s="140"/>
-      <c r="K2" s="140" t="s">
+      <c r="J2" s="148"/>
+      <c r="K2" s="148" t="s">
         <v>25</v>
       </c>
-      <c r="L2" s="140"/>
-      <c r="M2" s="140" t="s">
+      <c r="L2" s="148"/>
+      <c r="M2" s="148" t="s">
         <v>26</v>
       </c>
-      <c r="N2" s="140"/>
+      <c r="N2" s="148"/>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B3" s="138" t="s">
+      <c r="B3" s="145" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="138"/>
+      <c r="C3" s="145"/>
       <c r="D3" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="138"/>
-      <c r="F3" s="138"/>
-      <c r="G3" s="139"/>
-      <c r="H3" s="139"/>
-      <c r="I3" s="138"/>
-      <c r="J3" s="138"/>
-      <c r="K3" s="138"/>
-      <c r="L3" s="138"/>
-      <c r="M3" s="138"/>
-      <c r="N3" s="138"/>
+      <c r="E3" s="145"/>
+      <c r="F3" s="145"/>
+      <c r="G3" s="149"/>
+      <c r="H3" s="149"/>
+      <c r="I3" s="145"/>
+      <c r="J3" s="145"/>
+      <c r="K3" s="145"/>
+      <c r="L3" s="145"/>
+      <c r="M3" s="145"/>
+      <c r="N3" s="145"/>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B4" s="138"/>
-      <c r="C4" s="138"/>
+      <c r="B4" s="145"/>
+      <c r="C4" s="145"/>
       <c r="D4" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="E4" s="138"/>
-      <c r="F4" s="138"/>
-      <c r="G4" s="138"/>
-      <c r="H4" s="138"/>
-      <c r="I4" s="138"/>
-      <c r="J4" s="138"/>
-      <c r="K4" s="138"/>
-      <c r="L4" s="138"/>
-      <c r="M4" s="138"/>
-      <c r="N4" s="138"/>
+      <c r="E4" s="145"/>
+      <c r="F4" s="145"/>
+      <c r="G4" s="145"/>
+      <c r="H4" s="145"/>
+      <c r="I4" s="145"/>
+      <c r="J4" s="145"/>
+      <c r="K4" s="145"/>
+      <c r="L4" s="145"/>
+      <c r="M4" s="145"/>
+      <c r="N4" s="145"/>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B5" s="1"/>
@@ -2888,39 +2931,39 @@
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
-      <c r="E6" s="145" t="s">
+      <c r="E6" s="143" t="s">
         <v>22</v>
       </c>
-      <c r="F6" s="146"/>
-      <c r="G6" s="145" t="s">
+      <c r="F6" s="144"/>
+      <c r="G6" s="143" t="s">
         <v>23</v>
       </c>
-      <c r="H6" s="146"/>
-      <c r="I6" s="145" t="s">
+      <c r="H6" s="144"/>
+      <c r="I6" s="143" t="s">
         <v>24</v>
       </c>
-      <c r="J6" s="146"/>
-      <c r="K6" s="145" t="s">
+      <c r="J6" s="144"/>
+      <c r="K6" s="143" t="s">
         <v>25</v>
       </c>
-      <c r="L6" s="146"/>
-      <c r="M6" s="145" t="s">
+      <c r="L6" s="144"/>
+      <c r="M6" s="143" t="s">
         <v>26</v>
       </c>
-      <c r="N6" s="146"/>
+      <c r="N6" s="144"/>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B7" s="138" t="s">
+      <c r="B7" s="145" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="138"/>
+      <c r="C7" s="145"/>
       <c r="D7" s="26" t="s">
         <v>28</v>
       </c>
       <c r="E7" s="141"/>
       <c r="F7" s="142"/>
-      <c r="G7" s="143"/>
-      <c r="H7" s="144"/>
+      <c r="G7" s="146"/>
+      <c r="H7" s="147"/>
       <c r="I7" s="141"/>
       <c r="J7" s="142"/>
       <c r="K7" s="141"/>
@@ -2929,8 +2972,8 @@
       <c r="N7" s="142"/>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B8" s="138"/>
-      <c r="C8" s="138"/>
+      <c r="B8" s="145"/>
+      <c r="C8" s="145"/>
       <c r="D8" s="26" t="s">
         <v>29</v>
       </c>
@@ -2964,39 +3007,39 @@
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
-      <c r="E10" s="145" t="s">
+      <c r="E10" s="143" t="s">
         <v>22</v>
       </c>
-      <c r="F10" s="146"/>
-      <c r="G10" s="145" t="s">
+      <c r="F10" s="144"/>
+      <c r="G10" s="143" t="s">
         <v>23</v>
       </c>
-      <c r="H10" s="146"/>
-      <c r="I10" s="145" t="s">
+      <c r="H10" s="144"/>
+      <c r="I10" s="143" t="s">
         <v>24</v>
       </c>
-      <c r="J10" s="146"/>
-      <c r="K10" s="145" t="s">
+      <c r="J10" s="144"/>
+      <c r="K10" s="143" t="s">
         <v>25</v>
       </c>
-      <c r="L10" s="146"/>
-      <c r="M10" s="145" t="s">
+      <c r="L10" s="144"/>
+      <c r="M10" s="143" t="s">
         <v>26</v>
       </c>
-      <c r="N10" s="146"/>
+      <c r="N10" s="144"/>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B11" s="138" t="s">
+      <c r="B11" s="145" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="138"/>
+      <c r="C11" s="145"/>
       <c r="D11" s="26" t="s">
         <v>28</v>
       </c>
       <c r="E11" s="141"/>
       <c r="F11" s="142"/>
-      <c r="G11" s="143"/>
-      <c r="H11" s="144"/>
+      <c r="G11" s="146"/>
+      <c r="H11" s="147"/>
       <c r="I11" s="141"/>
       <c r="J11" s="142"/>
       <c r="K11" s="141"/>
@@ -3005,8 +3048,8 @@
       <c r="N11" s="142"/>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B12" s="138"/>
-      <c r="C12" s="138"/>
+      <c r="B12" s="145"/>
+      <c r="C12" s="145"/>
       <c r="D12" s="26" t="s">
         <v>29</v>
       </c>
@@ -3055,39 +3098,39 @@
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
-      <c r="E15" s="145" t="s">
+      <c r="E15" s="143" t="s">
         <v>22</v>
       </c>
-      <c r="F15" s="146"/>
-      <c r="G15" s="145" t="s">
+      <c r="F15" s="144"/>
+      <c r="G15" s="143" t="s">
         <v>23</v>
       </c>
-      <c r="H15" s="146"/>
-      <c r="I15" s="145" t="s">
+      <c r="H15" s="144"/>
+      <c r="I15" s="143" t="s">
         <v>24</v>
       </c>
-      <c r="J15" s="146"/>
-      <c r="K15" s="145" t="s">
+      <c r="J15" s="144"/>
+      <c r="K15" s="143" t="s">
         <v>25</v>
       </c>
-      <c r="L15" s="146"/>
-      <c r="M15" s="145" t="s">
+      <c r="L15" s="144"/>
+      <c r="M15" s="143" t="s">
         <v>26</v>
       </c>
-      <c r="N15" s="146"/>
+      <c r="N15" s="144"/>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B16" s="138" t="s">
+      <c r="B16" s="145" t="s">
         <v>32</v>
       </c>
-      <c r="C16" s="138"/>
+      <c r="C16" s="145"/>
       <c r="D16" s="26" t="s">
         <v>28</v>
       </c>
       <c r="E16" s="141"/>
       <c r="F16" s="142"/>
-      <c r="G16" s="143"/>
-      <c r="H16" s="144"/>
+      <c r="G16" s="146"/>
+      <c r="H16" s="147"/>
       <c r="I16" s="141"/>
       <c r="J16" s="142"/>
       <c r="K16" s="141"/>
@@ -3096,8 +3139,8 @@
       <c r="N16" s="142"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B17" s="138"/>
-      <c r="C17" s="138"/>
+      <c r="B17" s="145"/>
+      <c r="C17" s="145"/>
       <c r="D17" s="26" t="s">
         <v>29</v>
       </c>
@@ -3113,106 +3156,227 @@
       <c r="N17" s="142"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B20" s="147"/>
-      <c r="C20" s="147"/>
-      <c r="D20" s="147"/>
-      <c r="E20" s="147" t="s">
+      <c r="B20" s="138"/>
+      <c r="C20" s="138"/>
+      <c r="D20" s="138"/>
+      <c r="E20" s="138" t="s">
         <v>33</v>
       </c>
-      <c r="F20" s="147"/>
+      <c r="F20" s="138"/>
+      <c r="I20" s="138"/>
+      <c r="J20" s="138"/>
+      <c r="K20" s="138"/>
+      <c r="L20" s="138" t="s">
+        <v>33</v>
+      </c>
+      <c r="M20" s="138"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B21" s="147" t="s">
+      <c r="B21" s="138" t="s">
         <v>34</v>
       </c>
-      <c r="C21" s="147"/>
-      <c r="D21" s="147"/>
-      <c r="E21" s="148"/>
-      <c r="F21" s="148"/>
+      <c r="C21" s="138"/>
+      <c r="D21" s="138"/>
+      <c r="E21" s="139"/>
+      <c r="F21" s="139"/>
+      <c r="I21" s="138" t="s">
+        <v>44</v>
+      </c>
+      <c r="J21" s="138"/>
+      <c r="K21" s="138"/>
+      <c r="L21" s="139"/>
+      <c r="M21" s="139"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B22" s="147" t="s">
+      <c r="B22" s="138" t="s">
         <v>35</v>
       </c>
-      <c r="C22" s="147"/>
-      <c r="D22" s="147"/>
-      <c r="E22" s="148"/>
-      <c r="F22" s="148"/>
+      <c r="C22" s="138"/>
+      <c r="D22" s="138"/>
+      <c r="E22" s="139"/>
+      <c r="F22" s="139"/>
+      <c r="I22" s="138" t="s">
+        <v>45</v>
+      </c>
+      <c r="J22" s="138"/>
+      <c r="K22" s="138"/>
+      <c r="L22" s="139"/>
+      <c r="M22" s="139"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B23" s="147" t="s">
+      <c r="B23" s="138" t="s">
         <v>36</v>
       </c>
-      <c r="C23" s="147"/>
-      <c r="D23" s="147"/>
-      <c r="E23" s="148"/>
-      <c r="F23" s="148"/>
+      <c r="C23" s="138"/>
+      <c r="D23" s="138"/>
+      <c r="E23" s="139"/>
+      <c r="F23" s="139"/>
+      <c r="I23" s="138" t="s">
+        <v>46</v>
+      </c>
+      <c r="J23" s="138"/>
+      <c r="K23" s="138"/>
+      <c r="L23" s="139"/>
+      <c r="M23" s="139"/>
     </row>
     <row r="24" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B24" s="147" t="s">
+      <c r="B24" s="138" t="s">
         <v>37</v>
       </c>
-      <c r="C24" s="147"/>
-      <c r="D24" s="147"/>
-      <c r="E24" s="148"/>
-      <c r="F24" s="148"/>
+      <c r="C24" s="138"/>
+      <c r="D24" s="138"/>
+      <c r="E24" s="139"/>
+      <c r="F24" s="139"/>
+      <c r="I24" s="138" t="s">
+        <v>47</v>
+      </c>
+      <c r="J24" s="138"/>
+      <c r="K24" s="138"/>
+      <c r="L24" s="139"/>
+      <c r="M24" s="139"/>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B25" s="147" t="s">
+      <c r="B25" s="138" t="s">
         <v>38</v>
       </c>
-      <c r="C25" s="147"/>
-      <c r="D25" s="147"/>
-      <c r="E25" s="148"/>
-      <c r="F25" s="148"/>
+      <c r="C25" s="138"/>
+      <c r="D25" s="138"/>
+      <c r="E25" s="139"/>
+      <c r="F25" s="139"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B26" s="147" t="s">
+      <c r="B26" s="138" t="s">
         <v>39</v>
       </c>
-      <c r="C26" s="147"/>
-      <c r="D26" s="147"/>
-      <c r="E26" s="148"/>
-      <c r="F26" s="148"/>
+      <c r="C26" s="138"/>
+      <c r="D26" s="138"/>
+      <c r="E26" s="139"/>
+      <c r="F26" s="139"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B27" s="147" t="s">
+      <c r="B27" s="138" t="s">
         <v>40</v>
       </c>
-      <c r="C27" s="147"/>
-      <c r="D27" s="147"/>
-      <c r="E27" s="149"/>
-      <c r="F27" s="149"/>
+      <c r="C27" s="138"/>
+      <c r="D27" s="138"/>
+      <c r="E27" s="140"/>
+      <c r="F27" s="140"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B28" s="147" t="s">
+      <c r="B28" s="138" t="s">
         <v>41</v>
       </c>
-      <c r="C28" s="147"/>
-      <c r="D28" s="147"/>
-      <c r="E28" s="148"/>
-      <c r="F28" s="148"/>
+      <c r="C28" s="138"/>
+      <c r="D28" s="138"/>
+      <c r="E28" s="139"/>
+      <c r="F28" s="139"/>
     </row>
     <row r="29" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B29" s="147" t="s">
+      <c r="B29" s="138" t="s">
         <v>42</v>
       </c>
-      <c r="C29" s="147"/>
-      <c r="D29" s="147"/>
-      <c r="E29" s="148"/>
-      <c r="F29" s="148"/>
+      <c r="C29" s="138"/>
+      <c r="D29" s="138"/>
+      <c r="E29" s="139"/>
+      <c r="F29" s="139"/>
     </row>
     <row r="30" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B30" s="147" t="s">
+      <c r="B30" s="138" t="s">
         <v>43</v>
       </c>
-      <c r="C30" s="147"/>
-      <c r="D30" s="147"/>
-      <c r="E30" s="148"/>
-      <c r="F30" s="148"/>
+      <c r="C30" s="138"/>
+      <c r="D30" s="138"/>
+      <c r="E30" s="139"/>
+      <c r="F30" s="139"/>
     </row>
   </sheetData>
-  <mergeCells count="86">
+  <mergeCells count="96">
+    <mergeCell ref="I23:K23"/>
+    <mergeCell ref="L23:M23"/>
+    <mergeCell ref="I24:K24"/>
+    <mergeCell ref="L24:M24"/>
+    <mergeCell ref="I20:K20"/>
+    <mergeCell ref="L20:M20"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="L21:M21"/>
+    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="L22:M22"/>
+    <mergeCell ref="B3:C4"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="B7:C8"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="M8:N8"/>
+    <mergeCell ref="B11:C12"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="B16:C17"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="K16:L16"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="E25:F25"/>
     <mergeCell ref="B30:D30"/>
     <mergeCell ref="E30:F30"/>
     <mergeCell ref="B29:D29"/>
@@ -3223,82 +3387,6 @@
     <mergeCell ref="E27:F27"/>
     <mergeCell ref="B28:D28"/>
     <mergeCell ref="E28:F28"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="K15:L15"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="B16:C17"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="K16:L16"/>
-    <mergeCell ref="M11:N11"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="M10:N10"/>
-    <mergeCell ref="B11:C12"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="M7:N7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="M8:N8"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="B7:C8"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="B3:C4"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="K3:L3"/>
   </mergeCells>
   <phoneticPr fontId="20"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/storage/app/estimateTemplate/comprehensiveOfRecommend.xlsx
+++ b/storage/app/estimateTemplate/comprehensiveOfRecommend.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\192.168.100.1\エルフル事務局\yokoyama\火災見積システム(mitumo)\新mitumo\見積書Excelテンプレート\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yokoyama\Desktop\修正用ふぉうるだ\estimateTemplate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72482295-0CEA-42C7-90FB-7D7865C33016}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CA21EE4-39BA-4086-BA9D-18597BBF6294}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{0E9C5CA5-184F-4C06-AA15-1AF55B55AFB9}"/>
+    <workbookView xWindow="28680" yWindow="-75" windowWidth="29040" windowHeight="15720" xr2:uid="{0E9C5CA5-184F-4C06-AA15-1AF55B55AFB9}"/>
   </bookViews>
   <sheets>
     <sheet name="おすすめ(総合)" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="47">
   <si>
     <t>御　　見　　積　　書</t>
     <rPh sb="0" eb="1">
@@ -136,19 +136,6 @@
     </rPh>
     <rPh sb="2" eb="4">
       <t>ホウホウ</t>
-    </rPh>
-    <phoneticPr fontId="5"/>
-  </si>
-  <si>
-    <t>地域（等地）</t>
-    <rPh sb="0" eb="2">
-      <t>チイキ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>トウ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>チ</t>
     </rPh>
     <phoneticPr fontId="5"/>
   </si>
@@ -1142,7 +1129,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="6" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="150">
+  <cellXfs count="156">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1221,175 +1208,97 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="18" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="18" fillId="0" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="9" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="9" fillId="0" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="9" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="9" fillId="0" borderId="29" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="24" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="26" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="8" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="28" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="16" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="16" fillId="0" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="16" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="16" fillId="0" borderId="29" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="9" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="9" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="58" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -1399,18 +1308,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -1435,12 +1332,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1450,6 +1341,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="2" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1495,65 +1392,155 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="181" fontId="9" fillId="0" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="9" fillId="0" borderId="29" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="24" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="26" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="8" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="28" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="16" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="16" fillId="0" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="16" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="16" fillId="0" borderId="29" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1561,34 +1548,52 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="35" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="33" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="34" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="33" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="34" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="35" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1967,10 +1972,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="O1" s="84"/>
-      <c r="P1" s="84"/>
-      <c r="Q1" s="84"/>
-      <c r="R1" s="84"/>
+      <c r="O1" s="58"/>
+      <c r="P1" s="58"/>
+      <c r="Q1" s="58"/>
+      <c r="R1" s="58"/>
     </row>
     <row r="2" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="O2" s="25"/>
@@ -1980,16 +1985,16 @@
     </row>
     <row r="3" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A3" s="3"/>
-      <c r="O3" s="118"/>
-      <c r="P3" s="118"/>
-      <c r="Q3" s="118"/>
-      <c r="R3" s="118"/>
+      <c r="O3" s="27"/>
+      <c r="P3" s="27"/>
+      <c r="Q3" s="27"/>
+      <c r="R3" s="27"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="O4" s="118"/>
-      <c r="P4" s="118"/>
-      <c r="Q4" s="118"/>
-      <c r="R4" s="118"/>
+      <c r="O4" s="27"/>
+      <c r="P4" s="27"/>
+      <c r="Q4" s="27"/>
+      <c r="R4" s="27"/>
     </row>
     <row r="5" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="N5" s="24"/>
@@ -2052,196 +2057,196 @@
       <c r="R10" s="20"/>
     </row>
     <row r="11" spans="1:18" ht="21" x14ac:dyDescent="0.4">
-      <c r="A11" s="85" t="s">
+      <c r="A11" s="59" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="85"/>
-      <c r="C11" s="85"/>
-      <c r="D11" s="85"/>
-      <c r="E11" s="85"/>
-      <c r="F11" s="85"/>
-      <c r="G11" s="85"/>
-      <c r="H11" s="85"/>
-      <c r="I11" s="85"/>
-      <c r="J11" s="85"/>
-      <c r="K11" s="85"/>
-      <c r="L11" s="85"/>
-      <c r="M11" s="85"/>
-      <c r="N11" s="85"/>
-      <c r="O11" s="85"/>
-      <c r="P11" s="85"/>
-      <c r="Q11" s="85"/>
-      <c r="R11" s="85"/>
+      <c r="B11" s="59"/>
+      <c r="C11" s="59"/>
+      <c r="D11" s="59"/>
+      <c r="E11" s="59"/>
+      <c r="F11" s="59"/>
+      <c r="G11" s="59"/>
+      <c r="H11" s="59"/>
+      <c r="I11" s="59"/>
+      <c r="J11" s="59"/>
+      <c r="K11" s="59"/>
+      <c r="L11" s="59"/>
+      <c r="M11" s="59"/>
+      <c r="N11" s="59"/>
+      <c r="O11" s="59"/>
+      <c r="P11" s="59"/>
+      <c r="Q11" s="59"/>
+      <c r="R11" s="59"/>
     </row>
     <row r="14" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="15" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
-      <c r="A15" s="96" t="s">
+      <c r="A15" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="B15" s="96"/>
-      <c r="C15" s="96"/>
-      <c r="D15" s="96"/>
-      <c r="E15" s="96"/>
-      <c r="F15" s="96"/>
-      <c r="G15" s="96"/>
-      <c r="H15" s="96"/>
-      <c r="I15" s="96"/>
-      <c r="J15" s="96"/>
-      <c r="K15" s="96"/>
-      <c r="L15" s="96"/>
-      <c r="M15" s="96"/>
-      <c r="N15" s="96"/>
-      <c r="O15" s="96"/>
-      <c r="P15" s="96"/>
-      <c r="Q15" s="96"/>
-      <c r="R15" s="96"/>
+      <c r="B15" s="66"/>
+      <c r="C15" s="66"/>
+      <c r="D15" s="66"/>
+      <c r="E15" s="66"/>
+      <c r="F15" s="66"/>
+      <c r="G15" s="66"/>
+      <c r="H15" s="66"/>
+      <c r="I15" s="66"/>
+      <c r="J15" s="66"/>
+      <c r="K15" s="66"/>
+      <c r="L15" s="66"/>
+      <c r="M15" s="66"/>
+      <c r="N15" s="66"/>
+      <c r="O15" s="66"/>
+      <c r="P15" s="66"/>
+      <c r="Q15" s="66"/>
+      <c r="R15" s="66"/>
     </row>
     <row r="18" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
-      <c r="A18" s="97" t="s">
+      <c r="A18" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="B18" s="97"/>
-      <c r="C18" s="97"/>
-      <c r="D18" s="97"/>
-      <c r="E18" s="97"/>
-      <c r="F18" s="97"/>
-      <c r="G18" s="97"/>
-      <c r="H18" s="97"/>
-      <c r="I18" s="97"/>
-      <c r="J18" s="97"/>
-      <c r="K18" s="97"/>
-      <c r="L18" s="97"/>
-      <c r="M18" s="97"/>
-      <c r="N18" s="97"/>
-      <c r="O18" s="97"/>
-      <c r="P18" s="97"/>
-      <c r="Q18" s="97"/>
-      <c r="R18" s="97"/>
+      <c r="B18" s="67"/>
+      <c r="C18" s="67"/>
+      <c r="D18" s="67"/>
+      <c r="E18" s="67"/>
+      <c r="F18" s="67"/>
+      <c r="G18" s="67"/>
+      <c r="H18" s="67"/>
+      <c r="I18" s="67"/>
+      <c r="J18" s="67"/>
+      <c r="K18" s="67"/>
+      <c r="L18" s="67"/>
+      <c r="M18" s="67"/>
+      <c r="N18" s="67"/>
+      <c r="O18" s="67"/>
+      <c r="P18" s="67"/>
+      <c r="Q18" s="67"/>
+      <c r="R18" s="67"/>
     </row>
     <row r="19" spans="1:18" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="20" spans="1:18" ht="12.75" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="89" t="s">
+      <c r="A20" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="B20" s="33"/>
-      <c r="C20" s="33"/>
-      <c r="D20" s="90"/>
-      <c r="E20" s="91"/>
-      <c r="F20" s="91"/>
-      <c r="G20" s="91"/>
-      <c r="H20" s="91"/>
-      <c r="I20" s="91"/>
-      <c r="J20" s="91"/>
-      <c r="K20" s="91"/>
-      <c r="L20" s="91"/>
-      <c r="M20" s="91"/>
-      <c r="N20" s="91"/>
-      <c r="O20" s="91"/>
-      <c r="P20" s="91"/>
-      <c r="Q20" s="91"/>
-      <c r="R20" s="92"/>
+      <c r="B20" s="46"/>
+      <c r="C20" s="46"/>
+      <c r="D20" s="60"/>
+      <c r="E20" s="61"/>
+      <c r="F20" s="61"/>
+      <c r="G20" s="61"/>
+      <c r="H20" s="61"/>
+      <c r="I20" s="61"/>
+      <c r="J20" s="61"/>
+      <c r="K20" s="61"/>
+      <c r="L20" s="61"/>
+      <c r="M20" s="61"/>
+      <c r="N20" s="61"/>
+      <c r="O20" s="61"/>
+      <c r="P20" s="61"/>
+      <c r="Q20" s="61"/>
+      <c r="R20" s="62"/>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A21" s="86"/>
-      <c r="B21" s="35"/>
-      <c r="C21" s="35"/>
-      <c r="D21" s="93"/>
-      <c r="E21" s="94"/>
-      <c r="F21" s="94"/>
-      <c r="G21" s="94"/>
-      <c r="H21" s="94"/>
-      <c r="I21" s="94"/>
-      <c r="J21" s="94"/>
-      <c r="K21" s="94"/>
-      <c r="L21" s="94"/>
-      <c r="M21" s="94"/>
-      <c r="N21" s="94"/>
-      <c r="O21" s="94"/>
-      <c r="P21" s="94"/>
-      <c r="Q21" s="94"/>
-      <c r="R21" s="95"/>
+      <c r="A21" s="44"/>
+      <c r="B21" s="45"/>
+      <c r="C21" s="45"/>
+      <c r="D21" s="63"/>
+      <c r="E21" s="64"/>
+      <c r="F21" s="64"/>
+      <c r="G21" s="64"/>
+      <c r="H21" s="64"/>
+      <c r="I21" s="64"/>
+      <c r="J21" s="64"/>
+      <c r="K21" s="64"/>
+      <c r="L21" s="64"/>
+      <c r="M21" s="64"/>
+      <c r="N21" s="64"/>
+      <c r="O21" s="64"/>
+      <c r="P21" s="64"/>
+      <c r="Q21" s="64"/>
+      <c r="R21" s="65"/>
     </row>
     <row r="22" spans="1:18" ht="5.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="86" t="s">
+      <c r="A22" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="B22" s="35"/>
-      <c r="C22" s="35"/>
+      <c r="B22" s="45"/>
+      <c r="C22" s="45"/>
       <c r="D22" s="19"/>
       <c r="L22" s="18"/>
-      <c r="M22" s="63" t="s">
+      <c r="M22" s="88" t="s">
         <v>5</v>
       </c>
-      <c r="N22" s="64"/>
-      <c r="O22" s="109"/>
-      <c r="P22" s="110"/>
-      <c r="Q22" s="110"/>
-      <c r="R22" s="111"/>
+      <c r="N22" s="89"/>
+      <c r="O22" s="79"/>
+      <c r="P22" s="80"/>
+      <c r="Q22" s="80"/>
+      <c r="R22" s="81"/>
     </row>
     <row r="23" spans="1:18" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="86"/>
-      <c r="B23" s="35"/>
-      <c r="C23" s="35"/>
-      <c r="D23" s="37"/>
-      <c r="E23" s="38"/>
-      <c r="F23" s="38"/>
-      <c r="G23" s="38"/>
-      <c r="H23" s="38"/>
-      <c r="I23" s="38"/>
-      <c r="J23" s="38"/>
-      <c r="K23" s="38"/>
-      <c r="L23" s="39"/>
-      <c r="M23" s="63"/>
-      <c r="N23" s="64"/>
-      <c r="O23" s="112"/>
-      <c r="P23" s="113"/>
-      <c r="Q23" s="113"/>
-      <c r="R23" s="114"/>
+      <c r="A23" s="44"/>
+      <c r="B23" s="45"/>
+      <c r="C23" s="45"/>
+      <c r="D23" s="124"/>
+      <c r="E23" s="125"/>
+      <c r="F23" s="125"/>
+      <c r="G23" s="125"/>
+      <c r="H23" s="125"/>
+      <c r="I23" s="125"/>
+      <c r="J23" s="125"/>
+      <c r="K23" s="125"/>
+      <c r="L23" s="126"/>
+      <c r="M23" s="88"/>
+      <c r="N23" s="89"/>
+      <c r="O23" s="82"/>
+      <c r="P23" s="83"/>
+      <c r="Q23" s="83"/>
+      <c r="R23" s="84"/>
     </row>
     <row r="24" spans="1:18" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="86"/>
-      <c r="B24" s="35"/>
-      <c r="C24" s="35"/>
-      <c r="D24" s="40"/>
-      <c r="E24" s="38"/>
-      <c r="F24" s="38"/>
-      <c r="G24" s="38"/>
-      <c r="H24" s="38"/>
-      <c r="I24" s="38"/>
-      <c r="J24" s="38"/>
-      <c r="K24" s="38"/>
-      <c r="L24" s="39"/>
-      <c r="M24" s="63"/>
-      <c r="N24" s="64"/>
-      <c r="O24" s="112"/>
-      <c r="P24" s="113"/>
-      <c r="Q24" s="113"/>
-      <c r="R24" s="114"/>
+      <c r="A24" s="44"/>
+      <c r="B24" s="45"/>
+      <c r="C24" s="45"/>
+      <c r="D24" s="127"/>
+      <c r="E24" s="125"/>
+      <c r="F24" s="125"/>
+      <c r="G24" s="125"/>
+      <c r="H24" s="125"/>
+      <c r="I24" s="125"/>
+      <c r="J24" s="125"/>
+      <c r="K24" s="125"/>
+      <c r="L24" s="126"/>
+      <c r="M24" s="88"/>
+      <c r="N24" s="89"/>
+      <c r="O24" s="82"/>
+      <c r="P24" s="83"/>
+      <c r="Q24" s="83"/>
+      <c r="R24" s="84"/>
     </row>
     <row r="25" spans="1:18" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="86"/>
-      <c r="B25" s="35"/>
-      <c r="C25" s="35"/>
-      <c r="D25" s="40"/>
-      <c r="E25" s="38"/>
-      <c r="F25" s="38"/>
-      <c r="G25" s="38"/>
-      <c r="H25" s="38"/>
-      <c r="I25" s="38"/>
-      <c r="J25" s="38"/>
-      <c r="K25" s="38"/>
-      <c r="L25" s="39"/>
-      <c r="M25" s="63"/>
-      <c r="N25" s="64"/>
-      <c r="O25" s="112"/>
-      <c r="P25" s="113"/>
-      <c r="Q25" s="113"/>
-      <c r="R25" s="114"/>
+      <c r="A25" s="44"/>
+      <c r="B25" s="45"/>
+      <c r="C25" s="45"/>
+      <c r="D25" s="127"/>
+      <c r="E25" s="125"/>
+      <c r="F25" s="125"/>
+      <c r="G25" s="125"/>
+      <c r="H25" s="125"/>
+      <c r="I25" s="125"/>
+      <c r="J25" s="125"/>
+      <c r="K25" s="125"/>
+      <c r="L25" s="126"/>
+      <c r="M25" s="88"/>
+      <c r="N25" s="89"/>
+      <c r="O25" s="82"/>
+      <c r="P25" s="83"/>
+      <c r="Q25" s="83"/>
+      <c r="R25" s="84"/>
     </row>
     <row r="26" spans="1:18" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="86"/>
-      <c r="B26" s="35"/>
-      <c r="C26" s="35"/>
+      <c r="A26" s="44"/>
+      <c r="B26" s="45"/>
+      <c r="C26" s="45"/>
       <c r="D26" s="17"/>
       <c r="E26" s="16"/>
       <c r="F26" s="15"/>
@@ -2251,17 +2256,17 @@
       <c r="J26" s="14"/>
       <c r="K26" s="14"/>
       <c r="L26" s="13"/>
-      <c r="M26" s="63"/>
-      <c r="N26" s="64"/>
-      <c r="O26" s="112"/>
-      <c r="P26" s="113"/>
-      <c r="Q26" s="113"/>
-      <c r="R26" s="114"/>
+      <c r="M26" s="88"/>
+      <c r="N26" s="89"/>
+      <c r="O26" s="82"/>
+      <c r="P26" s="83"/>
+      <c r="Q26" s="83"/>
+      <c r="R26" s="84"/>
     </row>
     <row r="27" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="86"/>
-      <c r="B27" s="35"/>
-      <c r="C27" s="35"/>
+      <c r="A27" s="44"/>
+      <c r="B27" s="45"/>
+      <c r="C27" s="45"/>
       <c r="D27" s="12"/>
       <c r="F27" s="10"/>
       <c r="G27" s="11"/>
@@ -2269,17 +2274,17 @@
       <c r="I27" s="9"/>
       <c r="J27" s="9"/>
       <c r="L27" s="8"/>
-      <c r="M27" s="63"/>
-      <c r="N27" s="64"/>
-      <c r="O27" s="112"/>
-      <c r="P27" s="113"/>
-      <c r="Q27" s="113"/>
-      <c r="R27" s="114"/>
+      <c r="M27" s="88"/>
+      <c r="N27" s="89"/>
+      <c r="O27" s="82"/>
+      <c r="P27" s="83"/>
+      <c r="Q27" s="83"/>
+      <c r="R27" s="84"/>
     </row>
     <row r="28" spans="1:18" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="87"/>
-      <c r="B28" s="88"/>
-      <c r="C28" s="88"/>
+      <c r="A28" s="49"/>
+      <c r="B28" s="50"/>
+      <c r="C28" s="50"/>
       <c r="D28" s="7"/>
       <c r="E28" s="6"/>
       <c r="F28" s="6"/>
@@ -2289,346 +2294,344 @@
       <c r="J28" s="6"/>
       <c r="K28" s="6"/>
       <c r="L28" s="5"/>
-      <c r="M28" s="65"/>
-      <c r="N28" s="66"/>
-      <c r="O28" s="115"/>
-      <c r="P28" s="116"/>
-      <c r="Q28" s="116"/>
-      <c r="R28" s="117"/>
+      <c r="M28" s="90"/>
+      <c r="N28" s="91"/>
+      <c r="O28" s="85"/>
+      <c r="P28" s="86"/>
+      <c r="Q28" s="86"/>
+      <c r="R28" s="87"/>
     </row>
     <row r="29" spans="1:18" ht="12.75" thickTop="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="1:18" ht="12.75" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="31" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="89" t="s">
+      <c r="A31" s="57" t="s">
         <v>6</v>
       </c>
-      <c r="B31" s="33"/>
-      <c r="C31" s="33"/>
-      <c r="D31" s="98"/>
-      <c r="E31" s="98"/>
-      <c r="F31" s="98"/>
-      <c r="G31" s="98"/>
-      <c r="H31" s="98"/>
-      <c r="I31" s="98"/>
-      <c r="J31" s="33" t="s">
+      <c r="B31" s="46"/>
+      <c r="C31" s="46"/>
+      <c r="D31" s="40"/>
+      <c r="E31" s="40"/>
+      <c r="F31" s="40"/>
+      <c r="G31" s="40"/>
+      <c r="H31" s="40"/>
+      <c r="I31" s="40"/>
+      <c r="J31" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="K31" s="33"/>
-      <c r="L31" s="33"/>
-      <c r="M31" s="98"/>
-      <c r="N31" s="98"/>
-      <c r="O31" s="98"/>
-      <c r="P31" s="98"/>
-      <c r="Q31" s="98"/>
-      <c r="R31" s="128"/>
+      <c r="K31" s="46"/>
+      <c r="L31" s="46"/>
+      <c r="M31" s="40"/>
+      <c r="N31" s="40"/>
+      <c r="O31" s="40"/>
+      <c r="P31" s="40"/>
+      <c r="Q31" s="40"/>
+      <c r="R31" s="41"/>
     </row>
     <row r="32" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="86"/>
-      <c r="B32" s="35"/>
-      <c r="C32" s="35"/>
-      <c r="D32" s="99"/>
-      <c r="E32" s="99"/>
-      <c r="F32" s="99"/>
-      <c r="G32" s="99"/>
-      <c r="H32" s="99"/>
-      <c r="I32" s="99"/>
-      <c r="J32" s="35"/>
-      <c r="K32" s="35"/>
-      <c r="L32" s="35"/>
-      <c r="M32" s="99"/>
-      <c r="N32" s="99"/>
-      <c r="O32" s="99"/>
-      <c r="P32" s="99"/>
-      <c r="Q32" s="99"/>
-      <c r="R32" s="129"/>
+      <c r="A32" s="44"/>
+      <c r="B32" s="45"/>
+      <c r="C32" s="45"/>
+      <c r="D32" s="42"/>
+      <c r="E32" s="42"/>
+      <c r="F32" s="42"/>
+      <c r="G32" s="42"/>
+      <c r="H32" s="42"/>
+      <c r="I32" s="42"/>
+      <c r="J32" s="45"/>
+      <c r="K32" s="45"/>
+      <c r="L32" s="45"/>
+      <c r="M32" s="42"/>
+      <c r="N32" s="42"/>
+      <c r="O32" s="42"/>
+      <c r="P32" s="42"/>
+      <c r="Q32" s="42"/>
+      <c r="R32" s="43"/>
     </row>
     <row r="33" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="86" t="s">
+      <c r="A33" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="B33" s="35"/>
-      <c r="C33" s="35"/>
-      <c r="D33" s="99"/>
-      <c r="E33" s="99"/>
-      <c r="F33" s="99"/>
-      <c r="G33" s="99"/>
-      <c r="H33" s="99"/>
-      <c r="I33" s="99"/>
-      <c r="J33" s="35" t="s">
+      <c r="B33" s="45"/>
+      <c r="C33" s="45"/>
+      <c r="D33" s="150"/>
+      <c r="E33" s="151"/>
+      <c r="F33" s="151"/>
+      <c r="G33" s="151"/>
+      <c r="H33" s="151"/>
+      <c r="I33" s="151"/>
+      <c r="J33" s="151"/>
+      <c r="K33" s="151"/>
+      <c r="L33" s="151"/>
+      <c r="M33" s="151"/>
+      <c r="N33" s="151"/>
+      <c r="O33" s="151"/>
+      <c r="P33" s="151"/>
+      <c r="Q33" s="151"/>
+      <c r="R33" s="152"/>
+    </row>
+    <row r="34" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A34" s="44"/>
+      <c r="B34" s="45"/>
+      <c r="C34" s="45"/>
+      <c r="D34" s="153"/>
+      <c r="E34" s="154"/>
+      <c r="F34" s="154"/>
+      <c r="G34" s="154"/>
+      <c r="H34" s="154"/>
+      <c r="I34" s="154"/>
+      <c r="J34" s="154"/>
+      <c r="K34" s="154"/>
+      <c r="L34" s="154"/>
+      <c r="M34" s="154"/>
+      <c r="N34" s="154"/>
+      <c r="O34" s="154"/>
+      <c r="P34" s="154"/>
+      <c r="Q34" s="154"/>
+      <c r="R34" s="155"/>
+    </row>
+    <row r="35" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A35" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="K33" s="35"/>
-      <c r="L33" s="35"/>
-      <c r="M33" s="99"/>
-      <c r="N33" s="99"/>
-      <c r="O33" s="99"/>
-      <c r="P33" s="99"/>
-      <c r="Q33" s="99"/>
-      <c r="R33" s="129"/>
-    </row>
-    <row r="34" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="86"/>
-      <c r="B34" s="35"/>
-      <c r="C34" s="35"/>
-      <c r="D34" s="99"/>
-      <c r="E34" s="99"/>
-      <c r="F34" s="99"/>
-      <c r="G34" s="99"/>
-      <c r="H34" s="99"/>
-      <c r="I34" s="99"/>
-      <c r="J34" s="35"/>
-      <c r="K34" s="35"/>
-      <c r="L34" s="35"/>
-      <c r="M34" s="99"/>
-      <c r="N34" s="99"/>
-      <c r="O34" s="99"/>
-      <c r="P34" s="99"/>
-      <c r="Q34" s="99"/>
-      <c r="R34" s="129"/>
-    </row>
-    <row r="35" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="86" t="s">
+      <c r="B35" s="45"/>
+      <c r="C35" s="45"/>
+      <c r="D35" s="51"/>
+      <c r="E35" s="52"/>
+      <c r="F35" s="52"/>
+      <c r="G35" s="52"/>
+      <c r="H35" s="52"/>
+      <c r="I35" s="52"/>
+      <c r="J35" s="52"/>
+      <c r="K35" s="52"/>
+      <c r="L35" s="52"/>
+      <c r="M35" s="52"/>
+      <c r="N35" s="52"/>
+      <c r="O35" s="52"/>
+      <c r="P35" s="52"/>
+      <c r="Q35" s="52"/>
+      <c r="R35" s="53"/>
+    </row>
+    <row r="36" spans="1:18" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A36" s="49"/>
+      <c r="B36" s="50"/>
+      <c r="C36" s="50"/>
+      <c r="D36" s="54"/>
+      <c r="E36" s="55"/>
+      <c r="F36" s="55"/>
+      <c r="G36" s="55"/>
+      <c r="H36" s="55"/>
+      <c r="I36" s="55"/>
+      <c r="J36" s="55"/>
+      <c r="K36" s="55"/>
+      <c r="L36" s="55"/>
+      <c r="M36" s="55"/>
+      <c r="N36" s="55"/>
+      <c r="O36" s="55"/>
+      <c r="P36" s="55"/>
+      <c r="Q36" s="55"/>
+      <c r="R36" s="56"/>
+    </row>
+    <row r="37" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
+      <c r="A37" s="68"/>
+      <c r="B37" s="69"/>
+      <c r="C37" s="69"/>
+      <c r="D37" s="69"/>
+      <c r="E37" s="69"/>
+      <c r="F37" s="69"/>
+      <c r="G37" s="69"/>
+      <c r="H37" s="69"/>
+      <c r="I37" s="69"/>
+      <c r="J37" s="69"/>
+      <c r="K37" s="69"/>
+      <c r="L37" s="69"/>
+      <c r="M37" s="69"/>
+      <c r="N37" s="69"/>
+      <c r="O37" s="69"/>
+      <c r="P37" s="69"/>
+      <c r="Q37" s="69"/>
+      <c r="R37" s="69"/>
+    </row>
+    <row r="38" spans="1:18" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A38" s="70"/>
+      <c r="B38" s="70"/>
+      <c r="C38" s="70"/>
+      <c r="D38" s="70"/>
+      <c r="E38" s="70"/>
+      <c r="F38" s="70"/>
+      <c r="G38" s="70"/>
+      <c r="H38" s="70"/>
+      <c r="I38" s="70"/>
+      <c r="J38" s="70"/>
+      <c r="K38" s="70"/>
+      <c r="L38" s="70"/>
+      <c r="M38" s="70"/>
+      <c r="N38" s="70"/>
+      <c r="O38" s="70"/>
+      <c r="P38" s="70"/>
+      <c r="Q38" s="70"/>
+      <c r="R38" s="70"/>
+    </row>
+    <row r="39" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
+      <c r="A39" s="57" t="s">
         <v>10</v>
       </c>
-      <c r="B35" s="35"/>
-      <c r="C35" s="35"/>
-      <c r="D35" s="132"/>
-      <c r="E35" s="133"/>
-      <c r="F35" s="133"/>
-      <c r="G35" s="133"/>
-      <c r="H35" s="133"/>
-      <c r="I35" s="133"/>
-      <c r="J35" s="133"/>
-      <c r="K35" s="133"/>
-      <c r="L35" s="133"/>
-      <c r="M35" s="133"/>
-      <c r="N35" s="133"/>
-      <c r="O35" s="133"/>
-      <c r="P35" s="133"/>
-      <c r="Q35" s="133"/>
-      <c r="R35" s="134"/>
-    </row>
-    <row r="36" spans="1:18" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A36" s="87"/>
-      <c r="B36" s="88"/>
-      <c r="C36" s="88"/>
-      <c r="D36" s="135"/>
-      <c r="E36" s="136"/>
-      <c r="F36" s="136"/>
-      <c r="G36" s="136"/>
-      <c r="H36" s="136"/>
-      <c r="I36" s="136"/>
-      <c r="J36" s="136"/>
-      <c r="K36" s="136"/>
-      <c r="L36" s="136"/>
-      <c r="M36" s="136"/>
-      <c r="N36" s="136"/>
-      <c r="O36" s="136"/>
-      <c r="P36" s="136"/>
-      <c r="Q36" s="136"/>
-      <c r="R36" s="137"/>
-    </row>
-    <row r="37" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="100"/>
-      <c r="B37" s="101"/>
-      <c r="C37" s="101"/>
-      <c r="D37" s="101"/>
-      <c r="E37" s="101"/>
-      <c r="F37" s="101"/>
-      <c r="G37" s="101"/>
-      <c r="H37" s="101"/>
-      <c r="I37" s="101"/>
-      <c r="J37" s="101"/>
-      <c r="K37" s="101"/>
-      <c r="L37" s="101"/>
-      <c r="M37" s="101"/>
-      <c r="N37" s="101"/>
-      <c r="O37" s="101"/>
-      <c r="P37" s="101"/>
-      <c r="Q37" s="101"/>
-      <c r="R37" s="101"/>
-    </row>
-    <row r="38" spans="1:18" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="102"/>
-      <c r="B38" s="102"/>
-      <c r="C38" s="102"/>
-      <c r="D38" s="102"/>
-      <c r="E38" s="102"/>
-      <c r="F38" s="102"/>
-      <c r="G38" s="102"/>
-      <c r="H38" s="102"/>
-      <c r="I38" s="102"/>
-      <c r="J38" s="102"/>
-      <c r="K38" s="102"/>
-      <c r="L38" s="102"/>
-      <c r="M38" s="102"/>
-      <c r="N38" s="102"/>
-      <c r="O38" s="102"/>
-      <c r="P38" s="102"/>
-      <c r="Q38" s="102"/>
-      <c r="R38" s="102"/>
-    </row>
-    <row r="39" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="89" t="s">
+      <c r="B39" s="46"/>
+      <c r="C39" s="46"/>
+      <c r="D39" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="B39" s="33"/>
-      <c r="C39" s="33"/>
-      <c r="D39" s="33" t="s">
+      <c r="E39" s="46"/>
+      <c r="F39" s="46"/>
+      <c r="G39" s="71"/>
+      <c r="H39" s="46" t="s">
+        <v>10</v>
+      </c>
+      <c r="I39" s="46"/>
+      <c r="J39" s="46"/>
+      <c r="K39" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="L39" s="46"/>
+      <c r="M39" s="46"/>
+      <c r="N39" s="71"/>
+      <c r="O39" s="46" t="s">
+        <v>20</v>
+      </c>
+      <c r="P39" s="46"/>
+      <c r="Q39" s="46"/>
+      <c r="R39" s="47"/>
+    </row>
+    <row r="40" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A40" s="44"/>
+      <c r="B40" s="45"/>
+      <c r="C40" s="45"/>
+      <c r="D40" s="45"/>
+      <c r="E40" s="45"/>
+      <c r="F40" s="45"/>
+      <c r="G40" s="72"/>
+      <c r="H40" s="45"/>
+      <c r="I40" s="45"/>
+      <c r="J40" s="45"/>
+      <c r="K40" s="45"/>
+      <c r="L40" s="45"/>
+      <c r="M40" s="45"/>
+      <c r="N40" s="72"/>
+      <c r="O40" s="45"/>
+      <c r="P40" s="45"/>
+      <c r="Q40" s="45"/>
+      <c r="R40" s="48"/>
+    </row>
+    <row r="41" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A41" s="118" t="s">
         <v>12</v>
       </c>
-      <c r="E39" s="33"/>
-      <c r="F39" s="33"/>
-      <c r="G39" s="34"/>
-      <c r="H39" s="33" t="s">
-        <v>11</v>
-      </c>
-      <c r="I39" s="33"/>
-      <c r="J39" s="33"/>
-      <c r="K39" s="33" t="s">
-        <v>12</v>
-      </c>
-      <c r="L39" s="33"/>
-      <c r="M39" s="33"/>
-      <c r="N39" s="34"/>
-      <c r="O39" s="33" t="s">
-        <v>21</v>
-      </c>
-      <c r="P39" s="33"/>
-      <c r="Q39" s="33"/>
-      <c r="R39" s="130"/>
-    </row>
-    <row r="40" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="86"/>
-      <c r="B40" s="35"/>
-      <c r="C40" s="35"/>
-      <c r="D40" s="35"/>
-      <c r="E40" s="35"/>
-      <c r="F40" s="35"/>
-      <c r="G40" s="36"/>
-      <c r="H40" s="35"/>
-      <c r="I40" s="35"/>
-      <c r="J40" s="35"/>
-      <c r="K40" s="35"/>
-      <c r="L40" s="35"/>
-      <c r="M40" s="35"/>
-      <c r="N40" s="36"/>
-      <c r="O40" s="35"/>
-      <c r="P40" s="35"/>
-      <c r="Q40" s="35"/>
-      <c r="R40" s="131"/>
-    </row>
-    <row r="41" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="27" t="s">
+      <c r="B41" s="119"/>
+      <c r="C41" s="120"/>
+      <c r="D41" s="102"/>
+      <c r="E41" s="103"/>
+      <c r="F41" s="103"/>
+      <c r="G41" s="104"/>
+      <c r="H41" s="108" t="s">
         <v>13</v>
       </c>
-      <c r="B41" s="28"/>
-      <c r="C41" s="29"/>
-      <c r="D41" s="55"/>
-      <c r="E41" s="56"/>
-      <c r="F41" s="56"/>
-      <c r="G41" s="57"/>
-      <c r="H41" s="71" t="s">
+      <c r="I41" s="109"/>
+      <c r="J41" s="110"/>
+      <c r="K41" s="102"/>
+      <c r="L41" s="103"/>
+      <c r="M41" s="103"/>
+      <c r="N41" s="104"/>
+      <c r="O41" s="114"/>
+      <c r="P41" s="114"/>
+      <c r="Q41" s="114"/>
+      <c r="R41" s="115"/>
+    </row>
+    <row r="42" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A42" s="121"/>
+      <c r="B42" s="122"/>
+      <c r="C42" s="123"/>
+      <c r="D42" s="105"/>
+      <c r="E42" s="106"/>
+      <c r="F42" s="106"/>
+      <c r="G42" s="107"/>
+      <c r="H42" s="111"/>
+      <c r="I42" s="112"/>
+      <c r="J42" s="113"/>
+      <c r="K42" s="105"/>
+      <c r="L42" s="106"/>
+      <c r="M42" s="106"/>
+      <c r="N42" s="107"/>
+      <c r="O42" s="114"/>
+      <c r="P42" s="114"/>
+      <c r="Q42" s="114"/>
+      <c r="R42" s="115"/>
+    </row>
+    <row r="43" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A43" s="118" t="s">
         <v>14</v>
       </c>
-      <c r="I41" s="72"/>
-      <c r="J41" s="73"/>
-      <c r="K41" s="55"/>
-      <c r="L41" s="56"/>
-      <c r="M41" s="56"/>
-      <c r="N41" s="57"/>
-      <c r="O41" s="77"/>
-      <c r="P41" s="77"/>
-      <c r="Q41" s="77"/>
-      <c r="R41" s="78"/>
-    </row>
-    <row r="42" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="30"/>
-      <c r="B42" s="31"/>
-      <c r="C42" s="32"/>
-      <c r="D42" s="58"/>
-      <c r="E42" s="59"/>
-      <c r="F42" s="59"/>
-      <c r="G42" s="60"/>
-      <c r="H42" s="74"/>
-      <c r="I42" s="75"/>
-      <c r="J42" s="76"/>
-      <c r="K42" s="58"/>
-      <c r="L42" s="59"/>
-      <c r="M42" s="59"/>
-      <c r="N42" s="60"/>
-      <c r="O42" s="77"/>
-      <c r="P42" s="77"/>
-      <c r="Q42" s="77"/>
-      <c r="R42" s="78"/>
-    </row>
-    <row r="43" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="27" t="s">
+      <c r="B43" s="119"/>
+      <c r="C43" s="120"/>
+      <c r="D43" s="102"/>
+      <c r="E43" s="103"/>
+      <c r="F43" s="103"/>
+      <c r="G43" s="104"/>
+      <c r="H43" s="136" t="s">
         <v>15</v>
       </c>
-      <c r="B43" s="28"/>
-      <c r="C43" s="29"/>
-      <c r="D43" s="55"/>
-      <c r="E43" s="56"/>
-      <c r="F43" s="56"/>
-      <c r="G43" s="57"/>
-      <c r="H43" s="61" t="s">
+      <c r="I43" s="119"/>
+      <c r="J43" s="120"/>
+      <c r="K43" s="102"/>
+      <c r="L43" s="103"/>
+      <c r="M43" s="103"/>
+      <c r="N43" s="104"/>
+      <c r="O43" s="114"/>
+      <c r="P43" s="114"/>
+      <c r="Q43" s="114"/>
+      <c r="R43" s="115"/>
+    </row>
+    <row r="44" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A44" s="121"/>
+      <c r="B44" s="122"/>
+      <c r="C44" s="123"/>
+      <c r="D44" s="105"/>
+      <c r="E44" s="106"/>
+      <c r="F44" s="106"/>
+      <c r="G44" s="107"/>
+      <c r="H44" s="137"/>
+      <c r="I44" s="122"/>
+      <c r="J44" s="123"/>
+      <c r="K44" s="105"/>
+      <c r="L44" s="106"/>
+      <c r="M44" s="106"/>
+      <c r="N44" s="107"/>
+      <c r="O44" s="114"/>
+      <c r="P44" s="114"/>
+      <c r="Q44" s="114"/>
+      <c r="R44" s="115"/>
+    </row>
+    <row r="45" spans="1:18" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A45" s="134" t="s">
         <v>16</v>
       </c>
-      <c r="I43" s="28"/>
-      <c r="J43" s="29"/>
-      <c r="K43" s="55"/>
-      <c r="L43" s="56"/>
-      <c r="M43" s="56"/>
-      <c r="N43" s="57"/>
-      <c r="O43" s="77"/>
-      <c r="P43" s="77"/>
-      <c r="Q43" s="77"/>
-      <c r="R43" s="78"/>
-    </row>
-    <row r="44" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="30"/>
-      <c r="B44" s="31"/>
-      <c r="C44" s="32"/>
-      <c r="D44" s="58"/>
-      <c r="E44" s="59"/>
-      <c r="F44" s="59"/>
-      <c r="G44" s="60"/>
-      <c r="H44" s="62"/>
-      <c r="I44" s="31"/>
-      <c r="J44" s="32"/>
-      <c r="K44" s="58"/>
-      <c r="L44" s="59"/>
-      <c r="M44" s="59"/>
-      <c r="N44" s="60"/>
-      <c r="O44" s="77"/>
-      <c r="P44" s="77"/>
-      <c r="Q44" s="77"/>
-      <c r="R44" s="78"/>
-    </row>
-    <row r="45" spans="1:18" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A45" s="53" t="s">
-        <v>17</v>
-      </c>
-      <c r="B45" s="54"/>
-      <c r="C45" s="54"/>
-      <c r="D45" s="69"/>
-      <c r="E45" s="69"/>
-      <c r="F45" s="69"/>
-      <c r="G45" s="70"/>
-      <c r="H45" s="54" t="s">
-        <v>17</v>
-      </c>
-      <c r="I45" s="54"/>
-      <c r="J45" s="54"/>
-      <c r="K45" s="69"/>
-      <c r="L45" s="69"/>
-      <c r="M45" s="69"/>
-      <c r="N45" s="70"/>
-      <c r="O45" s="79"/>
-      <c r="P45" s="79"/>
-      <c r="Q45" s="79"/>
-      <c r="R45" s="80"/>
+      <c r="B45" s="135"/>
+      <c r="C45" s="135"/>
+      <c r="D45" s="100"/>
+      <c r="E45" s="100"/>
+      <c r="F45" s="100"/>
+      <c r="G45" s="101"/>
+      <c r="H45" s="135" t="s">
+        <v>16</v>
+      </c>
+      <c r="I45" s="135"/>
+      <c r="J45" s="135"/>
+      <c r="K45" s="100"/>
+      <c r="L45" s="100"/>
+      <c r="M45" s="100"/>
+      <c r="N45" s="101"/>
+      <c r="O45" s="116"/>
+      <c r="P45" s="116"/>
+      <c r="Q45" s="116"/>
+      <c r="R45" s="117"/>
     </row>
     <row r="46" spans="1:18" ht="20.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.4"/>
     <row r="47" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -2636,132 +2639,132 @@
     </row>
     <row r="48" spans="1:18" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A48" s="3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
+      <c r="A49" s="128"/>
+      <c r="B49" s="129"/>
+      <c r="C49" s="130"/>
+      <c r="D49" s="92"/>
+      <c r="E49" s="93"/>
+      <c r="F49" s="93"/>
+      <c r="G49" s="93"/>
+      <c r="H49" s="98"/>
+      <c r="I49" s="92"/>
+      <c r="J49" s="93"/>
+      <c r="K49" s="93"/>
+      <c r="L49" s="93"/>
+      <c r="M49" s="98"/>
+      <c r="N49" s="92"/>
+      <c r="O49" s="93"/>
+      <c r="P49" s="93"/>
+      <c r="Q49" s="93"/>
+      <c r="R49" s="94"/>
+    </row>
+    <row r="50" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A50" s="131"/>
+      <c r="B50" s="132"/>
+      <c r="C50" s="133"/>
+      <c r="D50" s="95"/>
+      <c r="E50" s="96"/>
+      <c r="F50" s="96"/>
+      <c r="G50" s="96"/>
+      <c r="H50" s="99"/>
+      <c r="I50" s="95"/>
+      <c r="J50" s="96"/>
+      <c r="K50" s="96"/>
+      <c r="L50" s="96"/>
+      <c r="M50" s="99"/>
+      <c r="N50" s="95"/>
+      <c r="O50" s="96"/>
+      <c r="P50" s="96"/>
+      <c r="Q50" s="96"/>
+      <c r="R50" s="97"/>
+    </row>
+    <row r="51" spans="1:18" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A51" s="30" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="49" spans="1:18" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="41"/>
-      <c r="B49" s="42"/>
-      <c r="C49" s="43"/>
-      <c r="D49" s="47"/>
-      <c r="E49" s="48"/>
-      <c r="F49" s="48"/>
-      <c r="G49" s="48"/>
-      <c r="H49" s="49"/>
-      <c r="I49" s="47"/>
-      <c r="J49" s="48"/>
-      <c r="K49" s="48"/>
-      <c r="L49" s="48"/>
-      <c r="M49" s="49"/>
-      <c r="N49" s="47"/>
-      <c r="O49" s="48"/>
-      <c r="P49" s="48"/>
-      <c r="Q49" s="48"/>
-      <c r="R49" s="67"/>
-    </row>
-    <row r="50" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="44"/>
-      <c r="B50" s="45"/>
-      <c r="C50" s="46"/>
-      <c r="D50" s="50"/>
-      <c r="E50" s="51"/>
-      <c r="F50" s="51"/>
-      <c r="G50" s="51"/>
-      <c r="H50" s="52"/>
-      <c r="I50" s="50"/>
-      <c r="J50" s="51"/>
-      <c r="K50" s="51"/>
-      <c r="L50" s="51"/>
-      <c r="M50" s="52"/>
-      <c r="N50" s="50"/>
-      <c r="O50" s="51"/>
-      <c r="P50" s="51"/>
-      <c r="Q50" s="51"/>
-      <c r="R50" s="68"/>
-    </row>
-    <row r="51" spans="1:18" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A51" s="120" t="s">
+      <c r="B51" s="31"/>
+      <c r="C51" s="32"/>
+      <c r="D51" s="28"/>
+      <c r="E51" s="28"/>
+      <c r="F51" s="28"/>
+      <c r="G51" s="28"/>
+      <c r="H51" s="28"/>
+      <c r="I51" s="28"/>
+      <c r="J51" s="28"/>
+      <c r="K51" s="28"/>
+      <c r="L51" s="28"/>
+      <c r="M51" s="28"/>
+      <c r="N51" s="28"/>
+      <c r="O51" s="28"/>
+      <c r="P51" s="28"/>
+      <c r="Q51" s="28"/>
+      <c r="R51" s="29"/>
+    </row>
+    <row r="52" spans="1:18" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A52" s="33"/>
+      <c r="B52" s="34"/>
+      <c r="C52" s="35"/>
+      <c r="D52" s="28"/>
+      <c r="E52" s="28"/>
+      <c r="F52" s="28"/>
+      <c r="G52" s="28"/>
+      <c r="H52" s="28"/>
+      <c r="I52" s="28"/>
+      <c r="J52" s="28"/>
+      <c r="K52" s="28"/>
+      <c r="L52" s="28"/>
+      <c r="M52" s="28"/>
+      <c r="N52" s="28"/>
+      <c r="O52" s="28"/>
+      <c r="P52" s="28"/>
+      <c r="Q52" s="28"/>
+      <c r="R52" s="29"/>
+    </row>
+    <row r="53" spans="1:18" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A53" s="73" t="s">
         <v>19</v>
       </c>
-      <c r="B51" s="121"/>
-      <c r="C51" s="122"/>
-      <c r="D51" s="83"/>
-      <c r="E51" s="83"/>
-      <c r="F51" s="83"/>
-      <c r="G51" s="83"/>
-      <c r="H51" s="83"/>
-      <c r="I51" s="83"/>
-      <c r="J51" s="83"/>
-      <c r="K51" s="83"/>
-      <c r="L51" s="83"/>
-      <c r="M51" s="83"/>
-      <c r="N51" s="83"/>
-      <c r="O51" s="83"/>
-      <c r="P51" s="83"/>
-      <c r="Q51" s="83"/>
-      <c r="R51" s="119"/>
-    </row>
-    <row r="52" spans="1:18" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A52" s="123"/>
-      <c r="B52" s="124"/>
-      <c r="C52" s="125"/>
-      <c r="D52" s="83"/>
-      <c r="E52" s="83"/>
-      <c r="F52" s="83"/>
-      <c r="G52" s="83"/>
-      <c r="H52" s="83"/>
-      <c r="I52" s="83"/>
-      <c r="J52" s="83"/>
-      <c r="K52" s="83"/>
-      <c r="L52" s="83"/>
-      <c r="M52" s="83"/>
-      <c r="N52" s="83"/>
-      <c r="O52" s="83"/>
-      <c r="P52" s="83"/>
-      <c r="Q52" s="83"/>
-      <c r="R52" s="119"/>
-    </row>
-    <row r="53" spans="1:18" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A53" s="103" t="s">
-        <v>20</v>
-      </c>
-      <c r="B53" s="104"/>
-      <c r="C53" s="105"/>
-      <c r="D53" s="81"/>
-      <c r="E53" s="81"/>
-      <c r="F53" s="81"/>
-      <c r="G53" s="81"/>
-      <c r="H53" s="81"/>
-      <c r="I53" s="81"/>
-      <c r="J53" s="81"/>
-      <c r="K53" s="81"/>
-      <c r="L53" s="81"/>
-      <c r="M53" s="81"/>
-      <c r="N53" s="81"/>
-      <c r="O53" s="81"/>
-      <c r="P53" s="81"/>
-      <c r="Q53" s="81"/>
-      <c r="R53" s="126"/>
+      <c r="B53" s="74"/>
+      <c r="C53" s="75"/>
+      <c r="D53" s="36"/>
+      <c r="E53" s="36"/>
+      <c r="F53" s="36"/>
+      <c r="G53" s="36"/>
+      <c r="H53" s="36"/>
+      <c r="I53" s="36"/>
+      <c r="J53" s="36"/>
+      <c r="K53" s="36"/>
+      <c r="L53" s="36"/>
+      <c r="M53" s="36"/>
+      <c r="N53" s="36"/>
+      <c r="O53" s="36"/>
+      <c r="P53" s="36"/>
+      <c r="Q53" s="36"/>
+      <c r="R53" s="37"/>
     </row>
     <row r="54" spans="1:18" s="2" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="106"/>
-      <c r="B54" s="107"/>
-      <c r="C54" s="108"/>
-      <c r="D54" s="82"/>
-      <c r="E54" s="82"/>
-      <c r="F54" s="82"/>
-      <c r="G54" s="82"/>
-      <c r="H54" s="82"/>
-      <c r="I54" s="82"/>
-      <c r="J54" s="82"/>
-      <c r="K54" s="82"/>
-      <c r="L54" s="82"/>
-      <c r="M54" s="82"/>
-      <c r="N54" s="82"/>
-      <c r="O54" s="82"/>
-      <c r="P54" s="82"/>
-      <c r="Q54" s="82"/>
-      <c r="R54" s="127"/>
+      <c r="A54" s="76"/>
+      <c r="B54" s="77"/>
+      <c r="C54" s="78"/>
+      <c r="D54" s="38"/>
+      <c r="E54" s="38"/>
+      <c r="F54" s="38"/>
+      <c r="G54" s="38"/>
+      <c r="H54" s="38"/>
+      <c r="I54" s="38"/>
+      <c r="J54" s="38"/>
+      <c r="K54" s="38"/>
+      <c r="L54" s="38"/>
+      <c r="M54" s="38"/>
+      <c r="N54" s="38"/>
+      <c r="O54" s="38"/>
+      <c r="P54" s="38"/>
+      <c r="Q54" s="38"/>
+      <c r="R54" s="39"/>
     </row>
     <row r="55" spans="1:18" s="2" customFormat="1" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.15"/>
     <row r="56" spans="1:18" s="2" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -2775,23 +2778,28 @@
     <row r="64" spans="1:18" s="2" customFormat="1" ht="13.5" x14ac:dyDescent="0.15"/>
   </sheetData>
   <sheetProtection formatCells="0"/>
-  <mergeCells count="52">
-    <mergeCell ref="O3:R4"/>
-    <mergeCell ref="D51:H52"/>
-    <mergeCell ref="N51:R52"/>
-    <mergeCell ref="A51:C52"/>
-    <mergeCell ref="N53:R54"/>
-    <mergeCell ref="M31:R32"/>
-    <mergeCell ref="M33:R34"/>
-    <mergeCell ref="A33:C34"/>
-    <mergeCell ref="O39:R40"/>
-    <mergeCell ref="A35:C36"/>
-    <mergeCell ref="D33:I34"/>
-    <mergeCell ref="J33:L34"/>
-    <mergeCell ref="D35:R36"/>
-    <mergeCell ref="A31:C32"/>
-    <mergeCell ref="J31:L32"/>
-    <mergeCell ref="D53:H54"/>
+  <mergeCells count="50">
+    <mergeCell ref="A43:C44"/>
+    <mergeCell ref="D39:G40"/>
+    <mergeCell ref="D23:L25"/>
+    <mergeCell ref="A49:C50"/>
+    <mergeCell ref="D49:H50"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="H45:J45"/>
+    <mergeCell ref="A41:C42"/>
+    <mergeCell ref="D43:G44"/>
+    <mergeCell ref="H43:J44"/>
+    <mergeCell ref="D33:R34"/>
+    <mergeCell ref="M22:N28"/>
+    <mergeCell ref="N49:R50"/>
+    <mergeCell ref="I49:M50"/>
+    <mergeCell ref="D45:G45"/>
+    <mergeCell ref="D41:G42"/>
+    <mergeCell ref="H41:J42"/>
+    <mergeCell ref="K41:N42"/>
+    <mergeCell ref="O41:R45"/>
+    <mergeCell ref="K43:N44"/>
+    <mergeCell ref="K45:N45"/>
     <mergeCell ref="I53:M54"/>
     <mergeCell ref="I51:M52"/>
     <mergeCell ref="O1:R1"/>
@@ -2808,26 +2816,19 @@
     <mergeCell ref="K39:N40"/>
     <mergeCell ref="A53:C54"/>
     <mergeCell ref="O22:R28"/>
-    <mergeCell ref="M22:N28"/>
-    <mergeCell ref="N49:R50"/>
-    <mergeCell ref="I49:M50"/>
-    <mergeCell ref="D45:G45"/>
-    <mergeCell ref="D41:G42"/>
-    <mergeCell ref="H41:J42"/>
-    <mergeCell ref="K41:N42"/>
-    <mergeCell ref="O41:R45"/>
-    <mergeCell ref="K43:N44"/>
-    <mergeCell ref="K45:N45"/>
-    <mergeCell ref="A43:C44"/>
-    <mergeCell ref="D39:G40"/>
-    <mergeCell ref="D23:L25"/>
-    <mergeCell ref="A49:C50"/>
-    <mergeCell ref="D49:H50"/>
-    <mergeCell ref="A45:C45"/>
-    <mergeCell ref="H45:J45"/>
-    <mergeCell ref="A41:C42"/>
-    <mergeCell ref="D43:G44"/>
-    <mergeCell ref="H43:J44"/>
+    <mergeCell ref="O3:R4"/>
+    <mergeCell ref="D51:H52"/>
+    <mergeCell ref="N51:R52"/>
+    <mergeCell ref="A51:C52"/>
+    <mergeCell ref="N53:R54"/>
+    <mergeCell ref="M31:R32"/>
+    <mergeCell ref="A33:C34"/>
+    <mergeCell ref="O39:R40"/>
+    <mergeCell ref="A35:C36"/>
+    <mergeCell ref="D35:R36"/>
+    <mergeCell ref="A31:C32"/>
+    <mergeCell ref="J31:L32"/>
+    <mergeCell ref="D53:H54"/>
   </mergeCells>
   <phoneticPr fontId="20"/>
   <printOptions horizontalCentered="1"/>
@@ -2855,62 +2856,62 @@
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="148" t="s">
+      <c r="E2" s="142" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" s="142"/>
+      <c r="G2" s="142" t="s">
         <v>22</v>
       </c>
-      <c r="F2" s="148"/>
-      <c r="G2" s="148" t="s">
+      <c r="H2" s="142"/>
+      <c r="I2" s="142" t="s">
         <v>23</v>
       </c>
-      <c r="H2" s="148"/>
-      <c r="I2" s="148" t="s">
+      <c r="J2" s="142"/>
+      <c r="K2" s="142" t="s">
         <v>24</v>
       </c>
-      <c r="J2" s="148"/>
-      <c r="K2" s="148" t="s">
+      <c r="L2" s="142"/>
+      <c r="M2" s="142" t="s">
         <v>25</v>
       </c>
-      <c r="L2" s="148"/>
-      <c r="M2" s="148" t="s">
+      <c r="N2" s="142"/>
+    </row>
+    <row r="3" spans="2:14" x14ac:dyDescent="0.4">
+      <c r="B3" s="140" t="s">
         <v>26</v>
       </c>
-      <c r="N2" s="148"/>
-    </row>
-    <row r="3" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B3" s="145" t="s">
+      <c r="C3" s="140"/>
+      <c r="D3" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="C3" s="145"/>
-      <c r="D3" s="26" t="s">
+      <c r="E3" s="140"/>
+      <c r="F3" s="140"/>
+      <c r="G3" s="141"/>
+      <c r="H3" s="141"/>
+      <c r="I3" s="140"/>
+      <c r="J3" s="140"/>
+      <c r="K3" s="140"/>
+      <c r="L3" s="140"/>
+      <c r="M3" s="140"/>
+      <c r="N3" s="140"/>
+    </row>
+    <row r="4" spans="2:14" x14ac:dyDescent="0.4">
+      <c r="B4" s="140"/>
+      <c r="C4" s="140"/>
+      <c r="D4" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="145"/>
-      <c r="F3" s="145"/>
-      <c r="G3" s="149"/>
-      <c r="H3" s="149"/>
-      <c r="I3" s="145"/>
-      <c r="J3" s="145"/>
-      <c r="K3" s="145"/>
-      <c r="L3" s="145"/>
-      <c r="M3" s="145"/>
-      <c r="N3" s="145"/>
-    </row>
-    <row r="4" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B4" s="145"/>
-      <c r="C4" s="145"/>
-      <c r="D4" s="26" t="s">
-        <v>29</v>
-      </c>
-      <c r="E4" s="145"/>
-      <c r="F4" s="145"/>
-      <c r="G4" s="145"/>
-      <c r="H4" s="145"/>
-      <c r="I4" s="145"/>
-      <c r="J4" s="145"/>
-      <c r="K4" s="145"/>
-      <c r="L4" s="145"/>
-      <c r="M4" s="145"/>
-      <c r="N4" s="145"/>
+      <c r="E4" s="140"/>
+      <c r="F4" s="140"/>
+      <c r="G4" s="140"/>
+      <c r="H4" s="140"/>
+      <c r="I4" s="140"/>
+      <c r="J4" s="140"/>
+      <c r="K4" s="140"/>
+      <c r="L4" s="140"/>
+      <c r="M4" s="140"/>
+      <c r="N4" s="140"/>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B5" s="1"/>
@@ -2931,62 +2932,62 @@
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
-      <c r="E6" s="143" t="s">
+      <c r="E6" s="147" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="148"/>
+      <c r="G6" s="147" t="s">
         <v>22</v>
       </c>
-      <c r="F6" s="144"/>
-      <c r="G6" s="143" t="s">
+      <c r="H6" s="148"/>
+      <c r="I6" s="147" t="s">
         <v>23</v>
       </c>
-      <c r="H6" s="144"/>
-      <c r="I6" s="143" t="s">
+      <c r="J6" s="148"/>
+      <c r="K6" s="147" t="s">
         <v>24</v>
       </c>
-      <c r="J6" s="144"/>
-      <c r="K6" s="143" t="s">
+      <c r="L6" s="148"/>
+      <c r="M6" s="147" t="s">
         <v>25</v>
       </c>
-      <c r="L6" s="144"/>
-      <c r="M6" s="143" t="s">
-        <v>26</v>
-      </c>
-      <c r="N6" s="144"/>
+      <c r="N6" s="148"/>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B7" s="145" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" s="145"/>
+      <c r="B7" s="140" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" s="140"/>
       <c r="D7" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="143"/>
+      <c r="F7" s="144"/>
+      <c r="G7" s="145"/>
+      <c r="H7" s="146"/>
+      <c r="I7" s="143"/>
+      <c r="J7" s="144"/>
+      <c r="K7" s="143"/>
+      <c r="L7" s="144"/>
+      <c r="M7" s="143"/>
+      <c r="N7" s="144"/>
+    </row>
+    <row r="8" spans="2:14" x14ac:dyDescent="0.4">
+      <c r="B8" s="140"/>
+      <c r="C8" s="140"/>
+      <c r="D8" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="E7" s="141"/>
-      <c r="F7" s="142"/>
-      <c r="G7" s="146"/>
-      <c r="H7" s="147"/>
-      <c r="I7" s="141"/>
-      <c r="J7" s="142"/>
-      <c r="K7" s="141"/>
-      <c r="L7" s="142"/>
-      <c r="M7" s="141"/>
-      <c r="N7" s="142"/>
-    </row>
-    <row r="8" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B8" s="145"/>
-      <c r="C8" s="145"/>
-      <c r="D8" s="26" t="s">
-        <v>29</v>
-      </c>
-      <c r="E8" s="141"/>
-      <c r="F8" s="142"/>
-      <c r="G8" s="141"/>
-      <c r="H8" s="142"/>
-      <c r="I8" s="141"/>
-      <c r="J8" s="142"/>
-      <c r="K8" s="141"/>
-      <c r="L8" s="142"/>
-      <c r="M8" s="141"/>
-      <c r="N8" s="142"/>
+      <c r="E8" s="143"/>
+      <c r="F8" s="144"/>
+      <c r="G8" s="143"/>
+      <c r="H8" s="144"/>
+      <c r="I8" s="143"/>
+      <c r="J8" s="144"/>
+      <c r="K8" s="143"/>
+      <c r="L8" s="144"/>
+      <c r="M8" s="143"/>
+      <c r="N8" s="144"/>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B9" s="1"/>
@@ -3007,62 +3008,62 @@
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
-      <c r="E10" s="143" t="s">
+      <c r="E10" s="147" t="s">
+        <v>21</v>
+      </c>
+      <c r="F10" s="148"/>
+      <c r="G10" s="147" t="s">
         <v>22</v>
       </c>
-      <c r="F10" s="144"/>
-      <c r="G10" s="143" t="s">
+      <c r="H10" s="148"/>
+      <c r="I10" s="147" t="s">
         <v>23</v>
       </c>
-      <c r="H10" s="144"/>
-      <c r="I10" s="143" t="s">
+      <c r="J10" s="148"/>
+      <c r="K10" s="147" t="s">
         <v>24</v>
       </c>
-      <c r="J10" s="144"/>
-      <c r="K10" s="143" t="s">
+      <c r="L10" s="148"/>
+      <c r="M10" s="147" t="s">
         <v>25</v>
       </c>
-      <c r="L10" s="144"/>
-      <c r="M10" s="143" t="s">
-        <v>26</v>
-      </c>
-      <c r="N10" s="144"/>
+      <c r="N10" s="148"/>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B11" s="145" t="s">
-        <v>31</v>
-      </c>
-      <c r="C11" s="145"/>
+      <c r="B11" s="140" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" s="140"/>
       <c r="D11" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="E11" s="143"/>
+      <c r="F11" s="144"/>
+      <c r="G11" s="145"/>
+      <c r="H11" s="146"/>
+      <c r="I11" s="143"/>
+      <c r="J11" s="144"/>
+      <c r="K11" s="143"/>
+      <c r="L11" s="144"/>
+      <c r="M11" s="143"/>
+      <c r="N11" s="144"/>
+    </row>
+    <row r="12" spans="2:14" x14ac:dyDescent="0.4">
+      <c r="B12" s="140"/>
+      <c r="C12" s="140"/>
+      <c r="D12" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="E11" s="141"/>
-      <c r="F11" s="142"/>
-      <c r="G11" s="146"/>
-      <c r="H11" s="147"/>
-      <c r="I11" s="141"/>
-      <c r="J11" s="142"/>
-      <c r="K11" s="141"/>
-      <c r="L11" s="142"/>
-      <c r="M11" s="141"/>
-      <c r="N11" s="142"/>
-    </row>
-    <row r="12" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B12" s="145"/>
-      <c r="C12" s="145"/>
-      <c r="D12" s="26" t="s">
-        <v>29</v>
-      </c>
-      <c r="E12" s="141"/>
-      <c r="F12" s="142"/>
-      <c r="G12" s="141"/>
-      <c r="H12" s="142"/>
-      <c r="I12" s="141"/>
-      <c r="J12" s="142"/>
-      <c r="K12" s="141"/>
-      <c r="L12" s="142"/>
-      <c r="M12" s="141"/>
-      <c r="N12" s="142"/>
+      <c r="E12" s="143"/>
+      <c r="F12" s="144"/>
+      <c r="G12" s="143"/>
+      <c r="H12" s="144"/>
+      <c r="I12" s="143"/>
+      <c r="J12" s="144"/>
+      <c r="K12" s="143"/>
+      <c r="L12" s="144"/>
+      <c r="M12" s="143"/>
+      <c r="N12" s="144"/>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B13" s="1"/>
@@ -3098,89 +3099,89 @@
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
-      <c r="E15" s="143" t="s">
+      <c r="E15" s="147" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="148"/>
+      <c r="G15" s="147" t="s">
         <v>22</v>
       </c>
-      <c r="F15" s="144"/>
-      <c r="G15" s="143" t="s">
+      <c r="H15" s="148"/>
+      <c r="I15" s="147" t="s">
         <v>23</v>
       </c>
-      <c r="H15" s="144"/>
-      <c r="I15" s="143" t="s">
+      <c r="J15" s="148"/>
+      <c r="K15" s="147" t="s">
         <v>24</v>
       </c>
-      <c r="J15" s="144"/>
-      <c r="K15" s="143" t="s">
+      <c r="L15" s="148"/>
+      <c r="M15" s="147" t="s">
         <v>25</v>
       </c>
-      <c r="L15" s="144"/>
-      <c r="M15" s="143" t="s">
-        <v>26</v>
-      </c>
-      <c r="N15" s="144"/>
+      <c r="N15" s="148"/>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B16" s="145" t="s">
-        <v>32</v>
-      </c>
-      <c r="C16" s="145"/>
+      <c r="B16" s="140" t="s">
+        <v>31</v>
+      </c>
+      <c r="C16" s="140"/>
       <c r="D16" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16" s="143"/>
+      <c r="F16" s="144"/>
+      <c r="G16" s="145"/>
+      <c r="H16" s="146"/>
+      <c r="I16" s="143"/>
+      <c r="J16" s="144"/>
+      <c r="K16" s="143"/>
+      <c r="L16" s="144"/>
+      <c r="M16" s="143"/>
+      <c r="N16" s="144"/>
+    </row>
+    <row r="17" spans="2:14" x14ac:dyDescent="0.4">
+      <c r="B17" s="140"/>
+      <c r="C17" s="140"/>
+      <c r="D17" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="E16" s="141"/>
-      <c r="F16" s="142"/>
-      <c r="G16" s="146"/>
-      <c r="H16" s="147"/>
-      <c r="I16" s="141"/>
-      <c r="J16" s="142"/>
-      <c r="K16" s="141"/>
-      <c r="L16" s="142"/>
-      <c r="M16" s="141"/>
-      <c r="N16" s="142"/>
-    </row>
-    <row r="17" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B17" s="145"/>
-      <c r="C17" s="145"/>
-      <c r="D17" s="26" t="s">
-        <v>29</v>
-      </c>
-      <c r="E17" s="141"/>
-      <c r="F17" s="142"/>
-      <c r="G17" s="141"/>
-      <c r="H17" s="142"/>
-      <c r="I17" s="141"/>
-      <c r="J17" s="142"/>
-      <c r="K17" s="141"/>
-      <c r="L17" s="142"/>
-      <c r="M17" s="141"/>
-      <c r="N17" s="142"/>
+      <c r="E17" s="143"/>
+      <c r="F17" s="144"/>
+      <c r="G17" s="143"/>
+      <c r="H17" s="144"/>
+      <c r="I17" s="143"/>
+      <c r="J17" s="144"/>
+      <c r="K17" s="143"/>
+      <c r="L17" s="144"/>
+      <c r="M17" s="143"/>
+      <c r="N17" s="144"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B20" s="138"/>
       <c r="C20" s="138"/>
       <c r="D20" s="138"/>
       <c r="E20" s="138" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F20" s="138"/>
       <c r="I20" s="138"/>
       <c r="J20" s="138"/>
       <c r="K20" s="138"/>
       <c r="L20" s="138" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M20" s="138"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B21" s="138" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C21" s="138"/>
       <c r="D21" s="138"/>
       <c r="E21" s="139"/>
       <c r="F21" s="139"/>
       <c r="I21" s="138" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J21" s="138"/>
       <c r="K21" s="138"/>
@@ -3189,14 +3190,14 @@
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B22" s="138" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C22" s="138"/>
       <c r="D22" s="138"/>
       <c r="E22" s="139"/>
       <c r="F22" s="139"/>
       <c r="I22" s="138" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J22" s="138"/>
       <c r="K22" s="138"/>
@@ -3205,14 +3206,14 @@
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B23" s="138" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C23" s="138"/>
       <c r="D23" s="138"/>
       <c r="E23" s="139"/>
       <c r="F23" s="139"/>
       <c r="I23" s="138" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J23" s="138"/>
       <c r="K23" s="138"/>
@@ -3221,14 +3222,14 @@
     </row>
     <row r="24" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B24" s="138" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C24" s="138"/>
       <c r="D24" s="138"/>
       <c r="E24" s="139"/>
       <c r="F24" s="139"/>
       <c r="I24" s="138" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J24" s="138"/>
       <c r="K24" s="138"/>
@@ -3237,7 +3238,7 @@
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B25" s="138" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C25" s="138"/>
       <c r="D25" s="138"/>
@@ -3246,7 +3247,7 @@
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B26" s="138" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C26" s="138"/>
       <c r="D26" s="138"/>
@@ -3255,16 +3256,16 @@
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B27" s="138" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C27" s="138"/>
       <c r="D27" s="138"/>
-      <c r="E27" s="140"/>
-      <c r="F27" s="140"/>
+      <c r="E27" s="149"/>
+      <c r="F27" s="149"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B28" s="138" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C28" s="138"/>
       <c r="D28" s="138"/>
@@ -3273,7 +3274,7 @@
     </row>
     <row r="29" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B29" s="138" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C29" s="138"/>
       <c r="D29" s="138"/>
@@ -3282,7 +3283,7 @@
     </row>
     <row r="30" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B30" s="138" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C30" s="138"/>
       <c r="D30" s="138"/>
@@ -3291,6 +3292,92 @@
     </row>
   </sheetData>
   <mergeCells count="96">
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="E30:F30"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="B16:C17"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="K16:L16"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="B11:C12"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="M8:N8"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="B7:C8"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="B3:C4"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="K3:L3"/>
     <mergeCell ref="I23:K23"/>
     <mergeCell ref="L23:M23"/>
     <mergeCell ref="I24:K24"/>
@@ -3301,92 +3388,6 @@
     <mergeCell ref="L21:M21"/>
     <mergeCell ref="I22:K22"/>
     <mergeCell ref="L22:M22"/>
-    <mergeCell ref="B3:C4"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="B7:C8"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="M7:N7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="M8:N8"/>
-    <mergeCell ref="B11:C12"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="M10:N10"/>
-    <mergeCell ref="M11:N11"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="B16:C17"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="K16:L16"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="K15:L15"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="E28:F28"/>
   </mergeCells>
   <phoneticPr fontId="20"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/storage/app/estimateTemplate/comprehensiveOfRecommend.xlsx
+++ b/storage/app/estimateTemplate/comprehensiveOfRecommend.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yokoyama\Desktop\修正用ふぉうるだ\estimateTemplate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CA21EE4-39BA-4086-BA9D-18597BBF6294}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46EF2F5B-DCDB-4959-92E3-5DC6579A0002}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-75" windowWidth="29040" windowHeight="15720" xr2:uid="{0E9C5CA5-184F-4C06-AA15-1AF55B55AFB9}"/>
+    <workbookView xWindow="45" yWindow="90" windowWidth="28755" windowHeight="15435" activeTab="1" xr2:uid="{0E9C5CA5-184F-4C06-AA15-1AF55B55AFB9}"/>
   </bookViews>
   <sheets>
     <sheet name="おすすめ(総合)" sheetId="2" r:id="rId1"/>
@@ -1208,97 +1208,193 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="26" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="8" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="28" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="16" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="16" fillId="0" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="16" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="16" fillId="0" borderId="29" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="9" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="9" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="180" fontId="18" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="181" fontId="9" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="9" fillId="0" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="9" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="9" fillId="0" borderId="29" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="24" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="58" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -1308,6 +1404,18 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -1332,6 +1440,12 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1341,12 +1455,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="2" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1392,155 +1500,65 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="26" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="8" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="28" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="16" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="16" fillId="0" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="16" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="16" fillId="0" borderId="29" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="18" fillId="0" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="9" fillId="0" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="9" fillId="0" borderId="29" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="24" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1548,52 +1566,34 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="33" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="34" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="35" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="33" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="34" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1972,10 +1972,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="O1" s="58"/>
-      <c r="P1" s="58"/>
-      <c r="Q1" s="58"/>
-      <c r="R1" s="58"/>
+      <c r="O1" s="90"/>
+      <c r="P1" s="90"/>
+      <c r="Q1" s="90"/>
+      <c r="R1" s="90"/>
     </row>
     <row r="2" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="O2" s="25"/>
@@ -1985,16 +1985,16 @@
     </row>
     <row r="3" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A3" s="3"/>
-      <c r="O3" s="27"/>
-      <c r="P3" s="27"/>
-      <c r="Q3" s="27"/>
-      <c r="R3" s="27"/>
+      <c r="O3" s="124"/>
+      <c r="P3" s="124"/>
+      <c r="Q3" s="124"/>
+      <c r="R3" s="124"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="O4" s="27"/>
-      <c r="P4" s="27"/>
-      <c r="Q4" s="27"/>
-      <c r="R4" s="27"/>
+      <c r="O4" s="124"/>
+      <c r="P4" s="124"/>
+      <c r="Q4" s="124"/>
+      <c r="R4" s="124"/>
     </row>
     <row r="5" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="N5" s="24"/>
@@ -2057,196 +2057,196 @@
       <c r="R10" s="20"/>
     </row>
     <row r="11" spans="1:18" ht="21" x14ac:dyDescent="0.4">
-      <c r="A11" s="59" t="s">
+      <c r="A11" s="91" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="59"/>
-      <c r="C11" s="59"/>
-      <c r="D11" s="59"/>
-      <c r="E11" s="59"/>
-      <c r="F11" s="59"/>
-      <c r="G11" s="59"/>
-      <c r="H11" s="59"/>
-      <c r="I11" s="59"/>
-      <c r="J11" s="59"/>
-      <c r="K11" s="59"/>
-      <c r="L11" s="59"/>
-      <c r="M11" s="59"/>
-      <c r="N11" s="59"/>
-      <c r="O11" s="59"/>
-      <c r="P11" s="59"/>
-      <c r="Q11" s="59"/>
-      <c r="R11" s="59"/>
+      <c r="B11" s="91"/>
+      <c r="C11" s="91"/>
+      <c r="D11" s="91"/>
+      <c r="E11" s="91"/>
+      <c r="F11" s="91"/>
+      <c r="G11" s="91"/>
+      <c r="H11" s="91"/>
+      <c r="I11" s="91"/>
+      <c r="J11" s="91"/>
+      <c r="K11" s="91"/>
+      <c r="L11" s="91"/>
+      <c r="M11" s="91"/>
+      <c r="N11" s="91"/>
+      <c r="O11" s="91"/>
+      <c r="P11" s="91"/>
+      <c r="Q11" s="91"/>
+      <c r="R11" s="91"/>
     </row>
     <row r="14" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="15" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
-      <c r="A15" s="66" t="s">
+      <c r="A15" s="102" t="s">
         <v>1</v>
       </c>
-      <c r="B15" s="66"/>
-      <c r="C15" s="66"/>
-      <c r="D15" s="66"/>
-      <c r="E15" s="66"/>
-      <c r="F15" s="66"/>
-      <c r="G15" s="66"/>
-      <c r="H15" s="66"/>
-      <c r="I15" s="66"/>
-      <c r="J15" s="66"/>
-      <c r="K15" s="66"/>
-      <c r="L15" s="66"/>
-      <c r="M15" s="66"/>
-      <c r="N15" s="66"/>
-      <c r="O15" s="66"/>
-      <c r="P15" s="66"/>
-      <c r="Q15" s="66"/>
-      <c r="R15" s="66"/>
+      <c r="B15" s="102"/>
+      <c r="C15" s="102"/>
+      <c r="D15" s="102"/>
+      <c r="E15" s="102"/>
+      <c r="F15" s="102"/>
+      <c r="G15" s="102"/>
+      <c r="H15" s="102"/>
+      <c r="I15" s="102"/>
+      <c r="J15" s="102"/>
+      <c r="K15" s="102"/>
+      <c r="L15" s="102"/>
+      <c r="M15" s="102"/>
+      <c r="N15" s="102"/>
+      <c r="O15" s="102"/>
+      <c r="P15" s="102"/>
+      <c r="Q15" s="102"/>
+      <c r="R15" s="102"/>
     </row>
     <row r="18" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
-      <c r="A18" s="67" t="s">
+      <c r="A18" s="103" t="s">
         <v>2</v>
       </c>
-      <c r="B18" s="67"/>
-      <c r="C18" s="67"/>
-      <c r="D18" s="67"/>
-      <c r="E18" s="67"/>
-      <c r="F18" s="67"/>
-      <c r="G18" s="67"/>
-      <c r="H18" s="67"/>
-      <c r="I18" s="67"/>
-      <c r="J18" s="67"/>
-      <c r="K18" s="67"/>
-      <c r="L18" s="67"/>
-      <c r="M18" s="67"/>
-      <c r="N18" s="67"/>
-      <c r="O18" s="67"/>
-      <c r="P18" s="67"/>
-      <c r="Q18" s="67"/>
-      <c r="R18" s="67"/>
+      <c r="B18" s="103"/>
+      <c r="C18" s="103"/>
+      <c r="D18" s="103"/>
+      <c r="E18" s="103"/>
+      <c r="F18" s="103"/>
+      <c r="G18" s="103"/>
+      <c r="H18" s="103"/>
+      <c r="I18" s="103"/>
+      <c r="J18" s="103"/>
+      <c r="K18" s="103"/>
+      <c r="L18" s="103"/>
+      <c r="M18" s="103"/>
+      <c r="N18" s="103"/>
+      <c r="O18" s="103"/>
+      <c r="P18" s="103"/>
+      <c r="Q18" s="103"/>
+      <c r="R18" s="103"/>
     </row>
     <row r="19" spans="1:18" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="20" spans="1:18" ht="12.75" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="57" t="s">
+      <c r="A20" s="95" t="s">
         <v>3</v>
       </c>
-      <c r="B20" s="46"/>
-      <c r="C20" s="46"/>
-      <c r="D20" s="60"/>
-      <c r="E20" s="61"/>
-      <c r="F20" s="61"/>
-      <c r="G20" s="61"/>
-      <c r="H20" s="61"/>
-      <c r="I20" s="61"/>
-      <c r="J20" s="61"/>
-      <c r="K20" s="61"/>
-      <c r="L20" s="61"/>
-      <c r="M20" s="61"/>
-      <c r="N20" s="61"/>
-      <c r="O20" s="61"/>
-      <c r="P20" s="61"/>
-      <c r="Q20" s="61"/>
-      <c r="R20" s="62"/>
+      <c r="B20" s="33"/>
+      <c r="C20" s="33"/>
+      <c r="D20" s="96"/>
+      <c r="E20" s="97"/>
+      <c r="F20" s="97"/>
+      <c r="G20" s="97"/>
+      <c r="H20" s="97"/>
+      <c r="I20" s="97"/>
+      <c r="J20" s="97"/>
+      <c r="K20" s="97"/>
+      <c r="L20" s="97"/>
+      <c r="M20" s="97"/>
+      <c r="N20" s="97"/>
+      <c r="O20" s="97"/>
+      <c r="P20" s="97"/>
+      <c r="Q20" s="97"/>
+      <c r="R20" s="98"/>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A21" s="44"/>
-      <c r="B21" s="45"/>
-      <c r="C21" s="45"/>
-      <c r="D21" s="63"/>
-      <c r="E21" s="64"/>
-      <c r="F21" s="64"/>
-      <c r="G21" s="64"/>
-      <c r="H21" s="64"/>
-      <c r="I21" s="64"/>
-      <c r="J21" s="64"/>
-      <c r="K21" s="64"/>
-      <c r="L21" s="64"/>
-      <c r="M21" s="64"/>
-      <c r="N21" s="64"/>
-      <c r="O21" s="64"/>
-      <c r="P21" s="64"/>
-      <c r="Q21" s="64"/>
-      <c r="R21" s="65"/>
+      <c r="A21" s="92"/>
+      <c r="B21" s="35"/>
+      <c r="C21" s="35"/>
+      <c r="D21" s="99"/>
+      <c r="E21" s="100"/>
+      <c r="F21" s="100"/>
+      <c r="G21" s="100"/>
+      <c r="H21" s="100"/>
+      <c r="I21" s="100"/>
+      <c r="J21" s="100"/>
+      <c r="K21" s="100"/>
+      <c r="L21" s="100"/>
+      <c r="M21" s="100"/>
+      <c r="N21" s="100"/>
+      <c r="O21" s="100"/>
+      <c r="P21" s="100"/>
+      <c r="Q21" s="100"/>
+      <c r="R21" s="101"/>
     </row>
     <row r="22" spans="1:18" ht="5.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="44" t="s">
+      <c r="A22" s="92" t="s">
         <v>4</v>
       </c>
-      <c r="B22" s="45"/>
-      <c r="C22" s="45"/>
+      <c r="B22" s="35"/>
+      <c r="C22" s="35"/>
       <c r="D22" s="19"/>
       <c r="L22" s="18"/>
-      <c r="M22" s="88" t="s">
+      <c r="M22" s="69" t="s">
         <v>5</v>
       </c>
-      <c r="N22" s="89"/>
-      <c r="O22" s="79"/>
-      <c r="P22" s="80"/>
-      <c r="Q22" s="80"/>
-      <c r="R22" s="81"/>
+      <c r="N22" s="70"/>
+      <c r="O22" s="115"/>
+      <c r="P22" s="116"/>
+      <c r="Q22" s="116"/>
+      <c r="R22" s="117"/>
     </row>
     <row r="23" spans="1:18" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="44"/>
-      <c r="B23" s="45"/>
-      <c r="C23" s="45"/>
-      <c r="D23" s="124"/>
-      <c r="E23" s="125"/>
-      <c r="F23" s="125"/>
-      <c r="G23" s="125"/>
-      <c r="H23" s="125"/>
-      <c r="I23" s="125"/>
-      <c r="J23" s="125"/>
-      <c r="K23" s="125"/>
-      <c r="L23" s="126"/>
-      <c r="M23" s="88"/>
-      <c r="N23" s="89"/>
-      <c r="O23" s="82"/>
-      <c r="P23" s="83"/>
-      <c r="Q23" s="83"/>
-      <c r="R23" s="84"/>
+      <c r="A23" s="92"/>
+      <c r="B23" s="35"/>
+      <c r="C23" s="35"/>
+      <c r="D23" s="37"/>
+      <c r="E23" s="38"/>
+      <c r="F23" s="38"/>
+      <c r="G23" s="38"/>
+      <c r="H23" s="38"/>
+      <c r="I23" s="38"/>
+      <c r="J23" s="38"/>
+      <c r="K23" s="38"/>
+      <c r="L23" s="39"/>
+      <c r="M23" s="69"/>
+      <c r="N23" s="70"/>
+      <c r="O23" s="118"/>
+      <c r="P23" s="119"/>
+      <c r="Q23" s="119"/>
+      <c r="R23" s="120"/>
     </row>
     <row r="24" spans="1:18" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="44"/>
-      <c r="B24" s="45"/>
-      <c r="C24" s="45"/>
-      <c r="D24" s="127"/>
-      <c r="E24" s="125"/>
-      <c r="F24" s="125"/>
-      <c r="G24" s="125"/>
-      <c r="H24" s="125"/>
-      <c r="I24" s="125"/>
-      <c r="J24" s="125"/>
-      <c r="K24" s="125"/>
-      <c r="L24" s="126"/>
-      <c r="M24" s="88"/>
-      <c r="N24" s="89"/>
-      <c r="O24" s="82"/>
-      <c r="P24" s="83"/>
-      <c r="Q24" s="83"/>
-      <c r="R24" s="84"/>
+      <c r="A24" s="92"/>
+      <c r="B24" s="35"/>
+      <c r="C24" s="35"/>
+      <c r="D24" s="40"/>
+      <c r="E24" s="38"/>
+      <c r="F24" s="38"/>
+      <c r="G24" s="38"/>
+      <c r="H24" s="38"/>
+      <c r="I24" s="38"/>
+      <c r="J24" s="38"/>
+      <c r="K24" s="38"/>
+      <c r="L24" s="39"/>
+      <c r="M24" s="69"/>
+      <c r="N24" s="70"/>
+      <c r="O24" s="118"/>
+      <c r="P24" s="119"/>
+      <c r="Q24" s="119"/>
+      <c r="R24" s="120"/>
     </row>
     <row r="25" spans="1:18" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="44"/>
-      <c r="B25" s="45"/>
-      <c r="C25" s="45"/>
-      <c r="D25" s="127"/>
-      <c r="E25" s="125"/>
-      <c r="F25" s="125"/>
-      <c r="G25" s="125"/>
-      <c r="H25" s="125"/>
-      <c r="I25" s="125"/>
-      <c r="J25" s="125"/>
-      <c r="K25" s="125"/>
-      <c r="L25" s="126"/>
-      <c r="M25" s="88"/>
-      <c r="N25" s="89"/>
-      <c r="O25" s="82"/>
-      <c r="P25" s="83"/>
-      <c r="Q25" s="83"/>
-      <c r="R25" s="84"/>
+      <c r="A25" s="92"/>
+      <c r="B25" s="35"/>
+      <c r="C25" s="35"/>
+      <c r="D25" s="40"/>
+      <c r="E25" s="38"/>
+      <c r="F25" s="38"/>
+      <c r="G25" s="38"/>
+      <c r="H25" s="38"/>
+      <c r="I25" s="38"/>
+      <c r="J25" s="38"/>
+      <c r="K25" s="38"/>
+      <c r="L25" s="39"/>
+      <c r="M25" s="69"/>
+      <c r="N25" s="70"/>
+      <c r="O25" s="118"/>
+      <c r="P25" s="119"/>
+      <c r="Q25" s="119"/>
+      <c r="R25" s="120"/>
     </row>
     <row r="26" spans="1:18" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="44"/>
-      <c r="B26" s="45"/>
-      <c r="C26" s="45"/>
+      <c r="A26" s="92"/>
+      <c r="B26" s="35"/>
+      <c r="C26" s="35"/>
       <c r="D26" s="17"/>
       <c r="E26" s="16"/>
       <c r="F26" s="15"/>
@@ -2256,17 +2256,17 @@
       <c r="J26" s="14"/>
       <c r="K26" s="14"/>
       <c r="L26" s="13"/>
-      <c r="M26" s="88"/>
-      <c r="N26" s="89"/>
-      <c r="O26" s="82"/>
-      <c r="P26" s="83"/>
-      <c r="Q26" s="83"/>
-      <c r="R26" s="84"/>
+      <c r="M26" s="69"/>
+      <c r="N26" s="70"/>
+      <c r="O26" s="118"/>
+      <c r="P26" s="119"/>
+      <c r="Q26" s="119"/>
+      <c r="R26" s="120"/>
     </row>
     <row r="27" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="44"/>
-      <c r="B27" s="45"/>
-      <c r="C27" s="45"/>
+      <c r="A27" s="92"/>
+      <c r="B27" s="35"/>
+      <c r="C27" s="35"/>
       <c r="D27" s="12"/>
       <c r="F27" s="10"/>
       <c r="G27" s="11"/>
@@ -2274,17 +2274,17 @@
       <c r="I27" s="9"/>
       <c r="J27" s="9"/>
       <c r="L27" s="8"/>
-      <c r="M27" s="88"/>
-      <c r="N27" s="89"/>
-      <c r="O27" s="82"/>
-      <c r="P27" s="83"/>
-      <c r="Q27" s="83"/>
-      <c r="R27" s="84"/>
+      <c r="M27" s="69"/>
+      <c r="N27" s="70"/>
+      <c r="O27" s="118"/>
+      <c r="P27" s="119"/>
+      <c r="Q27" s="119"/>
+      <c r="R27" s="120"/>
     </row>
     <row r="28" spans="1:18" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="49"/>
-      <c r="B28" s="50"/>
-      <c r="C28" s="50"/>
+      <c r="A28" s="93"/>
+      <c r="B28" s="94"/>
+      <c r="C28" s="94"/>
       <c r="D28" s="7"/>
       <c r="E28" s="6"/>
       <c r="F28" s="6"/>
@@ -2294,344 +2294,344 @@
       <c r="J28" s="6"/>
       <c r="K28" s="6"/>
       <c r="L28" s="5"/>
-      <c r="M28" s="90"/>
-      <c r="N28" s="91"/>
-      <c r="O28" s="85"/>
-      <c r="P28" s="86"/>
-      <c r="Q28" s="86"/>
-      <c r="R28" s="87"/>
+      <c r="M28" s="71"/>
+      <c r="N28" s="72"/>
+      <c r="O28" s="121"/>
+      <c r="P28" s="122"/>
+      <c r="Q28" s="122"/>
+      <c r="R28" s="123"/>
     </row>
     <row r="29" spans="1:18" ht="12.75" thickTop="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="1:18" ht="12.75" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="31" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="57" t="s">
+      <c r="A31" s="95" t="s">
         <v>6</v>
       </c>
-      <c r="B31" s="46"/>
-      <c r="C31" s="46"/>
-      <c r="D31" s="40"/>
-      <c r="E31" s="40"/>
-      <c r="F31" s="40"/>
-      <c r="G31" s="40"/>
-      <c r="H31" s="40"/>
-      <c r="I31" s="40"/>
-      <c r="J31" s="46" t="s">
+      <c r="B31" s="33"/>
+      <c r="C31" s="33"/>
+      <c r="D31" s="104"/>
+      <c r="E31" s="104"/>
+      <c r="F31" s="104"/>
+      <c r="G31" s="104"/>
+      <c r="H31" s="104"/>
+      <c r="I31" s="104"/>
+      <c r="J31" s="33" t="s">
         <v>7</v>
       </c>
-      <c r="K31" s="46"/>
-      <c r="L31" s="46"/>
-      <c r="M31" s="40"/>
-      <c r="N31" s="40"/>
-      <c r="O31" s="40"/>
-      <c r="P31" s="40"/>
-      <c r="Q31" s="40"/>
-      <c r="R31" s="41"/>
+      <c r="K31" s="33"/>
+      <c r="L31" s="33"/>
+      <c r="M31" s="104"/>
+      <c r="N31" s="104"/>
+      <c r="O31" s="104"/>
+      <c r="P31" s="104"/>
+      <c r="Q31" s="104"/>
+      <c r="R31" s="134"/>
     </row>
     <row r="32" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="44"/>
-      <c r="B32" s="45"/>
-      <c r="C32" s="45"/>
-      <c r="D32" s="42"/>
-      <c r="E32" s="42"/>
-      <c r="F32" s="42"/>
-      <c r="G32" s="42"/>
-      <c r="H32" s="42"/>
-      <c r="I32" s="42"/>
-      <c r="J32" s="45"/>
-      <c r="K32" s="45"/>
-      <c r="L32" s="45"/>
-      <c r="M32" s="42"/>
-      <c r="N32" s="42"/>
-      <c r="O32" s="42"/>
-      <c r="P32" s="42"/>
-      <c r="Q32" s="42"/>
-      <c r="R32" s="43"/>
+      <c r="A32" s="92"/>
+      <c r="B32" s="35"/>
+      <c r="C32" s="35"/>
+      <c r="D32" s="105"/>
+      <c r="E32" s="105"/>
+      <c r="F32" s="105"/>
+      <c r="G32" s="105"/>
+      <c r="H32" s="105"/>
+      <c r="I32" s="105"/>
+      <c r="J32" s="35"/>
+      <c r="K32" s="35"/>
+      <c r="L32" s="35"/>
+      <c r="M32" s="105"/>
+      <c r="N32" s="105"/>
+      <c r="O32" s="105"/>
+      <c r="P32" s="105"/>
+      <c r="Q32" s="105"/>
+      <c r="R32" s="135"/>
     </row>
     <row r="33" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="44" t="s">
+      <c r="A33" s="92" t="s">
         <v>8</v>
       </c>
-      <c r="B33" s="45"/>
-      <c r="C33" s="45"/>
-      <c r="D33" s="150"/>
-      <c r="E33" s="151"/>
-      <c r="F33" s="151"/>
-      <c r="G33" s="151"/>
-      <c r="H33" s="151"/>
-      <c r="I33" s="151"/>
-      <c r="J33" s="151"/>
-      <c r="K33" s="151"/>
-      <c r="L33" s="151"/>
-      <c r="M33" s="151"/>
-      <c r="N33" s="151"/>
-      <c r="O33" s="151"/>
-      <c r="P33" s="151"/>
-      <c r="Q33" s="151"/>
-      <c r="R33" s="152"/>
+      <c r="B33" s="35"/>
+      <c r="C33" s="35"/>
+      <c r="D33" s="63"/>
+      <c r="E33" s="64"/>
+      <c r="F33" s="64"/>
+      <c r="G33" s="64"/>
+      <c r="H33" s="64"/>
+      <c r="I33" s="64"/>
+      <c r="J33" s="64"/>
+      <c r="K33" s="64"/>
+      <c r="L33" s="64"/>
+      <c r="M33" s="64"/>
+      <c r="N33" s="64"/>
+      <c r="O33" s="64"/>
+      <c r="P33" s="64"/>
+      <c r="Q33" s="64"/>
+      <c r="R33" s="65"/>
     </row>
     <row r="34" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="44"/>
-      <c r="B34" s="45"/>
-      <c r="C34" s="45"/>
-      <c r="D34" s="153"/>
-      <c r="E34" s="154"/>
-      <c r="F34" s="154"/>
-      <c r="G34" s="154"/>
-      <c r="H34" s="154"/>
-      <c r="I34" s="154"/>
-      <c r="J34" s="154"/>
-      <c r="K34" s="154"/>
-      <c r="L34" s="154"/>
-      <c r="M34" s="154"/>
-      <c r="N34" s="154"/>
-      <c r="O34" s="154"/>
-      <c r="P34" s="154"/>
-      <c r="Q34" s="154"/>
-      <c r="R34" s="155"/>
+      <c r="A34" s="92"/>
+      <c r="B34" s="35"/>
+      <c r="C34" s="35"/>
+      <c r="D34" s="66"/>
+      <c r="E34" s="67"/>
+      <c r="F34" s="67"/>
+      <c r="G34" s="67"/>
+      <c r="H34" s="67"/>
+      <c r="I34" s="67"/>
+      <c r="J34" s="67"/>
+      <c r="K34" s="67"/>
+      <c r="L34" s="67"/>
+      <c r="M34" s="67"/>
+      <c r="N34" s="67"/>
+      <c r="O34" s="67"/>
+      <c r="P34" s="67"/>
+      <c r="Q34" s="67"/>
+      <c r="R34" s="68"/>
     </row>
     <row r="35" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="44" t="s">
+      <c r="A35" s="92" t="s">
         <v>9</v>
       </c>
-      <c r="B35" s="45"/>
-      <c r="C35" s="45"/>
-      <c r="D35" s="51"/>
-      <c r="E35" s="52"/>
-      <c r="F35" s="52"/>
-      <c r="G35" s="52"/>
-      <c r="H35" s="52"/>
-      <c r="I35" s="52"/>
-      <c r="J35" s="52"/>
-      <c r="K35" s="52"/>
-      <c r="L35" s="52"/>
-      <c r="M35" s="52"/>
-      <c r="N35" s="52"/>
-      <c r="O35" s="52"/>
-      <c r="P35" s="52"/>
-      <c r="Q35" s="52"/>
-      <c r="R35" s="53"/>
+      <c r="B35" s="35"/>
+      <c r="C35" s="35"/>
+      <c r="D35" s="138"/>
+      <c r="E35" s="139"/>
+      <c r="F35" s="139"/>
+      <c r="G35" s="139"/>
+      <c r="H35" s="139"/>
+      <c r="I35" s="139"/>
+      <c r="J35" s="139"/>
+      <c r="K35" s="139"/>
+      <c r="L35" s="139"/>
+      <c r="M35" s="139"/>
+      <c r="N35" s="139"/>
+      <c r="O35" s="139"/>
+      <c r="P35" s="139"/>
+      <c r="Q35" s="139"/>
+      <c r="R35" s="140"/>
     </row>
     <row r="36" spans="1:18" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A36" s="49"/>
-      <c r="B36" s="50"/>
-      <c r="C36" s="50"/>
-      <c r="D36" s="54"/>
-      <c r="E36" s="55"/>
-      <c r="F36" s="55"/>
-      <c r="G36" s="55"/>
-      <c r="H36" s="55"/>
-      <c r="I36" s="55"/>
-      <c r="J36" s="55"/>
-      <c r="K36" s="55"/>
-      <c r="L36" s="55"/>
-      <c r="M36" s="55"/>
-      <c r="N36" s="55"/>
-      <c r="O36" s="55"/>
-      <c r="P36" s="55"/>
-      <c r="Q36" s="55"/>
-      <c r="R36" s="56"/>
+      <c r="A36" s="93"/>
+      <c r="B36" s="94"/>
+      <c r="C36" s="94"/>
+      <c r="D36" s="141"/>
+      <c r="E36" s="142"/>
+      <c r="F36" s="142"/>
+      <c r="G36" s="142"/>
+      <c r="H36" s="142"/>
+      <c r="I36" s="142"/>
+      <c r="J36" s="142"/>
+      <c r="K36" s="142"/>
+      <c r="L36" s="142"/>
+      <c r="M36" s="142"/>
+      <c r="N36" s="142"/>
+      <c r="O36" s="142"/>
+      <c r="P36" s="142"/>
+      <c r="Q36" s="142"/>
+      <c r="R36" s="143"/>
     </row>
     <row r="37" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="68"/>
-      <c r="B37" s="69"/>
-      <c r="C37" s="69"/>
-      <c r="D37" s="69"/>
-      <c r="E37" s="69"/>
-      <c r="F37" s="69"/>
-      <c r="G37" s="69"/>
-      <c r="H37" s="69"/>
-      <c r="I37" s="69"/>
-      <c r="J37" s="69"/>
-      <c r="K37" s="69"/>
-      <c r="L37" s="69"/>
-      <c r="M37" s="69"/>
-      <c r="N37" s="69"/>
-      <c r="O37" s="69"/>
-      <c r="P37" s="69"/>
-      <c r="Q37" s="69"/>
-      <c r="R37" s="69"/>
+      <c r="A37" s="106"/>
+      <c r="B37" s="107"/>
+      <c r="C37" s="107"/>
+      <c r="D37" s="107"/>
+      <c r="E37" s="107"/>
+      <c r="F37" s="107"/>
+      <c r="G37" s="107"/>
+      <c r="H37" s="107"/>
+      <c r="I37" s="107"/>
+      <c r="J37" s="107"/>
+      <c r="K37" s="107"/>
+      <c r="L37" s="107"/>
+      <c r="M37" s="107"/>
+      <c r="N37" s="107"/>
+      <c r="O37" s="107"/>
+      <c r="P37" s="107"/>
+      <c r="Q37" s="107"/>
+      <c r="R37" s="107"/>
     </row>
     <row r="38" spans="1:18" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="70"/>
-      <c r="B38" s="70"/>
-      <c r="C38" s="70"/>
-      <c r="D38" s="70"/>
-      <c r="E38" s="70"/>
-      <c r="F38" s="70"/>
-      <c r="G38" s="70"/>
-      <c r="H38" s="70"/>
-      <c r="I38" s="70"/>
-      <c r="J38" s="70"/>
-      <c r="K38" s="70"/>
-      <c r="L38" s="70"/>
-      <c r="M38" s="70"/>
-      <c r="N38" s="70"/>
-      <c r="O38" s="70"/>
-      <c r="P38" s="70"/>
-      <c r="Q38" s="70"/>
-      <c r="R38" s="70"/>
+      <c r="A38" s="108"/>
+      <c r="B38" s="108"/>
+      <c r="C38" s="108"/>
+      <c r="D38" s="108"/>
+      <c r="E38" s="108"/>
+      <c r="F38" s="108"/>
+      <c r="G38" s="108"/>
+      <c r="H38" s="108"/>
+      <c r="I38" s="108"/>
+      <c r="J38" s="108"/>
+      <c r="K38" s="108"/>
+      <c r="L38" s="108"/>
+      <c r="M38" s="108"/>
+      <c r="N38" s="108"/>
+      <c r="O38" s="108"/>
+      <c r="P38" s="108"/>
+      <c r="Q38" s="108"/>
+      <c r="R38" s="108"/>
     </row>
     <row r="39" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="57" t="s">
+      <c r="A39" s="95" t="s">
         <v>10</v>
       </c>
-      <c r="B39" s="46"/>
-      <c r="C39" s="46"/>
-      <c r="D39" s="46" t="s">
+      <c r="B39" s="33"/>
+      <c r="C39" s="33"/>
+      <c r="D39" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="E39" s="46"/>
-      <c r="F39" s="46"/>
-      <c r="G39" s="71"/>
-      <c r="H39" s="46" t="s">
+      <c r="E39" s="33"/>
+      <c r="F39" s="33"/>
+      <c r="G39" s="34"/>
+      <c r="H39" s="33" t="s">
         <v>10</v>
       </c>
-      <c r="I39" s="46"/>
-      <c r="J39" s="46"/>
-      <c r="K39" s="46" t="s">
+      <c r="I39" s="33"/>
+      <c r="J39" s="33"/>
+      <c r="K39" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="L39" s="46"/>
-      <c r="M39" s="46"/>
-      <c r="N39" s="71"/>
-      <c r="O39" s="46" t="s">
+      <c r="L39" s="33"/>
+      <c r="M39" s="33"/>
+      <c r="N39" s="34"/>
+      <c r="O39" s="33" t="s">
         <v>20</v>
       </c>
-      <c r="P39" s="46"/>
-      <c r="Q39" s="46"/>
-      <c r="R39" s="47"/>
+      <c r="P39" s="33"/>
+      <c r="Q39" s="33"/>
+      <c r="R39" s="136"/>
     </row>
     <row r="40" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="44"/>
-      <c r="B40" s="45"/>
-      <c r="C40" s="45"/>
-      <c r="D40" s="45"/>
-      <c r="E40" s="45"/>
-      <c r="F40" s="45"/>
-      <c r="G40" s="72"/>
-      <c r="H40" s="45"/>
-      <c r="I40" s="45"/>
-      <c r="J40" s="45"/>
-      <c r="K40" s="45"/>
-      <c r="L40" s="45"/>
-      <c r="M40" s="45"/>
-      <c r="N40" s="72"/>
-      <c r="O40" s="45"/>
-      <c r="P40" s="45"/>
-      <c r="Q40" s="45"/>
-      <c r="R40" s="48"/>
+      <c r="A40" s="92"/>
+      <c r="B40" s="35"/>
+      <c r="C40" s="35"/>
+      <c r="D40" s="35"/>
+      <c r="E40" s="35"/>
+      <c r="F40" s="35"/>
+      <c r="G40" s="36"/>
+      <c r="H40" s="35"/>
+      <c r="I40" s="35"/>
+      <c r="J40" s="35"/>
+      <c r="K40" s="35"/>
+      <c r="L40" s="35"/>
+      <c r="M40" s="35"/>
+      <c r="N40" s="36"/>
+      <c r="O40" s="35"/>
+      <c r="P40" s="35"/>
+      <c r="Q40" s="35"/>
+      <c r="R40" s="137"/>
     </row>
     <row r="41" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="118" t="s">
+      <c r="A41" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="B41" s="119"/>
-      <c r="C41" s="120"/>
-      <c r="D41" s="102"/>
-      <c r="E41" s="103"/>
-      <c r="F41" s="103"/>
-      <c r="G41" s="104"/>
-      <c r="H41" s="108" t="s">
+      <c r="B41" s="28"/>
+      <c r="C41" s="29"/>
+      <c r="D41" s="55"/>
+      <c r="E41" s="56"/>
+      <c r="F41" s="56"/>
+      <c r="G41" s="57"/>
+      <c r="H41" s="77" t="s">
         <v>13</v>
       </c>
-      <c r="I41" s="109"/>
-      <c r="J41" s="110"/>
-      <c r="K41" s="102"/>
-      <c r="L41" s="103"/>
-      <c r="M41" s="103"/>
-      <c r="N41" s="104"/>
-      <c r="O41" s="114"/>
-      <c r="P41" s="114"/>
-      <c r="Q41" s="114"/>
-      <c r="R41" s="115"/>
+      <c r="I41" s="78"/>
+      <c r="J41" s="79"/>
+      <c r="K41" s="55"/>
+      <c r="L41" s="56"/>
+      <c r="M41" s="56"/>
+      <c r="N41" s="57"/>
+      <c r="O41" s="83"/>
+      <c r="P41" s="83"/>
+      <c r="Q41" s="83"/>
+      <c r="R41" s="84"/>
     </row>
     <row r="42" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="121"/>
-      <c r="B42" s="122"/>
-      <c r="C42" s="123"/>
-      <c r="D42" s="105"/>
-      <c r="E42" s="106"/>
-      <c r="F42" s="106"/>
-      <c r="G42" s="107"/>
-      <c r="H42" s="111"/>
-      <c r="I42" s="112"/>
-      <c r="J42" s="113"/>
-      <c r="K42" s="105"/>
-      <c r="L42" s="106"/>
-      <c r="M42" s="106"/>
-      <c r="N42" s="107"/>
-      <c r="O42" s="114"/>
-      <c r="P42" s="114"/>
-      <c r="Q42" s="114"/>
-      <c r="R42" s="115"/>
+      <c r="A42" s="30"/>
+      <c r="B42" s="31"/>
+      <c r="C42" s="32"/>
+      <c r="D42" s="58"/>
+      <c r="E42" s="59"/>
+      <c r="F42" s="59"/>
+      <c r="G42" s="60"/>
+      <c r="H42" s="80"/>
+      <c r="I42" s="81"/>
+      <c r="J42" s="82"/>
+      <c r="K42" s="58"/>
+      <c r="L42" s="59"/>
+      <c r="M42" s="59"/>
+      <c r="N42" s="60"/>
+      <c r="O42" s="83"/>
+      <c r="P42" s="83"/>
+      <c r="Q42" s="83"/>
+      <c r="R42" s="84"/>
     </row>
     <row r="43" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="118" t="s">
+      <c r="A43" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="B43" s="119"/>
-      <c r="C43" s="120"/>
-      <c r="D43" s="102"/>
-      <c r="E43" s="103"/>
-      <c r="F43" s="103"/>
-      <c r="G43" s="104"/>
-      <c r="H43" s="136" t="s">
+      <c r="B43" s="28"/>
+      <c r="C43" s="29"/>
+      <c r="D43" s="55"/>
+      <c r="E43" s="56"/>
+      <c r="F43" s="56"/>
+      <c r="G43" s="57"/>
+      <c r="H43" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="I43" s="119"/>
-      <c r="J43" s="120"/>
-      <c r="K43" s="102"/>
-      <c r="L43" s="103"/>
-      <c r="M43" s="103"/>
-      <c r="N43" s="104"/>
-      <c r="O43" s="114"/>
-      <c r="P43" s="114"/>
-      <c r="Q43" s="114"/>
-      <c r="R43" s="115"/>
+      <c r="I43" s="28"/>
+      <c r="J43" s="29"/>
+      <c r="K43" s="55"/>
+      <c r="L43" s="56"/>
+      <c r="M43" s="56"/>
+      <c r="N43" s="57"/>
+      <c r="O43" s="83"/>
+      <c r="P43" s="83"/>
+      <c r="Q43" s="83"/>
+      <c r="R43" s="84"/>
     </row>
     <row r="44" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="121"/>
-      <c r="B44" s="122"/>
-      <c r="C44" s="123"/>
-      <c r="D44" s="105"/>
-      <c r="E44" s="106"/>
-      <c r="F44" s="106"/>
-      <c r="G44" s="107"/>
-      <c r="H44" s="137"/>
-      <c r="I44" s="122"/>
-      <c r="J44" s="123"/>
-      <c r="K44" s="105"/>
-      <c r="L44" s="106"/>
-      <c r="M44" s="106"/>
-      <c r="N44" s="107"/>
-      <c r="O44" s="114"/>
-      <c r="P44" s="114"/>
-      <c r="Q44" s="114"/>
-      <c r="R44" s="115"/>
+      <c r="A44" s="30"/>
+      <c r="B44" s="31"/>
+      <c r="C44" s="32"/>
+      <c r="D44" s="58"/>
+      <c r="E44" s="59"/>
+      <c r="F44" s="59"/>
+      <c r="G44" s="60"/>
+      <c r="H44" s="62"/>
+      <c r="I44" s="31"/>
+      <c r="J44" s="32"/>
+      <c r="K44" s="58"/>
+      <c r="L44" s="59"/>
+      <c r="M44" s="59"/>
+      <c r="N44" s="60"/>
+      <c r="O44" s="83"/>
+      <c r="P44" s="83"/>
+      <c r="Q44" s="83"/>
+      <c r="R44" s="84"/>
     </row>
     <row r="45" spans="1:18" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A45" s="134" t="s">
+      <c r="A45" s="53" t="s">
         <v>16</v>
       </c>
-      <c r="B45" s="135"/>
-      <c r="C45" s="135"/>
-      <c r="D45" s="100"/>
-      <c r="E45" s="100"/>
-      <c r="F45" s="100"/>
-      <c r="G45" s="101"/>
-      <c r="H45" s="135" t="s">
+      <c r="B45" s="54"/>
+      <c r="C45" s="54"/>
+      <c r="D45" s="75"/>
+      <c r="E45" s="75"/>
+      <c r="F45" s="75"/>
+      <c r="G45" s="76"/>
+      <c r="H45" s="54" t="s">
         <v>16</v>
       </c>
-      <c r="I45" s="135"/>
-      <c r="J45" s="135"/>
-      <c r="K45" s="100"/>
-      <c r="L45" s="100"/>
-      <c r="M45" s="100"/>
-      <c r="N45" s="101"/>
-      <c r="O45" s="116"/>
-      <c r="P45" s="116"/>
-      <c r="Q45" s="116"/>
-      <c r="R45" s="117"/>
+      <c r="I45" s="54"/>
+      <c r="J45" s="54"/>
+      <c r="K45" s="75"/>
+      <c r="L45" s="75"/>
+      <c r="M45" s="75"/>
+      <c r="N45" s="76"/>
+      <c r="O45" s="85"/>
+      <c r="P45" s="85"/>
+      <c r="Q45" s="85"/>
+      <c r="R45" s="86"/>
     </row>
     <row r="46" spans="1:18" ht="20.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.4"/>
     <row r="47" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -2643,128 +2643,128 @@
       </c>
     </row>
     <row r="49" spans="1:18" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="128"/>
-      <c r="B49" s="129"/>
-      <c r="C49" s="130"/>
-      <c r="D49" s="92"/>
-      <c r="E49" s="93"/>
-      <c r="F49" s="93"/>
-      <c r="G49" s="93"/>
-      <c r="H49" s="98"/>
-      <c r="I49" s="92"/>
-      <c r="J49" s="93"/>
-      <c r="K49" s="93"/>
-      <c r="L49" s="93"/>
-      <c r="M49" s="98"/>
-      <c r="N49" s="92"/>
-      <c r="O49" s="93"/>
-      <c r="P49" s="93"/>
-      <c r="Q49" s="93"/>
-      <c r="R49" s="94"/>
+      <c r="A49" s="41"/>
+      <c r="B49" s="42"/>
+      <c r="C49" s="43"/>
+      <c r="D49" s="47"/>
+      <c r="E49" s="48"/>
+      <c r="F49" s="48"/>
+      <c r="G49" s="48"/>
+      <c r="H49" s="49"/>
+      <c r="I49" s="47"/>
+      <c r="J49" s="48"/>
+      <c r="K49" s="48"/>
+      <c r="L49" s="48"/>
+      <c r="M49" s="49"/>
+      <c r="N49" s="47"/>
+      <c r="O49" s="48"/>
+      <c r="P49" s="48"/>
+      <c r="Q49" s="48"/>
+      <c r="R49" s="73"/>
     </row>
     <row r="50" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="131"/>
-      <c r="B50" s="132"/>
-      <c r="C50" s="133"/>
-      <c r="D50" s="95"/>
-      <c r="E50" s="96"/>
-      <c r="F50" s="96"/>
-      <c r="G50" s="96"/>
-      <c r="H50" s="99"/>
-      <c r="I50" s="95"/>
-      <c r="J50" s="96"/>
-      <c r="K50" s="96"/>
-      <c r="L50" s="96"/>
-      <c r="M50" s="99"/>
-      <c r="N50" s="95"/>
-      <c r="O50" s="96"/>
-      <c r="P50" s="96"/>
-      <c r="Q50" s="96"/>
-      <c r="R50" s="97"/>
+      <c r="A50" s="44"/>
+      <c r="B50" s="45"/>
+      <c r="C50" s="46"/>
+      <c r="D50" s="50"/>
+      <c r="E50" s="51"/>
+      <c r="F50" s="51"/>
+      <c r="G50" s="51"/>
+      <c r="H50" s="52"/>
+      <c r="I50" s="50"/>
+      <c r="J50" s="51"/>
+      <c r="K50" s="51"/>
+      <c r="L50" s="51"/>
+      <c r="M50" s="52"/>
+      <c r="N50" s="50"/>
+      <c r="O50" s="51"/>
+      <c r="P50" s="51"/>
+      <c r="Q50" s="51"/>
+      <c r="R50" s="74"/>
     </row>
     <row r="51" spans="1:18" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A51" s="30" t="s">
+      <c r="A51" s="126" t="s">
         <v>18</v>
       </c>
-      <c r="B51" s="31"/>
-      <c r="C51" s="32"/>
-      <c r="D51" s="28"/>
-      <c r="E51" s="28"/>
-      <c r="F51" s="28"/>
-      <c r="G51" s="28"/>
-      <c r="H51" s="28"/>
-      <c r="I51" s="28"/>
-      <c r="J51" s="28"/>
-      <c r="K51" s="28"/>
-      <c r="L51" s="28"/>
-      <c r="M51" s="28"/>
-      <c r="N51" s="28"/>
-      <c r="O51" s="28"/>
-      <c r="P51" s="28"/>
-      <c r="Q51" s="28"/>
-      <c r="R51" s="29"/>
+      <c r="B51" s="127"/>
+      <c r="C51" s="128"/>
+      <c r="D51" s="89"/>
+      <c r="E51" s="89"/>
+      <c r="F51" s="89"/>
+      <c r="G51" s="89"/>
+      <c r="H51" s="89"/>
+      <c r="I51" s="89"/>
+      <c r="J51" s="89"/>
+      <c r="K51" s="89"/>
+      <c r="L51" s="89"/>
+      <c r="M51" s="89"/>
+      <c r="N51" s="89"/>
+      <c r="O51" s="89"/>
+      <c r="P51" s="89"/>
+      <c r="Q51" s="89"/>
+      <c r="R51" s="125"/>
     </row>
     <row r="52" spans="1:18" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A52" s="33"/>
-      <c r="B52" s="34"/>
-      <c r="C52" s="35"/>
-      <c r="D52" s="28"/>
-      <c r="E52" s="28"/>
-      <c r="F52" s="28"/>
-      <c r="G52" s="28"/>
-      <c r="H52" s="28"/>
-      <c r="I52" s="28"/>
-      <c r="J52" s="28"/>
-      <c r="K52" s="28"/>
-      <c r="L52" s="28"/>
-      <c r="M52" s="28"/>
-      <c r="N52" s="28"/>
-      <c r="O52" s="28"/>
-      <c r="P52" s="28"/>
-      <c r="Q52" s="28"/>
-      <c r="R52" s="29"/>
+      <c r="A52" s="129"/>
+      <c r="B52" s="130"/>
+      <c r="C52" s="131"/>
+      <c r="D52" s="89"/>
+      <c r="E52" s="89"/>
+      <c r="F52" s="89"/>
+      <c r="G52" s="89"/>
+      <c r="H52" s="89"/>
+      <c r="I52" s="89"/>
+      <c r="J52" s="89"/>
+      <c r="K52" s="89"/>
+      <c r="L52" s="89"/>
+      <c r="M52" s="89"/>
+      <c r="N52" s="89"/>
+      <c r="O52" s="89"/>
+      <c r="P52" s="89"/>
+      <c r="Q52" s="89"/>
+      <c r="R52" s="125"/>
     </row>
     <row r="53" spans="1:18" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A53" s="73" t="s">
+      <c r="A53" s="109" t="s">
         <v>19</v>
       </c>
-      <c r="B53" s="74"/>
-      <c r="C53" s="75"/>
-      <c r="D53" s="36"/>
-      <c r="E53" s="36"/>
-      <c r="F53" s="36"/>
-      <c r="G53" s="36"/>
-      <c r="H53" s="36"/>
-      <c r="I53" s="36"/>
-      <c r="J53" s="36"/>
-      <c r="K53" s="36"/>
-      <c r="L53" s="36"/>
-      <c r="M53" s="36"/>
-      <c r="N53" s="36"/>
-      <c r="O53" s="36"/>
-      <c r="P53" s="36"/>
-      <c r="Q53" s="36"/>
-      <c r="R53" s="37"/>
+      <c r="B53" s="110"/>
+      <c r="C53" s="111"/>
+      <c r="D53" s="87"/>
+      <c r="E53" s="87"/>
+      <c r="F53" s="87"/>
+      <c r="G53" s="87"/>
+      <c r="H53" s="87"/>
+      <c r="I53" s="87"/>
+      <c r="J53" s="87"/>
+      <c r="K53" s="87"/>
+      <c r="L53" s="87"/>
+      <c r="M53" s="87"/>
+      <c r="N53" s="87"/>
+      <c r="O53" s="87"/>
+      <c r="P53" s="87"/>
+      <c r="Q53" s="87"/>
+      <c r="R53" s="132"/>
     </row>
     <row r="54" spans="1:18" s="2" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="76"/>
-      <c r="B54" s="77"/>
-      <c r="C54" s="78"/>
-      <c r="D54" s="38"/>
-      <c r="E54" s="38"/>
-      <c r="F54" s="38"/>
-      <c r="G54" s="38"/>
-      <c r="H54" s="38"/>
-      <c r="I54" s="38"/>
-      <c r="J54" s="38"/>
-      <c r="K54" s="38"/>
-      <c r="L54" s="38"/>
-      <c r="M54" s="38"/>
-      <c r="N54" s="38"/>
-      <c r="O54" s="38"/>
-      <c r="P54" s="38"/>
-      <c r="Q54" s="38"/>
-      <c r="R54" s="39"/>
+      <c r="A54" s="112"/>
+      <c r="B54" s="113"/>
+      <c r="C54" s="114"/>
+      <c r="D54" s="88"/>
+      <c r="E54" s="88"/>
+      <c r="F54" s="88"/>
+      <c r="G54" s="88"/>
+      <c r="H54" s="88"/>
+      <c r="I54" s="88"/>
+      <c r="J54" s="88"/>
+      <c r="K54" s="88"/>
+      <c r="L54" s="88"/>
+      <c r="M54" s="88"/>
+      <c r="N54" s="88"/>
+      <c r="O54" s="88"/>
+      <c r="P54" s="88"/>
+      <c r="Q54" s="88"/>
+      <c r="R54" s="133"/>
     </row>
     <row r="55" spans="1:18" s="2" customFormat="1" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.15"/>
     <row r="56" spans="1:18" s="2" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -2779,6 +2779,40 @@
   </sheetData>
   <sheetProtection formatCells="0"/>
   <mergeCells count="50">
+    <mergeCell ref="O3:R4"/>
+    <mergeCell ref="D51:H52"/>
+    <mergeCell ref="N51:R52"/>
+    <mergeCell ref="A51:C52"/>
+    <mergeCell ref="N53:R54"/>
+    <mergeCell ref="M31:R32"/>
+    <mergeCell ref="A33:C34"/>
+    <mergeCell ref="O39:R40"/>
+    <mergeCell ref="A35:C36"/>
+    <mergeCell ref="D35:R36"/>
+    <mergeCell ref="A31:C32"/>
+    <mergeCell ref="J31:L32"/>
+    <mergeCell ref="D53:H54"/>
+    <mergeCell ref="I53:M54"/>
+    <mergeCell ref="I51:M52"/>
+    <mergeCell ref="O1:R1"/>
+    <mergeCell ref="A11:R11"/>
+    <mergeCell ref="A22:C28"/>
+    <mergeCell ref="A20:C21"/>
+    <mergeCell ref="D20:R21"/>
+    <mergeCell ref="A15:R15"/>
+    <mergeCell ref="A18:R18"/>
+    <mergeCell ref="D31:I32"/>
+    <mergeCell ref="A37:R38"/>
+    <mergeCell ref="H39:J40"/>
+    <mergeCell ref="A39:C40"/>
+    <mergeCell ref="K39:N40"/>
+    <mergeCell ref="A53:C54"/>
+    <mergeCell ref="O22:R28"/>
+    <mergeCell ref="H41:J42"/>
+    <mergeCell ref="K41:N42"/>
+    <mergeCell ref="O41:R45"/>
+    <mergeCell ref="K43:N44"/>
+    <mergeCell ref="K45:N45"/>
     <mergeCell ref="A43:C44"/>
     <mergeCell ref="D39:G40"/>
     <mergeCell ref="D23:L25"/>
@@ -2795,40 +2829,6 @@
     <mergeCell ref="I49:M50"/>
     <mergeCell ref="D45:G45"/>
     <mergeCell ref="D41:G42"/>
-    <mergeCell ref="H41:J42"/>
-    <mergeCell ref="K41:N42"/>
-    <mergeCell ref="O41:R45"/>
-    <mergeCell ref="K43:N44"/>
-    <mergeCell ref="K45:N45"/>
-    <mergeCell ref="I53:M54"/>
-    <mergeCell ref="I51:M52"/>
-    <mergeCell ref="O1:R1"/>
-    <mergeCell ref="A11:R11"/>
-    <mergeCell ref="A22:C28"/>
-    <mergeCell ref="A20:C21"/>
-    <mergeCell ref="D20:R21"/>
-    <mergeCell ref="A15:R15"/>
-    <mergeCell ref="A18:R18"/>
-    <mergeCell ref="D31:I32"/>
-    <mergeCell ref="A37:R38"/>
-    <mergeCell ref="H39:J40"/>
-    <mergeCell ref="A39:C40"/>
-    <mergeCell ref="K39:N40"/>
-    <mergeCell ref="A53:C54"/>
-    <mergeCell ref="O22:R28"/>
-    <mergeCell ref="O3:R4"/>
-    <mergeCell ref="D51:H52"/>
-    <mergeCell ref="N51:R52"/>
-    <mergeCell ref="A51:C52"/>
-    <mergeCell ref="N53:R54"/>
-    <mergeCell ref="M31:R32"/>
-    <mergeCell ref="A33:C34"/>
-    <mergeCell ref="O39:R40"/>
-    <mergeCell ref="A35:C36"/>
-    <mergeCell ref="D35:R36"/>
-    <mergeCell ref="A31:C32"/>
-    <mergeCell ref="J31:L32"/>
-    <mergeCell ref="D53:H54"/>
   </mergeCells>
   <phoneticPr fontId="20"/>
   <printOptions horizontalCentered="1"/>
@@ -2846,7 +2846,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{980EFC93-3554-4863-A81F-3ECF9A45AFCC}">
-  <dimension ref="B2:N30"/>
+  <dimension ref="B2:N28"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="15" width="4.625" customWidth="1"/>
@@ -2856,62 +2856,62 @@
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="142" t="s">
+      <c r="E2" s="154" t="s">
         <v>21</v>
       </c>
-      <c r="F2" s="142"/>
-      <c r="G2" s="142" t="s">
+      <c r="F2" s="154"/>
+      <c r="G2" s="154" t="s">
         <v>22</v>
       </c>
-      <c r="H2" s="142"/>
-      <c r="I2" s="142" t="s">
+      <c r="H2" s="154"/>
+      <c r="I2" s="154" t="s">
         <v>23</v>
       </c>
-      <c r="J2" s="142"/>
-      <c r="K2" s="142" t="s">
+      <c r="J2" s="154"/>
+      <c r="K2" s="154" t="s">
         <v>24</v>
       </c>
-      <c r="L2" s="142"/>
-      <c r="M2" s="142" t="s">
+      <c r="L2" s="154"/>
+      <c r="M2" s="154" t="s">
         <v>25</v>
       </c>
-      <c r="N2" s="142"/>
+      <c r="N2" s="154"/>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B3" s="140" t="s">
+      <c r="B3" s="151" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="140"/>
+      <c r="C3" s="151"/>
       <c r="D3" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="140"/>
-      <c r="F3" s="140"/>
-      <c r="G3" s="141"/>
-      <c r="H3" s="141"/>
-      <c r="I3" s="140"/>
-      <c r="J3" s="140"/>
-      <c r="K3" s="140"/>
-      <c r="L3" s="140"/>
-      <c r="M3" s="140"/>
-      <c r="N3" s="140"/>
+      <c r="E3" s="151"/>
+      <c r="F3" s="151"/>
+      <c r="G3" s="155"/>
+      <c r="H3" s="155"/>
+      <c r="I3" s="151"/>
+      <c r="J3" s="151"/>
+      <c r="K3" s="151"/>
+      <c r="L3" s="151"/>
+      <c r="M3" s="151"/>
+      <c r="N3" s="151"/>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B4" s="140"/>
-      <c r="C4" s="140"/>
+      <c r="B4" s="151"/>
+      <c r="C4" s="151"/>
       <c r="D4" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="140"/>
-      <c r="F4" s="140"/>
-      <c r="G4" s="140"/>
-      <c r="H4" s="140"/>
-      <c r="I4" s="140"/>
-      <c r="J4" s="140"/>
-      <c r="K4" s="140"/>
-      <c r="L4" s="140"/>
-      <c r="M4" s="140"/>
-      <c r="N4" s="140"/>
+      <c r="E4" s="151"/>
+      <c r="F4" s="151"/>
+      <c r="G4" s="151"/>
+      <c r="H4" s="151"/>
+      <c r="I4" s="151"/>
+      <c r="J4" s="151"/>
+      <c r="K4" s="151"/>
+      <c r="L4" s="151"/>
+      <c r="M4" s="151"/>
+      <c r="N4" s="151"/>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B5" s="1"/>
@@ -2932,62 +2932,62 @@
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
-      <c r="E6" s="147" t="s">
+      <c r="E6" s="149" t="s">
         <v>21</v>
       </c>
-      <c r="F6" s="148"/>
-      <c r="G6" s="147" t="s">
+      <c r="F6" s="150"/>
+      <c r="G6" s="149" t="s">
         <v>22</v>
       </c>
-      <c r="H6" s="148"/>
-      <c r="I6" s="147" t="s">
+      <c r="H6" s="150"/>
+      <c r="I6" s="149" t="s">
         <v>23</v>
       </c>
-      <c r="J6" s="148"/>
-      <c r="K6" s="147" t="s">
+      <c r="J6" s="150"/>
+      <c r="K6" s="149" t="s">
         <v>24</v>
       </c>
-      <c r="L6" s="148"/>
-      <c r="M6" s="147" t="s">
+      <c r="L6" s="150"/>
+      <c r="M6" s="149" t="s">
         <v>25</v>
       </c>
-      <c r="N6" s="148"/>
+      <c r="N6" s="150"/>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B7" s="140" t="s">
+      <c r="B7" s="151" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="140"/>
+      <c r="C7" s="151"/>
       <c r="D7" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="E7" s="143"/>
-      <c r="F7" s="144"/>
-      <c r="G7" s="145"/>
-      <c r="H7" s="146"/>
-      <c r="I7" s="143"/>
-      <c r="J7" s="144"/>
-      <c r="K7" s="143"/>
-      <c r="L7" s="144"/>
-      <c r="M7" s="143"/>
-      <c r="N7" s="144"/>
+      <c r="E7" s="147"/>
+      <c r="F7" s="148"/>
+      <c r="G7" s="152"/>
+      <c r="H7" s="153"/>
+      <c r="I7" s="147"/>
+      <c r="J7" s="148"/>
+      <c r="K7" s="147"/>
+      <c r="L7" s="148"/>
+      <c r="M7" s="147"/>
+      <c r="N7" s="148"/>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B8" s="140"/>
-      <c r="C8" s="140"/>
+      <c r="B8" s="151"/>
+      <c r="C8" s="151"/>
       <c r="D8" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="E8" s="143"/>
-      <c r="F8" s="144"/>
-      <c r="G8" s="143"/>
-      <c r="H8" s="144"/>
-      <c r="I8" s="143"/>
-      <c r="J8" s="144"/>
-      <c r="K8" s="143"/>
-      <c r="L8" s="144"/>
-      <c r="M8" s="143"/>
-      <c r="N8" s="144"/>
+      <c r="E8" s="147"/>
+      <c r="F8" s="148"/>
+      <c r="G8" s="147"/>
+      <c r="H8" s="148"/>
+      <c r="I8" s="147"/>
+      <c r="J8" s="148"/>
+      <c r="K8" s="147"/>
+      <c r="L8" s="148"/>
+      <c r="M8" s="147"/>
+      <c r="N8" s="148"/>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B9" s="1"/>
@@ -3008,62 +3008,62 @@
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
-      <c r="E10" s="147" t="s">
+      <c r="E10" s="149" t="s">
         <v>21</v>
       </c>
-      <c r="F10" s="148"/>
-      <c r="G10" s="147" t="s">
+      <c r="F10" s="150"/>
+      <c r="G10" s="149" t="s">
         <v>22</v>
       </c>
-      <c r="H10" s="148"/>
-      <c r="I10" s="147" t="s">
+      <c r="H10" s="150"/>
+      <c r="I10" s="149" t="s">
         <v>23</v>
       </c>
-      <c r="J10" s="148"/>
-      <c r="K10" s="147" t="s">
+      <c r="J10" s="150"/>
+      <c r="K10" s="149" t="s">
         <v>24</v>
       </c>
-      <c r="L10" s="148"/>
-      <c r="M10" s="147" t="s">
+      <c r="L10" s="150"/>
+      <c r="M10" s="149" t="s">
         <v>25</v>
       </c>
-      <c r="N10" s="148"/>
+      <c r="N10" s="150"/>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B11" s="140" t="s">
+      <c r="B11" s="151" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="140"/>
+      <c r="C11" s="151"/>
       <c r="D11" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="E11" s="143"/>
-      <c r="F11" s="144"/>
-      <c r="G11" s="145"/>
-      <c r="H11" s="146"/>
-      <c r="I11" s="143"/>
-      <c r="J11" s="144"/>
-      <c r="K11" s="143"/>
-      <c r="L11" s="144"/>
-      <c r="M11" s="143"/>
-      <c r="N11" s="144"/>
+      <c r="E11" s="147"/>
+      <c r="F11" s="148"/>
+      <c r="G11" s="152"/>
+      <c r="H11" s="153"/>
+      <c r="I11" s="147"/>
+      <c r="J11" s="148"/>
+      <c r="K11" s="147"/>
+      <c r="L11" s="148"/>
+      <c r="M11" s="147"/>
+      <c r="N11" s="148"/>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B12" s="140"/>
-      <c r="C12" s="140"/>
+      <c r="B12" s="151"/>
+      <c r="C12" s="151"/>
       <c r="D12" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="E12" s="143"/>
-      <c r="F12" s="144"/>
-      <c r="G12" s="143"/>
-      <c r="H12" s="144"/>
-      <c r="I12" s="143"/>
-      <c r="J12" s="144"/>
-      <c r="K12" s="143"/>
-      <c r="L12" s="144"/>
-      <c r="M12" s="143"/>
-      <c r="N12" s="144"/>
+      <c r="E12" s="147"/>
+      <c r="F12" s="148"/>
+      <c r="G12" s="147"/>
+      <c r="H12" s="148"/>
+      <c r="I12" s="147"/>
+      <c r="J12" s="148"/>
+      <c r="K12" s="147"/>
+      <c r="L12" s="148"/>
+      <c r="M12" s="147"/>
+      <c r="N12" s="148"/>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B13" s="1"/>
@@ -3099,285 +3099,195 @@
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
-      <c r="E15" s="147" t="s">
+      <c r="E15" s="149" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="148"/>
-      <c r="G15" s="147" t="s">
+      <c r="F15" s="150"/>
+      <c r="G15" s="149" t="s">
         <v>22</v>
       </c>
-      <c r="H15" s="148"/>
-      <c r="I15" s="147" t="s">
+      <c r="H15" s="150"/>
+      <c r="I15" s="149" t="s">
         <v>23</v>
       </c>
-      <c r="J15" s="148"/>
-      <c r="K15" s="147" t="s">
+      <c r="J15" s="150"/>
+      <c r="K15" s="149" t="s">
         <v>24</v>
       </c>
-      <c r="L15" s="148"/>
-      <c r="M15" s="147" t="s">
+      <c r="L15" s="150"/>
+      <c r="M15" s="149" t="s">
         <v>25</v>
       </c>
-      <c r="N15" s="148"/>
+      <c r="N15" s="150"/>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B16" s="140" t="s">
+      <c r="B16" s="151" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="140"/>
+      <c r="C16" s="151"/>
       <c r="D16" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="E16" s="143"/>
-      <c r="F16" s="144"/>
-      <c r="G16" s="145"/>
-      <c r="H16" s="146"/>
-      <c r="I16" s="143"/>
-      <c r="J16" s="144"/>
-      <c r="K16" s="143"/>
-      <c r="L16" s="144"/>
-      <c r="M16" s="143"/>
-      <c r="N16" s="144"/>
+      <c r="E16" s="147"/>
+      <c r="F16" s="148"/>
+      <c r="G16" s="152"/>
+      <c r="H16" s="153"/>
+      <c r="I16" s="147"/>
+      <c r="J16" s="148"/>
+      <c r="K16" s="147"/>
+      <c r="L16" s="148"/>
+      <c r="M16" s="147"/>
+      <c r="N16" s="148"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B17" s="140"/>
-      <c r="C17" s="140"/>
+      <c r="B17" s="151"/>
+      <c r="C17" s="151"/>
       <c r="D17" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="E17" s="143"/>
-      <c r="F17" s="144"/>
-      <c r="G17" s="143"/>
-      <c r="H17" s="144"/>
-      <c r="I17" s="143"/>
-      <c r="J17" s="144"/>
-      <c r="K17" s="143"/>
-      <c r="L17" s="144"/>
-      <c r="M17" s="143"/>
-      <c r="N17" s="144"/>
+      <c r="E17" s="147"/>
+      <c r="F17" s="148"/>
+      <c r="G17" s="147"/>
+      <c r="H17" s="148"/>
+      <c r="I17" s="147"/>
+      <c r="J17" s="148"/>
+      <c r="K17" s="147"/>
+      <c r="L17" s="148"/>
+      <c r="M17" s="147"/>
+      <c r="N17" s="148"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B20" s="138"/>
-      <c r="C20" s="138"/>
-      <c r="D20" s="138"/>
-      <c r="E20" s="138" t="s">
+      <c r="B20" s="144"/>
+      <c r="C20" s="144"/>
+      <c r="D20" s="144"/>
+      <c r="E20" s="144" t="s">
         <v>32</v>
       </c>
-      <c r="F20" s="138"/>
-      <c r="I20" s="138"/>
-      <c r="J20" s="138"/>
-      <c r="K20" s="138"/>
-      <c r="L20" s="138" t="s">
+      <c r="F20" s="144"/>
+      <c r="I20" s="144"/>
+      <c r="J20" s="144"/>
+      <c r="K20" s="144"/>
+      <c r="L20" s="144" t="s">
         <v>32</v>
       </c>
-      <c r="M20" s="138"/>
+      <c r="M20" s="144"/>
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B21" s="138" t="s">
+      <c r="B21" s="144" t="s">
         <v>33</v>
       </c>
-      <c r="C21" s="138"/>
-      <c r="D21" s="138"/>
-      <c r="E21" s="139"/>
-      <c r="F21" s="139"/>
-      <c r="I21" s="138" t="s">
+      <c r="C21" s="144"/>
+      <c r="D21" s="144"/>
+      <c r="E21" s="145"/>
+      <c r="F21" s="145"/>
+      <c r="I21" s="144" t="s">
         <v>43</v>
       </c>
-      <c r="J21" s="138"/>
-      <c r="K21" s="138"/>
-      <c r="L21" s="139"/>
-      <c r="M21" s="139"/>
+      <c r="J21" s="144"/>
+      <c r="K21" s="144"/>
+      <c r="L21" s="145"/>
+      <c r="M21" s="145"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B22" s="138" t="s">
+      <c r="B22" s="144" t="s">
         <v>34</v>
       </c>
-      <c r="C22" s="138"/>
-      <c r="D22" s="138"/>
-      <c r="E22" s="139"/>
-      <c r="F22" s="139"/>
-      <c r="I22" s="138" t="s">
+      <c r="C22" s="144"/>
+      <c r="D22" s="144"/>
+      <c r="E22" s="145"/>
+      <c r="F22" s="145"/>
+      <c r="I22" s="144" t="s">
         <v>44</v>
       </c>
-      <c r="J22" s="138"/>
-      <c r="K22" s="138"/>
-      <c r="L22" s="139"/>
-      <c r="M22" s="139"/>
+      <c r="J22" s="144"/>
+      <c r="K22" s="144"/>
+      <c r="L22" s="145"/>
+      <c r="M22" s="145"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B23" s="138" t="s">
+      <c r="B23" s="144" t="s">
         <v>35</v>
       </c>
-      <c r="C23" s="138"/>
-      <c r="D23" s="138"/>
-      <c r="E23" s="139"/>
-      <c r="F23" s="139"/>
-      <c r="I23" s="138" t="s">
+      <c r="C23" s="144"/>
+      <c r="D23" s="144"/>
+      <c r="E23" s="145"/>
+      <c r="F23" s="145"/>
+      <c r="I23" s="144" t="s">
         <v>45</v>
       </c>
-      <c r="J23" s="138"/>
-      <c r="K23" s="138"/>
-      <c r="L23" s="139"/>
-      <c r="M23" s="139"/>
+      <c r="J23" s="144"/>
+      <c r="K23" s="144"/>
+      <c r="L23" s="145"/>
+      <c r="M23" s="145"/>
     </row>
     <row r="24" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B24" s="138" t="s">
+      <c r="B24" s="144" t="s">
         <v>36</v>
       </c>
-      <c r="C24" s="138"/>
-      <c r="D24" s="138"/>
-      <c r="E24" s="139"/>
-      <c r="F24" s="139"/>
-      <c r="I24" s="138" t="s">
+      <c r="C24" s="144"/>
+      <c r="D24" s="144"/>
+      <c r="E24" s="145"/>
+      <c r="F24" s="145"/>
+      <c r="I24" s="144" t="s">
         <v>46</v>
       </c>
-      <c r="J24" s="138"/>
-      <c r="K24" s="138"/>
-      <c r="L24" s="139"/>
-      <c r="M24" s="139"/>
+      <c r="J24" s="144"/>
+      <c r="K24" s="144"/>
+      <c r="L24" s="145"/>
+      <c r="M24" s="145"/>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B25" s="138" t="s">
+      <c r="B25" s="144" t="s">
         <v>37</v>
       </c>
-      <c r="C25" s="138"/>
-      <c r="D25" s="138"/>
-      <c r="E25" s="139"/>
-      <c r="F25" s="139"/>
+      <c r="C25" s="144"/>
+      <c r="D25" s="144"/>
+      <c r="E25" s="145"/>
+      <c r="F25" s="145"/>
+      <c r="I25" s="144" t="s">
+        <v>38</v>
+      </c>
+      <c r="J25" s="144"/>
+      <c r="K25" s="144"/>
+      <c r="L25" s="145"/>
+      <c r="M25" s="145"/>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B26" s="138" t="s">
-        <v>38</v>
-      </c>
-      <c r="C26" s="138"/>
-      <c r="D26" s="138"/>
-      <c r="E26" s="139"/>
-      <c r="F26" s="139"/>
+      <c r="B26" s="144" t="s">
+        <v>39</v>
+      </c>
+      <c r="C26" s="144"/>
+      <c r="D26" s="144"/>
+      <c r="E26" s="146"/>
+      <c r="F26" s="146"/>
+      <c r="I26" s="144" t="s">
+        <v>42</v>
+      </c>
+      <c r="J26" s="144"/>
+      <c r="K26" s="144"/>
+      <c r="L26" s="145"/>
+      <c r="M26" s="145"/>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B27" s="138" t="s">
-        <v>39</v>
-      </c>
-      <c r="C27" s="138"/>
-      <c r="D27" s="138"/>
-      <c r="E27" s="149"/>
-      <c r="F27" s="149"/>
+      <c r="B27" s="144" t="s">
+        <v>40</v>
+      </c>
+      <c r="C27" s="144"/>
+      <c r="D27" s="144"/>
+      <c r="E27" s="145"/>
+      <c r="F27" s="145"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B28" s="138" t="s">
-        <v>40</v>
-      </c>
-      <c r="C28" s="138"/>
-      <c r="D28" s="138"/>
-      <c r="E28" s="139"/>
-      <c r="F28" s="139"/>
-    </row>
-    <row r="29" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B29" s="138" t="s">
+      <c r="B28" s="144" t="s">
         <v>41</v>
       </c>
-      <c r="C29" s="138"/>
-      <c r="D29" s="138"/>
-      <c r="E29" s="139"/>
-      <c r="F29" s="139"/>
-    </row>
-    <row r="30" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B30" s="138" t="s">
-        <v>42</v>
-      </c>
-      <c r="C30" s="138"/>
-      <c r="D30" s="138"/>
-      <c r="E30" s="139"/>
-      <c r="F30" s="139"/>
+      <c r="C28" s="144"/>
+      <c r="D28" s="144"/>
+      <c r="E28" s="145"/>
+      <c r="F28" s="145"/>
     </row>
   </sheetData>
   <mergeCells count="96">
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="K15:L15"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="B16:C17"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="K16:L16"/>
-    <mergeCell ref="M11:N11"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="M10:N10"/>
-    <mergeCell ref="B11:C12"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="M7:N7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="M8:N8"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="B7:C8"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="B3:C4"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="K3:L3"/>
     <mergeCell ref="I23:K23"/>
     <mergeCell ref="L23:M23"/>
     <mergeCell ref="I24:K24"/>
@@ -3388,6 +3298,92 @@
     <mergeCell ref="L21:M21"/>
     <mergeCell ref="I22:K22"/>
     <mergeCell ref="L22:M22"/>
+    <mergeCell ref="B3:C4"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="B7:C8"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="M8:N8"/>
+    <mergeCell ref="B11:C12"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="B16:C17"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="K16:L16"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="I26:K26"/>
+    <mergeCell ref="L26:M26"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="I25:K25"/>
+    <mergeCell ref="L25:M25"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="E27:F27"/>
   </mergeCells>
   <phoneticPr fontId="20"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/storage/app/estimateTemplate/comprehensiveOfRecommend.xlsx
+++ b/storage/app/estimateTemplate/comprehensiveOfRecommend.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yokoyama\Desktop\修正用ふぉうるだ\estimateTemplate\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\ohno\eruful\mitumo\storage\app\estimateTemplate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46EF2F5B-DCDB-4959-92E3-5DC6579A0002}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67448822-BB5A-46C1-A468-84E003EFF818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="45" yWindow="90" windowWidth="28755" windowHeight="15435" activeTab="1" xr2:uid="{0E9C5CA5-184F-4C06-AA15-1AF55B55AFB9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0E9C5CA5-184F-4C06-AA15-1AF55B55AFB9}"/>
   </bookViews>
   <sheets>
     <sheet name="おすすめ(総合)" sheetId="2" r:id="rId1"/>
@@ -1208,193 +1208,97 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="18" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="18" fillId="0" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="9" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="9" fillId="0" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="9" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="9" fillId="0" borderId="29" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="24" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="26" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="8" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="28" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="180" fontId="16" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="16" fillId="0" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="16" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="16" fillId="0" borderId="29" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="9" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="9" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="58" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -1404,18 +1308,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -1440,12 +1332,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1455,6 +1341,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="2" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1500,65 +1392,173 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="181" fontId="9" fillId="0" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="9" fillId="0" borderId="29" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="24" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="8" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="28" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="26" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="16" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="16" fillId="0" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="16" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="16" fillId="0" borderId="29" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1566,34 +1566,34 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="35" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="33" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="34" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="33" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="34" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="33" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="34" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="35" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1666,9 +1666,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 テーマ">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1706,7 +1706,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1812,7 +1812,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1954,7 +1954,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1972,10 +1972,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="O1" s="90"/>
-      <c r="P1" s="90"/>
-      <c r="Q1" s="90"/>
-      <c r="R1" s="90"/>
+      <c r="O1" s="58"/>
+      <c r="P1" s="58"/>
+      <c r="Q1" s="58"/>
+      <c r="R1" s="58"/>
     </row>
     <row r="2" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="O2" s="25"/>
@@ -1985,16 +1985,16 @@
     </row>
     <row r="3" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A3" s="3"/>
-      <c r="O3" s="124"/>
-      <c r="P3" s="124"/>
-      <c r="Q3" s="124"/>
-      <c r="R3" s="124"/>
+      <c r="O3" s="27"/>
+      <c r="P3" s="27"/>
+      <c r="Q3" s="27"/>
+      <c r="R3" s="27"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="O4" s="124"/>
-      <c r="P4" s="124"/>
-      <c r="Q4" s="124"/>
-      <c r="R4" s="124"/>
+      <c r="O4" s="27"/>
+      <c r="P4" s="27"/>
+      <c r="Q4" s="27"/>
+      <c r="R4" s="27"/>
     </row>
     <row r="5" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="N5" s="24"/>
@@ -2057,196 +2057,196 @@
       <c r="R10" s="20"/>
     </row>
     <row r="11" spans="1:18" ht="21" x14ac:dyDescent="0.4">
-      <c r="A11" s="91" t="s">
+      <c r="A11" s="59" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="91"/>
-      <c r="C11" s="91"/>
-      <c r="D11" s="91"/>
-      <c r="E11" s="91"/>
-      <c r="F11" s="91"/>
-      <c r="G11" s="91"/>
-      <c r="H11" s="91"/>
-      <c r="I11" s="91"/>
-      <c r="J11" s="91"/>
-      <c r="K11" s="91"/>
-      <c r="L11" s="91"/>
-      <c r="M11" s="91"/>
-      <c r="N11" s="91"/>
-      <c r="O11" s="91"/>
-      <c r="P11" s="91"/>
-      <c r="Q11" s="91"/>
-      <c r="R11" s="91"/>
+      <c r="B11" s="59"/>
+      <c r="C11" s="59"/>
+      <c r="D11" s="59"/>
+      <c r="E11" s="59"/>
+      <c r="F11" s="59"/>
+      <c r="G11" s="59"/>
+      <c r="H11" s="59"/>
+      <c r="I11" s="59"/>
+      <c r="J11" s="59"/>
+      <c r="K11" s="59"/>
+      <c r="L11" s="59"/>
+      <c r="M11" s="59"/>
+      <c r="N11" s="59"/>
+      <c r="O11" s="59"/>
+      <c r="P11" s="59"/>
+      <c r="Q11" s="59"/>
+      <c r="R11" s="59"/>
     </row>
     <row r="14" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="15" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
-      <c r="A15" s="102" t="s">
+      <c r="A15" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="B15" s="102"/>
-      <c r="C15" s="102"/>
-      <c r="D15" s="102"/>
-      <c r="E15" s="102"/>
-      <c r="F15" s="102"/>
-      <c r="G15" s="102"/>
-      <c r="H15" s="102"/>
-      <c r="I15" s="102"/>
-      <c r="J15" s="102"/>
-      <c r="K15" s="102"/>
-      <c r="L15" s="102"/>
-      <c r="M15" s="102"/>
-      <c r="N15" s="102"/>
-      <c r="O15" s="102"/>
-      <c r="P15" s="102"/>
-      <c r="Q15" s="102"/>
-      <c r="R15" s="102"/>
+      <c r="B15" s="66"/>
+      <c r="C15" s="66"/>
+      <c r="D15" s="66"/>
+      <c r="E15" s="66"/>
+      <c r="F15" s="66"/>
+      <c r="G15" s="66"/>
+      <c r="H15" s="66"/>
+      <c r="I15" s="66"/>
+      <c r="J15" s="66"/>
+      <c r="K15" s="66"/>
+      <c r="L15" s="66"/>
+      <c r="M15" s="66"/>
+      <c r="N15" s="66"/>
+      <c r="O15" s="66"/>
+      <c r="P15" s="66"/>
+      <c r="Q15" s="66"/>
+      <c r="R15" s="66"/>
     </row>
     <row r="18" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
-      <c r="A18" s="103" t="s">
+      <c r="A18" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="B18" s="103"/>
-      <c r="C18" s="103"/>
-      <c r="D18" s="103"/>
-      <c r="E18" s="103"/>
-      <c r="F18" s="103"/>
-      <c r="G18" s="103"/>
-      <c r="H18" s="103"/>
-      <c r="I18" s="103"/>
-      <c r="J18" s="103"/>
-      <c r="K18" s="103"/>
-      <c r="L18" s="103"/>
-      <c r="M18" s="103"/>
-      <c r="N18" s="103"/>
-      <c r="O18" s="103"/>
-      <c r="P18" s="103"/>
-      <c r="Q18" s="103"/>
-      <c r="R18" s="103"/>
+      <c r="B18" s="67"/>
+      <c r="C18" s="67"/>
+      <c r="D18" s="67"/>
+      <c r="E18" s="67"/>
+      <c r="F18" s="67"/>
+      <c r="G18" s="67"/>
+      <c r="H18" s="67"/>
+      <c r="I18" s="67"/>
+      <c r="J18" s="67"/>
+      <c r="K18" s="67"/>
+      <c r="L18" s="67"/>
+      <c r="M18" s="67"/>
+      <c r="N18" s="67"/>
+      <c r="O18" s="67"/>
+      <c r="P18" s="67"/>
+      <c r="Q18" s="67"/>
+      <c r="R18" s="67"/>
     </row>
     <row r="19" spans="1:18" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="20" spans="1:18" ht="12.75" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="95" t="s">
+      <c r="A20" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="B20" s="33"/>
-      <c r="C20" s="33"/>
-      <c r="D20" s="96"/>
-      <c r="E20" s="97"/>
-      <c r="F20" s="97"/>
-      <c r="G20" s="97"/>
-      <c r="H20" s="97"/>
-      <c r="I20" s="97"/>
-      <c r="J20" s="97"/>
-      <c r="K20" s="97"/>
-      <c r="L20" s="97"/>
-      <c r="M20" s="97"/>
-      <c r="N20" s="97"/>
-      <c r="O20" s="97"/>
-      <c r="P20" s="97"/>
-      <c r="Q20" s="97"/>
-      <c r="R20" s="98"/>
+      <c r="B20" s="46"/>
+      <c r="C20" s="46"/>
+      <c r="D20" s="60"/>
+      <c r="E20" s="61"/>
+      <c r="F20" s="61"/>
+      <c r="G20" s="61"/>
+      <c r="H20" s="61"/>
+      <c r="I20" s="61"/>
+      <c r="J20" s="61"/>
+      <c r="K20" s="61"/>
+      <c r="L20" s="61"/>
+      <c r="M20" s="61"/>
+      <c r="N20" s="61"/>
+      <c r="O20" s="61"/>
+      <c r="P20" s="61"/>
+      <c r="Q20" s="61"/>
+      <c r="R20" s="62"/>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A21" s="92"/>
-      <c r="B21" s="35"/>
-      <c r="C21" s="35"/>
-      <c r="D21" s="99"/>
-      <c r="E21" s="100"/>
-      <c r="F21" s="100"/>
-      <c r="G21" s="100"/>
-      <c r="H21" s="100"/>
-      <c r="I21" s="100"/>
-      <c r="J21" s="100"/>
-      <c r="K21" s="100"/>
-      <c r="L21" s="100"/>
-      <c r="M21" s="100"/>
-      <c r="N21" s="100"/>
-      <c r="O21" s="100"/>
-      <c r="P21" s="100"/>
-      <c r="Q21" s="100"/>
-      <c r="R21" s="101"/>
+      <c r="A21" s="44"/>
+      <c r="B21" s="45"/>
+      <c r="C21" s="45"/>
+      <c r="D21" s="63"/>
+      <c r="E21" s="64"/>
+      <c r="F21" s="64"/>
+      <c r="G21" s="64"/>
+      <c r="H21" s="64"/>
+      <c r="I21" s="64"/>
+      <c r="J21" s="64"/>
+      <c r="K21" s="64"/>
+      <c r="L21" s="64"/>
+      <c r="M21" s="64"/>
+      <c r="N21" s="64"/>
+      <c r="O21" s="64"/>
+      <c r="P21" s="64"/>
+      <c r="Q21" s="64"/>
+      <c r="R21" s="65"/>
     </row>
     <row r="22" spans="1:18" ht="5.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="92" t="s">
+      <c r="A22" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="B22" s="35"/>
-      <c r="C22" s="35"/>
+      <c r="B22" s="45"/>
+      <c r="C22" s="45"/>
       <c r="D22" s="19"/>
       <c r="L22" s="18"/>
-      <c r="M22" s="69" t="s">
+      <c r="M22" s="138" t="s">
         <v>5</v>
       </c>
-      <c r="N22" s="70"/>
-      <c r="O22" s="115"/>
-      <c r="P22" s="116"/>
-      <c r="Q22" s="116"/>
-      <c r="R22" s="117"/>
+      <c r="N22" s="139"/>
+      <c r="O22" s="79"/>
+      <c r="P22" s="80"/>
+      <c r="Q22" s="80"/>
+      <c r="R22" s="81"/>
     </row>
     <row r="23" spans="1:18" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="92"/>
-      <c r="B23" s="35"/>
-      <c r="C23" s="35"/>
-      <c r="D23" s="37"/>
-      <c r="E23" s="38"/>
-      <c r="F23" s="38"/>
-      <c r="G23" s="38"/>
-      <c r="H23" s="38"/>
-      <c r="I23" s="38"/>
-      <c r="J23" s="38"/>
-      <c r="K23" s="38"/>
-      <c r="L23" s="39"/>
-      <c r="M23" s="69"/>
-      <c r="N23" s="70"/>
-      <c r="O23" s="118"/>
-      <c r="P23" s="119"/>
-      <c r="Q23" s="119"/>
-      <c r="R23" s="120"/>
+      <c r="A23" s="44"/>
+      <c r="B23" s="45"/>
+      <c r="C23" s="45"/>
+      <c r="D23" s="112"/>
+      <c r="E23" s="113"/>
+      <c r="F23" s="113"/>
+      <c r="G23" s="113"/>
+      <c r="H23" s="113"/>
+      <c r="I23" s="113"/>
+      <c r="J23" s="113"/>
+      <c r="K23" s="113"/>
+      <c r="L23" s="114"/>
+      <c r="M23" s="138"/>
+      <c r="N23" s="139"/>
+      <c r="O23" s="82"/>
+      <c r="P23" s="83"/>
+      <c r="Q23" s="83"/>
+      <c r="R23" s="84"/>
     </row>
     <row r="24" spans="1:18" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="92"/>
-      <c r="B24" s="35"/>
-      <c r="C24" s="35"/>
-      <c r="D24" s="40"/>
-      <c r="E24" s="38"/>
-      <c r="F24" s="38"/>
-      <c r="G24" s="38"/>
-      <c r="H24" s="38"/>
-      <c r="I24" s="38"/>
-      <c r="J24" s="38"/>
-      <c r="K24" s="38"/>
-      <c r="L24" s="39"/>
-      <c r="M24" s="69"/>
-      <c r="N24" s="70"/>
-      <c r="O24" s="118"/>
-      <c r="P24" s="119"/>
-      <c r="Q24" s="119"/>
-      <c r="R24" s="120"/>
+      <c r="A24" s="44"/>
+      <c r="B24" s="45"/>
+      <c r="C24" s="45"/>
+      <c r="D24" s="115"/>
+      <c r="E24" s="113"/>
+      <c r="F24" s="113"/>
+      <c r="G24" s="113"/>
+      <c r="H24" s="113"/>
+      <c r="I24" s="113"/>
+      <c r="J24" s="113"/>
+      <c r="K24" s="113"/>
+      <c r="L24" s="114"/>
+      <c r="M24" s="138"/>
+      <c r="N24" s="139"/>
+      <c r="O24" s="82"/>
+      <c r="P24" s="83"/>
+      <c r="Q24" s="83"/>
+      <c r="R24" s="84"/>
     </row>
     <row r="25" spans="1:18" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="92"/>
-      <c r="B25" s="35"/>
-      <c r="C25" s="35"/>
-      <c r="D25" s="40"/>
-      <c r="E25" s="38"/>
-      <c r="F25" s="38"/>
-      <c r="G25" s="38"/>
-      <c r="H25" s="38"/>
-      <c r="I25" s="38"/>
-      <c r="J25" s="38"/>
-      <c r="K25" s="38"/>
-      <c r="L25" s="39"/>
-      <c r="M25" s="69"/>
-      <c r="N25" s="70"/>
-      <c r="O25" s="118"/>
-      <c r="P25" s="119"/>
-      <c r="Q25" s="119"/>
-      <c r="R25" s="120"/>
+      <c r="A25" s="44"/>
+      <c r="B25" s="45"/>
+      <c r="C25" s="45"/>
+      <c r="D25" s="115"/>
+      <c r="E25" s="113"/>
+      <c r="F25" s="113"/>
+      <c r="G25" s="113"/>
+      <c r="H25" s="113"/>
+      <c r="I25" s="113"/>
+      <c r="J25" s="113"/>
+      <c r="K25" s="113"/>
+      <c r="L25" s="114"/>
+      <c r="M25" s="138"/>
+      <c r="N25" s="139"/>
+      <c r="O25" s="82"/>
+      <c r="P25" s="83"/>
+      <c r="Q25" s="83"/>
+      <c r="R25" s="84"/>
     </row>
     <row r="26" spans="1:18" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="92"/>
-      <c r="B26" s="35"/>
-      <c r="C26" s="35"/>
+      <c r="A26" s="44"/>
+      <c r="B26" s="45"/>
+      <c r="C26" s="45"/>
       <c r="D26" s="17"/>
       <c r="E26" s="16"/>
       <c r="F26" s="15"/>
@@ -2256,17 +2256,17 @@
       <c r="J26" s="14"/>
       <c r="K26" s="14"/>
       <c r="L26" s="13"/>
-      <c r="M26" s="69"/>
-      <c r="N26" s="70"/>
-      <c r="O26" s="118"/>
-      <c r="P26" s="119"/>
-      <c r="Q26" s="119"/>
-      <c r="R26" s="120"/>
+      <c r="M26" s="138"/>
+      <c r="N26" s="139"/>
+      <c r="O26" s="82"/>
+      <c r="P26" s="83"/>
+      <c r="Q26" s="83"/>
+      <c r="R26" s="84"/>
     </row>
     <row r="27" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="92"/>
-      <c r="B27" s="35"/>
-      <c r="C27" s="35"/>
+      <c r="A27" s="44"/>
+      <c r="B27" s="45"/>
+      <c r="C27" s="45"/>
       <c r="D27" s="12"/>
       <c r="F27" s="10"/>
       <c r="G27" s="11"/>
@@ -2274,17 +2274,17 @@
       <c r="I27" s="9"/>
       <c r="J27" s="9"/>
       <c r="L27" s="8"/>
-      <c r="M27" s="69"/>
-      <c r="N27" s="70"/>
-      <c r="O27" s="118"/>
-      <c r="P27" s="119"/>
-      <c r="Q27" s="119"/>
-      <c r="R27" s="120"/>
+      <c r="M27" s="138"/>
+      <c r="N27" s="139"/>
+      <c r="O27" s="82"/>
+      <c r="P27" s="83"/>
+      <c r="Q27" s="83"/>
+      <c r="R27" s="84"/>
     </row>
     <row r="28" spans="1:18" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="93"/>
-      <c r="B28" s="94"/>
-      <c r="C28" s="94"/>
+      <c r="A28" s="49"/>
+      <c r="B28" s="50"/>
+      <c r="C28" s="50"/>
       <c r="D28" s="7"/>
       <c r="E28" s="6"/>
       <c r="F28" s="6"/>
@@ -2294,344 +2294,344 @@
       <c r="J28" s="6"/>
       <c r="K28" s="6"/>
       <c r="L28" s="5"/>
-      <c r="M28" s="71"/>
-      <c r="N28" s="72"/>
-      <c r="O28" s="121"/>
-      <c r="P28" s="122"/>
-      <c r="Q28" s="122"/>
-      <c r="R28" s="123"/>
+      <c r="M28" s="140"/>
+      <c r="N28" s="141"/>
+      <c r="O28" s="85"/>
+      <c r="P28" s="86"/>
+      <c r="Q28" s="86"/>
+      <c r="R28" s="87"/>
     </row>
     <row r="29" spans="1:18" ht="12.75" thickTop="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="1:18" ht="12.75" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="31" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="95" t="s">
+      <c r="A31" s="57" t="s">
         <v>6</v>
       </c>
-      <c r="B31" s="33"/>
-      <c r="C31" s="33"/>
-      <c r="D31" s="104"/>
-      <c r="E31" s="104"/>
-      <c r="F31" s="104"/>
-      <c r="G31" s="104"/>
-      <c r="H31" s="104"/>
-      <c r="I31" s="104"/>
-      <c r="J31" s="33" t="s">
+      <c r="B31" s="46"/>
+      <c r="C31" s="46"/>
+      <c r="D31" s="40"/>
+      <c r="E31" s="40"/>
+      <c r="F31" s="40"/>
+      <c r="G31" s="40"/>
+      <c r="H31" s="40"/>
+      <c r="I31" s="40"/>
+      <c r="J31" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="K31" s="33"/>
-      <c r="L31" s="33"/>
-      <c r="M31" s="104"/>
-      <c r="N31" s="104"/>
-      <c r="O31" s="104"/>
-      <c r="P31" s="104"/>
-      <c r="Q31" s="104"/>
-      <c r="R31" s="134"/>
+      <c r="K31" s="46"/>
+      <c r="L31" s="46"/>
+      <c r="M31" s="40"/>
+      <c r="N31" s="40"/>
+      <c r="O31" s="40"/>
+      <c r="P31" s="40"/>
+      <c r="Q31" s="40"/>
+      <c r="R31" s="41"/>
     </row>
     <row r="32" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="92"/>
-      <c r="B32" s="35"/>
-      <c r="C32" s="35"/>
-      <c r="D32" s="105"/>
-      <c r="E32" s="105"/>
-      <c r="F32" s="105"/>
-      <c r="G32" s="105"/>
-      <c r="H32" s="105"/>
-      <c r="I32" s="105"/>
-      <c r="J32" s="35"/>
-      <c r="K32" s="35"/>
-      <c r="L32" s="35"/>
-      <c r="M32" s="105"/>
-      <c r="N32" s="105"/>
-      <c r="O32" s="105"/>
-      <c r="P32" s="105"/>
-      <c r="Q32" s="105"/>
-      <c r="R32" s="135"/>
+      <c r="A32" s="44"/>
+      <c r="B32" s="45"/>
+      <c r="C32" s="45"/>
+      <c r="D32" s="42"/>
+      <c r="E32" s="42"/>
+      <c r="F32" s="42"/>
+      <c r="G32" s="42"/>
+      <c r="H32" s="42"/>
+      <c r="I32" s="42"/>
+      <c r="J32" s="45"/>
+      <c r="K32" s="45"/>
+      <c r="L32" s="45"/>
+      <c r="M32" s="42"/>
+      <c r="N32" s="42"/>
+      <c r="O32" s="42"/>
+      <c r="P32" s="42"/>
+      <c r="Q32" s="42"/>
+      <c r="R32" s="43"/>
     </row>
     <row r="33" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="92" t="s">
+      <c r="A33" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="B33" s="35"/>
-      <c r="C33" s="35"/>
-      <c r="D33" s="63"/>
-      <c r="E33" s="64"/>
-      <c r="F33" s="64"/>
-      <c r="G33" s="64"/>
-      <c r="H33" s="64"/>
-      <c r="I33" s="64"/>
-      <c r="J33" s="64"/>
-      <c r="K33" s="64"/>
-      <c r="L33" s="64"/>
-      <c r="M33" s="64"/>
-      <c r="N33" s="64"/>
-      <c r="O33" s="64"/>
-      <c r="P33" s="64"/>
-      <c r="Q33" s="64"/>
-      <c r="R33" s="65"/>
+      <c r="B33" s="45"/>
+      <c r="C33" s="45"/>
+      <c r="D33" s="132"/>
+      <c r="E33" s="133"/>
+      <c r="F33" s="133"/>
+      <c r="G33" s="133"/>
+      <c r="H33" s="133"/>
+      <c r="I33" s="133"/>
+      <c r="J33" s="133"/>
+      <c r="K33" s="133"/>
+      <c r="L33" s="133"/>
+      <c r="M33" s="133"/>
+      <c r="N33" s="133"/>
+      <c r="O33" s="133"/>
+      <c r="P33" s="133"/>
+      <c r="Q33" s="133"/>
+      <c r="R33" s="134"/>
     </row>
     <row r="34" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="92"/>
-      <c r="B34" s="35"/>
-      <c r="C34" s="35"/>
-      <c r="D34" s="66"/>
-      <c r="E34" s="67"/>
-      <c r="F34" s="67"/>
-      <c r="G34" s="67"/>
-      <c r="H34" s="67"/>
-      <c r="I34" s="67"/>
-      <c r="J34" s="67"/>
-      <c r="K34" s="67"/>
-      <c r="L34" s="67"/>
-      <c r="M34" s="67"/>
-      <c r="N34" s="67"/>
-      <c r="O34" s="67"/>
-      <c r="P34" s="67"/>
-      <c r="Q34" s="67"/>
-      <c r="R34" s="68"/>
+      <c r="A34" s="44"/>
+      <c r="B34" s="45"/>
+      <c r="C34" s="45"/>
+      <c r="D34" s="135"/>
+      <c r="E34" s="136"/>
+      <c r="F34" s="136"/>
+      <c r="G34" s="136"/>
+      <c r="H34" s="136"/>
+      <c r="I34" s="136"/>
+      <c r="J34" s="136"/>
+      <c r="K34" s="136"/>
+      <c r="L34" s="136"/>
+      <c r="M34" s="136"/>
+      <c r="N34" s="136"/>
+      <c r="O34" s="136"/>
+      <c r="P34" s="136"/>
+      <c r="Q34" s="136"/>
+      <c r="R34" s="137"/>
     </row>
     <row r="35" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="92" t="s">
+      <c r="A35" s="44" t="s">
         <v>9</v>
       </c>
-      <c r="B35" s="35"/>
-      <c r="C35" s="35"/>
-      <c r="D35" s="138"/>
-      <c r="E35" s="139"/>
-      <c r="F35" s="139"/>
-      <c r="G35" s="139"/>
-      <c r="H35" s="139"/>
-      <c r="I35" s="139"/>
-      <c r="J35" s="139"/>
-      <c r="K35" s="139"/>
-      <c r="L35" s="139"/>
-      <c r="M35" s="139"/>
-      <c r="N35" s="139"/>
-      <c r="O35" s="139"/>
-      <c r="P35" s="139"/>
-      <c r="Q35" s="139"/>
-      <c r="R35" s="140"/>
+      <c r="B35" s="45"/>
+      <c r="C35" s="45"/>
+      <c r="D35" s="51"/>
+      <c r="E35" s="52"/>
+      <c r="F35" s="52"/>
+      <c r="G35" s="52"/>
+      <c r="H35" s="52"/>
+      <c r="I35" s="52"/>
+      <c r="J35" s="52"/>
+      <c r="K35" s="52"/>
+      <c r="L35" s="52"/>
+      <c r="M35" s="52"/>
+      <c r="N35" s="52"/>
+      <c r="O35" s="52"/>
+      <c r="P35" s="52"/>
+      <c r="Q35" s="52"/>
+      <c r="R35" s="53"/>
     </row>
     <row r="36" spans="1:18" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A36" s="93"/>
-      <c r="B36" s="94"/>
-      <c r="C36" s="94"/>
-      <c r="D36" s="141"/>
-      <c r="E36" s="142"/>
-      <c r="F36" s="142"/>
-      <c r="G36" s="142"/>
-      <c r="H36" s="142"/>
-      <c r="I36" s="142"/>
-      <c r="J36" s="142"/>
-      <c r="K36" s="142"/>
-      <c r="L36" s="142"/>
-      <c r="M36" s="142"/>
-      <c r="N36" s="142"/>
-      <c r="O36" s="142"/>
-      <c r="P36" s="142"/>
-      <c r="Q36" s="142"/>
-      <c r="R36" s="143"/>
+      <c r="A36" s="49"/>
+      <c r="B36" s="50"/>
+      <c r="C36" s="50"/>
+      <c r="D36" s="54"/>
+      <c r="E36" s="55"/>
+      <c r="F36" s="55"/>
+      <c r="G36" s="55"/>
+      <c r="H36" s="55"/>
+      <c r="I36" s="55"/>
+      <c r="J36" s="55"/>
+      <c r="K36" s="55"/>
+      <c r="L36" s="55"/>
+      <c r="M36" s="55"/>
+      <c r="N36" s="55"/>
+      <c r="O36" s="55"/>
+      <c r="P36" s="55"/>
+      <c r="Q36" s="55"/>
+      <c r="R36" s="56"/>
     </row>
     <row r="37" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="106"/>
-      <c r="B37" s="107"/>
-      <c r="C37" s="107"/>
-      <c r="D37" s="107"/>
-      <c r="E37" s="107"/>
-      <c r="F37" s="107"/>
-      <c r="G37" s="107"/>
-      <c r="H37" s="107"/>
-      <c r="I37" s="107"/>
-      <c r="J37" s="107"/>
-      <c r="K37" s="107"/>
-      <c r="L37" s="107"/>
-      <c r="M37" s="107"/>
-      <c r="N37" s="107"/>
-      <c r="O37" s="107"/>
-      <c r="P37" s="107"/>
-      <c r="Q37" s="107"/>
-      <c r="R37" s="107"/>
+      <c r="A37" s="68"/>
+      <c r="B37" s="69"/>
+      <c r="C37" s="69"/>
+      <c r="D37" s="69"/>
+      <c r="E37" s="69"/>
+      <c r="F37" s="69"/>
+      <c r="G37" s="69"/>
+      <c r="H37" s="69"/>
+      <c r="I37" s="69"/>
+      <c r="J37" s="69"/>
+      <c r="K37" s="69"/>
+      <c r="L37" s="69"/>
+      <c r="M37" s="69"/>
+      <c r="N37" s="69"/>
+      <c r="O37" s="69"/>
+      <c r="P37" s="69"/>
+      <c r="Q37" s="69"/>
+      <c r="R37" s="69"/>
     </row>
     <row r="38" spans="1:18" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="108"/>
-      <c r="B38" s="108"/>
-      <c r="C38" s="108"/>
-      <c r="D38" s="108"/>
-      <c r="E38" s="108"/>
-      <c r="F38" s="108"/>
-      <c r="G38" s="108"/>
-      <c r="H38" s="108"/>
-      <c r="I38" s="108"/>
-      <c r="J38" s="108"/>
-      <c r="K38" s="108"/>
-      <c r="L38" s="108"/>
-      <c r="M38" s="108"/>
-      <c r="N38" s="108"/>
-      <c r="O38" s="108"/>
-      <c r="P38" s="108"/>
-      <c r="Q38" s="108"/>
-      <c r="R38" s="108"/>
+      <c r="A38" s="70"/>
+      <c r="B38" s="70"/>
+      <c r="C38" s="70"/>
+      <c r="D38" s="70"/>
+      <c r="E38" s="70"/>
+      <c r="F38" s="70"/>
+      <c r="G38" s="70"/>
+      <c r="H38" s="70"/>
+      <c r="I38" s="70"/>
+      <c r="J38" s="70"/>
+      <c r="K38" s="70"/>
+      <c r="L38" s="70"/>
+      <c r="M38" s="70"/>
+      <c r="N38" s="70"/>
+      <c r="O38" s="70"/>
+      <c r="P38" s="70"/>
+      <c r="Q38" s="70"/>
+      <c r="R38" s="70"/>
     </row>
     <row r="39" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="95" t="s">
+      <c r="A39" s="57" t="s">
         <v>10</v>
       </c>
-      <c r="B39" s="33"/>
-      <c r="C39" s="33"/>
-      <c r="D39" s="33" t="s">
+      <c r="B39" s="46"/>
+      <c r="C39" s="46"/>
+      <c r="D39" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="E39" s="33"/>
-      <c r="F39" s="33"/>
-      <c r="G39" s="34"/>
-      <c r="H39" s="33" t="s">
+      <c r="E39" s="46"/>
+      <c r="F39" s="46"/>
+      <c r="G39" s="71"/>
+      <c r="H39" s="46" t="s">
         <v>10</v>
       </c>
-      <c r="I39" s="33"/>
-      <c r="J39" s="33"/>
-      <c r="K39" s="33" t="s">
+      <c r="I39" s="46"/>
+      <c r="J39" s="46"/>
+      <c r="K39" s="46" t="s">
         <v>11</v>
       </c>
-      <c r="L39" s="33"/>
-      <c r="M39" s="33"/>
-      <c r="N39" s="34"/>
-      <c r="O39" s="33" t="s">
+      <c r="L39" s="46"/>
+      <c r="M39" s="46"/>
+      <c r="N39" s="71"/>
+      <c r="O39" s="46" t="s">
         <v>20</v>
       </c>
-      <c r="P39" s="33"/>
-      <c r="Q39" s="33"/>
-      <c r="R39" s="136"/>
+      <c r="P39" s="46"/>
+      <c r="Q39" s="46"/>
+      <c r="R39" s="47"/>
     </row>
     <row r="40" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="92"/>
-      <c r="B40" s="35"/>
-      <c r="C40" s="35"/>
-      <c r="D40" s="35"/>
-      <c r="E40" s="35"/>
-      <c r="F40" s="35"/>
-      <c r="G40" s="36"/>
-      <c r="H40" s="35"/>
-      <c r="I40" s="35"/>
-      <c r="J40" s="35"/>
-      <c r="K40" s="35"/>
-      <c r="L40" s="35"/>
-      <c r="M40" s="35"/>
-      <c r="N40" s="36"/>
-      <c r="O40" s="35"/>
-      <c r="P40" s="35"/>
-      <c r="Q40" s="35"/>
-      <c r="R40" s="137"/>
+      <c r="A40" s="44"/>
+      <c r="B40" s="45"/>
+      <c r="C40" s="45"/>
+      <c r="D40" s="45"/>
+      <c r="E40" s="45"/>
+      <c r="F40" s="45"/>
+      <c r="G40" s="72"/>
+      <c r="H40" s="45"/>
+      <c r="I40" s="45"/>
+      <c r="J40" s="45"/>
+      <c r="K40" s="45"/>
+      <c r="L40" s="45"/>
+      <c r="M40" s="45"/>
+      <c r="N40" s="72"/>
+      <c r="O40" s="45"/>
+      <c r="P40" s="45"/>
+      <c r="Q40" s="45"/>
+      <c r="R40" s="48"/>
     </row>
     <row r="41" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="27" t="s">
+      <c r="A41" s="106" t="s">
         <v>12</v>
       </c>
-      <c r="B41" s="28"/>
-      <c r="C41" s="29"/>
-      <c r="D41" s="55"/>
-      <c r="E41" s="56"/>
-      <c r="F41" s="56"/>
-      <c r="G41" s="57"/>
-      <c r="H41" s="77" t="s">
+      <c r="B41" s="107"/>
+      <c r="C41" s="108"/>
+      <c r="D41" s="94"/>
+      <c r="E41" s="95"/>
+      <c r="F41" s="95"/>
+      <c r="G41" s="96"/>
+      <c r="H41" s="88" t="s">
         <v>13</v>
       </c>
-      <c r="I41" s="78"/>
-      <c r="J41" s="79"/>
-      <c r="K41" s="55"/>
-      <c r="L41" s="56"/>
-      <c r="M41" s="56"/>
-      <c r="N41" s="57"/>
-      <c r="O41" s="83"/>
-      <c r="P41" s="83"/>
-      <c r="Q41" s="83"/>
-      <c r="R41" s="84"/>
+      <c r="I41" s="89"/>
+      <c r="J41" s="90"/>
+      <c r="K41" s="94"/>
+      <c r="L41" s="95"/>
+      <c r="M41" s="95"/>
+      <c r="N41" s="96"/>
+      <c r="O41" s="100"/>
+      <c r="P41" s="100"/>
+      <c r="Q41" s="100"/>
+      <c r="R41" s="101"/>
     </row>
     <row r="42" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="30"/>
-      <c r="B42" s="31"/>
-      <c r="C42" s="32"/>
-      <c r="D42" s="58"/>
-      <c r="E42" s="59"/>
-      <c r="F42" s="59"/>
-      <c r="G42" s="60"/>
-      <c r="H42" s="80"/>
-      <c r="I42" s="81"/>
-      <c r="J42" s="82"/>
-      <c r="K42" s="58"/>
-      <c r="L42" s="59"/>
-      <c r="M42" s="59"/>
-      <c r="N42" s="60"/>
-      <c r="O42" s="83"/>
-      <c r="P42" s="83"/>
-      <c r="Q42" s="83"/>
-      <c r="R42" s="84"/>
+      <c r="A42" s="109"/>
+      <c r="B42" s="110"/>
+      <c r="C42" s="111"/>
+      <c r="D42" s="97"/>
+      <c r="E42" s="98"/>
+      <c r="F42" s="98"/>
+      <c r="G42" s="99"/>
+      <c r="H42" s="91"/>
+      <c r="I42" s="92"/>
+      <c r="J42" s="93"/>
+      <c r="K42" s="97"/>
+      <c r="L42" s="98"/>
+      <c r="M42" s="98"/>
+      <c r="N42" s="99"/>
+      <c r="O42" s="100"/>
+      <c r="P42" s="100"/>
+      <c r="Q42" s="100"/>
+      <c r="R42" s="101"/>
     </row>
     <row r="43" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="27" t="s">
+      <c r="A43" s="106" t="s">
         <v>14</v>
       </c>
-      <c r="B43" s="28"/>
-      <c r="C43" s="29"/>
-      <c r="D43" s="55"/>
-      <c r="E43" s="56"/>
-      <c r="F43" s="56"/>
-      <c r="G43" s="57"/>
-      <c r="H43" s="61" t="s">
+      <c r="B43" s="107"/>
+      <c r="C43" s="108"/>
+      <c r="D43" s="94"/>
+      <c r="E43" s="95"/>
+      <c r="F43" s="95"/>
+      <c r="G43" s="96"/>
+      <c r="H43" s="130" t="s">
         <v>15</v>
       </c>
-      <c r="I43" s="28"/>
-      <c r="J43" s="29"/>
-      <c r="K43" s="55"/>
-      <c r="L43" s="56"/>
-      <c r="M43" s="56"/>
-      <c r="N43" s="57"/>
-      <c r="O43" s="83"/>
-      <c r="P43" s="83"/>
-      <c r="Q43" s="83"/>
-      <c r="R43" s="84"/>
+      <c r="I43" s="107"/>
+      <c r="J43" s="108"/>
+      <c r="K43" s="94"/>
+      <c r="L43" s="95"/>
+      <c r="M43" s="95"/>
+      <c r="N43" s="96"/>
+      <c r="O43" s="100"/>
+      <c r="P43" s="100"/>
+      <c r="Q43" s="100"/>
+      <c r="R43" s="101"/>
     </row>
     <row r="44" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="30"/>
-      <c r="B44" s="31"/>
-      <c r="C44" s="32"/>
-      <c r="D44" s="58"/>
-      <c r="E44" s="59"/>
-      <c r="F44" s="59"/>
-      <c r="G44" s="60"/>
-      <c r="H44" s="62"/>
-      <c r="I44" s="31"/>
-      <c r="J44" s="32"/>
-      <c r="K44" s="58"/>
-      <c r="L44" s="59"/>
-      <c r="M44" s="59"/>
-      <c r="N44" s="60"/>
-      <c r="O44" s="83"/>
-      <c r="P44" s="83"/>
-      <c r="Q44" s="83"/>
-      <c r="R44" s="84"/>
+      <c r="A44" s="109"/>
+      <c r="B44" s="110"/>
+      <c r="C44" s="111"/>
+      <c r="D44" s="97"/>
+      <c r="E44" s="98"/>
+      <c r="F44" s="98"/>
+      <c r="G44" s="99"/>
+      <c r="H44" s="131"/>
+      <c r="I44" s="110"/>
+      <c r="J44" s="111"/>
+      <c r="K44" s="97"/>
+      <c r="L44" s="98"/>
+      <c r="M44" s="98"/>
+      <c r="N44" s="99"/>
+      <c r="O44" s="100"/>
+      <c r="P44" s="100"/>
+      <c r="Q44" s="100"/>
+      <c r="R44" s="101"/>
     </row>
     <row r="45" spans="1:18" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A45" s="53" t="s">
+      <c r="A45" s="128" t="s">
         <v>16</v>
       </c>
-      <c r="B45" s="54"/>
-      <c r="C45" s="54"/>
-      <c r="D45" s="75"/>
-      <c r="E45" s="75"/>
-      <c r="F45" s="75"/>
-      <c r="G45" s="76"/>
-      <c r="H45" s="54" t="s">
+      <c r="B45" s="129"/>
+      <c r="C45" s="129"/>
+      <c r="D45" s="104"/>
+      <c r="E45" s="104"/>
+      <c r="F45" s="104"/>
+      <c r="G45" s="105"/>
+      <c r="H45" s="129" t="s">
         <v>16</v>
       </c>
-      <c r="I45" s="54"/>
-      <c r="J45" s="54"/>
-      <c r="K45" s="75"/>
-      <c r="L45" s="75"/>
-      <c r="M45" s="75"/>
-      <c r="N45" s="76"/>
-      <c r="O45" s="85"/>
-      <c r="P45" s="85"/>
-      <c r="Q45" s="85"/>
-      <c r="R45" s="86"/>
+      <c r="I45" s="129"/>
+      <c r="J45" s="129"/>
+      <c r="K45" s="104"/>
+      <c r="L45" s="104"/>
+      <c r="M45" s="104"/>
+      <c r="N45" s="105"/>
+      <c r="O45" s="102"/>
+      <c r="P45" s="102"/>
+      <c r="Q45" s="102"/>
+      <c r="R45" s="103"/>
     </row>
     <row r="46" spans="1:18" ht="20.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.4"/>
     <row r="47" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -2643,128 +2643,128 @@
       </c>
     </row>
     <row r="49" spans="1:18" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="41"/>
-      <c r="B49" s="42"/>
-      <c r="C49" s="43"/>
-      <c r="D49" s="47"/>
-      <c r="E49" s="48"/>
-      <c r="F49" s="48"/>
-      <c r="G49" s="48"/>
-      <c r="H49" s="49"/>
-      <c r="I49" s="47"/>
-      <c r="J49" s="48"/>
-      <c r="K49" s="48"/>
-      <c r="L49" s="48"/>
-      <c r="M49" s="49"/>
-      <c r="N49" s="47"/>
-      <c r="O49" s="48"/>
-      <c r="P49" s="48"/>
-      <c r="Q49" s="48"/>
-      <c r="R49" s="73"/>
+      <c r="A49" s="116"/>
+      <c r="B49" s="117"/>
+      <c r="C49" s="118"/>
+      <c r="D49" s="122"/>
+      <c r="E49" s="123"/>
+      <c r="F49" s="123"/>
+      <c r="G49" s="123"/>
+      <c r="H49" s="124"/>
+      <c r="I49" s="122"/>
+      <c r="J49" s="123"/>
+      <c r="K49" s="123"/>
+      <c r="L49" s="123"/>
+      <c r="M49" s="124"/>
+      <c r="N49" s="122"/>
+      <c r="O49" s="123"/>
+      <c r="P49" s="123"/>
+      <c r="Q49" s="123"/>
+      <c r="R49" s="142"/>
     </row>
     <row r="50" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="44"/>
-      <c r="B50" s="45"/>
-      <c r="C50" s="46"/>
-      <c r="D50" s="50"/>
-      <c r="E50" s="51"/>
-      <c r="F50" s="51"/>
-      <c r="G50" s="51"/>
-      <c r="H50" s="52"/>
-      <c r="I50" s="50"/>
-      <c r="J50" s="51"/>
-      <c r="K50" s="51"/>
-      <c r="L50" s="51"/>
-      <c r="M50" s="52"/>
-      <c r="N50" s="50"/>
-      <c r="O50" s="51"/>
-      <c r="P50" s="51"/>
-      <c r="Q50" s="51"/>
-      <c r="R50" s="74"/>
+      <c r="A50" s="119"/>
+      <c r="B50" s="120"/>
+      <c r="C50" s="121"/>
+      <c r="D50" s="125"/>
+      <c r="E50" s="126"/>
+      <c r="F50" s="126"/>
+      <c r="G50" s="126"/>
+      <c r="H50" s="127"/>
+      <c r="I50" s="125"/>
+      <c r="J50" s="126"/>
+      <c r="K50" s="126"/>
+      <c r="L50" s="126"/>
+      <c r="M50" s="127"/>
+      <c r="N50" s="125"/>
+      <c r="O50" s="126"/>
+      <c r="P50" s="126"/>
+      <c r="Q50" s="126"/>
+      <c r="R50" s="143"/>
     </row>
     <row r="51" spans="1:18" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A51" s="126" t="s">
+      <c r="A51" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="B51" s="127"/>
-      <c r="C51" s="128"/>
-      <c r="D51" s="89"/>
-      <c r="E51" s="89"/>
-      <c r="F51" s="89"/>
-      <c r="G51" s="89"/>
-      <c r="H51" s="89"/>
-      <c r="I51" s="89"/>
-      <c r="J51" s="89"/>
-      <c r="K51" s="89"/>
-      <c r="L51" s="89"/>
-      <c r="M51" s="89"/>
-      <c r="N51" s="89"/>
-      <c r="O51" s="89"/>
-      <c r="P51" s="89"/>
-      <c r="Q51" s="89"/>
-      <c r="R51" s="125"/>
+      <c r="B51" s="31"/>
+      <c r="C51" s="32"/>
+      <c r="D51" s="28"/>
+      <c r="E51" s="28"/>
+      <c r="F51" s="28"/>
+      <c r="G51" s="28"/>
+      <c r="H51" s="28"/>
+      <c r="I51" s="28"/>
+      <c r="J51" s="28"/>
+      <c r="K51" s="28"/>
+      <c r="L51" s="28"/>
+      <c r="M51" s="28"/>
+      <c r="N51" s="28"/>
+      <c r="O51" s="28"/>
+      <c r="P51" s="28"/>
+      <c r="Q51" s="28"/>
+      <c r="R51" s="29"/>
     </row>
     <row r="52" spans="1:18" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A52" s="129"/>
-      <c r="B52" s="130"/>
-      <c r="C52" s="131"/>
-      <c r="D52" s="89"/>
-      <c r="E52" s="89"/>
-      <c r="F52" s="89"/>
-      <c r="G52" s="89"/>
-      <c r="H52" s="89"/>
-      <c r="I52" s="89"/>
-      <c r="J52" s="89"/>
-      <c r="K52" s="89"/>
-      <c r="L52" s="89"/>
-      <c r="M52" s="89"/>
-      <c r="N52" s="89"/>
-      <c r="O52" s="89"/>
-      <c r="P52" s="89"/>
-      <c r="Q52" s="89"/>
-      <c r="R52" s="125"/>
+      <c r="A52" s="33"/>
+      <c r="B52" s="34"/>
+      <c r="C52" s="35"/>
+      <c r="D52" s="28"/>
+      <c r="E52" s="28"/>
+      <c r="F52" s="28"/>
+      <c r="G52" s="28"/>
+      <c r="H52" s="28"/>
+      <c r="I52" s="28"/>
+      <c r="J52" s="28"/>
+      <c r="K52" s="28"/>
+      <c r="L52" s="28"/>
+      <c r="M52" s="28"/>
+      <c r="N52" s="28"/>
+      <c r="O52" s="28"/>
+      <c r="P52" s="28"/>
+      <c r="Q52" s="28"/>
+      <c r="R52" s="29"/>
     </row>
     <row r="53" spans="1:18" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A53" s="109" t="s">
+      <c r="A53" s="73" t="s">
         <v>19</v>
       </c>
-      <c r="B53" s="110"/>
-      <c r="C53" s="111"/>
-      <c r="D53" s="87"/>
-      <c r="E53" s="87"/>
-      <c r="F53" s="87"/>
-      <c r="G53" s="87"/>
-      <c r="H53" s="87"/>
-      <c r="I53" s="87"/>
-      <c r="J53" s="87"/>
-      <c r="K53" s="87"/>
-      <c r="L53" s="87"/>
-      <c r="M53" s="87"/>
-      <c r="N53" s="87"/>
-      <c r="O53" s="87"/>
-      <c r="P53" s="87"/>
-      <c r="Q53" s="87"/>
-      <c r="R53" s="132"/>
+      <c r="B53" s="74"/>
+      <c r="C53" s="75"/>
+      <c r="D53" s="36"/>
+      <c r="E53" s="36"/>
+      <c r="F53" s="36"/>
+      <c r="G53" s="36"/>
+      <c r="H53" s="36"/>
+      <c r="I53" s="36"/>
+      <c r="J53" s="36"/>
+      <c r="K53" s="36"/>
+      <c r="L53" s="36"/>
+      <c r="M53" s="36"/>
+      <c r="N53" s="36"/>
+      <c r="O53" s="36"/>
+      <c r="P53" s="36"/>
+      <c r="Q53" s="36"/>
+      <c r="R53" s="37"/>
     </row>
     <row r="54" spans="1:18" s="2" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="112"/>
-      <c r="B54" s="113"/>
-      <c r="C54" s="114"/>
-      <c r="D54" s="88"/>
-      <c r="E54" s="88"/>
-      <c r="F54" s="88"/>
-      <c r="G54" s="88"/>
-      <c r="H54" s="88"/>
-      <c r="I54" s="88"/>
-      <c r="J54" s="88"/>
-      <c r="K54" s="88"/>
-      <c r="L54" s="88"/>
-      <c r="M54" s="88"/>
-      <c r="N54" s="88"/>
-      <c r="O54" s="88"/>
-      <c r="P54" s="88"/>
-      <c r="Q54" s="88"/>
-      <c r="R54" s="133"/>
+      <c r="A54" s="76"/>
+      <c r="B54" s="77"/>
+      <c r="C54" s="78"/>
+      <c r="D54" s="38"/>
+      <c r="E54" s="38"/>
+      <c r="F54" s="38"/>
+      <c r="G54" s="38"/>
+      <c r="H54" s="38"/>
+      <c r="I54" s="38"/>
+      <c r="J54" s="38"/>
+      <c r="K54" s="38"/>
+      <c r="L54" s="38"/>
+      <c r="M54" s="38"/>
+      <c r="N54" s="38"/>
+      <c r="O54" s="38"/>
+      <c r="P54" s="38"/>
+      <c r="Q54" s="38"/>
+      <c r="R54" s="39"/>
     </row>
     <row r="55" spans="1:18" s="2" customFormat="1" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.15"/>
     <row r="56" spans="1:18" s="2" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -2779,6 +2779,40 @@
   </sheetData>
   <sheetProtection formatCells="0"/>
   <mergeCells count="50">
+    <mergeCell ref="N49:R50"/>
+    <mergeCell ref="I49:M50"/>
+    <mergeCell ref="D45:G45"/>
+    <mergeCell ref="D41:G42"/>
+    <mergeCell ref="A41:C42"/>
+    <mergeCell ref="D43:G44"/>
+    <mergeCell ref="H43:J44"/>
+    <mergeCell ref="D33:R34"/>
+    <mergeCell ref="M22:N28"/>
+    <mergeCell ref="A37:R38"/>
+    <mergeCell ref="H39:J40"/>
+    <mergeCell ref="A39:C40"/>
+    <mergeCell ref="K39:N40"/>
+    <mergeCell ref="A53:C54"/>
+    <mergeCell ref="H41:J42"/>
+    <mergeCell ref="K41:N42"/>
+    <mergeCell ref="O41:R45"/>
+    <mergeCell ref="K43:N44"/>
+    <mergeCell ref="K45:N45"/>
+    <mergeCell ref="A43:C44"/>
+    <mergeCell ref="D39:G40"/>
+    <mergeCell ref="A49:C50"/>
+    <mergeCell ref="D49:H50"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="H45:J45"/>
+    <mergeCell ref="O1:R1"/>
+    <mergeCell ref="A11:R11"/>
+    <mergeCell ref="A22:C28"/>
+    <mergeCell ref="A20:C21"/>
+    <mergeCell ref="D20:R21"/>
+    <mergeCell ref="A15:R15"/>
+    <mergeCell ref="A18:R18"/>
+    <mergeCell ref="O22:R28"/>
+    <mergeCell ref="D23:L25"/>
     <mergeCell ref="O3:R4"/>
     <mergeCell ref="D51:H52"/>
     <mergeCell ref="N51:R52"/>
@@ -2794,49 +2828,13 @@
     <mergeCell ref="D53:H54"/>
     <mergeCell ref="I53:M54"/>
     <mergeCell ref="I51:M52"/>
-    <mergeCell ref="O1:R1"/>
-    <mergeCell ref="A11:R11"/>
-    <mergeCell ref="A22:C28"/>
-    <mergeCell ref="A20:C21"/>
-    <mergeCell ref="D20:R21"/>
-    <mergeCell ref="A15:R15"/>
-    <mergeCell ref="A18:R18"/>
     <mergeCell ref="D31:I32"/>
-    <mergeCell ref="A37:R38"/>
-    <mergeCell ref="H39:J40"/>
-    <mergeCell ref="A39:C40"/>
-    <mergeCell ref="K39:N40"/>
-    <mergeCell ref="A53:C54"/>
-    <mergeCell ref="O22:R28"/>
-    <mergeCell ref="H41:J42"/>
-    <mergeCell ref="K41:N42"/>
-    <mergeCell ref="O41:R45"/>
-    <mergeCell ref="K43:N44"/>
-    <mergeCell ref="K45:N45"/>
-    <mergeCell ref="A43:C44"/>
-    <mergeCell ref="D39:G40"/>
-    <mergeCell ref="D23:L25"/>
-    <mergeCell ref="A49:C50"/>
-    <mergeCell ref="D49:H50"/>
-    <mergeCell ref="A45:C45"/>
-    <mergeCell ref="H45:J45"/>
-    <mergeCell ref="A41:C42"/>
-    <mergeCell ref="D43:G44"/>
-    <mergeCell ref="H43:J44"/>
-    <mergeCell ref="D33:R34"/>
-    <mergeCell ref="M22:N28"/>
-    <mergeCell ref="N49:R50"/>
-    <mergeCell ref="I49:M50"/>
-    <mergeCell ref="D45:G45"/>
-    <mergeCell ref="D41:G42"/>
   </mergeCells>
   <phoneticPr fontId="20"/>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.47244094488188981" right="0.47244094488188981" top="0.44" bottom="0.55118110236220474" header="0.25" footer="0.31496062992125984"/>
+  <pageMargins left="0.47244094488188981" right="0.47244094488188981" top="0.43307086614173229" bottom="0.55118110236220474" header="0.23622047244094491" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="95" orientation="portrait" r:id="rId1"/>
-  <headerFooter alignWithMargins="0">
-    <oddFooter>&amp;R&amp;"ＭＳ Ｐ明朝,標準"&amp;7Ver.3-12.03-01</oddFooter>
-  </headerFooter>
+  <headerFooter alignWithMargins="0"/>
   <colBreaks count="1" manualBreakCount="1">
     <brk id="18" max="1048575" man="1"/>
   </colBreaks>
@@ -2856,62 +2854,62 @@
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
-      <c r="E2" s="154" t="s">
+      <c r="E2" s="148" t="s">
         <v>21</v>
       </c>
-      <c r="F2" s="154"/>
-      <c r="G2" s="154" t="s">
+      <c r="F2" s="148"/>
+      <c r="G2" s="148" t="s">
         <v>22</v>
       </c>
-      <c r="H2" s="154"/>
-      <c r="I2" s="154" t="s">
+      <c r="H2" s="148"/>
+      <c r="I2" s="148" t="s">
         <v>23</v>
       </c>
-      <c r="J2" s="154"/>
-      <c r="K2" s="154" t="s">
+      <c r="J2" s="148"/>
+      <c r="K2" s="148" t="s">
         <v>24</v>
       </c>
-      <c r="L2" s="154"/>
-      <c r="M2" s="154" t="s">
+      <c r="L2" s="148"/>
+      <c r="M2" s="148" t="s">
         <v>25</v>
       </c>
-      <c r="N2" s="154"/>
+      <c r="N2" s="148"/>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B3" s="151" t="s">
+      <c r="B3" s="146" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="151"/>
+      <c r="C3" s="146"/>
       <c r="D3" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="151"/>
-      <c r="F3" s="151"/>
-      <c r="G3" s="155"/>
-      <c r="H3" s="155"/>
-      <c r="I3" s="151"/>
-      <c r="J3" s="151"/>
-      <c r="K3" s="151"/>
-      <c r="L3" s="151"/>
-      <c r="M3" s="151"/>
-      <c r="N3" s="151"/>
+      <c r="E3" s="146"/>
+      <c r="F3" s="146"/>
+      <c r="G3" s="147"/>
+      <c r="H3" s="147"/>
+      <c r="I3" s="146"/>
+      <c r="J3" s="146"/>
+      <c r="K3" s="146"/>
+      <c r="L3" s="146"/>
+      <c r="M3" s="146"/>
+      <c r="N3" s="146"/>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B4" s="151"/>
-      <c r="C4" s="151"/>
+      <c r="B4" s="146"/>
+      <c r="C4" s="146"/>
       <c r="D4" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="151"/>
-      <c r="F4" s="151"/>
-      <c r="G4" s="151"/>
-      <c r="H4" s="151"/>
-      <c r="I4" s="151"/>
-      <c r="J4" s="151"/>
-      <c r="K4" s="151"/>
-      <c r="L4" s="151"/>
-      <c r="M4" s="151"/>
-      <c r="N4" s="151"/>
+      <c r="E4" s="146"/>
+      <c r="F4" s="146"/>
+      <c r="G4" s="146"/>
+      <c r="H4" s="146"/>
+      <c r="I4" s="146"/>
+      <c r="J4" s="146"/>
+      <c r="K4" s="146"/>
+      <c r="L4" s="146"/>
+      <c r="M4" s="146"/>
+      <c r="N4" s="146"/>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B5" s="1"/>
@@ -2932,62 +2930,62 @@
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
-      <c r="E6" s="149" t="s">
+      <c r="E6" s="153" t="s">
         <v>21</v>
       </c>
-      <c r="F6" s="150"/>
-      <c r="G6" s="149" t="s">
+      <c r="F6" s="154"/>
+      <c r="G6" s="153" t="s">
         <v>22</v>
       </c>
-      <c r="H6" s="150"/>
-      <c r="I6" s="149" t="s">
+      <c r="H6" s="154"/>
+      <c r="I6" s="153" t="s">
         <v>23</v>
       </c>
-      <c r="J6" s="150"/>
-      <c r="K6" s="149" t="s">
+      <c r="J6" s="154"/>
+      <c r="K6" s="153" t="s">
         <v>24</v>
       </c>
-      <c r="L6" s="150"/>
-      <c r="M6" s="149" t="s">
+      <c r="L6" s="154"/>
+      <c r="M6" s="153" t="s">
         <v>25</v>
       </c>
-      <c r="N6" s="150"/>
+      <c r="N6" s="154"/>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B7" s="151" t="s">
+      <c r="B7" s="146" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="151"/>
+      <c r="C7" s="146"/>
       <c r="D7" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="E7" s="147"/>
-      <c r="F7" s="148"/>
-      <c r="G7" s="152"/>
-      <c r="H7" s="153"/>
-      <c r="I7" s="147"/>
-      <c r="J7" s="148"/>
-      <c r="K7" s="147"/>
-      <c r="L7" s="148"/>
-      <c r="M7" s="147"/>
-      <c r="N7" s="148"/>
+      <c r="E7" s="149"/>
+      <c r="F7" s="150"/>
+      <c r="G7" s="151"/>
+      <c r="H7" s="152"/>
+      <c r="I7" s="149"/>
+      <c r="J7" s="150"/>
+      <c r="K7" s="149"/>
+      <c r="L7" s="150"/>
+      <c r="M7" s="149"/>
+      <c r="N7" s="150"/>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B8" s="151"/>
-      <c r="C8" s="151"/>
+      <c r="B8" s="146"/>
+      <c r="C8" s="146"/>
       <c r="D8" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="E8" s="147"/>
-      <c r="F8" s="148"/>
-      <c r="G8" s="147"/>
-      <c r="H8" s="148"/>
-      <c r="I8" s="147"/>
-      <c r="J8" s="148"/>
-      <c r="K8" s="147"/>
-      <c r="L8" s="148"/>
-      <c r="M8" s="147"/>
-      <c r="N8" s="148"/>
+      <c r="E8" s="149"/>
+      <c r="F8" s="150"/>
+      <c r="G8" s="149"/>
+      <c r="H8" s="150"/>
+      <c r="I8" s="149"/>
+      <c r="J8" s="150"/>
+      <c r="K8" s="149"/>
+      <c r="L8" s="150"/>
+      <c r="M8" s="149"/>
+      <c r="N8" s="150"/>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B9" s="1"/>
@@ -3008,62 +3006,62 @@
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
-      <c r="E10" s="149" t="s">
+      <c r="E10" s="153" t="s">
         <v>21</v>
       </c>
-      <c r="F10" s="150"/>
-      <c r="G10" s="149" t="s">
+      <c r="F10" s="154"/>
+      <c r="G10" s="153" t="s">
         <v>22</v>
       </c>
-      <c r="H10" s="150"/>
-      <c r="I10" s="149" t="s">
+      <c r="H10" s="154"/>
+      <c r="I10" s="153" t="s">
         <v>23</v>
       </c>
-      <c r="J10" s="150"/>
-      <c r="K10" s="149" t="s">
+      <c r="J10" s="154"/>
+      <c r="K10" s="153" t="s">
         <v>24</v>
       </c>
-      <c r="L10" s="150"/>
-      <c r="M10" s="149" t="s">
+      <c r="L10" s="154"/>
+      <c r="M10" s="153" t="s">
         <v>25</v>
       </c>
-      <c r="N10" s="150"/>
+      <c r="N10" s="154"/>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B11" s="151" t="s">
+      <c r="B11" s="146" t="s">
         <v>30</v>
       </c>
-      <c r="C11" s="151"/>
+      <c r="C11" s="146"/>
       <c r="D11" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="E11" s="147"/>
-      <c r="F11" s="148"/>
-      <c r="G11" s="152"/>
-      <c r="H11" s="153"/>
-      <c r="I11" s="147"/>
-      <c r="J11" s="148"/>
-      <c r="K11" s="147"/>
-      <c r="L11" s="148"/>
-      <c r="M11" s="147"/>
-      <c r="N11" s="148"/>
+      <c r="E11" s="149"/>
+      <c r="F11" s="150"/>
+      <c r="G11" s="151"/>
+      <c r="H11" s="152"/>
+      <c r="I11" s="149"/>
+      <c r="J11" s="150"/>
+      <c r="K11" s="149"/>
+      <c r="L11" s="150"/>
+      <c r="M11" s="149"/>
+      <c r="N11" s="150"/>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B12" s="151"/>
-      <c r="C12" s="151"/>
+      <c r="B12" s="146"/>
+      <c r="C12" s="146"/>
       <c r="D12" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="E12" s="147"/>
-      <c r="F12" s="148"/>
-      <c r="G12" s="147"/>
-      <c r="H12" s="148"/>
-      <c r="I12" s="147"/>
-      <c r="J12" s="148"/>
-      <c r="K12" s="147"/>
-      <c r="L12" s="148"/>
-      <c r="M12" s="147"/>
-      <c r="N12" s="148"/>
+      <c r="E12" s="149"/>
+      <c r="F12" s="150"/>
+      <c r="G12" s="149"/>
+      <c r="H12" s="150"/>
+      <c r="I12" s="149"/>
+      <c r="J12" s="150"/>
+      <c r="K12" s="149"/>
+      <c r="L12" s="150"/>
+      <c r="M12" s="149"/>
+      <c r="N12" s="150"/>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B13" s="1"/>
@@ -3099,62 +3097,62 @@
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
-      <c r="E15" s="149" t="s">
+      <c r="E15" s="153" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="150"/>
-      <c r="G15" s="149" t="s">
+      <c r="F15" s="154"/>
+      <c r="G15" s="153" t="s">
         <v>22</v>
       </c>
-      <c r="H15" s="150"/>
-      <c r="I15" s="149" t="s">
+      <c r="H15" s="154"/>
+      <c r="I15" s="153" t="s">
         <v>23</v>
       </c>
-      <c r="J15" s="150"/>
-      <c r="K15" s="149" t="s">
+      <c r="J15" s="154"/>
+      <c r="K15" s="153" t="s">
         <v>24</v>
       </c>
-      <c r="L15" s="150"/>
-      <c r="M15" s="149" t="s">
+      <c r="L15" s="154"/>
+      <c r="M15" s="153" t="s">
         <v>25</v>
       </c>
-      <c r="N15" s="150"/>
+      <c r="N15" s="154"/>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B16" s="151" t="s">
+      <c r="B16" s="146" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="151"/>
+      <c r="C16" s="146"/>
       <c r="D16" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="E16" s="147"/>
-      <c r="F16" s="148"/>
-      <c r="G16" s="152"/>
-      <c r="H16" s="153"/>
-      <c r="I16" s="147"/>
-      <c r="J16" s="148"/>
-      <c r="K16" s="147"/>
-      <c r="L16" s="148"/>
-      <c r="M16" s="147"/>
-      <c r="N16" s="148"/>
+      <c r="E16" s="149"/>
+      <c r="F16" s="150"/>
+      <c r="G16" s="151"/>
+      <c r="H16" s="152"/>
+      <c r="I16" s="149"/>
+      <c r="J16" s="150"/>
+      <c r="K16" s="149"/>
+      <c r="L16" s="150"/>
+      <c r="M16" s="149"/>
+      <c r="N16" s="150"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B17" s="151"/>
-      <c r="C17" s="151"/>
+      <c r="B17" s="146"/>
+      <c r="C17" s="146"/>
       <c r="D17" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="E17" s="147"/>
-      <c r="F17" s="148"/>
-      <c r="G17" s="147"/>
-      <c r="H17" s="148"/>
-      <c r="I17" s="147"/>
-      <c r="J17" s="148"/>
-      <c r="K17" s="147"/>
-      <c r="L17" s="148"/>
-      <c r="M17" s="147"/>
-      <c r="N17" s="148"/>
+      <c r="E17" s="149"/>
+      <c r="F17" s="150"/>
+      <c r="G17" s="149"/>
+      <c r="H17" s="150"/>
+      <c r="I17" s="149"/>
+      <c r="J17" s="150"/>
+      <c r="K17" s="149"/>
+      <c r="L17" s="150"/>
+      <c r="M17" s="149"/>
+      <c r="N17" s="150"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B20" s="144"/>
@@ -3258,8 +3256,8 @@
       </c>
       <c r="C26" s="144"/>
       <c r="D26" s="144"/>
-      <c r="E26" s="146"/>
-      <c r="F26" s="146"/>
+      <c r="E26" s="155"/>
+      <c r="F26" s="155"/>
       <c r="I26" s="144" t="s">
         <v>42</v>
       </c>
@@ -3288,6 +3286,92 @@
     </row>
   </sheetData>
   <mergeCells count="96">
+    <mergeCell ref="I26:K26"/>
+    <mergeCell ref="L26:M26"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="E28:F28"/>
+    <mergeCell ref="I25:K25"/>
+    <mergeCell ref="L25:M25"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="E26:F26"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="E27:F27"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="E24:F24"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="B22:D22"/>
+    <mergeCell ref="E22:F22"/>
+    <mergeCell ref="M16:N16"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="K17:L17"/>
+    <mergeCell ref="M17:N17"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="K15:L15"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="B16:C17"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="G16:H16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="K16:L16"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="B11:C12"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="K11:L11"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="K8:L8"/>
+    <mergeCell ref="M8:N8"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="K6:L6"/>
+    <mergeCell ref="M6:N6"/>
+    <mergeCell ref="B7:C8"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="K7:L7"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="B3:C4"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="K3:L3"/>
     <mergeCell ref="I23:K23"/>
     <mergeCell ref="L23:M23"/>
     <mergeCell ref="I24:K24"/>
@@ -3298,92 +3382,6 @@
     <mergeCell ref="L21:M21"/>
     <mergeCell ref="I22:K22"/>
     <mergeCell ref="L22:M22"/>
-    <mergeCell ref="B3:C4"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="B7:C8"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="K7:L7"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="K6:L6"/>
-    <mergeCell ref="M6:N6"/>
-    <mergeCell ref="M7:N7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="K8:L8"/>
-    <mergeCell ref="M8:N8"/>
-    <mergeCell ref="B11:C12"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="M10:N10"/>
-    <mergeCell ref="M11:N11"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="B16:C17"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="G16:H16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="K16:L16"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="K15:L15"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="K17:L17"/>
-    <mergeCell ref="M17:N17"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="B22:D22"/>
-    <mergeCell ref="E22:F22"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="E23:F23"/>
-    <mergeCell ref="B24:D24"/>
-    <mergeCell ref="E24:F24"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="I26:K26"/>
-    <mergeCell ref="L26:M26"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="I25:K25"/>
-    <mergeCell ref="L25:M25"/>
-    <mergeCell ref="B26:D26"/>
-    <mergeCell ref="E26:F26"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="E27:F27"/>
   </mergeCells>
   <phoneticPr fontId="20"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/storage/app/estimateTemplate/comprehensiveOfRecommend.xlsx
+++ b/storage/app/estimateTemplate/comprehensiveOfRecommend.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-22.04\home\ohno\eruful\mitumo\storage\app\estimateTemplate\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67448822-BB5A-46C1-A468-84E003EFF818}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3D90E36-BBEB-49C1-8569-5DE99601B27C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0E9C5CA5-184F-4C06-AA15-1AF55B55AFB9}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0E9C5CA5-184F-4C06-AA15-1AF55B55AFB9}"/>
   </bookViews>
   <sheets>
     <sheet name="おすすめ(総合)" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="48">
   <si>
     <t>御　　見　　積　　書</t>
     <rPh sb="0" eb="1">
@@ -481,6 +481,16 @@
     </rPh>
     <rPh sb="5" eb="7">
       <t>ワリビキ</t>
+    </rPh>
+    <phoneticPr fontId="20"/>
+  </si>
+  <si>
+    <t>作業員人数</t>
+    <rPh sb="0" eb="3">
+      <t>サギョウイン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ニンズ</t>
     </rPh>
     <phoneticPr fontId="20"/>
   </si>
@@ -665,7 +675,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="38">
+  <borders count="39">
     <border>
       <left/>
       <right/>
@@ -1120,6 +1130,17 @@
         <color indexed="64"/>
       </diagonal>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1129,7 +1150,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="6" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="156">
+  <cellXfs count="161">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1208,97 +1229,19 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="9" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="9" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="180" fontId="18" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="18" fillId="0" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="181" fontId="9" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="9" fillId="0" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="9" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="181" fontId="9" fillId="0" borderId="29" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="24" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="58" fontId="1" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -1308,6 +1251,24 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="7" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -1332,6 +1293,237 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="8" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="6" fontId="15" fillId="3" borderId="28" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="26" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="16" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="16" fillId="0" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="16" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="16" fillId="0" borderId="29" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="9" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="180" fontId="18" fillId="0" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="distributed" vertical="center" justifyLastLine="1"/>
+    </xf>
+    <xf numFmtId="181" fontId="9" fillId="0" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="9" fillId="0" borderId="29" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1347,176 +1539,41 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="32" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="20" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="22" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="13" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="14" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="26" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="8" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="9" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="6" fontId="15" fillId="3" borderId="28" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="13" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="26" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="8" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="28" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="16" fillId="0" borderId="7" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="16" fillId="0" borderId="24" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="16" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="180" fontId="16" fillId="0" borderId="29" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="9" fillId="0" borderId="18" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="25" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="26" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="30" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="3" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="4" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="31" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="28" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="17" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="23" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="24" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="23" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="24" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="13" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
@@ -1524,42 +1581,6 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="8" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" justifyLastLine="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="11" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="12" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="19" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="5" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="10" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1591,6 +1612,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="34" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="33" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="38" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -1972,10 +2008,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="O1" s="58"/>
-      <c r="P1" s="58"/>
-      <c r="Q1" s="58"/>
-      <c r="R1" s="58"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="32"/>
+      <c r="R1" s="32"/>
     </row>
     <row r="2" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="O2" s="25"/>
@@ -1985,16 +2021,16 @@
     </row>
     <row r="3" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
       <c r="A3" s="3"/>
-      <c r="O3" s="27"/>
-      <c r="P3" s="27"/>
-      <c r="Q3" s="27"/>
-      <c r="R3" s="27"/>
+      <c r="O3" s="61"/>
+      <c r="P3" s="61"/>
+      <c r="Q3" s="61"/>
+      <c r="R3" s="61"/>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="O4" s="27"/>
-      <c r="P4" s="27"/>
-      <c r="Q4" s="27"/>
-      <c r="R4" s="27"/>
+      <c r="O4" s="61"/>
+      <c r="P4" s="61"/>
+      <c r="Q4" s="61"/>
+      <c r="R4" s="61"/>
     </row>
     <row r="5" spans="1:18" ht="13.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="N5" s="24"/>
@@ -2057,196 +2093,196 @@
       <c r="R10" s="20"/>
     </row>
     <row r="11" spans="1:18" ht="21" x14ac:dyDescent="0.4">
-      <c r="A11" s="59" t="s">
+      <c r="A11" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B11" s="59"/>
-      <c r="C11" s="59"/>
-      <c r="D11" s="59"/>
-      <c r="E11" s="59"/>
-      <c r="F11" s="59"/>
-      <c r="G11" s="59"/>
-      <c r="H11" s="59"/>
-      <c r="I11" s="59"/>
-      <c r="J11" s="59"/>
-      <c r="K11" s="59"/>
-      <c r="L11" s="59"/>
-      <c r="M11" s="59"/>
-      <c r="N11" s="59"/>
-      <c r="O11" s="59"/>
-      <c r="P11" s="59"/>
-      <c r="Q11" s="59"/>
-      <c r="R11" s="59"/>
+      <c r="B11" s="33"/>
+      <c r="C11" s="33"/>
+      <c r="D11" s="33"/>
+      <c r="E11" s="33"/>
+      <c r="F11" s="33"/>
+      <c r="G11" s="33"/>
+      <c r="H11" s="33"/>
+      <c r="I11" s="33"/>
+      <c r="J11" s="33"/>
+      <c r="K11" s="33"/>
+      <c r="L11" s="33"/>
+      <c r="M11" s="33"/>
+      <c r="N11" s="33"/>
+      <c r="O11" s="33"/>
+      <c r="P11" s="33"/>
+      <c r="Q11" s="33"/>
+      <c r="R11" s="33"/>
     </row>
     <row r="14" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="15" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
-      <c r="A15" s="66" t="s">
+      <c r="A15" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="B15" s="66"/>
-      <c r="C15" s="66"/>
-      <c r="D15" s="66"/>
-      <c r="E15" s="66"/>
-      <c r="F15" s="66"/>
-      <c r="G15" s="66"/>
-      <c r="H15" s="66"/>
-      <c r="I15" s="66"/>
-      <c r="J15" s="66"/>
-      <c r="K15" s="66"/>
-      <c r="L15" s="66"/>
-      <c r="M15" s="66"/>
-      <c r="N15" s="66"/>
-      <c r="O15" s="66"/>
-      <c r="P15" s="66"/>
-      <c r="Q15" s="66"/>
-      <c r="R15" s="66"/>
+      <c r="B15" s="46"/>
+      <c r="C15" s="46"/>
+      <c r="D15" s="46"/>
+      <c r="E15" s="46"/>
+      <c r="F15" s="46"/>
+      <c r="G15" s="46"/>
+      <c r="H15" s="46"/>
+      <c r="I15" s="46"/>
+      <c r="J15" s="46"/>
+      <c r="K15" s="46"/>
+      <c r="L15" s="46"/>
+      <c r="M15" s="46"/>
+      <c r="N15" s="46"/>
+      <c r="O15" s="46"/>
+      <c r="P15" s="46"/>
+      <c r="Q15" s="46"/>
+      <c r="R15" s="46"/>
     </row>
     <row r="18" spans="1:18" ht="13.5" x14ac:dyDescent="0.4">
-      <c r="A18" s="67" t="s">
+      <c r="A18" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="B18" s="67"/>
-      <c r="C18" s="67"/>
-      <c r="D18" s="67"/>
-      <c r="E18" s="67"/>
-      <c r="F18" s="67"/>
-      <c r="G18" s="67"/>
-      <c r="H18" s="67"/>
-      <c r="I18" s="67"/>
-      <c r="J18" s="67"/>
-      <c r="K18" s="67"/>
-      <c r="L18" s="67"/>
-      <c r="M18" s="67"/>
-      <c r="N18" s="67"/>
-      <c r="O18" s="67"/>
-      <c r="P18" s="67"/>
-      <c r="Q18" s="67"/>
-      <c r="R18" s="67"/>
+      <c r="B18" s="47"/>
+      <c r="C18" s="47"/>
+      <c r="D18" s="47"/>
+      <c r="E18" s="47"/>
+      <c r="F18" s="47"/>
+      <c r="G18" s="47"/>
+      <c r="H18" s="47"/>
+      <c r="I18" s="47"/>
+      <c r="J18" s="47"/>
+      <c r="K18" s="47"/>
+      <c r="L18" s="47"/>
+      <c r="M18" s="47"/>
+      <c r="N18" s="47"/>
+      <c r="O18" s="47"/>
+      <c r="P18" s="47"/>
+      <c r="Q18" s="47"/>
+      <c r="R18" s="47"/>
     </row>
     <row r="19" spans="1:18" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="20" spans="1:18" ht="12.75" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="57" t="s">
+      <c r="A20" s="38" t="s">
         <v>3</v>
       </c>
-      <c r="B20" s="46"/>
-      <c r="C20" s="46"/>
-      <c r="D20" s="60"/>
-      <c r="E20" s="61"/>
-      <c r="F20" s="61"/>
-      <c r="G20" s="61"/>
-      <c r="H20" s="61"/>
-      <c r="I20" s="61"/>
-      <c r="J20" s="61"/>
-      <c r="K20" s="61"/>
-      <c r="L20" s="61"/>
-      <c r="M20" s="61"/>
-      <c r="N20" s="61"/>
-      <c r="O20" s="61"/>
-      <c r="P20" s="61"/>
-      <c r="Q20" s="61"/>
-      <c r="R20" s="62"/>
+      <c r="B20" s="39"/>
+      <c r="C20" s="39"/>
+      <c r="D20" s="40"/>
+      <c r="E20" s="41"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="41"/>
+      <c r="H20" s="41"/>
+      <c r="I20" s="41"/>
+      <c r="J20" s="41"/>
+      <c r="K20" s="41"/>
+      <c r="L20" s="41"/>
+      <c r="M20" s="41"/>
+      <c r="N20" s="41"/>
+      <c r="O20" s="41"/>
+      <c r="P20" s="41"/>
+      <c r="Q20" s="41"/>
+      <c r="R20" s="42"/>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.4">
-      <c r="A21" s="44"/>
-      <c r="B21" s="45"/>
-      <c r="C21" s="45"/>
-      <c r="D21" s="63"/>
-      <c r="E21" s="64"/>
-      <c r="F21" s="64"/>
-      <c r="G21" s="64"/>
-      <c r="H21" s="64"/>
-      <c r="I21" s="64"/>
-      <c r="J21" s="64"/>
-      <c r="K21" s="64"/>
-      <c r="L21" s="64"/>
-      <c r="M21" s="64"/>
-      <c r="N21" s="64"/>
-      <c r="O21" s="64"/>
-      <c r="P21" s="64"/>
-      <c r="Q21" s="64"/>
-      <c r="R21" s="65"/>
+      <c r="A21" s="34"/>
+      <c r="B21" s="35"/>
+      <c r="C21" s="35"/>
+      <c r="D21" s="43"/>
+      <c r="E21" s="44"/>
+      <c r="F21" s="44"/>
+      <c r="G21" s="44"/>
+      <c r="H21" s="44"/>
+      <c r="I21" s="44"/>
+      <c r="J21" s="44"/>
+      <c r="K21" s="44"/>
+      <c r="L21" s="44"/>
+      <c r="M21" s="44"/>
+      <c r="N21" s="44"/>
+      <c r="O21" s="44"/>
+      <c r="P21" s="44"/>
+      <c r="Q21" s="44"/>
+      <c r="R21" s="45"/>
     </row>
     <row r="22" spans="1:18" ht="5.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="44" t="s">
+      <c r="A22" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="B22" s="45"/>
-      <c r="C22" s="45"/>
+      <c r="B22" s="35"/>
+      <c r="C22" s="35"/>
       <c r="D22" s="19"/>
       <c r="L22" s="18"/>
-      <c r="M22" s="138" t="s">
+      <c r="M22" s="121" t="s">
         <v>5</v>
       </c>
-      <c r="N22" s="139"/>
-      <c r="O22" s="79"/>
-      <c r="P22" s="80"/>
-      <c r="Q22" s="80"/>
-      <c r="R22" s="81"/>
+      <c r="N22" s="122"/>
+      <c r="O22" s="48"/>
+      <c r="P22" s="49"/>
+      <c r="Q22" s="49"/>
+      <c r="R22" s="50"/>
     </row>
     <row r="23" spans="1:18" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="44"/>
-      <c r="B23" s="45"/>
-      <c r="C23" s="45"/>
-      <c r="D23" s="112"/>
-      <c r="E23" s="113"/>
-      <c r="F23" s="113"/>
-      <c r="G23" s="113"/>
-      <c r="H23" s="113"/>
-      <c r="I23" s="113"/>
-      <c r="J23" s="113"/>
-      <c r="K23" s="113"/>
-      <c r="L23" s="114"/>
-      <c r="M23" s="138"/>
-      <c r="N23" s="139"/>
-      <c r="O23" s="82"/>
-      <c r="P23" s="83"/>
-      <c r="Q23" s="83"/>
-      <c r="R23" s="84"/>
+      <c r="A23" s="34"/>
+      <c r="B23" s="35"/>
+      <c r="C23" s="35"/>
+      <c r="D23" s="57"/>
+      <c r="E23" s="58"/>
+      <c r="F23" s="58"/>
+      <c r="G23" s="58"/>
+      <c r="H23" s="58"/>
+      <c r="I23" s="58"/>
+      <c r="J23" s="58"/>
+      <c r="K23" s="58"/>
+      <c r="L23" s="59"/>
+      <c r="M23" s="121"/>
+      <c r="N23" s="122"/>
+      <c r="O23" s="51"/>
+      <c r="P23" s="52"/>
+      <c r="Q23" s="52"/>
+      <c r="R23" s="53"/>
     </row>
     <row r="24" spans="1:18" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="44"/>
-      <c r="B24" s="45"/>
-      <c r="C24" s="45"/>
-      <c r="D24" s="115"/>
-      <c r="E24" s="113"/>
-      <c r="F24" s="113"/>
-      <c r="G24" s="113"/>
-      <c r="H24" s="113"/>
-      <c r="I24" s="113"/>
-      <c r="J24" s="113"/>
-      <c r="K24" s="113"/>
-      <c r="L24" s="114"/>
-      <c r="M24" s="138"/>
-      <c r="N24" s="139"/>
-      <c r="O24" s="82"/>
-      <c r="P24" s="83"/>
-      <c r="Q24" s="83"/>
-      <c r="R24" s="84"/>
+      <c r="A24" s="34"/>
+      <c r="B24" s="35"/>
+      <c r="C24" s="35"/>
+      <c r="D24" s="60"/>
+      <c r="E24" s="58"/>
+      <c r="F24" s="58"/>
+      <c r="G24" s="58"/>
+      <c r="H24" s="58"/>
+      <c r="I24" s="58"/>
+      <c r="J24" s="58"/>
+      <c r="K24" s="58"/>
+      <c r="L24" s="59"/>
+      <c r="M24" s="121"/>
+      <c r="N24" s="122"/>
+      <c r="O24" s="51"/>
+      <c r="P24" s="52"/>
+      <c r="Q24" s="52"/>
+      <c r="R24" s="53"/>
     </row>
     <row r="25" spans="1:18" ht="9.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="44"/>
-      <c r="B25" s="45"/>
-      <c r="C25" s="45"/>
-      <c r="D25" s="115"/>
-      <c r="E25" s="113"/>
-      <c r="F25" s="113"/>
-      <c r="G25" s="113"/>
-      <c r="H25" s="113"/>
-      <c r="I25" s="113"/>
-      <c r="J25" s="113"/>
-      <c r="K25" s="113"/>
-      <c r="L25" s="114"/>
-      <c r="M25" s="138"/>
-      <c r="N25" s="139"/>
-      <c r="O25" s="82"/>
-      <c r="P25" s="83"/>
-      <c r="Q25" s="83"/>
-      <c r="R25" s="84"/>
+      <c r="A25" s="34"/>
+      <c r="B25" s="35"/>
+      <c r="C25" s="35"/>
+      <c r="D25" s="60"/>
+      <c r="E25" s="58"/>
+      <c r="F25" s="58"/>
+      <c r="G25" s="58"/>
+      <c r="H25" s="58"/>
+      <c r="I25" s="58"/>
+      <c r="J25" s="58"/>
+      <c r="K25" s="58"/>
+      <c r="L25" s="59"/>
+      <c r="M25" s="121"/>
+      <c r="N25" s="122"/>
+      <c r="O25" s="51"/>
+      <c r="P25" s="52"/>
+      <c r="Q25" s="52"/>
+      <c r="R25" s="53"/>
     </row>
     <row r="26" spans="1:18" ht="4.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="44"/>
-      <c r="B26" s="45"/>
-      <c r="C26" s="45"/>
+      <c r="A26" s="34"/>
+      <c r="B26" s="35"/>
+      <c r="C26" s="35"/>
       <c r="D26" s="17"/>
       <c r="E26" s="16"/>
       <c r="F26" s="15"/>
@@ -2256,17 +2292,17 @@
       <c r="J26" s="14"/>
       <c r="K26" s="14"/>
       <c r="L26" s="13"/>
-      <c r="M26" s="138"/>
-      <c r="N26" s="139"/>
-      <c r="O26" s="82"/>
-      <c r="P26" s="83"/>
-      <c r="Q26" s="83"/>
-      <c r="R26" s="84"/>
+      <c r="M26" s="121"/>
+      <c r="N26" s="122"/>
+      <c r="O26" s="51"/>
+      <c r="P26" s="52"/>
+      <c r="Q26" s="52"/>
+      <c r="R26" s="53"/>
     </row>
     <row r="27" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="44"/>
-      <c r="B27" s="45"/>
-      <c r="C27" s="45"/>
+      <c r="A27" s="34"/>
+      <c r="B27" s="35"/>
+      <c r="C27" s="35"/>
       <c r="D27" s="12"/>
       <c r="F27" s="10"/>
       <c r="G27" s="11"/>
@@ -2274,17 +2310,17 @@
       <c r="I27" s="9"/>
       <c r="J27" s="9"/>
       <c r="L27" s="8"/>
-      <c r="M27" s="138"/>
-      <c r="N27" s="139"/>
-      <c r="O27" s="82"/>
-      <c r="P27" s="83"/>
-      <c r="Q27" s="83"/>
-      <c r="R27" s="84"/>
+      <c r="M27" s="121"/>
+      <c r="N27" s="122"/>
+      <c r="O27" s="51"/>
+      <c r="P27" s="52"/>
+      <c r="Q27" s="52"/>
+      <c r="R27" s="53"/>
     </row>
     <row r="28" spans="1:18" ht="5.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="49"/>
-      <c r="B28" s="50"/>
-      <c r="C28" s="50"/>
+      <c r="A28" s="36"/>
+      <c r="B28" s="37"/>
+      <c r="C28" s="37"/>
       <c r="D28" s="7"/>
       <c r="E28" s="6"/>
       <c r="F28" s="6"/>
@@ -2294,344 +2330,344 @@
       <c r="J28" s="6"/>
       <c r="K28" s="6"/>
       <c r="L28" s="5"/>
-      <c r="M28" s="140"/>
-      <c r="N28" s="141"/>
-      <c r="O28" s="85"/>
-      <c r="P28" s="86"/>
-      <c r="Q28" s="86"/>
-      <c r="R28" s="87"/>
+      <c r="M28" s="123"/>
+      <c r="N28" s="124"/>
+      <c r="O28" s="54"/>
+      <c r="P28" s="55"/>
+      <c r="Q28" s="55"/>
+      <c r="R28" s="56"/>
     </row>
     <row r="29" spans="1:18" ht="12.75" thickTop="1" x14ac:dyDescent="0.4"/>
     <row r="30" spans="1:18" ht="12.75" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="31" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="57" t="s">
+      <c r="A31" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="B31" s="46"/>
-      <c r="C31" s="46"/>
-      <c r="D31" s="40"/>
-      <c r="E31" s="40"/>
-      <c r="F31" s="40"/>
-      <c r="G31" s="40"/>
-      <c r="H31" s="40"/>
-      <c r="I31" s="40"/>
-      <c r="J31" s="46" t="s">
+      <c r="B31" s="39"/>
+      <c r="C31" s="39"/>
+      <c r="D31" s="30"/>
+      <c r="E31" s="30"/>
+      <c r="F31" s="30"/>
+      <c r="G31" s="30"/>
+      <c r="H31" s="30"/>
+      <c r="I31" s="30"/>
+      <c r="J31" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="K31" s="46"/>
-      <c r="L31" s="46"/>
-      <c r="M31" s="40"/>
-      <c r="N31" s="40"/>
-      <c r="O31" s="40"/>
-      <c r="P31" s="40"/>
-      <c r="Q31" s="40"/>
-      <c r="R31" s="41"/>
+      <c r="K31" s="39"/>
+      <c r="L31" s="39"/>
+      <c r="M31" s="30"/>
+      <c r="N31" s="30"/>
+      <c r="O31" s="30"/>
+      <c r="P31" s="30"/>
+      <c r="Q31" s="30"/>
+      <c r="R31" s="130"/>
     </row>
     <row r="32" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A32" s="44"/>
-      <c r="B32" s="45"/>
-      <c r="C32" s="45"/>
-      <c r="D32" s="42"/>
-      <c r="E32" s="42"/>
-      <c r="F32" s="42"/>
-      <c r="G32" s="42"/>
-      <c r="H32" s="42"/>
-      <c r="I32" s="42"/>
-      <c r="J32" s="45"/>
-      <c r="K32" s="45"/>
-      <c r="L32" s="45"/>
-      <c r="M32" s="42"/>
-      <c r="N32" s="42"/>
-      <c r="O32" s="42"/>
-      <c r="P32" s="42"/>
-      <c r="Q32" s="42"/>
-      <c r="R32" s="43"/>
+      <c r="A32" s="34"/>
+      <c r="B32" s="35"/>
+      <c r="C32" s="35"/>
+      <c r="D32" s="31"/>
+      <c r="E32" s="31"/>
+      <c r="F32" s="31"/>
+      <c r="G32" s="31"/>
+      <c r="H32" s="31"/>
+      <c r="I32" s="31"/>
+      <c r="J32" s="35"/>
+      <c r="K32" s="35"/>
+      <c r="L32" s="35"/>
+      <c r="M32" s="31"/>
+      <c r="N32" s="31"/>
+      <c r="O32" s="31"/>
+      <c r="P32" s="31"/>
+      <c r="Q32" s="31"/>
+      <c r="R32" s="131"/>
     </row>
     <row r="33" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A33" s="44" t="s">
+      <c r="A33" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="B33" s="45"/>
-      <c r="C33" s="45"/>
-      <c r="D33" s="132"/>
-      <c r="E33" s="133"/>
-      <c r="F33" s="133"/>
-      <c r="G33" s="133"/>
-      <c r="H33" s="133"/>
-      <c r="I33" s="133"/>
-      <c r="J33" s="133"/>
-      <c r="K33" s="133"/>
-      <c r="L33" s="133"/>
-      <c r="M33" s="133"/>
-      <c r="N33" s="133"/>
-      <c r="O33" s="133"/>
-      <c r="P33" s="133"/>
-      <c r="Q33" s="133"/>
-      <c r="R33" s="134"/>
+      <c r="B33" s="35"/>
+      <c r="C33" s="35"/>
+      <c r="D33" s="115"/>
+      <c r="E33" s="116"/>
+      <c r="F33" s="116"/>
+      <c r="G33" s="116"/>
+      <c r="H33" s="116"/>
+      <c r="I33" s="116"/>
+      <c r="J33" s="116"/>
+      <c r="K33" s="116"/>
+      <c r="L33" s="116"/>
+      <c r="M33" s="116"/>
+      <c r="N33" s="116"/>
+      <c r="O33" s="116"/>
+      <c r="P33" s="116"/>
+      <c r="Q33" s="116"/>
+      <c r="R33" s="117"/>
     </row>
     <row r="34" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A34" s="44"/>
-      <c r="B34" s="45"/>
-      <c r="C34" s="45"/>
-      <c r="D34" s="135"/>
-      <c r="E34" s="136"/>
-      <c r="F34" s="136"/>
-      <c r="G34" s="136"/>
-      <c r="H34" s="136"/>
-      <c r="I34" s="136"/>
-      <c r="J34" s="136"/>
-      <c r="K34" s="136"/>
-      <c r="L34" s="136"/>
-      <c r="M34" s="136"/>
-      <c r="N34" s="136"/>
-      <c r="O34" s="136"/>
-      <c r="P34" s="136"/>
-      <c r="Q34" s="136"/>
-      <c r="R34" s="137"/>
+      <c r="A34" s="34"/>
+      <c r="B34" s="35"/>
+      <c r="C34" s="35"/>
+      <c r="D34" s="118"/>
+      <c r="E34" s="119"/>
+      <c r="F34" s="119"/>
+      <c r="G34" s="119"/>
+      <c r="H34" s="119"/>
+      <c r="I34" s="119"/>
+      <c r="J34" s="119"/>
+      <c r="K34" s="119"/>
+      <c r="L34" s="119"/>
+      <c r="M34" s="119"/>
+      <c r="N34" s="119"/>
+      <c r="O34" s="119"/>
+      <c r="P34" s="119"/>
+      <c r="Q34" s="119"/>
+      <c r="R34" s="120"/>
     </row>
     <row r="35" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A35" s="44" t="s">
+      <c r="A35" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="B35" s="45"/>
-      <c r="C35" s="45"/>
-      <c r="D35" s="51"/>
-      <c r="E35" s="52"/>
-      <c r="F35" s="52"/>
-      <c r="G35" s="52"/>
-      <c r="H35" s="52"/>
-      <c r="I35" s="52"/>
-      <c r="J35" s="52"/>
-      <c r="K35" s="52"/>
-      <c r="L35" s="52"/>
-      <c r="M35" s="52"/>
-      <c r="N35" s="52"/>
-      <c r="O35" s="52"/>
-      <c r="P35" s="52"/>
-      <c r="Q35" s="52"/>
-      <c r="R35" s="53"/>
+      <c r="B35" s="35"/>
+      <c r="C35" s="35"/>
+      <c r="D35" s="134"/>
+      <c r="E35" s="135"/>
+      <c r="F35" s="135"/>
+      <c r="G35" s="135"/>
+      <c r="H35" s="135"/>
+      <c r="I35" s="135"/>
+      <c r="J35" s="135"/>
+      <c r="K35" s="135"/>
+      <c r="L35" s="135"/>
+      <c r="M35" s="135"/>
+      <c r="N35" s="135"/>
+      <c r="O35" s="135"/>
+      <c r="P35" s="135"/>
+      <c r="Q35" s="135"/>
+      <c r="R35" s="136"/>
     </row>
     <row r="36" spans="1:18" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A36" s="49"/>
-      <c r="B36" s="50"/>
-      <c r="C36" s="50"/>
-      <c r="D36" s="54"/>
-      <c r="E36" s="55"/>
-      <c r="F36" s="55"/>
-      <c r="G36" s="55"/>
-      <c r="H36" s="55"/>
-      <c r="I36" s="55"/>
-      <c r="J36" s="55"/>
-      <c r="K36" s="55"/>
-      <c r="L36" s="55"/>
-      <c r="M36" s="55"/>
-      <c r="N36" s="55"/>
-      <c r="O36" s="55"/>
-      <c r="P36" s="55"/>
-      <c r="Q36" s="55"/>
-      <c r="R36" s="56"/>
+      <c r="A36" s="36"/>
+      <c r="B36" s="37"/>
+      <c r="C36" s="37"/>
+      <c r="D36" s="137"/>
+      <c r="E36" s="138"/>
+      <c r="F36" s="138"/>
+      <c r="G36" s="138"/>
+      <c r="H36" s="138"/>
+      <c r="I36" s="138"/>
+      <c r="J36" s="138"/>
+      <c r="K36" s="138"/>
+      <c r="L36" s="138"/>
+      <c r="M36" s="138"/>
+      <c r="N36" s="138"/>
+      <c r="O36" s="138"/>
+      <c r="P36" s="138"/>
+      <c r="Q36" s="138"/>
+      <c r="R36" s="139"/>
     </row>
     <row r="37" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A37" s="68"/>
-      <c r="B37" s="69"/>
-      <c r="C37" s="69"/>
-      <c r="D37" s="69"/>
-      <c r="E37" s="69"/>
-      <c r="F37" s="69"/>
-      <c r="G37" s="69"/>
-      <c r="H37" s="69"/>
-      <c r="I37" s="69"/>
-      <c r="J37" s="69"/>
-      <c r="K37" s="69"/>
-      <c r="L37" s="69"/>
-      <c r="M37" s="69"/>
-      <c r="N37" s="69"/>
-      <c r="O37" s="69"/>
-      <c r="P37" s="69"/>
-      <c r="Q37" s="69"/>
-      <c r="R37" s="69"/>
+      <c r="A37" s="125"/>
+      <c r="B37" s="126"/>
+      <c r="C37" s="126"/>
+      <c r="D37" s="126"/>
+      <c r="E37" s="126"/>
+      <c r="F37" s="126"/>
+      <c r="G37" s="126"/>
+      <c r="H37" s="126"/>
+      <c r="I37" s="126"/>
+      <c r="J37" s="126"/>
+      <c r="K37" s="126"/>
+      <c r="L37" s="126"/>
+      <c r="M37" s="126"/>
+      <c r="N37" s="126"/>
+      <c r="O37" s="126"/>
+      <c r="P37" s="126"/>
+      <c r="Q37" s="126"/>
+      <c r="R37" s="126"/>
     </row>
     <row r="38" spans="1:18" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A38" s="70"/>
-      <c r="B38" s="70"/>
-      <c r="C38" s="70"/>
-      <c r="D38" s="70"/>
-      <c r="E38" s="70"/>
-      <c r="F38" s="70"/>
-      <c r="G38" s="70"/>
-      <c r="H38" s="70"/>
-      <c r="I38" s="70"/>
-      <c r="J38" s="70"/>
-      <c r="K38" s="70"/>
-      <c r="L38" s="70"/>
-      <c r="M38" s="70"/>
-      <c r="N38" s="70"/>
-      <c r="O38" s="70"/>
-      <c r="P38" s="70"/>
-      <c r="Q38" s="70"/>
-      <c r="R38" s="70"/>
+      <c r="A38" s="127"/>
+      <c r="B38" s="127"/>
+      <c r="C38" s="127"/>
+      <c r="D38" s="127"/>
+      <c r="E38" s="127"/>
+      <c r="F38" s="127"/>
+      <c r="G38" s="127"/>
+      <c r="H38" s="127"/>
+      <c r="I38" s="127"/>
+      <c r="J38" s="127"/>
+      <c r="K38" s="127"/>
+      <c r="L38" s="127"/>
+      <c r="M38" s="127"/>
+      <c r="N38" s="127"/>
+      <c r="O38" s="127"/>
+      <c r="P38" s="127"/>
+      <c r="Q38" s="127"/>
+      <c r="R38" s="127"/>
     </row>
     <row r="39" spans="1:18" ht="12" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A39" s="57" t="s">
+      <c r="A39" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="B39" s="46"/>
-      <c r="C39" s="46"/>
-      <c r="D39" s="46" t="s">
+      <c r="B39" s="39"/>
+      <c r="C39" s="39"/>
+      <c r="D39" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="E39" s="46"/>
-      <c r="F39" s="46"/>
-      <c r="G39" s="71"/>
-      <c r="H39" s="46" t="s">
+      <c r="E39" s="39"/>
+      <c r="F39" s="39"/>
+      <c r="G39" s="128"/>
+      <c r="H39" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="I39" s="46"/>
-      <c r="J39" s="46"/>
-      <c r="K39" s="46" t="s">
+      <c r="I39" s="39"/>
+      <c r="J39" s="39"/>
+      <c r="K39" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="L39" s="46"/>
-      <c r="M39" s="46"/>
-      <c r="N39" s="71"/>
-      <c r="O39" s="46" t="s">
+      <c r="L39" s="39"/>
+      <c r="M39" s="39"/>
+      <c r="N39" s="128"/>
+      <c r="O39" s="39" t="s">
         <v>20</v>
       </c>
-      <c r="P39" s="46"/>
-      <c r="Q39" s="46"/>
-      <c r="R39" s="47"/>
+      <c r="P39" s="39"/>
+      <c r="Q39" s="39"/>
+      <c r="R39" s="132"/>
     </row>
     <row r="40" spans="1:18" ht="12" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A40" s="44"/>
-      <c r="B40" s="45"/>
-      <c r="C40" s="45"/>
-      <c r="D40" s="45"/>
-      <c r="E40" s="45"/>
-      <c r="F40" s="45"/>
-      <c r="G40" s="72"/>
-      <c r="H40" s="45"/>
-      <c r="I40" s="45"/>
-      <c r="J40" s="45"/>
-      <c r="K40" s="45"/>
-      <c r="L40" s="45"/>
-      <c r="M40" s="45"/>
-      <c r="N40" s="72"/>
-      <c r="O40" s="45"/>
-      <c r="P40" s="45"/>
-      <c r="Q40" s="45"/>
-      <c r="R40" s="48"/>
+      <c r="A40" s="34"/>
+      <c r="B40" s="35"/>
+      <c r="C40" s="35"/>
+      <c r="D40" s="35"/>
+      <c r="E40" s="35"/>
+      <c r="F40" s="35"/>
+      <c r="G40" s="129"/>
+      <c r="H40" s="35"/>
+      <c r="I40" s="35"/>
+      <c r="J40" s="35"/>
+      <c r="K40" s="35"/>
+      <c r="L40" s="35"/>
+      <c r="M40" s="35"/>
+      <c r="N40" s="129"/>
+      <c r="O40" s="35"/>
+      <c r="P40" s="35"/>
+      <c r="Q40" s="35"/>
+      <c r="R40" s="133"/>
     </row>
     <row r="41" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A41" s="106" t="s">
+      <c r="A41" s="86" t="s">
         <v>12</v>
       </c>
-      <c r="B41" s="107"/>
-      <c r="C41" s="108"/>
-      <c r="D41" s="94"/>
-      <c r="E41" s="95"/>
-      <c r="F41" s="95"/>
-      <c r="G41" s="96"/>
-      <c r="H41" s="88" t="s">
+      <c r="B41" s="87"/>
+      <c r="C41" s="88"/>
+      <c r="D41" s="74"/>
+      <c r="E41" s="75"/>
+      <c r="F41" s="75"/>
+      <c r="G41" s="76"/>
+      <c r="H41" s="68" t="s">
         <v>13</v>
       </c>
-      <c r="I41" s="89"/>
-      <c r="J41" s="90"/>
-      <c r="K41" s="94"/>
-      <c r="L41" s="95"/>
-      <c r="M41" s="95"/>
-      <c r="N41" s="96"/>
-      <c r="O41" s="100"/>
-      <c r="P41" s="100"/>
-      <c r="Q41" s="100"/>
-      <c r="R41" s="101"/>
+      <c r="I41" s="69"/>
+      <c r="J41" s="70"/>
+      <c r="K41" s="74"/>
+      <c r="L41" s="75"/>
+      <c r="M41" s="75"/>
+      <c r="N41" s="76"/>
+      <c r="O41" s="80"/>
+      <c r="P41" s="80"/>
+      <c r="Q41" s="80"/>
+      <c r="R41" s="81"/>
     </row>
     <row r="42" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A42" s="109"/>
-      <c r="B42" s="110"/>
-      <c r="C42" s="111"/>
-      <c r="D42" s="97"/>
-      <c r="E42" s="98"/>
-      <c r="F42" s="98"/>
-      <c r="G42" s="99"/>
-      <c r="H42" s="91"/>
-      <c r="I42" s="92"/>
-      <c r="J42" s="93"/>
-      <c r="K42" s="97"/>
-      <c r="L42" s="98"/>
-      <c r="M42" s="98"/>
-      <c r="N42" s="99"/>
-      <c r="O42" s="100"/>
-      <c r="P42" s="100"/>
-      <c r="Q42" s="100"/>
-      <c r="R42" s="101"/>
+      <c r="A42" s="89"/>
+      <c r="B42" s="90"/>
+      <c r="C42" s="91"/>
+      <c r="D42" s="77"/>
+      <c r="E42" s="78"/>
+      <c r="F42" s="78"/>
+      <c r="G42" s="79"/>
+      <c r="H42" s="71"/>
+      <c r="I42" s="72"/>
+      <c r="J42" s="73"/>
+      <c r="K42" s="77"/>
+      <c r="L42" s="78"/>
+      <c r="M42" s="78"/>
+      <c r="N42" s="79"/>
+      <c r="O42" s="80"/>
+      <c r="P42" s="80"/>
+      <c r="Q42" s="80"/>
+      <c r="R42" s="81"/>
     </row>
     <row r="43" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A43" s="106" t="s">
+      <c r="A43" s="86" t="s">
         <v>14</v>
       </c>
-      <c r="B43" s="107"/>
-      <c r="C43" s="108"/>
-      <c r="D43" s="94"/>
-      <c r="E43" s="95"/>
-      <c r="F43" s="95"/>
-      <c r="G43" s="96"/>
-      <c r="H43" s="130" t="s">
+      <c r="B43" s="87"/>
+      <c r="C43" s="88"/>
+      <c r="D43" s="74"/>
+      <c r="E43" s="75"/>
+      <c r="F43" s="75"/>
+      <c r="G43" s="76"/>
+      <c r="H43" s="142" t="s">
         <v>15</v>
       </c>
-      <c r="I43" s="107"/>
-      <c r="J43" s="108"/>
-      <c r="K43" s="94"/>
-      <c r="L43" s="95"/>
-      <c r="M43" s="95"/>
-      <c r="N43" s="96"/>
-      <c r="O43" s="100"/>
-      <c r="P43" s="100"/>
-      <c r="Q43" s="100"/>
-      <c r="R43" s="101"/>
+      <c r="I43" s="87"/>
+      <c r="J43" s="88"/>
+      <c r="K43" s="74"/>
+      <c r="L43" s="75"/>
+      <c r="M43" s="75"/>
+      <c r="N43" s="76"/>
+      <c r="O43" s="80"/>
+      <c r="P43" s="80"/>
+      <c r="Q43" s="80"/>
+      <c r="R43" s="81"/>
     </row>
     <row r="44" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A44" s="109"/>
-      <c r="B44" s="110"/>
-      <c r="C44" s="111"/>
-      <c r="D44" s="97"/>
-      <c r="E44" s="98"/>
-      <c r="F44" s="98"/>
-      <c r="G44" s="99"/>
-      <c r="H44" s="131"/>
-      <c r="I44" s="110"/>
-      <c r="J44" s="111"/>
-      <c r="K44" s="97"/>
-      <c r="L44" s="98"/>
-      <c r="M44" s="98"/>
-      <c r="N44" s="99"/>
-      <c r="O44" s="100"/>
-      <c r="P44" s="100"/>
-      <c r="Q44" s="100"/>
-      <c r="R44" s="101"/>
+      <c r="A44" s="89"/>
+      <c r="B44" s="90"/>
+      <c r="C44" s="91"/>
+      <c r="D44" s="77"/>
+      <c r="E44" s="78"/>
+      <c r="F44" s="78"/>
+      <c r="G44" s="79"/>
+      <c r="H44" s="143"/>
+      <c r="I44" s="90"/>
+      <c r="J44" s="91"/>
+      <c r="K44" s="77"/>
+      <c r="L44" s="78"/>
+      <c r="M44" s="78"/>
+      <c r="N44" s="79"/>
+      <c r="O44" s="80"/>
+      <c r="P44" s="80"/>
+      <c r="Q44" s="80"/>
+      <c r="R44" s="81"/>
     </row>
     <row r="45" spans="1:18" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A45" s="128" t="s">
+      <c r="A45" s="104" t="s">
         <v>16</v>
       </c>
-      <c r="B45" s="129"/>
-      <c r="C45" s="129"/>
-      <c r="D45" s="104"/>
-      <c r="E45" s="104"/>
-      <c r="F45" s="104"/>
-      <c r="G45" s="105"/>
-      <c r="H45" s="129" t="s">
+      <c r="B45" s="105"/>
+      <c r="C45" s="105"/>
+      <c r="D45" s="84"/>
+      <c r="E45" s="84"/>
+      <c r="F45" s="84"/>
+      <c r="G45" s="85"/>
+      <c r="H45" s="105" t="s">
         <v>16</v>
       </c>
-      <c r="I45" s="129"/>
-      <c r="J45" s="129"/>
-      <c r="K45" s="104"/>
-      <c r="L45" s="104"/>
-      <c r="M45" s="104"/>
-      <c r="N45" s="105"/>
-      <c r="O45" s="102"/>
-      <c r="P45" s="102"/>
-      <c r="Q45" s="102"/>
-      <c r="R45" s="103"/>
+      <c r="I45" s="105"/>
+      <c r="J45" s="105"/>
+      <c r="K45" s="84"/>
+      <c r="L45" s="84"/>
+      <c r="M45" s="84"/>
+      <c r="N45" s="85"/>
+      <c r="O45" s="82"/>
+      <c r="P45" s="82"/>
+      <c r="Q45" s="82"/>
+      <c r="R45" s="83"/>
     </row>
     <row r="46" spans="1:18" ht="20.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.4"/>
     <row r="47" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.4">
@@ -2643,128 +2679,128 @@
       </c>
     </row>
     <row r="49" spans="1:18" ht="18" customHeight="1" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="A49" s="116"/>
-      <c r="B49" s="117"/>
-      <c r="C49" s="118"/>
-      <c r="D49" s="122"/>
-      <c r="E49" s="123"/>
-      <c r="F49" s="123"/>
-      <c r="G49" s="123"/>
-      <c r="H49" s="124"/>
-      <c r="I49" s="122"/>
-      <c r="J49" s="123"/>
-      <c r="K49" s="123"/>
-      <c r="L49" s="123"/>
-      <c r="M49" s="124"/>
-      <c r="N49" s="122"/>
-      <c r="O49" s="123"/>
-      <c r="P49" s="123"/>
-      <c r="Q49" s="123"/>
-      <c r="R49" s="142"/>
+      <c r="A49" s="92"/>
+      <c r="B49" s="93"/>
+      <c r="C49" s="94"/>
+      <c r="D49" s="98"/>
+      <c r="E49" s="99"/>
+      <c r="F49" s="99"/>
+      <c r="G49" s="99"/>
+      <c r="H49" s="100"/>
+      <c r="I49" s="98"/>
+      <c r="J49" s="99"/>
+      <c r="K49" s="99"/>
+      <c r="L49" s="99"/>
+      <c r="M49" s="100"/>
+      <c r="N49" s="98"/>
+      <c r="O49" s="99"/>
+      <c r="P49" s="99"/>
+      <c r="Q49" s="99"/>
+      <c r="R49" s="140"/>
     </row>
     <row r="50" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A50" s="119"/>
-      <c r="B50" s="120"/>
-      <c r="C50" s="121"/>
-      <c r="D50" s="125"/>
-      <c r="E50" s="126"/>
-      <c r="F50" s="126"/>
-      <c r="G50" s="126"/>
-      <c r="H50" s="127"/>
-      <c r="I50" s="125"/>
-      <c r="J50" s="126"/>
-      <c r="K50" s="126"/>
-      <c r="L50" s="126"/>
-      <c r="M50" s="127"/>
-      <c r="N50" s="125"/>
-      <c r="O50" s="126"/>
-      <c r="P50" s="126"/>
-      <c r="Q50" s="126"/>
-      <c r="R50" s="143"/>
+      <c r="A50" s="95"/>
+      <c r="B50" s="96"/>
+      <c r="C50" s="97"/>
+      <c r="D50" s="101"/>
+      <c r="E50" s="102"/>
+      <c r="F50" s="102"/>
+      <c r="G50" s="102"/>
+      <c r="H50" s="103"/>
+      <c r="I50" s="101"/>
+      <c r="J50" s="102"/>
+      <c r="K50" s="102"/>
+      <c r="L50" s="102"/>
+      <c r="M50" s="103"/>
+      <c r="N50" s="101"/>
+      <c r="O50" s="102"/>
+      <c r="P50" s="102"/>
+      <c r="Q50" s="102"/>
+      <c r="R50" s="141"/>
     </row>
     <row r="51" spans="1:18" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A51" s="30" t="s">
+      <c r="A51" s="107" t="s">
         <v>18</v>
       </c>
-      <c r="B51" s="31"/>
-      <c r="C51" s="32"/>
-      <c r="D51" s="28"/>
-      <c r="E51" s="28"/>
-      <c r="F51" s="28"/>
-      <c r="G51" s="28"/>
-      <c r="H51" s="28"/>
-      <c r="I51" s="28"/>
-      <c r="J51" s="28"/>
-      <c r="K51" s="28"/>
-      <c r="L51" s="28"/>
-      <c r="M51" s="28"/>
-      <c r="N51" s="28"/>
-      <c r="O51" s="28"/>
-      <c r="P51" s="28"/>
-      <c r="Q51" s="28"/>
-      <c r="R51" s="29"/>
+      <c r="B51" s="108"/>
+      <c r="C51" s="109"/>
+      <c r="D51" s="29"/>
+      <c r="E51" s="29"/>
+      <c r="F51" s="29"/>
+      <c r="G51" s="29"/>
+      <c r="H51" s="29"/>
+      <c r="I51" s="29"/>
+      <c r="J51" s="29"/>
+      <c r="K51" s="29"/>
+      <c r="L51" s="29"/>
+      <c r="M51" s="29"/>
+      <c r="N51" s="29"/>
+      <c r="O51" s="29"/>
+      <c r="P51" s="29"/>
+      <c r="Q51" s="29"/>
+      <c r="R51" s="106"/>
     </row>
     <row r="52" spans="1:18" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A52" s="33"/>
-      <c r="B52" s="34"/>
-      <c r="C52" s="35"/>
-      <c r="D52" s="28"/>
-      <c r="E52" s="28"/>
-      <c r="F52" s="28"/>
-      <c r="G52" s="28"/>
-      <c r="H52" s="28"/>
-      <c r="I52" s="28"/>
-      <c r="J52" s="28"/>
-      <c r="K52" s="28"/>
-      <c r="L52" s="28"/>
-      <c r="M52" s="28"/>
-      <c r="N52" s="28"/>
-      <c r="O52" s="28"/>
-      <c r="P52" s="28"/>
-      <c r="Q52" s="28"/>
-      <c r="R52" s="29"/>
+      <c r="A52" s="110"/>
+      <c r="B52" s="111"/>
+      <c r="C52" s="112"/>
+      <c r="D52" s="29"/>
+      <c r="E52" s="29"/>
+      <c r="F52" s="29"/>
+      <c r="G52" s="29"/>
+      <c r="H52" s="29"/>
+      <c r="I52" s="29"/>
+      <c r="J52" s="29"/>
+      <c r="K52" s="29"/>
+      <c r="L52" s="29"/>
+      <c r="M52" s="29"/>
+      <c r="N52" s="29"/>
+      <c r="O52" s="29"/>
+      <c r="P52" s="29"/>
+      <c r="Q52" s="29"/>
+      <c r="R52" s="106"/>
     </row>
     <row r="53" spans="1:18" s="2" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A53" s="73" t="s">
+      <c r="A53" s="62" t="s">
         <v>19</v>
       </c>
-      <c r="B53" s="74"/>
-      <c r="C53" s="75"/>
-      <c r="D53" s="36"/>
-      <c r="E53" s="36"/>
-      <c r="F53" s="36"/>
-      <c r="G53" s="36"/>
-      <c r="H53" s="36"/>
-      <c r="I53" s="36"/>
-      <c r="J53" s="36"/>
-      <c r="K53" s="36"/>
-      <c r="L53" s="36"/>
-      <c r="M53" s="36"/>
-      <c r="N53" s="36"/>
-      <c r="O53" s="36"/>
-      <c r="P53" s="36"/>
-      <c r="Q53" s="36"/>
-      <c r="R53" s="37"/>
+      <c r="B53" s="63"/>
+      <c r="C53" s="64"/>
+      <c r="D53" s="27"/>
+      <c r="E53" s="27"/>
+      <c r="F53" s="27"/>
+      <c r="G53" s="27"/>
+      <c r="H53" s="27"/>
+      <c r="I53" s="27"/>
+      <c r="J53" s="27"/>
+      <c r="K53" s="27"/>
+      <c r="L53" s="27"/>
+      <c r="M53" s="27"/>
+      <c r="N53" s="27"/>
+      <c r="O53" s="27"/>
+      <c r="P53" s="27"/>
+      <c r="Q53" s="27"/>
+      <c r="R53" s="113"/>
     </row>
     <row r="54" spans="1:18" s="2" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="76"/>
-      <c r="B54" s="77"/>
-      <c r="C54" s="78"/>
-      <c r="D54" s="38"/>
-      <c r="E54" s="38"/>
-      <c r="F54" s="38"/>
-      <c r="G54" s="38"/>
-      <c r="H54" s="38"/>
-      <c r="I54" s="38"/>
-      <c r="J54" s="38"/>
-      <c r="K54" s="38"/>
-      <c r="L54" s="38"/>
-      <c r="M54" s="38"/>
-      <c r="N54" s="38"/>
-      <c r="O54" s="38"/>
-      <c r="P54" s="38"/>
-      <c r="Q54" s="38"/>
-      <c r="R54" s="39"/>
+      <c r="A54" s="65"/>
+      <c r="B54" s="66"/>
+      <c r="C54" s="67"/>
+      <c r="D54" s="28"/>
+      <c r="E54" s="28"/>
+      <c r="F54" s="28"/>
+      <c r="G54" s="28"/>
+      <c r="H54" s="28"/>
+      <c r="I54" s="28"/>
+      <c r="J54" s="28"/>
+      <c r="K54" s="28"/>
+      <c r="L54" s="28"/>
+      <c r="M54" s="28"/>
+      <c r="N54" s="28"/>
+      <c r="O54" s="28"/>
+      <c r="P54" s="28"/>
+      <c r="Q54" s="28"/>
+      <c r="R54" s="114"/>
     </row>
     <row r="55" spans="1:18" s="2" customFormat="1" ht="17.25" customHeight="1" thickTop="1" x14ac:dyDescent="0.15"/>
     <row r="56" spans="1:18" s="2" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.15"/>
@@ -2779,6 +2815,33 @@
   </sheetData>
   <sheetProtection formatCells="0"/>
   <mergeCells count="50">
+    <mergeCell ref="D33:R34"/>
+    <mergeCell ref="M22:N28"/>
+    <mergeCell ref="A37:R38"/>
+    <mergeCell ref="H39:J40"/>
+    <mergeCell ref="A39:C40"/>
+    <mergeCell ref="K39:N40"/>
+    <mergeCell ref="D39:G40"/>
+    <mergeCell ref="M31:R32"/>
+    <mergeCell ref="A33:C34"/>
+    <mergeCell ref="O39:R40"/>
+    <mergeCell ref="A35:C36"/>
+    <mergeCell ref="D35:R36"/>
+    <mergeCell ref="A31:C32"/>
+    <mergeCell ref="J31:L32"/>
+    <mergeCell ref="D51:H52"/>
+    <mergeCell ref="N51:R52"/>
+    <mergeCell ref="A51:C52"/>
+    <mergeCell ref="N53:R54"/>
+    <mergeCell ref="D53:H54"/>
+    <mergeCell ref="O41:R45"/>
+    <mergeCell ref="K43:N44"/>
+    <mergeCell ref="K45:N45"/>
+    <mergeCell ref="A43:C44"/>
+    <mergeCell ref="A49:C50"/>
+    <mergeCell ref="D49:H50"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="H45:J45"/>
     <mergeCell ref="N49:R50"/>
     <mergeCell ref="I49:M50"/>
     <mergeCell ref="D45:G45"/>
@@ -2786,24 +2849,9 @@
     <mergeCell ref="A41:C42"/>
     <mergeCell ref="D43:G44"/>
     <mergeCell ref="H43:J44"/>
-    <mergeCell ref="D33:R34"/>
-    <mergeCell ref="M22:N28"/>
-    <mergeCell ref="A37:R38"/>
-    <mergeCell ref="H39:J40"/>
-    <mergeCell ref="A39:C40"/>
-    <mergeCell ref="K39:N40"/>
-    <mergeCell ref="A53:C54"/>
-    <mergeCell ref="H41:J42"/>
-    <mergeCell ref="K41:N42"/>
-    <mergeCell ref="O41:R45"/>
-    <mergeCell ref="K43:N44"/>
-    <mergeCell ref="K45:N45"/>
-    <mergeCell ref="A43:C44"/>
-    <mergeCell ref="D39:G40"/>
-    <mergeCell ref="A49:C50"/>
-    <mergeCell ref="D49:H50"/>
-    <mergeCell ref="A45:C45"/>
-    <mergeCell ref="H45:J45"/>
+    <mergeCell ref="I53:M54"/>
+    <mergeCell ref="I51:M52"/>
+    <mergeCell ref="D31:I32"/>
     <mergeCell ref="O1:R1"/>
     <mergeCell ref="A11:R11"/>
     <mergeCell ref="A22:C28"/>
@@ -2814,21 +2862,9 @@
     <mergeCell ref="O22:R28"/>
     <mergeCell ref="D23:L25"/>
     <mergeCell ref="O3:R4"/>
-    <mergeCell ref="D51:H52"/>
-    <mergeCell ref="N51:R52"/>
-    <mergeCell ref="A51:C52"/>
-    <mergeCell ref="N53:R54"/>
-    <mergeCell ref="M31:R32"/>
-    <mergeCell ref="A33:C34"/>
-    <mergeCell ref="O39:R40"/>
-    <mergeCell ref="A35:C36"/>
-    <mergeCell ref="D35:R36"/>
-    <mergeCell ref="A31:C32"/>
-    <mergeCell ref="J31:L32"/>
-    <mergeCell ref="D53:H54"/>
-    <mergeCell ref="I53:M54"/>
-    <mergeCell ref="I51:M52"/>
-    <mergeCell ref="D31:I32"/>
+    <mergeCell ref="A53:C54"/>
+    <mergeCell ref="H41:J42"/>
+    <mergeCell ref="K41:N42"/>
   </mergeCells>
   <phoneticPr fontId="20"/>
   <printOptions horizontalCentered="1"/>
@@ -2844,7 +2880,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{980EFC93-3554-4863-A81F-3ECF9A45AFCC}">
-  <dimension ref="B2:N28"/>
+  <dimension ref="B2:N29"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="15" width="4.625" customWidth="1"/>
@@ -3219,13 +3255,13 @@
       <c r="M23" s="145"/>
     </row>
     <row r="24" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B24" s="144" t="s">
+      <c r="B24" s="155" t="s">
         <v>36</v>
       </c>
-      <c r="C24" s="144"/>
-      <c r="D24" s="144"/>
-      <c r="E24" s="145"/>
-      <c r="F24" s="145"/>
+      <c r="C24" s="156"/>
+      <c r="D24" s="157"/>
+      <c r="E24" s="158"/>
+      <c r="F24" s="159"/>
       <c r="I24" s="144" t="s">
         <v>46</v>
       </c>
@@ -3235,13 +3271,13 @@
       <c r="M24" s="145"/>
     </row>
     <row r="25" spans="2:14" x14ac:dyDescent="0.4">
-      <c r="B25" s="144" t="s">
-        <v>37</v>
-      </c>
-      <c r="C25" s="144"/>
-      <c r="D25" s="144"/>
-      <c r="E25" s="145"/>
-      <c r="F25" s="145"/>
+      <c r="B25" s="155" t="s">
+        <v>47</v>
+      </c>
+      <c r="C25" s="156"/>
+      <c r="D25" s="157"/>
+      <c r="E25" s="158"/>
+      <c r="F25" s="159"/>
       <c r="I25" s="144" t="s">
         <v>38</v>
       </c>
@@ -3252,12 +3288,12 @@
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B26" s="144" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C26" s="144"/>
       <c r="D26" s="144"/>
-      <c r="E26" s="155"/>
-      <c r="F26" s="155"/>
+      <c r="E26" s="145"/>
+      <c r="F26" s="145"/>
       <c r="I26" s="144" t="s">
         <v>42</v>
       </c>
@@ -3268,40 +3304,51 @@
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B27" s="144" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C27" s="144"/>
       <c r="D27" s="144"/>
-      <c r="E27" s="145"/>
-      <c r="F27" s="145"/>
+      <c r="E27" s="160"/>
+      <c r="F27" s="160"/>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B28" s="144" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C28" s="144"/>
       <c r="D28" s="144"/>
       <c r="E28" s="145"/>
       <c r="F28" s="145"/>
     </row>
+    <row r="29" spans="2:14" x14ac:dyDescent="0.4">
+      <c r="B29" s="144" t="s">
+        <v>41</v>
+      </c>
+      <c r="C29" s="144"/>
+      <c r="D29" s="144"/>
+      <c r="E29" s="145"/>
+      <c r="F29" s="145"/>
+    </row>
   </sheetData>
-  <mergeCells count="96">
+  <mergeCells count="98">
     <mergeCell ref="I26:K26"/>
     <mergeCell ref="L26:M26"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="E29:F29"/>
+    <mergeCell ref="I25:K25"/>
+    <mergeCell ref="L25:M25"/>
+    <mergeCell ref="B27:D27"/>
+    <mergeCell ref="E27:F27"/>
     <mergeCell ref="B28:D28"/>
     <mergeCell ref="E28:F28"/>
-    <mergeCell ref="I25:K25"/>
-    <mergeCell ref="L25:M25"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="E23:F23"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="E25:F25"/>
     <mergeCell ref="B26:D26"/>
     <mergeCell ref="E26:F26"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="B23:D23"/>
-    <mergeCell ref="E23:F23"/>
     <mergeCell ref="B24:D24"/>
     <mergeCell ref="E24:F24"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="E25:F25"/>
     <mergeCell ref="B20:D20"/>
     <mergeCell ref="E20:F20"/>
     <mergeCell ref="B21:D21"/>
